--- a/docs/Cottage Rummy Data File.xlsx
+++ b/docs/Cottage Rummy Data File.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\tomku\Dropbox\Personal\Cottage Rummy Stats\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D6C31678-76A9-4E3C-B786-842C6F98CC2B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BC9B3ED1-52DB-4838-AF4B-F11DCAA416AC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="945" yWindow="-14385" windowWidth="27915" windowHeight="14385" tabRatio="832" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="-14550" windowWidth="27915" windowHeight="14385" tabRatio="832" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Input" sheetId="6" r:id="rId1"/>
@@ -475,7 +475,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0300-000000000000}">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A1:AKI271"/>
+  <dimension ref="A1:AKI273"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="10.33203125" style="5" bestFit="1" customWidth="1"/>
@@ -5764,6 +5764,46 @@
         <v>175</v>
       </c>
     </row>
+    <row r="272" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A272" s="5">
+        <v>46230</v>
+      </c>
+      <c r="C272">
+        <v>415</v>
+      </c>
+      <c r="E272">
+        <v>240</v>
+      </c>
+      <c r="F272">
+        <v>290</v>
+      </c>
+      <c r="G272">
+        <v>315</v>
+      </c>
+      <c r="H272">
+        <v>125</v>
+      </c>
+    </row>
+    <row r="273" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A273" s="5">
+        <v>46230</v>
+      </c>
+      <c r="C273">
+        <v>200</v>
+      </c>
+      <c r="E273">
+        <v>160</v>
+      </c>
+      <c r="F273">
+        <v>500</v>
+      </c>
+      <c r="G273">
+        <v>360</v>
+      </c>
+      <c r="H273">
+        <v>185</v>
+      </c>
+    </row>
   </sheetData>
   <conditionalFormatting sqref="J134:J1048576 J1:J132">
     <cfRule type="colorScale" priority="21">

--- a/docs/Cottage Rummy Data File.xlsx
+++ b/docs/Cottage Rummy Data File.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\tomku\Dropbox\Personal\Cottage Rummy Stats\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BC9B3ED1-52DB-4838-AF4B-F11DCAA416AC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{930E3D62-9F07-48A2-A5FD-895F18687977}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="-14550" windowWidth="27915" windowHeight="14385" tabRatio="832" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="1152" windowWidth="23088" windowHeight="10824" tabRatio="832" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Input" sheetId="6" r:id="rId1"/>
@@ -475,7 +475,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0300-000000000000}">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A1:AKI273"/>
+  <dimension ref="A1:AKI276"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="10.33203125" style="5" bestFit="1" customWidth="1"/>
@@ -5804,6 +5804,57 @@
         <v>185</v>
       </c>
     </row>
+    <row r="274" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A274" s="5">
+        <v>46235</v>
+      </c>
+      <c r="E274">
+        <v>45</v>
+      </c>
+      <c r="F274">
+        <v>320</v>
+      </c>
+      <c r="G274">
+        <v>380</v>
+      </c>
+      <c r="H274">
+        <v>380</v>
+      </c>
+    </row>
+    <row r="275" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A275" s="5">
+        <v>46235</v>
+      </c>
+      <c r="E275">
+        <v>225</v>
+      </c>
+      <c r="F275">
+        <v>135</v>
+      </c>
+      <c r="G275">
+        <v>285</v>
+      </c>
+      <c r="H275">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="276" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A276" s="5">
+        <v>46236</v>
+      </c>
+      <c r="E276">
+        <v>270</v>
+      </c>
+      <c r="F276">
+        <v>330</v>
+      </c>
+      <c r="G276">
+        <v>330</v>
+      </c>
+      <c r="H276">
+        <v>540</v>
+      </c>
+    </row>
   </sheetData>
   <conditionalFormatting sqref="J134:J1048576 J1:J132">
     <cfRule type="colorScale" priority="21">

--- a/docs/Cottage Rummy Data File.xlsx
+++ b/docs/Cottage Rummy Data File.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\tomku\Dropbox\Personal\Cottage Rummy Stats\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{930E3D62-9F07-48A2-A5FD-895F18687977}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FD8F8784-6F8E-4144-8962-D1E5F32DF64A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="1152" windowWidth="23088" windowHeight="10824" tabRatio="832" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -475,7 +475,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0300-000000000000}">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A1:AKI276"/>
+  <dimension ref="A1:AKI277"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="10.33203125" style="5" bestFit="1" customWidth="1"/>
@@ -4664,59 +4664,59 @@
     </row>
     <row r="210" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A210" s="8">
-        <v>45936</v>
+        <v>45935</v>
       </c>
       <c r="E210">
-        <v>95</v>
+        <v>125</v>
       </c>
       <c r="F210">
-        <v>220</v>
+        <v>320</v>
       </c>
       <c r="G210">
-        <v>240</v>
+        <v>340</v>
       </c>
       <c r="H210">
-        <v>165</v>
+        <v>360</v>
       </c>
     </row>
     <row r="211" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A211" s="8">
-        <v>45940</v>
-      </c>
-      <c r="C211">
-        <v>275</v>
-      </c>
-      <c r="D211">
-        <v>125</v>
+        <v>45936</v>
       </c>
       <c r="E211">
-        <v>340</v>
+        <v>95</v>
       </c>
       <c r="F211">
-        <v>85</v>
+        <v>220</v>
       </c>
       <c r="G211">
-        <v>540</v>
+        <v>240</v>
       </c>
       <c r="H211">
-        <v>395</v>
+        <v>165</v>
       </c>
     </row>
     <row r="212" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A212" s="8">
-        <v>45942</v>
+        <v>45940</v>
       </c>
       <c r="C212">
-        <v>410</v>
+        <v>275</v>
       </c>
       <c r="D212">
-        <v>105</v>
+        <v>125</v>
+      </c>
+      <c r="E212">
+        <v>340</v>
+      </c>
+      <c r="F212">
+        <v>85</v>
       </c>
       <c r="G212">
-        <v>230</v>
+        <v>540</v>
       </c>
       <c r="H212">
-        <v>285</v>
+        <v>395</v>
       </c>
     </row>
     <row r="213" spans="1:8" x14ac:dyDescent="0.3">
@@ -4724,33 +4724,33 @@
         <v>45942</v>
       </c>
       <c r="C213">
-        <v>90</v>
+        <v>410</v>
       </c>
       <c r="D213">
-        <v>265</v>
+        <v>105</v>
       </c>
       <c r="G213">
-        <v>265</v>
+        <v>230</v>
       </c>
       <c r="H213">
-        <v>275</v>
+        <v>285</v>
       </c>
     </row>
     <row r="214" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A214" s="8">
-        <v>45948</v>
-      </c>
-      <c r="E214">
-        <v>355</v>
-      </c>
-      <c r="F214">
-        <v>55</v>
+        <v>45942</v>
+      </c>
+      <c r="C214">
+        <v>90</v>
+      </c>
+      <c r="D214">
+        <v>265</v>
       </c>
       <c r="G214">
-        <v>290</v>
+        <v>265</v>
       </c>
       <c r="H214">
-        <v>335</v>
+        <v>275</v>
       </c>
     </row>
     <row r="215" spans="1:8" x14ac:dyDescent="0.3">
@@ -4758,93 +4758,93 @@
         <v>45948</v>
       </c>
       <c r="E215">
-        <v>85</v>
+        <v>355</v>
       </c>
       <c r="F215">
-        <v>245</v>
+        <v>55</v>
       </c>
       <c r="G215">
-        <v>430</v>
+        <v>290</v>
       </c>
       <c r="H215">
-        <v>230</v>
+        <v>335</v>
       </c>
     </row>
     <row r="216" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A216" s="8">
-        <v>45955</v>
-      </c>
-      <c r="C216">
-        <v>135</v>
+        <v>45948</v>
       </c>
       <c r="E216">
-        <v>225</v>
+        <v>85</v>
       </c>
       <c r="F216">
-        <v>145</v>
+        <v>245</v>
+      </c>
+      <c r="G216">
+        <v>430</v>
       </c>
       <c r="H216">
-        <v>130</v>
+        <v>230</v>
       </c>
     </row>
     <row r="217" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A217" s="8">
+        <v>45955</v>
+      </c>
+      <c r="C217">
+        <v>135</v>
+      </c>
+      <c r="E217">
+        <v>225</v>
+      </c>
+      <c r="F217">
+        <v>145</v>
+      </c>
+      <c r="H217">
+        <v>130</v>
+      </c>
+    </row>
+    <row r="218" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A218" s="8">
         <v>45962</v>
       </c>
-      <c r="C217">
+      <c r="C218">
         <v>155</v>
       </c>
-      <c r="E217">
+      <c r="E218">
         <v>345</v>
       </c>
-      <c r="F217">
+      <c r="F218">
         <v>195</v>
       </c>
-      <c r="G217">
+      <c r="G218">
         <v>285</v>
       </c>
-      <c r="H217">
+      <c r="H218">
         <v>310</v>
       </c>
     </row>
-    <row r="218" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A218" s="5">
+    <row r="219" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A219" s="5">
         <v>45969</v>
       </c>
-      <c r="C218">
+      <c r="C219">
         <v>420</v>
       </c>
-      <c r="D218">
+      <c r="D219">
         <v>200</v>
       </c>
-      <c r="E218">
+      <c r="E219">
         <v>485</v>
       </c>
-      <c r="F218">
+      <c r="F219">
         <v>175</v>
       </c>
-      <c r="G218">
+      <c r="G219">
         <v>305</v>
       </c>
-      <c r="H218">
+      <c r="H219">
         <v>475</v>
-      </c>
-    </row>
-    <row r="219" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A219" s="8">
-        <v>45983</v>
-      </c>
-      <c r="B219">
-        <v>50</v>
-      </c>
-      <c r="C219">
-        <v>140</v>
-      </c>
-      <c r="E219">
-        <v>245</v>
-      </c>
-      <c r="F219">
-        <v>340</v>
       </c>
     </row>
     <row r="220" spans="1:8" x14ac:dyDescent="0.3">
@@ -4852,30 +4852,33 @@
         <v>45983</v>
       </c>
       <c r="B220">
-        <v>435</v>
+        <v>50</v>
       </c>
       <c r="C220">
-        <v>180</v>
+        <v>140</v>
       </c>
       <c r="E220">
-        <v>160</v>
+        <v>245</v>
       </c>
       <c r="F220">
-        <v>80</v>
+        <v>340</v>
       </c>
     </row>
     <row r="221" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A221" s="8">
-        <v>45990</v>
+        <v>45983</v>
+      </c>
+      <c r="B221">
+        <v>435</v>
       </c>
       <c r="C221">
-        <v>355</v>
+        <v>180</v>
       </c>
       <c r="E221">
-        <v>135</v>
+        <v>160</v>
       </c>
       <c r="F221">
-        <v>135</v>
+        <v>80</v>
       </c>
     </row>
     <row r="222" spans="1:8" x14ac:dyDescent="0.3">
@@ -4883,13 +4886,13 @@
         <v>45990</v>
       </c>
       <c r="C222">
-        <v>120</v>
+        <v>355</v>
       </c>
       <c r="E222">
-        <v>185</v>
+        <v>135</v>
       </c>
       <c r="F222">
-        <v>380</v>
+        <v>135</v>
       </c>
     </row>
     <row r="223" spans="1:8" x14ac:dyDescent="0.3">
@@ -4897,13 +4900,13 @@
         <v>45990</v>
       </c>
       <c r="C223">
-        <v>260</v>
+        <v>120</v>
       </c>
       <c r="E223">
-        <v>95</v>
+        <v>185</v>
       </c>
       <c r="F223">
-        <v>230</v>
+        <v>380</v>
       </c>
     </row>
     <row r="224" spans="1:8" x14ac:dyDescent="0.3">
@@ -4911,30 +4914,27 @@
         <v>45990</v>
       </c>
       <c r="C224">
-        <v>125</v>
+        <v>260</v>
       </c>
       <c r="E224">
-        <v>240</v>
+        <v>95</v>
       </c>
       <c r="F224">
-        <v>130</v>
+        <v>230</v>
       </c>
     </row>
     <row r="225" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A225" s="8">
-        <v>45997</v>
-      </c>
-      <c r="B225">
-        <v>175</v>
+        <v>45990</v>
       </c>
       <c r="C225">
-        <v>275</v>
+        <v>125</v>
       </c>
       <c r="E225">
-        <v>105</v>
+        <v>240</v>
       </c>
       <c r="F225">
-        <v>240</v>
+        <v>130</v>
       </c>
     </row>
     <row r="226" spans="1:8" x14ac:dyDescent="0.3">
@@ -4942,16 +4942,16 @@
         <v>45997</v>
       </c>
       <c r="B226">
-        <v>60</v>
+        <v>175</v>
       </c>
       <c r="C226">
-        <v>235</v>
+        <v>275</v>
       </c>
       <c r="E226">
-        <v>340</v>
+        <v>105</v>
       </c>
       <c r="F226">
-        <v>260</v>
+        <v>240</v>
       </c>
     </row>
     <row r="227" spans="1:8" x14ac:dyDescent="0.3">
@@ -4959,33 +4959,33 @@
         <v>45997</v>
       </c>
       <c r="B227">
+        <v>60</v>
+      </c>
+      <c r="C227">
+        <v>235</v>
+      </c>
+      <c r="E227">
+        <v>340</v>
+      </c>
+      <c r="F227">
+        <v>260</v>
+      </c>
+    </row>
+    <row r="228" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A228" s="8">
+        <v>45997</v>
+      </c>
+      <c r="B228">
         <v>370</v>
       </c>
-      <c r="C227">
+      <c r="C228">
         <v>415</v>
       </c>
-      <c r="E227">
+      <c r="E228">
         <v>230</v>
       </c>
-      <c r="F227">
+      <c r="F228">
         <v>370</v>
-      </c>
-    </row>
-    <row r="228" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A228" s="5">
-        <v>46005</v>
-      </c>
-      <c r="E228">
-        <v>215</v>
-      </c>
-      <c r="F228">
-        <v>110</v>
-      </c>
-      <c r="G228">
-        <v>370</v>
-      </c>
-      <c r="H228">
-        <v>275</v>
       </c>
     </row>
     <row r="229" spans="1:8" x14ac:dyDescent="0.3">
@@ -4993,53 +4993,53 @@
         <v>46005</v>
       </c>
       <c r="E229">
-        <v>325</v>
+        <v>215</v>
       </c>
       <c r="F229">
-        <v>285</v>
+        <v>110</v>
       </c>
       <c r="G229">
-        <v>270</v>
+        <v>370</v>
       </c>
       <c r="H229">
-        <v>215</v>
+        <v>275</v>
       </c>
     </row>
     <row r="230" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A230" s="5">
-        <v>46012</v>
-      </c>
-      <c r="C230">
-        <v>245</v>
+        <v>46005</v>
       </c>
       <c r="E230">
-        <v>185</v>
+        <v>325</v>
       </c>
       <c r="F230">
-        <v>255</v>
+        <v>285</v>
       </c>
       <c r="G230">
-        <v>275</v>
+        <v>270</v>
       </c>
       <c r="H230">
-        <v>365</v>
+        <v>215</v>
       </c>
     </row>
     <row r="231" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A231" s="5">
         <v>46012</v>
       </c>
+      <c r="C231">
+        <v>245</v>
+      </c>
       <c r="E231">
-        <v>345</v>
+        <v>185</v>
       </c>
       <c r="F231">
-        <v>90</v>
+        <v>255</v>
       </c>
       <c r="G231">
-        <v>180</v>
+        <v>275</v>
       </c>
       <c r="H231">
-        <v>145</v>
+        <v>365</v>
       </c>
     </row>
     <row r="232" spans="1:8" x14ac:dyDescent="0.3">
@@ -5047,99 +5047,102 @@
         <v>46012</v>
       </c>
       <c r="E232">
-        <v>210</v>
+        <v>345</v>
       </c>
       <c r="F232">
-        <v>170</v>
+        <v>90</v>
       </c>
       <c r="G232">
-        <v>190</v>
+        <v>180</v>
       </c>
       <c r="H232">
-        <v>225</v>
+        <v>145</v>
       </c>
     </row>
     <row r="233" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A233" s="5">
-        <v>46015</v>
-      </c>
-      <c r="B233">
-        <v>135</v>
-      </c>
-      <c r="C233">
-        <v>285</v>
+        <v>46012</v>
       </c>
       <c r="E233">
-        <v>185</v>
+        <v>210</v>
       </c>
       <c r="F233">
-        <v>405</v>
+        <v>170</v>
       </c>
       <c r="G233">
-        <v>450</v>
+        <v>190</v>
       </c>
       <c r="H233">
-        <v>345</v>
+        <v>225</v>
       </c>
     </row>
     <row r="234" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A234" s="5">
-        <v>46016</v>
+        <v>46015</v>
       </c>
       <c r="B234">
-        <v>465</v>
+        <v>135</v>
       </c>
       <c r="C234">
-        <v>270</v>
+        <v>285</v>
       </c>
       <c r="E234">
-        <v>200</v>
+        <v>185</v>
       </c>
       <c r="F234">
-        <v>445</v>
+        <v>405</v>
       </c>
       <c r="G234">
-        <v>380</v>
+        <v>450</v>
       </c>
       <c r="H234">
-        <v>565</v>
+        <v>345</v>
       </c>
     </row>
     <row r="235" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A235" s="5">
-        <v>46020</v>
+        <v>46016</v>
       </c>
       <c r="B235">
-        <v>405</v>
+        <v>465</v>
       </c>
       <c r="C235">
-        <v>370</v>
-      </c>
-      <c r="D235">
-        <v>385</v>
+        <v>270</v>
       </c>
       <c r="E235">
-        <v>185</v>
+        <v>200</v>
       </c>
       <c r="F235">
-        <v>430</v>
+        <v>445</v>
+      </c>
+      <c r="G235">
+        <v>380</v>
       </c>
       <c r="H235">
-        <v>270</v>
+        <v>565</v>
       </c>
     </row>
     <row r="236" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A236" s="5">
-        <v>46032</v>
+        <v>46020</v>
       </c>
       <c r="B236">
-        <v>340</v>
+        <v>405</v>
+      </c>
+      <c r="C236">
+        <v>370</v>
+      </c>
+      <c r="D236">
+        <v>385</v>
       </c>
       <c r="E236">
-        <v>65</v>
+        <v>185</v>
       </c>
       <c r="F236">
-        <v>255</v>
+        <v>430</v>
+      </c>
+      <c r="H236">
+        <v>270</v>
       </c>
     </row>
     <row r="237" spans="1:8" x14ac:dyDescent="0.3">
@@ -5147,30 +5150,27 @@
         <v>46032</v>
       </c>
       <c r="B237">
-        <v>245</v>
+        <v>340</v>
       </c>
       <c r="E237">
-        <v>210</v>
+        <v>65</v>
       </c>
       <c r="F237">
-        <v>190</v>
+        <v>255</v>
       </c>
     </row>
     <row r="238" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A238" s="5">
-        <v>46039</v>
+        <v>46032</v>
       </c>
       <c r="B238">
-        <v>135</v>
-      </c>
-      <c r="C238">
-        <v>145</v>
+        <v>245</v>
       </c>
       <c r="E238">
-        <v>120</v>
+        <v>210</v>
       </c>
       <c r="F238">
-        <v>70</v>
+        <v>190</v>
       </c>
     </row>
     <row r="239" spans="1:8" x14ac:dyDescent="0.3">
@@ -5178,16 +5178,16 @@
         <v>46039</v>
       </c>
       <c r="B239">
-        <v>180</v>
+        <v>135</v>
       </c>
       <c r="C239">
-        <v>140</v>
+        <v>145</v>
       </c>
       <c r="E239">
-        <v>145</v>
+        <v>120</v>
       </c>
       <c r="F239">
-        <v>425</v>
+        <v>70</v>
       </c>
     </row>
     <row r="240" spans="1:8" x14ac:dyDescent="0.3">
@@ -5195,70 +5195,70 @@
         <v>46039</v>
       </c>
       <c r="B240">
-        <v>285</v>
+        <v>180</v>
       </c>
       <c r="C240">
-        <v>245</v>
+        <v>140</v>
       </c>
       <c r="E240">
-        <v>105</v>
+        <v>145</v>
       </c>
       <c r="F240">
-        <v>130</v>
+        <v>425</v>
       </c>
     </row>
     <row r="241" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A241" s="5">
-        <v>46067</v>
+        <v>46039</v>
       </c>
       <c r="B241">
-        <v>325</v>
+        <v>285</v>
       </c>
       <c r="C241">
-        <v>225</v>
-      </c>
-      <c r="D241">
-        <v>250</v>
+        <v>245</v>
       </c>
       <c r="E241">
-        <v>420</v>
+        <v>105</v>
       </c>
       <c r="F241">
-        <v>340</v>
+        <v>130</v>
       </c>
     </row>
     <row r="242" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A242" s="5">
         <v>46067</v>
       </c>
+      <c r="B242">
+        <v>325</v>
+      </c>
       <c r="C242">
-        <v>205</v>
+        <v>225</v>
       </c>
       <c r="D242">
-        <v>240</v>
+        <v>250</v>
       </c>
       <c r="E242">
-        <v>385</v>
+        <v>420</v>
       </c>
       <c r="F242">
-        <v>170</v>
+        <v>340</v>
       </c>
     </row>
     <row r="243" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A243" s="5">
         <v>46067</v>
       </c>
-      <c r="B243">
-        <v>305</v>
-      </c>
       <c r="C243">
-        <v>45</v>
+        <v>205</v>
+      </c>
+      <c r="D243">
+        <v>240</v>
       </c>
       <c r="E243">
-        <v>230</v>
+        <v>385</v>
       </c>
       <c r="F243">
-        <v>290</v>
+        <v>170</v>
       </c>
     </row>
     <row r="244" spans="1:8" x14ac:dyDescent="0.3">
@@ -5266,33 +5266,33 @@
         <v>46067</v>
       </c>
       <c r="B244">
-        <v>285</v>
+        <v>305</v>
       </c>
       <c r="C244">
-        <v>60</v>
+        <v>45</v>
       </c>
       <c r="E244">
-        <v>225</v>
+        <v>230</v>
       </c>
       <c r="F244">
-        <v>270</v>
+        <v>290</v>
       </c>
     </row>
     <row r="245" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A245" s="5">
-        <v>46074</v>
+        <v>46067</v>
       </c>
       <c r="B245">
-        <v>95</v>
+        <v>285</v>
       </c>
       <c r="C245">
-        <v>340</v>
+        <v>60</v>
       </c>
       <c r="E245">
-        <v>215</v>
+        <v>225</v>
       </c>
       <c r="F245">
-        <v>260</v>
+        <v>270</v>
       </c>
     </row>
     <row r="246" spans="1:8" x14ac:dyDescent="0.3">
@@ -5300,30 +5300,33 @@
         <v>46074</v>
       </c>
       <c r="B246">
-        <v>250</v>
+        <v>95</v>
       </c>
       <c r="C246">
-        <v>285</v>
+        <v>340</v>
       </c>
       <c r="E246">
+        <v>215</v>
+      </c>
+      <c r="F246">
         <v>260</v>
-      </c>
-      <c r="F246">
-        <v>280</v>
       </c>
     </row>
     <row r="247" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A247" s="5">
-        <v>46081</v>
+        <v>46074</v>
       </c>
       <c r="B247">
-        <v>180</v>
+        <v>250</v>
+      </c>
+      <c r="C247">
+        <v>285</v>
       </c>
       <c r="E247">
-        <v>355</v>
+        <v>260</v>
       </c>
       <c r="F247">
-        <v>120</v>
+        <v>280</v>
       </c>
     </row>
     <row r="248" spans="1:8" x14ac:dyDescent="0.3">
@@ -5331,147 +5334,138 @@
         <v>46081</v>
       </c>
       <c r="B248">
-        <v>360</v>
+        <v>180</v>
       </c>
       <c r="E248">
-        <v>140</v>
+        <v>355</v>
       </c>
       <c r="F248">
-        <v>260</v>
+        <v>120</v>
       </c>
     </row>
     <row r="249" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A249" s="5">
-        <v>46109</v>
+        <v>46081</v>
       </c>
       <c r="B249">
-        <v>610</v>
-      </c>
-      <c r="C249">
-        <v>345</v>
+        <v>360</v>
       </c>
       <c r="E249">
-        <v>75</v>
+        <v>140</v>
       </c>
       <c r="F249">
-        <v>170</v>
+        <v>260</v>
       </c>
     </row>
     <row r="250" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A250" s="5">
-        <v>46115</v>
+        <v>46109</v>
       </c>
       <c r="B250">
-        <v>165</v>
+        <v>610</v>
       </c>
       <c r="C250">
-        <v>225</v>
-      </c>
-      <c r="G250">
-        <v>190</v>
-      </c>
-      <c r="H250">
-        <v>235</v>
+        <v>345</v>
+      </c>
+      <c r="E250">
+        <v>75</v>
+      </c>
+      <c r="F250">
+        <v>170</v>
       </c>
     </row>
     <row r="251" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A251" s="5">
-        <v>46123</v>
+        <v>46115</v>
       </c>
       <c r="B251">
-        <v>275</v>
+        <v>165</v>
       </c>
       <c r="C251">
-        <v>290</v>
-      </c>
-      <c r="E251">
-        <v>295</v>
-      </c>
-      <c r="F251">
-        <v>300</v>
+        <v>225</v>
       </c>
       <c r="G251">
-        <v>335</v>
+        <v>190</v>
       </c>
       <c r="H251">
-        <v>280</v>
+        <v>235</v>
       </c>
     </row>
     <row r="252" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A252" s="5">
-        <v>46130</v>
+        <v>46123</v>
+      </c>
+      <c r="B252">
+        <v>275</v>
+      </c>
+      <c r="C252">
+        <v>290</v>
       </c>
       <c r="E252">
-        <v>455</v>
+        <v>295</v>
       </c>
       <c r="F252">
+        <v>300</v>
+      </c>
+      <c r="G252">
         <v>335</v>
       </c>
-      <c r="G252">
-        <v>155</v>
-      </c>
       <c r="H252">
-        <v>230</v>
+        <v>280</v>
       </c>
     </row>
     <row r="253" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A253" s="5">
-        <v>46137</v>
+        <v>46130</v>
       </c>
       <c r="E253">
-        <v>340</v>
+        <v>455</v>
       </c>
       <c r="F253">
-        <v>440</v>
+        <v>335</v>
       </c>
       <c r="G253">
-        <v>260</v>
+        <v>155</v>
       </c>
       <c r="H253">
-        <v>420</v>
+        <v>230</v>
       </c>
     </row>
     <row r="254" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A254" s="5">
-        <v>46144</v>
-      </c>
-      <c r="C254">
-        <v>165</v>
+        <v>46137</v>
       </c>
       <c r="E254">
-        <v>215</v>
+        <v>340</v>
       </c>
       <c r="F254">
-        <v>490</v>
+        <v>440</v>
       </c>
       <c r="G254">
-        <v>150</v>
+        <v>260</v>
       </c>
       <c r="H254">
-        <v>365</v>
+        <v>420</v>
       </c>
     </row>
     <row r="255" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A255" s="5">
-        <v>46151</v>
+        <v>46144</v>
       </c>
       <c r="C255">
-        <v>475</v>
-      </c>
-      <c r="D255">
-        <v>300</v>
+        <v>165</v>
       </c>
       <c r="E255">
-        <v>240</v>
+        <v>215</v>
       </c>
       <c r="F255">
-        <v>355</v>
+        <v>490</v>
       </c>
       <c r="G255">
-        <v>440</v>
+        <v>150</v>
       </c>
       <c r="H255">
-        <v>390</v>
+        <v>365</v>
       </c>
     </row>
     <row r="256" spans="1:8" x14ac:dyDescent="0.3">
@@ -5479,39 +5473,45 @@
         <v>46151</v>
       </c>
       <c r="C256">
-        <v>95</v>
+        <v>475</v>
       </c>
       <c r="D256">
-        <v>370</v>
+        <v>300</v>
       </c>
       <c r="E256">
-        <v>415</v>
+        <v>240</v>
       </c>
       <c r="F256">
-        <v>610</v>
+        <v>355</v>
       </c>
       <c r="G256">
-        <v>335</v>
+        <v>440</v>
       </c>
       <c r="H256">
-        <v>335</v>
+        <v>390</v>
       </c>
     </row>
     <row r="257" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A257" s="5">
-        <v>46165</v>
+        <v>46151</v>
+      </c>
+      <c r="C257">
+        <v>95</v>
+      </c>
+      <c r="D257">
+        <v>370</v>
       </c>
       <c r="E257">
-        <v>310</v>
+        <v>415</v>
       </c>
       <c r="F257">
-        <v>180</v>
+        <v>610</v>
       </c>
       <c r="G257">
-        <v>175</v>
+        <v>335</v>
       </c>
       <c r="H257">
-        <v>220</v>
+        <v>335</v>
       </c>
     </row>
     <row r="258" spans="1:8" x14ac:dyDescent="0.3">
@@ -5519,96 +5519,96 @@
         <v>46165</v>
       </c>
       <c r="E258">
-        <v>100</v>
+        <v>310</v>
       </c>
       <c r="F258">
-        <v>480</v>
+        <v>180</v>
       </c>
       <c r="G258">
-        <v>120</v>
+        <v>175</v>
       </c>
       <c r="H258">
-        <v>180</v>
+        <v>220</v>
       </c>
     </row>
     <row r="259" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A259" s="5">
-        <v>46172</v>
-      </c>
-      <c r="B259">
-        <v>245</v>
-      </c>
-      <c r="C259">
-        <v>465</v>
+        <v>46165</v>
       </c>
       <c r="E259">
-        <v>370</v>
+        <v>100</v>
       </c>
       <c r="F259">
-        <v>80</v>
+        <v>480</v>
       </c>
       <c r="G259">
-        <v>310</v>
+        <v>120</v>
       </c>
       <c r="H259">
-        <v>275</v>
+        <v>180</v>
       </c>
     </row>
     <row r="260" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A260" s="5">
         <v>46172</v>
       </c>
+      <c r="B260">
+        <v>245</v>
+      </c>
       <c r="C260">
-        <v>40</v>
+        <v>465</v>
       </c>
       <c r="E260">
-        <v>200</v>
+        <v>370</v>
       </c>
       <c r="F260">
-        <v>390</v>
+        <v>80</v>
       </c>
       <c r="G260">
-        <v>235</v>
+        <v>310</v>
       </c>
       <c r="H260">
-        <v>350</v>
+        <v>275</v>
       </c>
     </row>
     <row r="261" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A261" s="5">
-        <v>46179</v>
+        <v>46172</v>
       </c>
       <c r="C261">
-        <v>180</v>
+        <v>40</v>
       </c>
       <c r="E261">
-        <v>475</v>
+        <v>200</v>
       </c>
       <c r="F261">
-        <v>410</v>
+        <v>390</v>
       </c>
       <c r="G261">
-        <v>300</v>
+        <v>235</v>
       </c>
       <c r="H261">
-        <v>195</v>
+        <v>350</v>
       </c>
     </row>
     <row r="262" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A262" s="5">
-        <v>46186</v>
+        <v>46179</v>
+      </c>
+      <c r="C262">
+        <v>180</v>
       </c>
       <c r="E262">
-        <v>398</v>
+        <v>475</v>
       </c>
       <c r="F262">
-        <v>490</v>
+        <v>410</v>
       </c>
       <c r="G262">
-        <v>210</v>
+        <v>300</v>
       </c>
       <c r="H262">
-        <v>305</v>
+        <v>195</v>
       </c>
     </row>
     <row r="263" spans="1:8" x14ac:dyDescent="0.3">
@@ -5616,16 +5616,16 @@
         <v>46186</v>
       </c>
       <c r="E263">
-        <v>235</v>
+        <v>398</v>
       </c>
       <c r="F263">
-        <v>250</v>
+        <v>490</v>
       </c>
       <c r="G263">
-        <v>315</v>
+        <v>210</v>
       </c>
       <c r="H263">
-        <v>325</v>
+        <v>305</v>
       </c>
     </row>
     <row r="264" spans="1:8" x14ac:dyDescent="0.3">
@@ -5633,67 +5633,67 @@
         <v>46186</v>
       </c>
       <c r="E264">
-        <v>245</v>
+        <v>235</v>
       </c>
       <c r="F264">
-        <v>180</v>
+        <v>250</v>
       </c>
       <c r="G264">
-        <v>190</v>
+        <v>315</v>
       </c>
       <c r="H264">
-        <v>295</v>
+        <v>325</v>
       </c>
     </row>
     <row r="265" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A265" s="5">
-        <v>46193</v>
+        <v>46186</v>
       </c>
       <c r="E265">
-        <v>145</v>
+        <v>245</v>
       </c>
       <c r="F265">
-        <v>125</v>
+        <v>180</v>
       </c>
       <c r="G265">
-        <v>280</v>
+        <v>190</v>
       </c>
       <c r="H265">
-        <v>240</v>
+        <v>295</v>
       </c>
     </row>
     <row r="266" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A266" s="5">
-        <v>46194</v>
+        <v>46193</v>
       </c>
       <c r="E266">
-        <v>345</v>
+        <v>145</v>
       </c>
       <c r="F266">
-        <v>185</v>
+        <v>125</v>
       </c>
       <c r="G266">
-        <v>115</v>
+        <v>280</v>
       </c>
       <c r="H266">
-        <v>300</v>
+        <v>240</v>
       </c>
     </row>
     <row r="267" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A267" s="5">
-        <v>46207</v>
+        <v>46194</v>
       </c>
       <c r="E267">
-        <v>275</v>
+        <v>345</v>
       </c>
       <c r="F267">
-        <v>150</v>
+        <v>185</v>
       </c>
       <c r="G267">
+        <v>115</v>
+      </c>
+      <c r="H267">
         <v>300</v>
-      </c>
-      <c r="H267">
-        <v>175</v>
       </c>
     </row>
     <row r="268" spans="1:8" x14ac:dyDescent="0.3">
@@ -5701,33 +5701,33 @@
         <v>46207</v>
       </c>
       <c r="E268">
-        <v>180</v>
+        <v>275</v>
       </c>
       <c r="F268">
-        <v>360</v>
+        <v>150</v>
       </c>
       <c r="G268">
-        <v>190</v>
+        <v>300</v>
       </c>
       <c r="H268">
-        <v>435</v>
+        <v>175</v>
       </c>
     </row>
     <row r="269" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A269" s="5">
-        <v>46214</v>
+        <v>46207</v>
       </c>
       <c r="E269">
-        <v>285</v>
+        <v>180</v>
       </c>
       <c r="F269">
-        <v>105</v>
+        <v>360</v>
       </c>
       <c r="G269">
-        <v>410</v>
+        <v>190</v>
       </c>
       <c r="H269">
-        <v>380</v>
+        <v>435</v>
       </c>
     </row>
     <row r="270" spans="1:8" x14ac:dyDescent="0.3">
@@ -5735,53 +5735,50 @@
         <v>46214</v>
       </c>
       <c r="E270">
-        <v>85</v>
+        <v>285</v>
       </c>
       <c r="F270">
-        <v>240</v>
+        <v>105</v>
       </c>
       <c r="G270">
-        <v>245</v>
+        <v>410</v>
       </c>
       <c r="H270">
-        <v>335</v>
+        <v>380</v>
       </c>
     </row>
     <row r="271" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A271" s="5">
-        <v>46220</v>
-      </c>
-      <c r="C271">
-        <v>40</v>
-      </c>
-      <c r="D271">
-        <v>370</v>
+        <v>46214</v>
+      </c>
+      <c r="E271">
+        <v>85</v>
+      </c>
+      <c r="F271">
+        <v>240</v>
       </c>
       <c r="G271">
-        <v>320</v>
+        <v>245</v>
       </c>
       <c r="H271">
-        <v>175</v>
+        <v>335</v>
       </c>
     </row>
     <row r="272" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A272" s="5">
-        <v>46230</v>
+        <v>46220</v>
       </c>
       <c r="C272">
-        <v>415</v>
-      </c>
-      <c r="E272">
-        <v>240</v>
-      </c>
-      <c r="F272">
-        <v>290</v>
+        <v>40</v>
+      </c>
+      <c r="D272">
+        <v>370</v>
       </c>
       <c r="G272">
-        <v>315</v>
+        <v>320</v>
       </c>
       <c r="H272">
-        <v>125</v>
+        <v>175</v>
       </c>
     </row>
     <row r="273" spans="1:8" x14ac:dyDescent="0.3">
@@ -5789,36 +5786,39 @@
         <v>46230</v>
       </c>
       <c r="C273">
-        <v>200</v>
+        <v>415</v>
       </c>
       <c r="E273">
-        <v>160</v>
+        <v>240</v>
       </c>
       <c r="F273">
-        <v>500</v>
+        <v>290</v>
       </c>
       <c r="G273">
-        <v>360</v>
+        <v>315</v>
       </c>
       <c r="H273">
-        <v>185</v>
+        <v>125</v>
       </c>
     </row>
     <row r="274" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A274" s="5">
-        <v>46235</v>
+        <v>46230</v>
+      </c>
+      <c r="C274">
+        <v>200</v>
       </c>
       <c r="E274">
-        <v>45</v>
+        <v>160</v>
       </c>
       <c r="F274">
-        <v>320</v>
+        <v>500</v>
       </c>
       <c r="G274">
-        <v>380</v>
+        <v>360</v>
       </c>
       <c r="H274">
-        <v>380</v>
+        <v>185</v>
       </c>
     </row>
     <row r="275" spans="1:8" x14ac:dyDescent="0.3">
@@ -5826,32 +5826,49 @@
         <v>46235</v>
       </c>
       <c r="E275">
-        <v>225</v>
+        <v>45</v>
       </c>
       <c r="F275">
-        <v>135</v>
+        <v>320</v>
       </c>
       <c r="G275">
-        <v>285</v>
+        <v>380</v>
       </c>
       <c r="H275">
-        <v>40</v>
+        <v>380</v>
       </c>
     </row>
     <row r="276" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A276" s="5">
+        <v>46235</v>
+      </c>
+      <c r="E276">
+        <v>225</v>
+      </c>
+      <c r="F276">
+        <v>135</v>
+      </c>
+      <c r="G276">
+        <v>285</v>
+      </c>
+      <c r="H276">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="277" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A277" s="5">
         <v>46236</v>
       </c>
-      <c r="E276">
+      <c r="E277">
         <v>270</v>
       </c>
-      <c r="F276">
+      <c r="F277">
         <v>330</v>
       </c>
-      <c r="G276">
+      <c r="G277">
         <v>330</v>
       </c>
-      <c r="H276">
+      <c r="H277">
         <v>540</v>
       </c>
     </row>

--- a/docs/Cottage Rummy Data File.xlsx
+++ b/docs/Cottage Rummy Data File.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\tomku\Dropbox\Personal\Cottage Rummy Stats\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FD8F8784-6F8E-4144-8962-D1E5F32DF64A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5F553057-ECFC-4507-A8C6-C746C475F170}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="1152" windowWidth="23088" windowHeight="10824" tabRatio="832" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="2325" yWindow="-13380" windowWidth="25755" windowHeight="12330" tabRatio="832" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Input" sheetId="6" r:id="rId1"/>
@@ -475,7 +475,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0300-000000000000}">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A1:AKI277"/>
+  <dimension ref="A1:AKI279"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="10.33203125" style="5" bestFit="1" customWidth="1"/>
@@ -5872,6 +5872,46 @@
         <v>540</v>
       </c>
     </row>
+    <row r="278" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A278" s="5">
+        <v>46256</v>
+      </c>
+      <c r="C278">
+        <v>200</v>
+      </c>
+      <c r="E278">
+        <v>305</v>
+      </c>
+      <c r="F278">
+        <v>420</v>
+      </c>
+      <c r="G278">
+        <v>130</v>
+      </c>
+      <c r="H278">
+        <v>175</v>
+      </c>
+    </row>
+    <row r="279" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A279" s="5">
+        <v>46256</v>
+      </c>
+      <c r="C279">
+        <v>220</v>
+      </c>
+      <c r="E279">
+        <v>390</v>
+      </c>
+      <c r="F279">
+        <v>425</v>
+      </c>
+      <c r="G279">
+        <v>215</v>
+      </c>
+      <c r="H279">
+        <v>355</v>
+      </c>
+    </row>
   </sheetData>
   <conditionalFormatting sqref="J134:J1048576 J1:J132">
     <cfRule type="colorScale" priority="21">

--- a/docs/Cottage Rummy Data File.xlsx
+++ b/docs/Cottage Rummy Data File.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\tomku\Dropbox\Personal\Cottage Rummy Stats\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5F553057-ECFC-4507-A8C6-C746C475F170}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{796DBE7C-D319-4109-8C05-56DB62DD8C21}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="2325" yWindow="-13380" windowWidth="25755" windowHeight="12330" tabRatio="832" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="384" yWindow="384" windowWidth="19764" windowHeight="11628" tabRatio="832" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Input" sheetId="6" r:id="rId1"/>
@@ -475,7 +475,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0300-000000000000}">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A1:AKI279"/>
+  <dimension ref="A1:AKI286"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="10.33203125" style="5" bestFit="1" customWidth="1"/>
@@ -5912,6 +5912,125 @@
         <v>355</v>
       </c>
     </row>
+    <row r="280" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A280" s="5">
+        <v>46271</v>
+      </c>
+      <c r="E280">
+        <v>25</v>
+      </c>
+      <c r="F280">
+        <v>395</v>
+      </c>
+      <c r="G280">
+        <v>290</v>
+      </c>
+      <c r="H280">
+        <v>385</v>
+      </c>
+    </row>
+    <row r="281" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A281" s="5">
+        <v>46272</v>
+      </c>
+      <c r="E281">
+        <v>320</v>
+      </c>
+      <c r="F281">
+        <v>420</v>
+      </c>
+      <c r="G281">
+        <v>245</v>
+      </c>
+      <c r="H281">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="282" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A282" s="5">
+        <v>46273</v>
+      </c>
+      <c r="E282">
+        <v>275</v>
+      </c>
+      <c r="F282">
+        <v>365</v>
+      </c>
+      <c r="G282">
+        <v>135</v>
+      </c>
+      <c r="H282">
+        <v>435</v>
+      </c>
+    </row>
+    <row r="283" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A283" s="5">
+        <v>46274</v>
+      </c>
+      <c r="E283">
+        <v>80</v>
+      </c>
+      <c r="F283">
+        <v>340</v>
+      </c>
+      <c r="G283">
+        <v>230</v>
+      </c>
+      <c r="H283">
+        <v>305</v>
+      </c>
+    </row>
+    <row r="284" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A284" s="5">
+        <v>46275</v>
+      </c>
+      <c r="E284">
+        <v>320</v>
+      </c>
+      <c r="F284">
+        <v>450</v>
+      </c>
+      <c r="G284">
+        <v>75</v>
+      </c>
+      <c r="H284">
+        <v>150</v>
+      </c>
+    </row>
+    <row r="285" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A285" s="5">
+        <v>46276</v>
+      </c>
+      <c r="E285">
+        <v>225</v>
+      </c>
+      <c r="F285">
+        <v>425</v>
+      </c>
+      <c r="G285">
+        <v>100</v>
+      </c>
+      <c r="H285">
+        <v>250</v>
+      </c>
+    </row>
+    <row r="286" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A286" s="5">
+        <v>46277</v>
+      </c>
+      <c r="E286">
+        <v>345</v>
+      </c>
+      <c r="F286">
+        <v>310</v>
+      </c>
+      <c r="G286">
+        <v>215</v>
+      </c>
+      <c r="H286">
+        <v>245</v>
+      </c>
+    </row>
   </sheetData>
   <conditionalFormatting sqref="J134:J1048576 J1:J132">
     <cfRule type="colorScale" priority="21">

--- a/docs/Cottage Rummy Data File.xlsx
+++ b/docs/Cottage Rummy Data File.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\tomku\Dropbox\Personal\Cottage Rummy Stats\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{796DBE7C-D319-4109-8C05-56DB62DD8C21}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DCEE5722-7C0A-4C39-B300-3AC55452413C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="384" yWindow="384" windowWidth="19764" windowHeight="11628" tabRatio="832" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="2304" yWindow="2304" windowWidth="17280" windowHeight="8880" tabRatio="832" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Input" sheetId="6" r:id="rId1"/>
@@ -475,7 +475,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0300-000000000000}">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A1:AKI286"/>
+  <dimension ref="A1:AKI287"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="10.33203125" style="5" bestFit="1" customWidth="1"/>
@@ -5914,120 +5914,137 @@
     </row>
     <row r="280" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A280" s="5">
-        <v>46271</v>
+        <v>46267</v>
       </c>
       <c r="E280">
-        <v>25</v>
+        <v>240</v>
       </c>
       <c r="F280">
-        <v>395</v>
+        <v>310</v>
       </c>
       <c r="G280">
-        <v>290</v>
+        <v>260</v>
       </c>
       <c r="H280">
-        <v>385</v>
+        <v>315</v>
       </c>
     </row>
     <row r="281" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A281" s="5">
-        <v>46272</v>
+        <v>46271</v>
       </c>
       <c r="E281">
-        <v>320</v>
+        <v>25</v>
       </c>
       <c r="F281">
-        <v>420</v>
+        <v>395</v>
       </c>
       <c r="G281">
-        <v>245</v>
+        <v>290</v>
       </c>
       <c r="H281">
-        <v>70</v>
+        <v>385</v>
       </c>
     </row>
     <row r="282" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A282" s="5">
-        <v>46273</v>
+        <v>46272</v>
       </c>
       <c r="E282">
-        <v>275</v>
+        <v>320</v>
       </c>
       <c r="F282">
-        <v>365</v>
+        <v>420</v>
       </c>
       <c r="G282">
-        <v>135</v>
+        <v>245</v>
       </c>
       <c r="H282">
-        <v>435</v>
+        <v>70</v>
       </c>
     </row>
     <row r="283" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A283" s="5">
-        <v>46274</v>
+        <v>46273</v>
       </c>
       <c r="E283">
-        <v>80</v>
+        <v>275</v>
       </c>
       <c r="F283">
-        <v>340</v>
+        <v>365</v>
       </c>
       <c r="G283">
-        <v>230</v>
+        <v>135</v>
       </c>
       <c r="H283">
-        <v>305</v>
+        <v>435</v>
       </c>
     </row>
     <row r="284" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A284" s="5">
-        <v>46275</v>
+        <v>46274</v>
       </c>
       <c r="E284">
-        <v>320</v>
+        <v>80</v>
       </c>
       <c r="F284">
-        <v>450</v>
+        <v>340</v>
       </c>
       <c r="G284">
-        <v>75</v>
+        <v>230</v>
       </c>
       <c r="H284">
-        <v>150</v>
+        <v>305</v>
       </c>
     </row>
     <row r="285" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A285" s="5">
-        <v>46276</v>
+        <v>46275</v>
       </c>
       <c r="E285">
-        <v>225</v>
+        <v>320</v>
       </c>
       <c r="F285">
-        <v>425</v>
+        <v>450</v>
       </c>
       <c r="G285">
-        <v>100</v>
+        <v>75</v>
       </c>
       <c r="H285">
-        <v>250</v>
+        <v>150</v>
       </c>
     </row>
     <row r="286" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A286" s="5">
+        <v>46276</v>
+      </c>
+      <c r="E286">
+        <v>225</v>
+      </c>
+      <c r="F286">
+        <v>425</v>
+      </c>
+      <c r="G286">
+        <v>100</v>
+      </c>
+      <c r="H286">
+        <v>250</v>
+      </c>
+    </row>
+    <row r="287" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A287" s="5">
         <v>46277</v>
       </c>
-      <c r="E286">
+      <c r="E287">
         <v>345</v>
       </c>
-      <c r="F286">
+      <c r="F287">
         <v>310</v>
       </c>
-      <c r="G286">
+      <c r="G287">
         <v>215</v>
       </c>
-      <c r="H286">
+      <c r="H287">
         <v>245</v>
       </c>
     </row>

--- a/docs/Cottage Rummy Data File.xlsx
+++ b/docs/Cottage Rummy Data File.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\tomku\Dropbox\Personal\Cottage Rummy Stats\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DCEE5722-7C0A-4C39-B300-3AC55452413C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FDA06F0A-D6E4-49E3-81B4-77F2DE5ABDFA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="2304" yWindow="2304" windowWidth="17280" windowHeight="8880" tabRatio="832" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="768" yWindow="768" windowWidth="17280" windowHeight="8880" tabRatio="832" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Input" sheetId="6" r:id="rId1"/>
@@ -475,7 +475,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0300-000000000000}">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A1:AKI287"/>
+  <dimension ref="A1:AKI288"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="10.33203125" style="5" bestFit="1" customWidth="1"/>
@@ -6048,6 +6048,23 @@
         <v>245</v>
       </c>
     </row>
+    <row r="288" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A288" s="5">
+        <v>46291</v>
+      </c>
+      <c r="E288">
+        <v>210</v>
+      </c>
+      <c r="F288">
+        <v>160</v>
+      </c>
+      <c r="G288">
+        <v>250</v>
+      </c>
+      <c r="H288">
+        <v>225</v>
+      </c>
+    </row>
   </sheetData>
   <conditionalFormatting sqref="J134:J1048576 J1:J132">
     <cfRule type="colorScale" priority="21">

--- a/docs/Cottage Rummy Data File.xlsx
+++ b/docs/Cottage Rummy Data File.xlsx
@@ -1,21 +1,21 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="27932"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30602"/>
   <workbookPr codeName="ThisWorkbook" defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\tomku\Dropbox\Personal\Cottage Rummy Stats\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FDA06F0A-D6E4-49E3-81B4-77F2DE5ABDFA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="5" documentId="13_ncr:1_{FDA06F0A-D6E4-49E3-81B4-77F2DE5ABDFA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{7D04D0CD-0FB9-4E24-AEEE-A29C6852EDD8}"/>
   <bookViews>
     <workbookView xWindow="768" yWindow="768" windowWidth="17280" windowHeight="8880" tabRatio="832" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Input" sheetId="6" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="191029"/>
+  <calcPr calcId="191028"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
@@ -31,15 +31,15 @@
         <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
       </xcalcf:calcFeatures>
     </ext>
-    <ext xmlns:xlwcv="http://schemas.microsoft.com/office/spreadsheetml/2024/workbookCompatibilityVersion" uri="{D14903EA-33C4-47F7-8F05-3474C54BE107}">
-      <xlwcv:version setVersion="1"/>
-    </ext>
   </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
 <sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="8" uniqueCount="8">
+  <si>
+    <t>Date</t>
+  </si>
   <si>
     <t>Christine</t>
   </si>
@@ -61,9 +61,6 @@
   <si>
     <t>Tom</t>
   </si>
-  <si>
-    <t>Date</t>
-  </si>
 </sst>
 </file>
 
@@ -72,7 +69,7 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="[$-1009]d/mmm/yy;@"/>
   </numFmts>
-  <fonts count="2" x14ac:knownFonts="1">
+  <fonts count="2">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -156,9 +153,9 @@
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office 2013 - 2022 Theme">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
   <a:themeElements>
-    <a:clrScheme name="Office 2013 - 2022">
+    <a:clrScheme name="Office">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -196,7 +193,7 @@
         <a:srgbClr val="954F72"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Office 2013 - 2022">
+    <a:fontScheme name="Office">
       <a:majorFont>
         <a:latin typeface="Calibri Light" panose="020F0302020204030204"/>
         <a:ea typeface=""/>
@@ -302,7 +299,7 @@
         <a:font script="Tfng" typeface="Ebrima"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Office 2013 - 2022">
+    <a:fmtScheme name="Office">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -444,7 +441,7 @@
   <a:extraClrSchemeLst/>
   <a:extLst>
     <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
-      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office 2013 - 2022 Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
+      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
     </a:ext>
   </a:extLst>
 </a:theme>
@@ -469,47 +466,52 @@
   </we:properties>
   <we:bindings/>
   <we:snapshot xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships"/>
+  <we:extLst>
+    <a:ext xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" uri="{D87F86FE-615C-45B5-9D79-34F1136793EB}">
+      <we:containsCustomFunctions/>
+    </a:ext>
+  </we:extLst>
 </we:webextension>
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0300-000000000000}">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A1:AKI288"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <dimension ref="A1:AKI289"/>
+  <sheetFormatPr defaultRowHeight="14.45"/>
   <cols>
-    <col min="1" max="1" width="10.33203125" style="5" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="15.6640625" customWidth="1"/>
+    <col min="1" max="1" width="10.28515625" style="5" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="15.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:10" s="2" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:10" s="2" customFormat="1">
       <c r="A1" s="6" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="F1" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="G1" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="H1" s="3" t="s">
         <v>7</v>
       </c>
-      <c r="B1" s="3" t="s">
-        <v>0</v>
-      </c>
-      <c r="C1" s="3" t="s">
-        <v>1</v>
-      </c>
-      <c r="D1" s="3" t="s">
-        <v>2</v>
-      </c>
-      <c r="E1" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="F1" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="G1" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="H1" s="3" t="s">
-        <v>6</v>
-      </c>
       <c r="J1" s="3"/>
     </row>
-    <row r="2" spans="1:10" s="2" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:10" s="2" customFormat="1">
       <c r="A2" s="7">
         <v>44580</v>
       </c>
@@ -530,7 +532,7 @@
       </c>
       <c r="J2"/>
     </row>
-    <row r="3" spans="1:10" s="2" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:10" s="2" customFormat="1">
       <c r="A3" s="7">
         <v>44580</v>
       </c>
@@ -551,7 +553,7 @@
       </c>
       <c r="J3"/>
     </row>
-    <row r="4" spans="1:10" s="2" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:10" s="2" customFormat="1">
       <c r="A4" s="7">
         <v>44580</v>
       </c>
@@ -572,7 +574,7 @@
       </c>
       <c r="J4"/>
     </row>
-    <row r="5" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:10">
       <c r="A5" s="5">
         <v>44617</v>
       </c>
@@ -592,7 +594,7 @@
         <v>235</v>
       </c>
     </row>
-    <row r="6" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:10">
       <c r="A6" s="5">
         <v>44618</v>
       </c>
@@ -615,7 +617,7 @@
         <v>520</v>
       </c>
     </row>
-    <row r="7" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:10">
       <c r="A7" s="5">
         <v>44627</v>
       </c>
@@ -632,7 +634,7 @@
         <v>305</v>
       </c>
     </row>
-    <row r="8" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:10">
       <c r="A8" s="5">
         <v>44632</v>
       </c>
@@ -658,7 +660,7 @@
         <v>375</v>
       </c>
     </row>
-    <row r="9" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:10">
       <c r="A9" s="5">
         <v>44635</v>
       </c>
@@ -684,7 +686,7 @@
         <v>495</v>
       </c>
     </row>
-    <row r="10" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:10">
       <c r="A10" s="5">
         <v>44636</v>
       </c>
@@ -710,7 +712,7 @@
         <v>425</v>
       </c>
     </row>
-    <row r="11" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:10">
       <c r="A11" s="5">
         <v>44637</v>
       </c>
@@ -736,7 +738,7 @@
         <v>435</v>
       </c>
     </row>
-    <row r="12" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:10">
       <c r="A12" s="5">
         <v>44666</v>
       </c>
@@ -759,7 +761,7 @@
         <v>460</v>
       </c>
     </row>
-    <row r="13" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:10">
       <c r="A13" s="5">
         <v>44667</v>
       </c>
@@ -785,7 +787,7 @@
         <v>220</v>
       </c>
     </row>
-    <row r="14" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:10">
       <c r="A14" s="5">
         <v>44681</v>
       </c>
@@ -808,7 +810,7 @@
         <v>410</v>
       </c>
     </row>
-    <row r="15" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:10">
       <c r="A15" s="5">
         <v>44688</v>
       </c>
@@ -828,7 +830,7 @@
         <v>210</v>
       </c>
     </row>
-    <row r="16" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:10">
       <c r="A16" s="5">
         <v>44695</v>
       </c>
@@ -845,7 +847,7 @@
         <v>385</v>
       </c>
     </row>
-    <row r="17" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:8">
       <c r="A17" s="5">
         <v>44842</v>
       </c>
@@ -865,7 +867,7 @@
         <v>80</v>
       </c>
     </row>
-    <row r="18" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:8">
       <c r="A18" s="5">
         <v>44849</v>
       </c>
@@ -885,7 +887,7 @@
         <v>450</v>
       </c>
     </row>
-    <row r="19" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:8">
       <c r="A19" s="5">
         <v>44877</v>
       </c>
@@ -905,7 +907,7 @@
         <v>120</v>
       </c>
     </row>
-    <row r="20" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:8">
       <c r="A20" s="5">
         <v>44884</v>
       </c>
@@ -922,7 +924,7 @@
         <v>185</v>
       </c>
     </row>
-    <row r="21" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:8">
       <c r="A21" s="5">
         <v>44884</v>
       </c>
@@ -939,7 +941,7 @@
         <v>200</v>
       </c>
     </row>
-    <row r="22" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:8">
       <c r="A22" s="5">
         <v>44905</v>
       </c>
@@ -956,7 +958,7 @@
         <v>515</v>
       </c>
     </row>
-    <row r="23" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:8">
       <c r="A23" s="5">
         <v>44919</v>
       </c>
@@ -982,7 +984,7 @@
         <v>385</v>
       </c>
     </row>
-    <row r="24" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:8">
       <c r="A24" s="5">
         <v>44920</v>
       </c>
@@ -1008,7 +1010,7 @@
         <v>590</v>
       </c>
     </row>
-    <row r="25" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:8">
       <c r="A25" s="5">
         <v>44921</v>
       </c>
@@ -1034,7 +1036,7 @@
         <v>380</v>
       </c>
     </row>
-    <row r="26" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:8">
       <c r="A26" s="5">
         <v>44923</v>
       </c>
@@ -1054,7 +1056,7 @@
         <v>370</v>
       </c>
     </row>
-    <row r="27" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:8">
       <c r="A27" s="5">
         <v>44924</v>
       </c>
@@ -1080,7 +1082,7 @@
         <v>390</v>
       </c>
     </row>
-    <row r="28" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:8">
       <c r="A28" s="5">
         <v>44925</v>
       </c>
@@ -1106,7 +1108,7 @@
         <v>580</v>
       </c>
     </row>
-    <row r="29" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:8">
       <c r="A29" s="5">
         <v>44926</v>
       </c>
@@ -1129,7 +1131,7 @@
         <v>475</v>
       </c>
     </row>
-    <row r="30" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="30" spans="1:8">
       <c r="A30" s="5">
         <v>44926</v>
       </c>
@@ -1152,7 +1154,7 @@
         <v>630</v>
       </c>
     </row>
-    <row r="31" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="31" spans="1:8">
       <c r="A31" s="5">
         <v>44927</v>
       </c>
@@ -1178,7 +1180,7 @@
         <v>340</v>
       </c>
     </row>
-    <row r="32" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="32" spans="1:8">
       <c r="A32" s="5">
         <v>44927</v>
       </c>
@@ -1195,7 +1197,7 @@
         <v>615</v>
       </c>
     </row>
-    <row r="33" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="33" spans="1:8">
       <c r="A33" s="5">
         <v>44947</v>
       </c>
@@ -1218,7 +1220,7 @@
         <v>285</v>
       </c>
     </row>
-    <row r="34" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="34" spans="1:8">
       <c r="A34" s="5">
         <v>44947</v>
       </c>
@@ -1238,7 +1240,7 @@
         <v>375</v>
       </c>
     </row>
-    <row r="35" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="35" spans="1:8">
       <c r="A35" s="5">
         <v>44952</v>
       </c>
@@ -1255,7 +1257,7 @@
         <v>325</v>
       </c>
     </row>
-    <row r="36" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="36" spans="1:8">
       <c r="A36" s="5">
         <v>44952</v>
       </c>
@@ -1272,7 +1274,7 @@
         <v>285</v>
       </c>
     </row>
-    <row r="37" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="37" spans="1:8">
       <c r="A37" s="5">
         <v>44953</v>
       </c>
@@ -1289,7 +1291,7 @@
         <v>140</v>
       </c>
     </row>
-    <row r="38" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="38" spans="1:8">
       <c r="A38" s="5">
         <v>44953</v>
       </c>
@@ -1306,7 +1308,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="39" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="39" spans="1:8">
       <c r="A39" s="5">
         <v>44957</v>
       </c>
@@ -1323,7 +1325,7 @@
         <v>310</v>
       </c>
     </row>
-    <row r="40" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="40" spans="1:8">
       <c r="A40" s="5">
         <v>44958</v>
       </c>
@@ -1340,7 +1342,7 @@
         <v>420</v>
       </c>
     </row>
-    <row r="41" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="41" spans="1:8">
       <c r="A41" s="5">
         <v>44959</v>
       </c>
@@ -1357,7 +1359,7 @@
         <v>235</v>
       </c>
     </row>
-    <row r="42" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="42" spans="1:8">
       <c r="A42" s="5">
         <v>44959</v>
       </c>
@@ -1374,7 +1376,7 @@
         <v>115</v>
       </c>
     </row>
-    <row r="43" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="43" spans="1:8">
       <c r="A43" s="5">
         <v>44960</v>
       </c>
@@ -1391,7 +1393,7 @@
         <v>230</v>
       </c>
     </row>
-    <row r="44" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="44" spans="1:8">
       <c r="A44" s="5">
         <v>44961</v>
       </c>
@@ -1408,7 +1410,7 @@
         <v>425</v>
       </c>
     </row>
-    <row r="45" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="45" spans="1:8">
       <c r="A45" s="5">
         <v>44961</v>
       </c>
@@ -1425,7 +1427,7 @@
         <v>285</v>
       </c>
     </row>
-    <row r="46" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="46" spans="1:8">
       <c r="A46" s="5">
         <v>44962</v>
       </c>
@@ -1442,7 +1444,7 @@
         <v>325</v>
       </c>
     </row>
-    <row r="47" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="47" spans="1:8">
       <c r="A47" s="5">
         <v>44996</v>
       </c>
@@ -1468,7 +1470,7 @@
         <v>340</v>
       </c>
     </row>
-    <row r="48" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="48" spans="1:8">
       <c r="A48" s="5">
         <v>44982</v>
       </c>
@@ -1485,7 +1487,7 @@
         <v>315</v>
       </c>
     </row>
-    <row r="49" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="49" spans="1:8">
       <c r="A49" s="5">
         <v>44982</v>
       </c>
@@ -1502,7 +1504,7 @@
         <v>175</v>
       </c>
     </row>
-    <row r="50" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="50" spans="1:8">
       <c r="A50" s="5">
         <v>44982</v>
       </c>
@@ -1519,7 +1521,7 @@
         <v>365</v>
       </c>
     </row>
-    <row r="51" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="51" spans="1:8">
       <c r="A51" s="5">
         <v>44989</v>
       </c>
@@ -1533,7 +1535,7 @@
         <v>140</v>
       </c>
     </row>
-    <row r="52" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="52" spans="1:8">
       <c r="A52" s="5">
         <v>44989</v>
       </c>
@@ -1547,7 +1549,7 @@
         <v>495</v>
       </c>
     </row>
-    <row r="53" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="53" spans="1:8">
       <c r="A53" s="5">
         <v>44989</v>
       </c>
@@ -1561,7 +1563,7 @@
         <v>80</v>
       </c>
     </row>
-    <row r="54" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="54" spans="1:8">
       <c r="A54" s="5">
         <v>44996</v>
       </c>
@@ -1587,7 +1589,7 @@
         <v>340</v>
       </c>
     </row>
-    <row r="55" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="55" spans="1:8">
       <c r="A55" s="5">
         <v>44996</v>
       </c>
@@ -1613,7 +1615,7 @@
         <v>490</v>
       </c>
     </row>
-    <row r="56" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="56" spans="1:8">
       <c r="A56" s="5">
         <v>44998</v>
       </c>
@@ -1639,7 +1641,7 @@
         <v>595</v>
       </c>
     </row>
-    <row r="57" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="57" spans="1:8">
       <c r="A57" s="5">
         <v>44999</v>
       </c>
@@ -1662,7 +1664,7 @@
         <v>250</v>
       </c>
     </row>
-    <row r="58" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="58" spans="1:8">
       <c r="A58" s="5">
         <v>45010</v>
       </c>
@@ -1679,7 +1681,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="59" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="59" spans="1:8">
       <c r="A59" s="5">
         <v>45017</v>
       </c>
@@ -1696,7 +1698,7 @@
         <v>160</v>
       </c>
     </row>
-    <row r="60" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="60" spans="1:8">
       <c r="A60" s="5">
         <v>45017</v>
       </c>
@@ -1713,7 +1715,7 @@
         <v>160</v>
       </c>
     </row>
-    <row r="61" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="61" spans="1:8">
       <c r="A61" s="5">
         <v>45038</v>
       </c>
@@ -1730,7 +1732,7 @@
         <v>135</v>
       </c>
     </row>
-    <row r="62" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="62" spans="1:8">
       <c r="A62" s="5">
         <v>45045</v>
       </c>
@@ -1753,7 +1755,7 @@
         <v>515</v>
       </c>
     </row>
-    <row r="63" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="63" spans="1:8">
       <c r="A63" s="5">
         <v>45052</v>
       </c>
@@ -1773,7 +1775,7 @@
         <v>185</v>
       </c>
     </row>
-    <row r="64" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="64" spans="1:8">
       <c r="A64" s="5">
         <v>45066</v>
       </c>
@@ -1799,7 +1801,7 @@
         <v>490</v>
       </c>
     </row>
-    <row r="65" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="65" spans="1:8">
       <c r="A65" s="5">
         <v>45067</v>
       </c>
@@ -1819,7 +1821,7 @@
         <v>285</v>
       </c>
     </row>
-    <row r="66" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="66" spans="1:8">
       <c r="A66" s="5">
         <v>45068</v>
       </c>
@@ -1839,7 +1841,7 @@
         <v>485</v>
       </c>
     </row>
-    <row r="67" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="67" spans="1:8">
       <c r="A67" s="5">
         <v>45094</v>
       </c>
@@ -1862,7 +1864,7 @@
         <v>165</v>
       </c>
     </row>
-    <row r="68" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="68" spans="1:8">
       <c r="A68" s="5">
         <v>45101</v>
       </c>
@@ -1882,7 +1884,7 @@
         <v>255</v>
       </c>
     </row>
-    <row r="69" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="69" spans="1:8">
       <c r="A69" s="5">
         <v>45101</v>
       </c>
@@ -1902,7 +1904,7 @@
         <v>130</v>
       </c>
     </row>
-    <row r="70" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="70" spans="1:8">
       <c r="A70" s="5">
         <v>45115</v>
       </c>
@@ -1919,7 +1921,7 @@
         <v>305</v>
       </c>
     </row>
-    <row r="71" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="71" spans="1:8">
       <c r="A71" s="5">
         <v>45115</v>
       </c>
@@ -1936,7 +1938,7 @@
         <v>140</v>
       </c>
     </row>
-    <row r="72" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="72" spans="1:8">
       <c r="A72" s="5">
         <v>45122</v>
       </c>
@@ -1956,7 +1958,7 @@
         <v>300</v>
       </c>
     </row>
-    <row r="73" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="73" spans="1:8">
       <c r="A73" s="5">
         <v>45129</v>
       </c>
@@ -1979,7 +1981,7 @@
         <v>200</v>
       </c>
     </row>
-    <row r="74" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="74" spans="1:8">
       <c r="A74" s="5">
         <v>45129</v>
       </c>
@@ -2002,7 +2004,7 @@
         <v>175</v>
       </c>
     </row>
-    <row r="75" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="75" spans="1:8">
       <c r="A75" s="5">
         <v>45136</v>
       </c>
@@ -2019,7 +2021,7 @@
         <v>270</v>
       </c>
     </row>
-    <row r="76" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="76" spans="1:8">
       <c r="A76" s="5">
         <v>45144</v>
       </c>
@@ -2039,7 +2041,7 @@
         <v>270</v>
       </c>
     </row>
-    <row r="77" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="77" spans="1:8">
       <c r="A77" s="5">
         <v>45150</v>
       </c>
@@ -2062,7 +2064,7 @@
         <v>205</v>
       </c>
     </row>
-    <row r="78" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="78" spans="1:8">
       <c r="A78" s="5">
         <v>45151</v>
       </c>
@@ -2085,7 +2087,7 @@
         <v>355</v>
       </c>
     </row>
-    <row r="79" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="79" spans="1:8">
       <c r="A79" s="5">
         <v>45157</v>
       </c>
@@ -2105,7 +2107,7 @@
         <v>155</v>
       </c>
     </row>
-    <row r="80" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="80" spans="1:8">
       <c r="A80" s="5">
         <v>45178</v>
       </c>
@@ -2125,7 +2127,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="81" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="81" spans="1:8">
       <c r="A81" s="5">
         <v>45179</v>
       </c>
@@ -2145,7 +2147,7 @@
         <v>215</v>
       </c>
     </row>
-    <row r="82" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="82" spans="1:8">
       <c r="A82" s="5">
         <v>45213</v>
       </c>
@@ -2168,7 +2170,7 @@
         <v>315</v>
       </c>
     </row>
-    <row r="83" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="83" spans="1:8">
       <c r="A83" s="5">
         <v>45213</v>
       </c>
@@ -2188,7 +2190,7 @@
         <v>360</v>
       </c>
     </row>
-    <row r="84" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="84" spans="1:8">
       <c r="A84" s="5">
         <v>45227</v>
       </c>
@@ -2208,7 +2210,7 @@
         <v>305</v>
       </c>
     </row>
-    <row r="85" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="85" spans="1:8">
       <c r="A85" s="5">
         <v>45248</v>
       </c>
@@ -2225,7 +2227,7 @@
         <v>200</v>
       </c>
     </row>
-    <row r="86" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="86" spans="1:8">
       <c r="A86" s="5">
         <v>45255</v>
       </c>
@@ -2242,7 +2244,7 @@
         <v>235</v>
       </c>
     </row>
-    <row r="87" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="87" spans="1:8">
       <c r="A87" s="5">
         <v>45255</v>
       </c>
@@ -2259,7 +2261,7 @@
         <v>300</v>
       </c>
     </row>
-    <row r="88" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="88" spans="1:8">
       <c r="A88" s="5">
         <v>45263</v>
       </c>
@@ -2276,7 +2278,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="89" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="89" spans="1:8">
       <c r="A89" s="5">
         <v>45263</v>
       </c>
@@ -2293,7 +2295,7 @@
         <v>230</v>
       </c>
     </row>
-    <row r="90" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="90" spans="1:8">
       <c r="A90" s="5">
         <v>45269</v>
       </c>
@@ -2310,7 +2312,7 @@
         <v>310</v>
       </c>
     </row>
-    <row r="91" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="91" spans="1:8">
       <c r="A91" s="5">
         <v>45269</v>
       </c>
@@ -2327,7 +2329,7 @@
         <v>195</v>
       </c>
     </row>
-    <row r="92" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="92" spans="1:8">
       <c r="A92" s="5">
         <v>45269</v>
       </c>
@@ -2344,7 +2346,7 @@
         <v>240</v>
       </c>
     </row>
-    <row r="93" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="93" spans="1:8">
       <c r="A93" s="5">
         <v>45283</v>
       </c>
@@ -2361,7 +2363,7 @@
         <v>245</v>
       </c>
     </row>
-    <row r="94" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="94" spans="1:8">
       <c r="A94" s="5">
         <v>45283</v>
       </c>
@@ -2378,7 +2380,7 @@
         <v>245</v>
       </c>
     </row>
-    <row r="95" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="95" spans="1:8">
       <c r="A95" s="5">
         <v>45283</v>
       </c>
@@ -2395,7 +2397,7 @@
         <v>150</v>
       </c>
     </row>
-    <row r="96" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="96" spans="1:8">
       <c r="A96" s="5">
         <v>45284</v>
       </c>
@@ -2421,7 +2423,7 @@
         <v>505</v>
       </c>
     </row>
-    <row r="97" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="97" spans="1:8">
       <c r="A97" s="5">
         <v>45285</v>
       </c>
@@ -2447,7 +2449,7 @@
         <v>410</v>
       </c>
     </row>
-    <row r="98" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="98" spans="1:8">
       <c r="A98" s="5">
         <v>45285</v>
       </c>
@@ -2473,7 +2475,7 @@
         <v>545</v>
       </c>
     </row>
-    <row r="99" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="99" spans="1:8">
       <c r="A99" s="5">
         <v>45286</v>
       </c>
@@ -2493,7 +2495,7 @@
         <v>75</v>
       </c>
     </row>
-    <row r="100" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="100" spans="1:8">
       <c r="A100" s="5">
         <v>45286</v>
       </c>
@@ -2519,7 +2521,7 @@
         <v>520</v>
       </c>
     </row>
-    <row r="101" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="101" spans="1:8">
       <c r="A101" s="5">
         <v>45290</v>
       </c>
@@ -2545,7 +2547,7 @@
         <v>300</v>
       </c>
     </row>
-    <row r="102" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="102" spans="1:8">
       <c r="A102" s="5">
         <v>45291</v>
       </c>
@@ -2565,7 +2567,7 @@
         <v>220</v>
       </c>
     </row>
-    <row r="103" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="103" spans="1:8">
       <c r="A103" s="5">
         <v>45297</v>
       </c>
@@ -2588,7 +2590,7 @@
         <v>450</v>
       </c>
     </row>
-    <row r="104" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="104" spans="1:8">
       <c r="A104" s="5">
         <v>45297</v>
       </c>
@@ -2611,7 +2613,7 @@
         <v>505</v>
       </c>
     </row>
-    <row r="105" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="105" spans="1:8">
       <c r="A105" s="5">
         <v>45304</v>
       </c>
@@ -2631,7 +2633,7 @@
         <v>225</v>
       </c>
     </row>
-    <row r="106" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="106" spans="1:8">
       <c r="A106" s="5">
         <v>45304</v>
       </c>
@@ -2654,7 +2656,7 @@
         <v>135</v>
       </c>
     </row>
-    <row r="107" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="107" spans="1:8">
       <c r="A107" s="5">
         <v>45318</v>
       </c>
@@ -2671,7 +2673,7 @@
         <v>365</v>
       </c>
     </row>
-    <row r="108" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="108" spans="1:8">
       <c r="A108" s="5">
         <v>45318</v>
       </c>
@@ -2688,7 +2690,7 @@
         <v>320</v>
       </c>
     </row>
-    <row r="109" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="109" spans="1:8">
       <c r="A109" s="5">
         <v>45325</v>
       </c>
@@ -2705,7 +2707,7 @@
         <v>270</v>
       </c>
     </row>
-    <row r="110" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="110" spans="1:8">
       <c r="A110" s="5">
         <v>45325</v>
       </c>
@@ -2722,7 +2724,7 @@
         <v>370</v>
       </c>
     </row>
-    <row r="111" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="111" spans="1:8">
       <c r="A111" s="5">
         <v>45346</v>
       </c>
@@ -2739,7 +2741,7 @@
         <v>305</v>
       </c>
     </row>
-    <row r="112" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="112" spans="1:8">
       <c r="A112" s="5">
         <v>45346</v>
       </c>
@@ -2756,7 +2758,7 @@
         <v>315</v>
       </c>
     </row>
-    <row r="113" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="113" spans="1:8">
       <c r="A113" s="5">
         <v>45356</v>
       </c>
@@ -2779,7 +2781,7 @@
         <v>475</v>
       </c>
     </row>
-    <row r="114" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="114" spans="1:8">
       <c r="A114" s="5">
         <v>45357</v>
       </c>
@@ -2799,7 +2801,7 @@
         <v>230</v>
       </c>
     </row>
-    <row r="115" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="115" spans="1:8">
       <c r="A115" s="5">
         <v>45358</v>
       </c>
@@ -2819,7 +2821,7 @@
         <v>235</v>
       </c>
     </row>
-    <row r="116" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="116" spans="1:8">
       <c r="A116" s="5">
         <v>45358</v>
       </c>
@@ -2839,7 +2841,7 @@
         <v>590</v>
       </c>
     </row>
-    <row r="117" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="117" spans="1:8">
       <c r="A117" s="5">
         <v>45374</v>
       </c>
@@ -2856,7 +2858,7 @@
         <v>135</v>
       </c>
     </row>
-    <row r="118" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="118" spans="1:8">
       <c r="A118" s="5">
         <v>45374</v>
       </c>
@@ -2873,7 +2875,7 @@
         <v>355</v>
       </c>
     </row>
-    <row r="119" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="119" spans="1:8">
       <c r="A119" s="5">
         <v>45388</v>
       </c>
@@ -2890,7 +2892,7 @@
         <v>225</v>
       </c>
     </row>
-    <row r="120" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="120" spans="1:8">
       <c r="A120" s="5">
         <v>45402</v>
       </c>
@@ -2910,7 +2912,7 @@
         <v>185</v>
       </c>
     </row>
-    <row r="121" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="121" spans="1:8">
       <c r="A121" s="5">
         <v>45409</v>
       </c>
@@ -2927,7 +2929,7 @@
         <v>415</v>
       </c>
     </row>
-    <row r="122" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="122" spans="1:8">
       <c r="A122" s="5">
         <v>45416</v>
       </c>
@@ -2947,7 +2949,7 @@
         <v>290</v>
       </c>
     </row>
-    <row r="123" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="123" spans="1:8">
       <c r="A123" s="5">
         <v>45416</v>
       </c>
@@ -2967,7 +2969,7 @@
         <v>280</v>
       </c>
     </row>
-    <row r="124" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="124" spans="1:8">
       <c r="A124" s="5">
         <v>45423</v>
       </c>
@@ -2984,7 +2986,7 @@
         <v>525</v>
       </c>
     </row>
-    <row r="125" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="125" spans="1:8">
       <c r="A125" s="5">
         <v>45423</v>
       </c>
@@ -3001,7 +3003,7 @@
         <v>150</v>
       </c>
     </row>
-    <row r="126" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="126" spans="1:8">
       <c r="A126" s="5">
         <v>45437</v>
       </c>
@@ -3021,7 +3023,7 @@
         <v>240</v>
       </c>
     </row>
-    <row r="127" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="127" spans="1:8">
       <c r="A127" s="5">
         <v>45437</v>
       </c>
@@ -3041,7 +3043,7 @@
         <v>300</v>
       </c>
     </row>
-    <row r="128" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="128" spans="1:8">
       <c r="A128" s="5">
         <v>45444</v>
       </c>
@@ -3061,7 +3063,7 @@
         <v>240</v>
       </c>
     </row>
-    <row r="129" spans="1:971" x14ac:dyDescent="0.3">
+    <row r="129" spans="1:971">
       <c r="A129" s="5">
         <v>45451</v>
       </c>
@@ -3078,7 +3080,7 @@
         <v>305</v>
       </c>
     </row>
-    <row r="130" spans="1:971" x14ac:dyDescent="0.3">
+    <row r="130" spans="1:971">
       <c r="A130" s="5">
         <v>45465</v>
       </c>
@@ -3095,7 +3097,7 @@
         <v>365</v>
       </c>
     </row>
-    <row r="131" spans="1:971" x14ac:dyDescent="0.3">
+    <row r="131" spans="1:971">
       <c r="A131" s="5">
         <v>45501</v>
       </c>
@@ -3115,7 +3117,7 @@
         <v>575</v>
       </c>
     </row>
-    <row r="132" spans="1:971" x14ac:dyDescent="0.3">
+    <row r="132" spans="1:971">
       <c r="A132" s="5">
         <v>45507</v>
       </c>
@@ -3135,7 +3137,7 @@
         <v>135</v>
       </c>
     </row>
-    <row r="133" spans="1:971" x14ac:dyDescent="0.3">
+    <row r="133" spans="1:971">
       <c r="A133" s="5">
         <v>45559</v>
       </c>
@@ -3277,7 +3279,7 @@
       <c r="AKA133" s="1"/>
       <c r="AKI133" s="1"/>
     </row>
-    <row r="134" spans="1:971" x14ac:dyDescent="0.3">
+    <row r="134" spans="1:971">
       <c r="A134" s="5">
         <v>45514</v>
       </c>
@@ -3294,7 +3296,7 @@
         <v>455</v>
       </c>
     </row>
-    <row r="135" spans="1:971" x14ac:dyDescent="0.3">
+    <row r="135" spans="1:971">
       <c r="A135" s="5">
         <v>45521</v>
       </c>
@@ -3311,7 +3313,7 @@
         <v>240</v>
       </c>
     </row>
-    <row r="136" spans="1:971" x14ac:dyDescent="0.3">
+    <row r="136" spans="1:971">
       <c r="A136" s="5">
         <v>45559</v>
       </c>
@@ -3331,7 +3333,7 @@
         <v>585</v>
       </c>
     </row>
-    <row r="137" spans="1:971" x14ac:dyDescent="0.3">
+    <row r="137" spans="1:971">
       <c r="A137" s="5">
         <v>45535</v>
       </c>
@@ -3348,7 +3350,7 @@
         <v>400</v>
       </c>
     </row>
-    <row r="138" spans="1:971" x14ac:dyDescent="0.3">
+    <row r="138" spans="1:971">
       <c r="A138" s="5">
         <v>45542</v>
       </c>
@@ -3365,7 +3367,7 @@
         <v>160</v>
       </c>
     </row>
-    <row r="139" spans="1:971" x14ac:dyDescent="0.3">
+    <row r="139" spans="1:971">
       <c r="A139" s="5">
         <v>45550</v>
       </c>
@@ -3382,7 +3384,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="140" spans="1:971" x14ac:dyDescent="0.3">
+    <row r="140" spans="1:971">
       <c r="A140" s="5">
         <v>45556</v>
       </c>
@@ -3399,7 +3401,7 @@
         <v>190</v>
       </c>
     </row>
-    <row r="141" spans="1:971" x14ac:dyDescent="0.3">
+    <row r="141" spans="1:971">
       <c r="A141" s="5">
         <v>45563</v>
       </c>
@@ -3419,7 +3421,7 @@
         <v>365</v>
       </c>
     </row>
-    <row r="142" spans="1:971" x14ac:dyDescent="0.3">
+    <row r="142" spans="1:971">
       <c r="A142" s="5">
         <v>45570</v>
       </c>
@@ -3436,7 +3438,7 @@
         <v>315</v>
       </c>
     </row>
-    <row r="143" spans="1:971" x14ac:dyDescent="0.3">
+    <row r="143" spans="1:971">
       <c r="A143" s="5">
         <v>45570</v>
       </c>
@@ -3453,7 +3455,7 @@
         <v>310</v>
       </c>
     </row>
-    <row r="144" spans="1:971" x14ac:dyDescent="0.3">
+    <row r="144" spans="1:971">
       <c r="A144" s="5">
         <v>45570</v>
       </c>
@@ -3470,7 +3472,7 @@
         <v>355</v>
       </c>
     </row>
-    <row r="145" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="145" spans="1:8">
       <c r="A145" s="5">
         <v>45577</v>
       </c>
@@ -3487,7 +3489,7 @@
         <v>195</v>
       </c>
     </row>
-    <row r="146" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="146" spans="1:8">
       <c r="A146" s="5">
         <v>45591</v>
       </c>
@@ -3504,7 +3506,7 @@
         <v>340</v>
       </c>
     </row>
-    <row r="147" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="147" spans="1:8">
       <c r="A147" s="5">
         <v>45619</v>
       </c>
@@ -3521,7 +3523,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="148" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="148" spans="1:8">
       <c r="A148" s="5">
         <v>45631</v>
       </c>
@@ -3538,7 +3540,7 @@
         <v>295</v>
       </c>
     </row>
-    <row r="149" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="149" spans="1:8">
       <c r="A149" s="5">
         <v>45647</v>
       </c>
@@ -3558,7 +3560,7 @@
         <v>110</v>
       </c>
     </row>
-    <row r="150" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="150" spans="1:8">
       <c r="A150" s="5">
         <v>45647</v>
       </c>
@@ -3575,7 +3577,7 @@
         <v>300</v>
       </c>
     </row>
-    <row r="151" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="151" spans="1:8">
       <c r="A151" s="5">
         <v>45650</v>
       </c>
@@ -3598,7 +3600,7 @@
         <v>395</v>
       </c>
     </row>
-    <row r="152" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="152" spans="1:8">
       <c r="A152" s="5">
         <v>45650</v>
       </c>
@@ -3618,7 +3620,7 @@
         <v>415</v>
       </c>
     </row>
-    <row r="153" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="153" spans="1:8">
       <c r="A153" s="5">
         <v>45651</v>
       </c>
@@ -3641,7 +3643,7 @@
         <v>250</v>
       </c>
     </row>
-    <row r="154" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="154" spans="1:8">
       <c r="A154" s="5">
         <v>45651</v>
       </c>
@@ -3661,7 +3663,7 @@
         <v>320</v>
       </c>
     </row>
-    <row r="155" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="155" spans="1:8">
       <c r="A155" s="5">
         <v>45652</v>
       </c>
@@ -3684,7 +3686,7 @@
         <v>545</v>
       </c>
     </row>
-    <row r="156" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="156" spans="1:8">
       <c r="A156" s="5">
         <v>45652</v>
       </c>
@@ -3704,7 +3706,7 @@
         <v>460</v>
       </c>
     </row>
-    <row r="157" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="157" spans="1:8">
       <c r="A157" s="5">
         <v>45654</v>
       </c>
@@ -3730,7 +3732,7 @@
         <v>230</v>
       </c>
     </row>
-    <row r="158" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="158" spans="1:8">
       <c r="A158" s="5">
         <v>45654</v>
       </c>
@@ -3753,7 +3755,7 @@
         <v>260</v>
       </c>
     </row>
-    <row r="159" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="159" spans="1:8">
       <c r="A159" s="5">
         <v>45655</v>
       </c>
@@ -3773,7 +3775,7 @@
         <v>265</v>
       </c>
     </row>
-    <row r="160" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="160" spans="1:8">
       <c r="A160" s="5">
         <v>45657</v>
       </c>
@@ -3796,7 +3798,7 @@
         <v>465</v>
       </c>
     </row>
-    <row r="161" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="161" spans="1:8">
       <c r="A161" s="5">
         <v>45657</v>
       </c>
@@ -3819,7 +3821,7 @@
         <v>190</v>
       </c>
     </row>
-    <row r="162" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="162" spans="1:8">
       <c r="A162" s="5">
         <v>45658</v>
       </c>
@@ -3845,7 +3847,7 @@
         <v>570</v>
       </c>
     </row>
-    <row r="163" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="163" spans="1:8">
       <c r="A163" s="5">
         <v>45661</v>
       </c>
@@ -3871,7 +3873,7 @@
         <v>645</v>
       </c>
     </row>
-    <row r="164" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="164" spans="1:8">
       <c r="A164" s="5">
         <v>45668</v>
       </c>
@@ -3885,7 +3887,7 @@
         <v>545</v>
       </c>
     </row>
-    <row r="165" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="165" spans="1:8">
       <c r="A165" s="5">
         <v>45675</v>
       </c>
@@ -3902,7 +3904,7 @@
         <v>45</v>
       </c>
     </row>
-    <row r="166" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="166" spans="1:8">
       <c r="A166" s="5">
         <v>45675</v>
       </c>
@@ -3916,7 +3918,7 @@
         <v>150</v>
       </c>
     </row>
-    <row r="167" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="167" spans="1:8">
       <c r="A167" s="5">
         <v>45682</v>
       </c>
@@ -3933,7 +3935,7 @@
         <v>265</v>
       </c>
     </row>
-    <row r="168" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="168" spans="1:8">
       <c r="A168" s="5">
         <v>45682</v>
       </c>
@@ -3947,7 +3949,7 @@
         <v>300</v>
       </c>
     </row>
-    <row r="169" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="169" spans="1:8">
       <c r="A169" s="5">
         <v>45689</v>
       </c>
@@ -3967,7 +3969,7 @@
         <v>305</v>
       </c>
     </row>
-    <row r="170" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="170" spans="1:8">
       <c r="A170" s="5">
         <v>45696</v>
       </c>
@@ -3981,7 +3983,7 @@
         <v>175</v>
       </c>
     </row>
-    <row r="171" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="171" spans="1:8">
       <c r="A171" s="5">
         <v>45696</v>
       </c>
@@ -3995,7 +3997,7 @@
         <v>205</v>
       </c>
     </row>
-    <row r="172" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="172" spans="1:8">
       <c r="A172" s="5">
         <v>45696</v>
       </c>
@@ -4009,7 +4011,7 @@
         <v>115</v>
       </c>
     </row>
-    <row r="173" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="173" spans="1:8">
       <c r="A173" s="5">
         <v>45705</v>
       </c>
@@ -4023,7 +4025,7 @@
         <v>105</v>
       </c>
     </row>
-    <row r="174" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="174" spans="1:8">
       <c r="A174" s="5">
         <v>45737</v>
       </c>
@@ -4040,7 +4042,7 @@
         <v>65</v>
       </c>
     </row>
-    <row r="175" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="175" spans="1:8">
       <c r="A175" s="5">
         <v>45740</v>
       </c>
@@ -4057,7 +4059,7 @@
         <v>220</v>
       </c>
     </row>
-    <row r="176" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="176" spans="1:8">
       <c r="A176" s="5">
         <v>45746</v>
       </c>
@@ -4074,7 +4076,7 @@
         <v>260</v>
       </c>
     </row>
-    <row r="177" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="177" spans="1:8">
       <c r="A177" s="5">
         <v>45752</v>
       </c>
@@ -4094,7 +4096,7 @@
         <v>605</v>
       </c>
     </row>
-    <row r="178" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="178" spans="1:8">
       <c r="A178" s="5">
         <v>45752</v>
       </c>
@@ -4111,7 +4113,7 @@
         <v>450</v>
       </c>
     </row>
-    <row r="179" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="179" spans="1:8">
       <c r="A179" s="5">
         <v>45759</v>
       </c>
@@ -4128,7 +4130,7 @@
         <v>285</v>
       </c>
     </row>
-    <row r="180" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="180" spans="1:8">
       <c r="A180" s="5">
         <v>45773</v>
       </c>
@@ -4148,7 +4150,7 @@
         <v>395</v>
       </c>
     </row>
-    <row r="181" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="181" spans="1:8">
       <c r="A181" s="5">
         <v>45780</v>
       </c>
@@ -4165,7 +4167,7 @@
         <v>390</v>
       </c>
     </row>
-    <row r="182" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="182" spans="1:8">
       <c r="A182" s="5">
         <v>45780</v>
       </c>
@@ -4182,7 +4184,7 @@
         <v>280</v>
       </c>
     </row>
-    <row r="183" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="183" spans="1:8">
       <c r="A183" s="5">
         <v>45801</v>
       </c>
@@ -4199,7 +4201,7 @@
         <v>150</v>
       </c>
     </row>
-    <row r="184" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="184" spans="1:8">
       <c r="A184" s="5">
         <v>45801</v>
       </c>
@@ -4216,7 +4218,7 @@
         <v>235</v>
       </c>
     </row>
-    <row r="185" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="185" spans="1:8">
       <c r="A185" s="5">
         <v>45801</v>
       </c>
@@ -4233,7 +4235,7 @@
         <v>140</v>
       </c>
     </row>
-    <row r="186" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="186" spans="1:8">
       <c r="A186" s="5">
         <v>45808</v>
       </c>
@@ -4256,7 +4258,7 @@
         <v>345</v>
       </c>
     </row>
-    <row r="187" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="187" spans="1:8">
       <c r="A187" s="5">
         <v>45815</v>
       </c>
@@ -4273,7 +4275,7 @@
         <v>310</v>
       </c>
     </row>
-    <row r="188" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="188" spans="1:8">
       <c r="A188" s="5">
         <v>45836</v>
       </c>
@@ -4293,7 +4295,7 @@
         <v>290</v>
       </c>
     </row>
-    <row r="189" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="189" spans="1:8">
       <c r="A189" s="5">
         <v>45843</v>
       </c>
@@ -4310,7 +4312,7 @@
         <v>280</v>
       </c>
     </row>
-    <row r="190" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="190" spans="1:8">
       <c r="A190" s="5">
         <v>45843</v>
       </c>
@@ -4327,7 +4329,7 @@
         <v>210</v>
       </c>
     </row>
-    <row r="191" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="191" spans="1:8">
       <c r="A191" s="5">
         <v>45850</v>
       </c>
@@ -4344,7 +4346,7 @@
         <v>80</v>
       </c>
     </row>
-    <row r="192" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="192" spans="1:8">
       <c r="A192" s="5">
         <v>45850</v>
       </c>
@@ -4361,7 +4363,7 @@
         <v>170</v>
       </c>
     </row>
-    <row r="193" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="193" spans="1:8">
       <c r="A193" s="5">
         <v>45857</v>
       </c>
@@ -4378,7 +4380,7 @@
         <v>305</v>
       </c>
     </row>
-    <row r="194" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="194" spans="1:8">
       <c r="A194" s="5">
         <v>45886</v>
       </c>
@@ -4395,7 +4397,7 @@
         <v>250</v>
       </c>
     </row>
-    <row r="195" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="195" spans="1:8">
       <c r="A195" s="5">
         <v>45892</v>
       </c>
@@ -4415,7 +4417,7 @@
         <v>400</v>
       </c>
     </row>
-    <row r="196" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="196" spans="1:8">
       <c r="A196" s="5">
         <v>45892</v>
       </c>
@@ -4432,7 +4434,7 @@
         <v>260</v>
       </c>
     </row>
-    <row r="197" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="197" spans="1:8">
       <c r="A197" s="5">
         <v>45899</v>
       </c>
@@ -4449,7 +4451,7 @@
         <v>220</v>
       </c>
     </row>
-    <row r="198" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="198" spans="1:8">
       <c r="A198" s="8">
         <v>45906</v>
       </c>
@@ -4472,7 +4474,7 @@
         <v>320</v>
       </c>
     </row>
-    <row r="199" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="199" spans="1:8">
       <c r="A199" s="8">
         <v>45906</v>
       </c>
@@ -4492,7 +4494,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="200" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="200" spans="1:8">
       <c r="A200" s="8">
         <v>45913</v>
       </c>
@@ -4506,7 +4508,7 @@
         <v>490</v>
       </c>
     </row>
-    <row r="201" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="201" spans="1:8">
       <c r="A201" s="8">
         <v>45913</v>
       </c>
@@ -4526,7 +4528,7 @@
         <v>435</v>
       </c>
     </row>
-    <row r="202" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="202" spans="1:8">
       <c r="A202" s="8">
         <v>45920</v>
       </c>
@@ -4543,7 +4545,7 @@
         <v>175</v>
       </c>
     </row>
-    <row r="203" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="203" spans="1:8">
       <c r="A203" s="8">
         <v>45928</v>
       </c>
@@ -4560,7 +4562,7 @@
         <v>215</v>
       </c>
     </row>
-    <row r="204" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="204" spans="1:8">
       <c r="A204" s="8">
         <v>45930</v>
       </c>
@@ -4577,7 +4579,7 @@
         <v>305</v>
       </c>
     </row>
-    <row r="205" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="205" spans="1:8">
       <c r="A205" s="8">
         <v>45932</v>
       </c>
@@ -4594,7 +4596,7 @@
         <v>290</v>
       </c>
     </row>
-    <row r="206" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="206" spans="1:8">
       <c r="A206" s="8">
         <v>45933</v>
       </c>
@@ -4611,7 +4613,7 @@
         <v>230</v>
       </c>
     </row>
-    <row r="207" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="207" spans="1:8">
       <c r="A207" s="8">
         <v>45934</v>
       </c>
@@ -4628,7 +4630,7 @@
         <v>110</v>
       </c>
     </row>
-    <row r="208" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="208" spans="1:8">
       <c r="A208" s="8">
         <v>45935</v>
       </c>
@@ -4645,7 +4647,7 @@
         <v>420</v>
       </c>
     </row>
-    <row r="209" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="209" spans="1:8">
       <c r="A209" s="8">
         <v>45935</v>
       </c>
@@ -4662,7 +4664,7 @@
         <v>140</v>
       </c>
     </row>
-    <row r="210" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="210" spans="1:8">
       <c r="A210" s="8">
         <v>45935</v>
       </c>
@@ -4679,7 +4681,7 @@
         <v>360</v>
       </c>
     </row>
-    <row r="211" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="211" spans="1:8">
       <c r="A211" s="8">
         <v>45936</v>
       </c>
@@ -4696,7 +4698,7 @@
         <v>165</v>
       </c>
     </row>
-    <row r="212" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="212" spans="1:8">
       <c r="A212" s="8">
         <v>45940</v>
       </c>
@@ -4719,7 +4721,7 @@
         <v>395</v>
       </c>
     </row>
-    <row r="213" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="213" spans="1:8">
       <c r="A213" s="8">
         <v>45942</v>
       </c>
@@ -4736,7 +4738,7 @@
         <v>285</v>
       </c>
     </row>
-    <row r="214" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="214" spans="1:8">
       <c r="A214" s="8">
         <v>45942</v>
       </c>
@@ -4753,7 +4755,7 @@
         <v>275</v>
       </c>
     </row>
-    <row r="215" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="215" spans="1:8">
       <c r="A215" s="8">
         <v>45948</v>
       </c>
@@ -4770,7 +4772,7 @@
         <v>335</v>
       </c>
     </row>
-    <row r="216" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="216" spans="1:8">
       <c r="A216" s="8">
         <v>45948</v>
       </c>
@@ -4787,7 +4789,7 @@
         <v>230</v>
       </c>
     </row>
-    <row r="217" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="217" spans="1:8">
       <c r="A217" s="8">
         <v>45955</v>
       </c>
@@ -4804,7 +4806,7 @@
         <v>130</v>
       </c>
     </row>
-    <row r="218" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="218" spans="1:8">
       <c r="A218" s="8">
         <v>45962</v>
       </c>
@@ -4824,7 +4826,7 @@
         <v>310</v>
       </c>
     </row>
-    <row r="219" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="219" spans="1:8">
       <c r="A219" s="5">
         <v>45969</v>
       </c>
@@ -4847,7 +4849,7 @@
         <v>475</v>
       </c>
     </row>
-    <row r="220" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="220" spans="1:8">
       <c r="A220" s="8">
         <v>45983</v>
       </c>
@@ -4864,7 +4866,7 @@
         <v>340</v>
       </c>
     </row>
-    <row r="221" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="221" spans="1:8">
       <c r="A221" s="8">
         <v>45983</v>
       </c>
@@ -4881,7 +4883,7 @@
         <v>80</v>
       </c>
     </row>
-    <row r="222" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="222" spans="1:8">
       <c r="A222" s="8">
         <v>45990</v>
       </c>
@@ -4895,7 +4897,7 @@
         <v>135</v>
       </c>
     </row>
-    <row r="223" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="223" spans="1:8">
       <c r="A223" s="8">
         <v>45990</v>
       </c>
@@ -4909,7 +4911,7 @@
         <v>380</v>
       </c>
     </row>
-    <row r="224" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="224" spans="1:8">
       <c r="A224" s="8">
         <v>45990</v>
       </c>
@@ -4923,7 +4925,7 @@
         <v>230</v>
       </c>
     </row>
-    <row r="225" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="225" spans="1:8">
       <c r="A225" s="8">
         <v>45990</v>
       </c>
@@ -4937,7 +4939,7 @@
         <v>130</v>
       </c>
     </row>
-    <row r="226" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="226" spans="1:8">
       <c r="A226" s="8">
         <v>45997</v>
       </c>
@@ -4954,7 +4956,7 @@
         <v>240</v>
       </c>
     </row>
-    <row r="227" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="227" spans="1:8">
       <c r="A227" s="8">
         <v>45997</v>
       </c>
@@ -4971,7 +4973,7 @@
         <v>260</v>
       </c>
     </row>
-    <row r="228" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="228" spans="1:8">
       <c r="A228" s="8">
         <v>45997</v>
       </c>
@@ -4988,7 +4990,7 @@
         <v>370</v>
       </c>
     </row>
-    <row r="229" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="229" spans="1:8">
       <c r="A229" s="5">
         <v>46005</v>
       </c>
@@ -5005,7 +5007,7 @@
         <v>275</v>
       </c>
     </row>
-    <row r="230" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="230" spans="1:8">
       <c r="A230" s="5">
         <v>46005</v>
       </c>
@@ -5022,7 +5024,7 @@
         <v>215</v>
       </c>
     </row>
-    <row r="231" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="231" spans="1:8">
       <c r="A231" s="5">
         <v>46012</v>
       </c>
@@ -5042,7 +5044,7 @@
         <v>365</v>
       </c>
     </row>
-    <row r="232" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="232" spans="1:8">
       <c r="A232" s="5">
         <v>46012</v>
       </c>
@@ -5059,7 +5061,7 @@
         <v>145</v>
       </c>
     </row>
-    <row r="233" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="233" spans="1:8">
       <c r="A233" s="5">
         <v>46012</v>
       </c>
@@ -5076,7 +5078,7 @@
         <v>225</v>
       </c>
     </row>
-    <row r="234" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="234" spans="1:8">
       <c r="A234" s="5">
         <v>46015</v>
       </c>
@@ -5099,7 +5101,7 @@
         <v>345</v>
       </c>
     </row>
-    <row r="235" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="235" spans="1:8">
       <c r="A235" s="5">
         <v>46016</v>
       </c>
@@ -5122,7 +5124,7 @@
         <v>565</v>
       </c>
     </row>
-    <row r="236" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="236" spans="1:8">
       <c r="A236" s="5">
         <v>46020</v>
       </c>
@@ -5145,7 +5147,7 @@
         <v>270</v>
       </c>
     </row>
-    <row r="237" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="237" spans="1:8">
       <c r="A237" s="5">
         <v>46032</v>
       </c>
@@ -5159,7 +5161,7 @@
         <v>255</v>
       </c>
     </row>
-    <row r="238" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="238" spans="1:8">
       <c r="A238" s="5">
         <v>46032</v>
       </c>
@@ -5173,7 +5175,7 @@
         <v>190</v>
       </c>
     </row>
-    <row r="239" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="239" spans="1:8">
       <c r="A239" s="5">
         <v>46039</v>
       </c>
@@ -5190,7 +5192,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="240" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="240" spans="1:8">
       <c r="A240" s="5">
         <v>46039</v>
       </c>
@@ -5207,7 +5209,7 @@
         <v>425</v>
       </c>
     </row>
-    <row r="241" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="241" spans="1:8">
       <c r="A241" s="5">
         <v>46039</v>
       </c>
@@ -5224,7 +5226,7 @@
         <v>130</v>
       </c>
     </row>
-    <row r="242" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="242" spans="1:8">
       <c r="A242" s="5">
         <v>46067</v>
       </c>
@@ -5244,7 +5246,7 @@
         <v>340</v>
       </c>
     </row>
-    <row r="243" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="243" spans="1:8">
       <c r="A243" s="5">
         <v>46067</v>
       </c>
@@ -5261,7 +5263,7 @@
         <v>170</v>
       </c>
     </row>
-    <row r="244" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="244" spans="1:8">
       <c r="A244" s="5">
         <v>46067</v>
       </c>
@@ -5278,7 +5280,7 @@
         <v>290</v>
       </c>
     </row>
-    <row r="245" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="245" spans="1:8">
       <c r="A245" s="5">
         <v>46067</v>
       </c>
@@ -5295,7 +5297,7 @@
         <v>270</v>
       </c>
     </row>
-    <row r="246" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="246" spans="1:8">
       <c r="A246" s="5">
         <v>46074</v>
       </c>
@@ -5312,7 +5314,7 @@
         <v>260</v>
       </c>
     </row>
-    <row r="247" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="247" spans="1:8">
       <c r="A247" s="5">
         <v>46074</v>
       </c>
@@ -5329,7 +5331,7 @@
         <v>280</v>
       </c>
     </row>
-    <row r="248" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="248" spans="1:8">
       <c r="A248" s="5">
         <v>46081</v>
       </c>
@@ -5343,7 +5345,7 @@
         <v>120</v>
       </c>
     </row>
-    <row r="249" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="249" spans="1:8">
       <c r="A249" s="5">
         <v>46081</v>
       </c>
@@ -5357,7 +5359,7 @@
         <v>260</v>
       </c>
     </row>
-    <row r="250" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="250" spans="1:8">
       <c r="A250" s="5">
         <v>46109</v>
       </c>
@@ -5374,7 +5376,7 @@
         <v>170</v>
       </c>
     </row>
-    <row r="251" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="251" spans="1:8">
       <c r="A251" s="5">
         <v>46115</v>
       </c>
@@ -5391,7 +5393,7 @@
         <v>235</v>
       </c>
     </row>
-    <row r="252" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="252" spans="1:8">
       <c r="A252" s="5">
         <v>46123</v>
       </c>
@@ -5414,7 +5416,7 @@
         <v>280</v>
       </c>
     </row>
-    <row r="253" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="253" spans="1:8">
       <c r="A253" s="5">
         <v>46130</v>
       </c>
@@ -5431,7 +5433,7 @@
         <v>230</v>
       </c>
     </row>
-    <row r="254" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="254" spans="1:8">
       <c r="A254" s="5">
         <v>46137</v>
       </c>
@@ -5448,7 +5450,7 @@
         <v>420</v>
       </c>
     </row>
-    <row r="255" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="255" spans="1:8">
       <c r="A255" s="5">
         <v>46144</v>
       </c>
@@ -5468,7 +5470,7 @@
         <v>365</v>
       </c>
     </row>
-    <row r="256" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="256" spans="1:8">
       <c r="A256" s="5">
         <v>46151</v>
       </c>
@@ -5491,7 +5493,7 @@
         <v>390</v>
       </c>
     </row>
-    <row r="257" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="257" spans="1:8">
       <c r="A257" s="5">
         <v>46151</v>
       </c>
@@ -5514,7 +5516,7 @@
         <v>335</v>
       </c>
     </row>
-    <row r="258" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="258" spans="1:8">
       <c r="A258" s="5">
         <v>46165</v>
       </c>
@@ -5531,7 +5533,7 @@
         <v>220</v>
       </c>
     </row>
-    <row r="259" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="259" spans="1:8">
       <c r="A259" s="5">
         <v>46165</v>
       </c>
@@ -5548,7 +5550,7 @@
         <v>180</v>
       </c>
     </row>
-    <row r="260" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="260" spans="1:8">
       <c r="A260" s="5">
         <v>46172</v>
       </c>
@@ -5571,7 +5573,7 @@
         <v>275</v>
       </c>
     </row>
-    <row r="261" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="261" spans="1:8">
       <c r="A261" s="5">
         <v>46172</v>
       </c>
@@ -5591,7 +5593,7 @@
         <v>350</v>
       </c>
     </row>
-    <row r="262" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="262" spans="1:8">
       <c r="A262" s="5">
         <v>46179</v>
       </c>
@@ -5611,7 +5613,7 @@
         <v>195</v>
       </c>
     </row>
-    <row r="263" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="263" spans="1:8">
       <c r="A263" s="5">
         <v>46186</v>
       </c>
@@ -5628,7 +5630,7 @@
         <v>305</v>
       </c>
     </row>
-    <row r="264" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="264" spans="1:8">
       <c r="A264" s="5">
         <v>46186</v>
       </c>
@@ -5645,7 +5647,7 @@
         <v>325</v>
       </c>
     </row>
-    <row r="265" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="265" spans="1:8">
       <c r="A265" s="5">
         <v>46186</v>
       </c>
@@ -5662,7 +5664,7 @@
         <v>295</v>
       </c>
     </row>
-    <row r="266" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="266" spans="1:8">
       <c r="A266" s="5">
         <v>46193</v>
       </c>
@@ -5679,7 +5681,7 @@
         <v>240</v>
       </c>
     </row>
-    <row r="267" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="267" spans="1:8">
       <c r="A267" s="5">
         <v>46194</v>
       </c>
@@ -5696,7 +5698,7 @@
         <v>300</v>
       </c>
     </row>
-    <row r="268" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="268" spans="1:8">
       <c r="A268" s="5">
         <v>46207</v>
       </c>
@@ -5713,7 +5715,7 @@
         <v>175</v>
       </c>
     </row>
-    <row r="269" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="269" spans="1:8">
       <c r="A269" s="5">
         <v>46207</v>
       </c>
@@ -5730,7 +5732,7 @@
         <v>435</v>
       </c>
     </row>
-    <row r="270" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="270" spans="1:8">
       <c r="A270" s="5">
         <v>46214</v>
       </c>
@@ -5747,7 +5749,7 @@
         <v>380</v>
       </c>
     </row>
-    <row r="271" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="271" spans="1:8">
       <c r="A271" s="5">
         <v>46214</v>
       </c>
@@ -5764,7 +5766,7 @@
         <v>335</v>
       </c>
     </row>
-    <row r="272" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="272" spans="1:8">
       <c r="A272" s="5">
         <v>46220</v>
       </c>
@@ -5781,7 +5783,7 @@
         <v>175</v>
       </c>
     </row>
-    <row r="273" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="273" spans="1:8">
       <c r="A273" s="5">
         <v>46230</v>
       </c>
@@ -5801,7 +5803,7 @@
         <v>125</v>
       </c>
     </row>
-    <row r="274" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="274" spans="1:8">
       <c r="A274" s="5">
         <v>46230</v>
       </c>
@@ -5821,7 +5823,7 @@
         <v>185</v>
       </c>
     </row>
-    <row r="275" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="275" spans="1:8">
       <c r="A275" s="5">
         <v>46235</v>
       </c>
@@ -5838,7 +5840,7 @@
         <v>380</v>
       </c>
     </row>
-    <row r="276" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="276" spans="1:8">
       <c r="A276" s="5">
         <v>46235</v>
       </c>
@@ -5855,7 +5857,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="277" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="277" spans="1:8">
       <c r="A277" s="5">
         <v>46236</v>
       </c>
@@ -5872,7 +5874,7 @@
         <v>540</v>
       </c>
     </row>
-    <row r="278" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="278" spans="1:8">
       <c r="A278" s="5">
         <v>46256</v>
       </c>
@@ -5892,7 +5894,7 @@
         <v>175</v>
       </c>
     </row>
-    <row r="279" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="279" spans="1:8">
       <c r="A279" s="5">
         <v>46256</v>
       </c>
@@ -5912,7 +5914,7 @@
         <v>355</v>
       </c>
     </row>
-    <row r="280" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="280" spans="1:8">
       <c r="A280" s="5">
         <v>46267</v>
       </c>
@@ -5929,7 +5931,7 @@
         <v>315</v>
       </c>
     </row>
-    <row r="281" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="281" spans="1:8">
       <c r="A281" s="5">
         <v>46271</v>
       </c>
@@ -5946,7 +5948,7 @@
         <v>385</v>
       </c>
     </row>
-    <row r="282" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="282" spans="1:8">
       <c r="A282" s="5">
         <v>46272</v>
       </c>
@@ -5963,7 +5965,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="283" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="283" spans="1:8">
       <c r="A283" s="5">
         <v>46273</v>
       </c>
@@ -5980,7 +5982,7 @@
         <v>435</v>
       </c>
     </row>
-    <row r="284" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="284" spans="1:8">
       <c r="A284" s="5">
         <v>46274</v>
       </c>
@@ -5997,7 +5999,7 @@
         <v>305</v>
       </c>
     </row>
-    <row r="285" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="285" spans="1:8">
       <c r="A285" s="5">
         <v>46275</v>
       </c>
@@ -6014,7 +6016,7 @@
         <v>150</v>
       </c>
     </row>
-    <row r="286" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="286" spans="1:8">
       <c r="A286" s="5">
         <v>46276</v>
       </c>
@@ -6031,7 +6033,7 @@
         <v>250</v>
       </c>
     </row>
-    <row r="287" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="287" spans="1:8">
       <c r="A287" s="5">
         <v>46277</v>
       </c>
@@ -6048,7 +6050,7 @@
         <v>245</v>
       </c>
     </row>
-    <row r="288" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="288" spans="1:8">
       <c r="A288" s="5">
         <v>46291</v>
       </c>
@@ -6063,6 +6065,23 @@
       </c>
       <c r="H288">
         <v>225</v>
+      </c>
+    </row>
+    <row r="289" spans="1:8">
+      <c r="A289" s="5">
+        <v>46298</v>
+      </c>
+      <c r="E289">
+        <v>180</v>
+      </c>
+      <c r="F289">
+        <v>115</v>
+      </c>
+      <c r="G289">
+        <v>105</v>
+      </c>
+      <c r="H289">
+        <v>360</v>
       </c>
     </row>
   </sheetData>

--- a/docs/Cottage Rummy Data File.xlsx
+++ b/docs/Cottage Rummy Data File.xlsx
@@ -1,35 +1,19 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30602"/>
-  <workbookPr codeName="ThisWorkbook" defaultThemeVersion="166925"/>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\tomku\Dropbox\Personal\Cottage Rummy Stats\"/>
-    </mc:Choice>
-  </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="5" documentId="13_ncr:1_{FDA06F0A-D6E4-49E3-81B4-77F2DE5ABDFA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{7D04D0CD-0FB9-4E24-AEEE-A29C6852EDD8}"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <fileVersion appName="Calc"/>
+  <workbookPr backupFile="false" showObjects="all" date1904="false"/>
+  <workbookProtection/>
   <bookViews>
-    <workbookView xWindow="768" yWindow="768" windowWidth="17280" windowHeight="8880" tabRatio="832" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView showHorizontalScroll="true" showVerticalScroll="true" showSheetTabs="true" xWindow="0" yWindow="0" windowWidth="16384" windowHeight="8192" tabRatio="500" firstSheet="0" activeTab="0"/>
   </bookViews>
   <sheets>
-    <sheet name="Input" sheetId="6" r:id="rId1"/>
+    <sheet name="Input" sheetId="1" state="visible" r:id="rId3"/>
   </sheets>
-  <calcPr calcId="191028"/>
+  <calcPr iterateCount="100" refMode="A1" iterate="false" iterateDelta="0.0001"/>
   <extLst>
-    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
-      <x15:workbookPr chartTrackingRefBase="1"/>
-    </ext>
-    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
-      <xcalcf:calcFeatures>
-        <xcalcf:feature name="microsoft.com:RD"/>
-        <xcalcf:feature name="microsoft.com:Single"/>
-        <xcalcf:feature name="microsoft.com:FV"/>
-        <xcalcf:feature name="microsoft.com:CNMTM"/>
-        <xcalcf:feature name="microsoft.com:LET_WF"/>
-        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
-        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
-      </xcalcf:calcFeatures>
+    <ext xmlns:loext="http://schemas.libreoffice.org/" uri="{7626C862-2A13-11E5-B345-FEFF819CDC9F}">
+      <loext:extCalcPr stringRefSyntax="ExcelA1"/>
     </ext>
   </extLst>
 </workbook>
@@ -38,52 +22,69 @@
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
 <sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="8" uniqueCount="8">
   <si>
-    <t>Date</t>
+    <t xml:space="preserve">Date</t>
   </si>
   <si>
-    <t>Christine</t>
+    <t xml:space="preserve">Christine</t>
   </si>
   <si>
-    <t>Michael</t>
+    <t xml:space="preserve">Michael</t>
   </si>
   <si>
-    <t>Alaura</t>
+    <t xml:space="preserve">Alaura</t>
   </si>
   <si>
-    <t>Matthew</t>
+    <t xml:space="preserve">Matthew</t>
   </si>
   <si>
-    <t>Kirby</t>
+    <t xml:space="preserve">Kirby</t>
   </si>
   <si>
-    <t>Annmarie</t>
+    <t xml:space="preserve">Annmarie</t>
   </si>
   <si>
-    <t>Tom</t>
+    <t xml:space="preserve">Tom</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr9="http://schemas.microsoft.com/office/spreadsheetml/2016/revision9" mc:Ignorable="x14ac x16r2 xr xr9">
-  <numFmts count="1">
-    <numFmt numFmtId="164" formatCode="[$-1009]d/mmm/yy;@"/>
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <numFmts count="3">
+    <numFmt numFmtId="164" formatCode="General"/>
+    <numFmt numFmtId="165" formatCode="[$-1009]d/mmm/yy;@"/>
+    <numFmt numFmtId="166" formatCode="dd/mmm/yy"/>
   </numFmts>
-  <fonts count="2">
+  <fonts count="5">
     <font>
       <sz val="11"/>
       <color theme="1"/>
       <name val="Calibri"/>
       <family val="2"/>
-      <scheme val="minor"/>
+      <charset val="1"/>
     </font>
     <font>
-      <b/>
+      <sz val="10"/>
+      <name val="Arial"/>
+      <family val="0"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+      <family val="0"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+      <family val="0"/>
+    </font>
+    <font>
+      <b val="true"/>
       <sz val="11"/>
       <color theme="1"/>
       <name val="Calibri"/>
       <family val="2"/>
-      <scheme val="minor"/>
+      <charset val="1"/>
     </font>
   </fonts>
   <fills count="2">
@@ -95,7 +96,7 @@
     </fill>
   </fills>
   <borders count="1">
-    <border>
+    <border diagonalUp="false" diagonalDown="false">
       <left/>
       <right/>
       <top/>
@@ -103,245 +104,172 @@
       <diagonal/>
     </border>
   </borders>
-  <cellStyleXfs count="1">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
+  <cellStyleXfs count="20">
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
+    <xf numFmtId="43" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
+    <xf numFmtId="41" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
+    <xf numFmtId="44" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
+    <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
+    <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
   </cellStyleXfs>
   <cellXfs count="9">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="15" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="center"/>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center"/>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="right"/>
+    <xf numFmtId="165" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="164" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center"/>
+    <xf numFmtId="164" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
-      <alignment horizontal="center"/>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
-      <alignment horizontal="right"/>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="right" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="166" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="right" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
     </xf>
   </cellXfs>
-  <cellStyles count="1">
+  <cellStyles count="6">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
+    <cellStyle name="Comma" xfId="15" builtinId="3"/>
+    <cellStyle name="Comma [0]" xfId="16" builtinId="6"/>
+    <cellStyle name="Currency" xfId="17" builtinId="4"/>
+    <cellStyle name="Currency [0]" xfId="18" builtinId="7"/>
+    <cellStyle name="Percent" xfId="19" builtinId="5"/>
   </cellStyles>
-  <dxfs count="0"/>
-  <tableStyles count="1" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16">
-    <tableStyle name="Invisible" pivot="0" table="0" count="0" xr9:uid="{00000000-0011-0000-FFFF-FFFF00000000}"/>
-  </tableStyles>
-  <colors>
-    <mruColors>
-      <color rgb="FFF4BFBE"/>
-    </mruColors>
-  </colors>
-  <extLst>
-    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
-      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
-    </ext>
-    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
-      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
-    </ext>
-  </extLst>
 </styleSheet>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Office Theme">
   <a:themeElements>
     <a:clrScheme name="Office">
       <a:dk1>
-        <a:sysClr val="windowText" lastClr="000000"/>
+        <a:srgbClr val="000000"/>
       </a:dk1>
       <a:lt1>
-        <a:sysClr val="window" lastClr="FFFFFF"/>
+        <a:srgbClr val="ffffff"/>
       </a:lt1>
       <a:dk2>
-        <a:srgbClr val="44546A"/>
+        <a:srgbClr val="44546a"/>
       </a:dk2>
       <a:lt2>
-        <a:srgbClr val="E7E6E6"/>
+        <a:srgbClr val="e7e6e6"/>
       </a:lt2>
       <a:accent1>
-        <a:srgbClr val="4472C4"/>
+        <a:srgbClr val="4472c4"/>
       </a:accent1>
       <a:accent2>
-        <a:srgbClr val="ED7D31"/>
+        <a:srgbClr val="ed7d31"/>
       </a:accent2>
       <a:accent3>
-        <a:srgbClr val="A5A5A5"/>
+        <a:srgbClr val="a5a5a5"/>
       </a:accent3>
       <a:accent4>
-        <a:srgbClr val="FFC000"/>
+        <a:srgbClr val="ffc000"/>
       </a:accent4>
       <a:accent5>
-        <a:srgbClr val="5B9BD5"/>
+        <a:srgbClr val="5b9bd5"/>
       </a:accent5>
       <a:accent6>
-        <a:srgbClr val="70AD47"/>
+        <a:srgbClr val="70ad47"/>
       </a:accent6>
       <a:hlink>
-        <a:srgbClr val="0563C1"/>
+        <a:srgbClr val="0563c1"/>
       </a:hlink>
       <a:folHlink>
-        <a:srgbClr val="954F72"/>
+        <a:srgbClr val="954f72"/>
       </a:folHlink>
     </a:clrScheme>
     <a:fontScheme name="Office">
       <a:majorFont>
-        <a:latin typeface="Calibri Light" panose="020F0302020204030204"/>
+        <a:latin typeface="Calibri Light" panose="020F0302020204030204" pitchFamily="0" charset="1"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
-        <a:font script="Jpan" typeface="游ゴシック Light"/>
-        <a:font script="Hang" typeface="맑은 고딕"/>
-        <a:font script="Hans" typeface="等线 Light"/>
-        <a:font script="Hant" typeface="新細明體"/>
-        <a:font script="Arab" typeface="Times New Roman"/>
-        <a:font script="Hebr" typeface="Times New Roman"/>
-        <a:font script="Thai" typeface="Tahoma"/>
-        <a:font script="Ethi" typeface="Nyala"/>
-        <a:font script="Beng" typeface="Vrinda"/>
-        <a:font script="Gujr" typeface="Shruti"/>
-        <a:font script="Khmr" typeface="MoolBoran"/>
-        <a:font script="Knda" typeface="Tunga"/>
-        <a:font script="Guru" typeface="Raavi"/>
-        <a:font script="Cans" typeface="Euphemia"/>
-        <a:font script="Cher" typeface="Plantagenet Cherokee"/>
-        <a:font script="Yiii" typeface="Microsoft Yi Baiti"/>
-        <a:font script="Tibt" typeface="Microsoft Himalaya"/>
-        <a:font script="Thaa" typeface="MV Boli"/>
-        <a:font script="Deva" typeface="Mangal"/>
-        <a:font script="Telu" typeface="Gautami"/>
-        <a:font script="Taml" typeface="Latha"/>
-        <a:font script="Syrc" typeface="Estrangelo Edessa"/>
-        <a:font script="Orya" typeface="Kalinga"/>
-        <a:font script="Mlym" typeface="Kartika"/>
-        <a:font script="Laoo" typeface="DokChampa"/>
-        <a:font script="Sinh" typeface="Iskoola Pota"/>
-        <a:font script="Mong" typeface="Mongolian Baiti"/>
-        <a:font script="Viet" typeface="Times New Roman"/>
-        <a:font script="Uigh" typeface="Microsoft Uighur"/>
-        <a:font script="Geor" typeface="Sylfaen"/>
-        <a:font script="Armn" typeface="Arial"/>
-        <a:font script="Bugi" typeface="Leelawadee UI"/>
-        <a:font script="Bopo" typeface="Microsoft JhengHei"/>
-        <a:font script="Java" typeface="Javanese Text"/>
-        <a:font script="Lisu" typeface="Segoe UI"/>
-        <a:font script="Mymr" typeface="Myanmar Text"/>
-        <a:font script="Nkoo" typeface="Ebrima"/>
-        <a:font script="Olck" typeface="Nirmala UI"/>
-        <a:font script="Osma" typeface="Ebrima"/>
-        <a:font script="Phag" typeface="Phagspa"/>
-        <a:font script="Syrn" typeface="Estrangelo Edessa"/>
-        <a:font script="Syrj" typeface="Estrangelo Edessa"/>
-        <a:font script="Syre" typeface="Estrangelo Edessa"/>
-        <a:font script="Sora" typeface="Nirmala UI"/>
-        <a:font script="Tale" typeface="Microsoft Tai Le"/>
-        <a:font script="Talu" typeface="Microsoft New Tai Lue"/>
-        <a:font script="Tfng" typeface="Ebrima"/>
       </a:majorFont>
       <a:minorFont>
-        <a:latin typeface="Calibri" panose="020F0502020204030204"/>
+        <a:latin typeface="Calibri" panose="020F0502020204030204" pitchFamily="0" charset="1"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
-        <a:font script="Jpan" typeface="游ゴシック"/>
-        <a:font script="Hang" typeface="맑은 고딕"/>
-        <a:font script="Hans" typeface="等线"/>
-        <a:font script="Hant" typeface="新細明體"/>
-        <a:font script="Arab" typeface="Arial"/>
-        <a:font script="Hebr" typeface="Arial"/>
-        <a:font script="Thai" typeface="Tahoma"/>
-        <a:font script="Ethi" typeface="Nyala"/>
-        <a:font script="Beng" typeface="Vrinda"/>
-        <a:font script="Gujr" typeface="Shruti"/>
-        <a:font script="Khmr" typeface="DaunPenh"/>
-        <a:font script="Knda" typeface="Tunga"/>
-        <a:font script="Guru" typeface="Raavi"/>
-        <a:font script="Cans" typeface="Euphemia"/>
-        <a:font script="Cher" typeface="Plantagenet Cherokee"/>
-        <a:font script="Yiii" typeface="Microsoft Yi Baiti"/>
-        <a:font script="Tibt" typeface="Microsoft Himalaya"/>
-        <a:font script="Thaa" typeface="MV Boli"/>
-        <a:font script="Deva" typeface="Mangal"/>
-        <a:font script="Telu" typeface="Gautami"/>
-        <a:font script="Taml" typeface="Latha"/>
-        <a:font script="Syrc" typeface="Estrangelo Edessa"/>
-        <a:font script="Orya" typeface="Kalinga"/>
-        <a:font script="Mlym" typeface="Kartika"/>
-        <a:font script="Laoo" typeface="DokChampa"/>
-        <a:font script="Sinh" typeface="Iskoola Pota"/>
-        <a:font script="Mong" typeface="Mongolian Baiti"/>
-        <a:font script="Viet" typeface="Arial"/>
-        <a:font script="Uigh" typeface="Microsoft Uighur"/>
-        <a:font script="Geor" typeface="Sylfaen"/>
-        <a:font script="Armn" typeface="Arial"/>
-        <a:font script="Bugi" typeface="Leelawadee UI"/>
-        <a:font script="Bopo" typeface="Microsoft JhengHei"/>
-        <a:font script="Java" typeface="Javanese Text"/>
-        <a:font script="Lisu" typeface="Segoe UI"/>
-        <a:font script="Mymr" typeface="Myanmar Text"/>
-        <a:font script="Nkoo" typeface="Ebrima"/>
-        <a:font script="Olck" typeface="Nirmala UI"/>
-        <a:font script="Osma" typeface="Ebrima"/>
-        <a:font script="Phag" typeface="Phagspa"/>
-        <a:font script="Syrn" typeface="Estrangelo Edessa"/>
-        <a:font script="Syrj" typeface="Estrangelo Edessa"/>
-        <a:font script="Syre" typeface="Estrangelo Edessa"/>
-        <a:font script="Sora" typeface="Nirmala UI"/>
-        <a:font script="Tale" typeface="Microsoft Tai Le"/>
-        <a:font script="Talu" typeface="Microsoft New Tai Lue"/>
-        <a:font script="Tfng" typeface="Ebrima"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Office">
+    <a:fmtScheme>
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
         </a:solidFill>
-        <a:gradFill rotWithShape="1">
+        <a:gradFill>
           <a:gsLst>
             <a:gs pos="0">
               <a:schemeClr val="phClr">
                 <a:lumMod val="110000"/>
-                <a:satMod val="105000"/>
                 <a:tint val="67000"/>
               </a:schemeClr>
             </a:gs>
             <a:gs pos="50000">
               <a:schemeClr val="phClr">
                 <a:lumMod val="105000"/>
-                <a:satMod val="103000"/>
                 <a:tint val="73000"/>
               </a:schemeClr>
             </a:gs>
             <a:gs pos="100000">
               <a:schemeClr val="phClr">
                 <a:lumMod val="105000"/>
-                <a:satMod val="109000"/>
                 <a:tint val="81000"/>
               </a:schemeClr>
             </a:gs>
           </a:gsLst>
           <a:lin ang="5400000" scaled="0"/>
+          <a:tileRect l="0" t="0" r="0" b="0"/>
         </a:gradFill>
-        <a:gradFill rotWithShape="1">
+        <a:gradFill>
           <a:gsLst>
             <a:gs pos="0">
               <a:schemeClr val="phClr">
-                <a:satMod val="103000"/>
                 <a:lumMod val="102000"/>
                 <a:tint val="94000"/>
               </a:schemeClr>
             </a:gs>
             <a:gs pos="50000">
               <a:schemeClr val="phClr">
-                <a:satMod val="110000"/>
                 <a:lumMod val="100000"/>
                 <a:shade val="100000"/>
               </a:schemeClr>
@@ -349,33 +277,24 @@
             <a:gs pos="100000">
               <a:schemeClr val="phClr">
                 <a:lumMod val="99000"/>
-                <a:satMod val="120000"/>
                 <a:shade val="78000"/>
               </a:schemeClr>
             </a:gs>
           </a:gsLst>
           <a:lin ang="5400000" scaled="0"/>
+          <a:tileRect l="0" t="0" r="0" b="0"/>
         </a:gradFill>
       </a:fillStyleLst>
       <a:lnStyleLst>
         <a:ln w="6350" cap="flat" cmpd="sng" algn="ctr">
-          <a:solidFill>
-            <a:schemeClr val="phClr"/>
-          </a:solidFill>
           <a:prstDash val="solid"/>
           <a:miter lim="800000"/>
         </a:ln>
         <a:ln w="12700" cap="flat" cmpd="sng" algn="ctr">
-          <a:solidFill>
-            <a:schemeClr val="phClr"/>
-          </a:solidFill>
           <a:prstDash val="solid"/>
           <a:miter lim="800000"/>
         </a:ln>
         <a:ln w="19050" cap="flat" cmpd="sng" algn="ctr">
-          <a:solidFill>
-            <a:schemeClr val="phClr"/>
-          </a:solidFill>
           <a:prstDash val="solid"/>
           <a:miter lim="800000"/>
         </a:ln>
@@ -388,13 +307,7 @@
           <a:effectLst/>
         </a:effectStyle>
         <a:effectStyle>
-          <a:effectLst>
-            <a:outerShdw blurRad="57150" dist="19050" dir="5400000" algn="ctr" rotWithShape="0">
-              <a:srgbClr val="000000">
-                <a:alpha val="63000"/>
-              </a:srgbClr>
-            </a:outerShdw>
-          </a:effectLst>
+          <a:effectLst/>
         </a:effectStyle>
       </a:effectStyleLst>
       <a:bgFillStyleLst>
@@ -404,15 +317,13 @@
         <a:solidFill>
           <a:schemeClr val="phClr">
             <a:tint val="95000"/>
-            <a:satMod val="170000"/>
           </a:schemeClr>
         </a:solidFill>
-        <a:gradFill rotWithShape="1">
+        <a:gradFill>
           <a:gsLst>
             <a:gs pos="0">
               <a:schemeClr val="phClr">
                 <a:tint val="93000"/>
-                <a:satMod val="150000"/>
                 <a:shade val="98000"/>
                 <a:lumMod val="102000"/>
               </a:schemeClr>
@@ -420,7 +331,6 @@
             <a:gs pos="50000">
               <a:schemeClr val="phClr">
                 <a:tint val="98000"/>
-                <a:satMod val="130000"/>
                 <a:shade val="90000"/>
                 <a:lumMod val="103000"/>
               </a:schemeClr>
@@ -428,22 +338,15 @@
             <a:gs pos="100000">
               <a:schemeClr val="phClr">
                 <a:shade val="63000"/>
-                <a:satMod val="120000"/>
               </a:schemeClr>
             </a:gs>
           </a:gsLst>
           <a:lin ang="5400000" scaled="0"/>
+          <a:tileRect l="0" t="0" r="0" b="0"/>
         </a:gradFill>
       </a:bgFillStyleLst>
     </a:fmtScheme>
   </a:themeElements>
-  <a:objectDefaults/>
-  <a:extraClrSchemeLst/>
-  <a:extLst>
-    <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
-      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
-    </a:ext>
-  </a:extLst>
 </a:theme>
 </file>
 
@@ -455,37 +358,20 @@
 </wetp:taskpanes>
 </file>
 
-<file path=xl/webextensions/webextension1.xml><?xml version="1.0" encoding="utf-8"?>
-<we:webextension xmlns:we="http://schemas.microsoft.com/office/webextensions/webextension/2010/11" id="{5EAA29D7-D4FD-4ED6-9069-A41C45D10D62}">
-  <we:reference id="wa200009404" version="1.0.0.8" store="en-US" storeType="OMEX"/>
-  <we:alternateReferences>
-    <we:reference id="wa200009404" version="1.0.0.8" store="en-US" storeType="OMEX"/>
-  </we:alternateReferences>
-  <we:properties>
-    <we:property name="claude.fileId" value="&quot;0819c0bc-6d73-4b54-bcd8-c2d5d2c69d40&quot;"/>
-  </we:properties>
-  <we:bindings/>
-  <we:snapshot xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships"/>
-  <we:extLst>
-    <a:ext xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" uri="{D87F86FE-615C-45B5-9D79-34F1136793EB}">
-      <we:containsCustomFunctions/>
-    </a:ext>
-  </we:extLst>
-</we:webextension>
-</file>
-
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0300-000000000000}">
-  <sheetPr codeName="Sheet2"/>
-  <dimension ref="A1:AKI289"/>
-  <sheetFormatPr defaultRowHeight="14.45"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+  <sheetPr filterMode="false">
+    <pageSetUpPr fitToPage="false"/>
+  </sheetPr>
+  <dimension ref="A1:AKI291"/>
+  <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="14.25" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col min="1" max="1" width="10.28515625" style="5" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="15.7109375" customWidth="1"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="10.29"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="10" min="10" style="0" width="15.71"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:10" s="2" customFormat="1">
-      <c r="A1" s="6" t="s">
+    <row r="1" s="4" customFormat="true" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
       <c r="B1" s="3" t="s">
@@ -511,5593 +397,5632 @@
       </c>
       <c r="J1" s="3"/>
     </row>
-    <row r="2" spans="1:10" s="2" customFormat="1">
-      <c r="A2" s="7">
+    <row r="2" s="4" customFormat="true" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A2" s="5" t="n">
         <v>44580</v>
       </c>
-      <c r="B2" s="4">
+      <c r="B2" s="6" t="n">
         <v>225</v>
       </c>
-      <c r="C2" s="4">
+      <c r="C2" s="6" t="n">
         <v>390</v>
       </c>
-      <c r="D2" s="4"/>
-      <c r="E2" s="4"/>
-      <c r="F2" s="4"/>
-      <c r="G2" s="4">
+      <c r="D2" s="6"/>
+      <c r="E2" s="6"/>
+      <c r="F2" s="6"/>
+      <c r="G2" s="6" t="n">
         <v>290</v>
       </c>
-      <c r="H2" s="4">
+      <c r="H2" s="6" t="n">
         <v>5</v>
       </c>
-      <c r="J2"/>
-    </row>
-    <row r="3" spans="1:10" s="2" customFormat="1">
-      <c r="A3" s="7">
+    </row>
+    <row r="3" s="4" customFormat="true" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A3" s="5" t="n">
         <v>44580</v>
       </c>
-      <c r="B3" s="4"/>
-      <c r="C3" s="4">
+      <c r="B3" s="6"/>
+      <c r="C3" s="6" t="n">
         <v>155</v>
       </c>
-      <c r="D3" s="4">
+      <c r="D3" s="6" t="n">
         <v>185</v>
       </c>
-      <c r="E3" s="4"/>
-      <c r="F3" s="4"/>
-      <c r="G3" s="4">
+      <c r="E3" s="6"/>
+      <c r="F3" s="6"/>
+      <c r="G3" s="6" t="n">
         <v>310</v>
       </c>
-      <c r="H3" s="4">
+      <c r="H3" s="6" t="n">
         <v>295</v>
       </c>
-      <c r="J3"/>
-    </row>
-    <row r="4" spans="1:10" s="2" customFormat="1">
-      <c r="A4" s="7">
+    </row>
+    <row r="4" s="4" customFormat="true" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A4" s="5" t="n">
         <v>44580</v>
       </c>
-      <c r="B4" s="4"/>
-      <c r="C4" s="4">
+      <c r="B4" s="6"/>
+      <c r="C4" s="6" t="n">
         <v>380</v>
       </c>
-      <c r="D4" s="4">
+      <c r="D4" s="6" t="n">
         <v>100</v>
       </c>
-      <c r="E4" s="4"/>
-      <c r="F4" s="4"/>
-      <c r="G4" s="4">
+      <c r="E4" s="6"/>
+      <c r="F4" s="6"/>
+      <c r="G4" s="6" t="n">
         <v>215</v>
       </c>
-      <c r="H4" s="4">
+      <c r="H4" s="6" t="n">
         <v>195</v>
       </c>
-      <c r="J4"/>
-    </row>
-    <row r="5" spans="1:10">
-      <c r="A5" s="5">
+    </row>
+    <row r="5" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A5" s="1" t="n">
         <v>44617</v>
       </c>
-      <c r="B5">
+      <c r="B5" s="0" t="n">
         <v>310</v>
       </c>
-      <c r="C5">
+      <c r="C5" s="0" t="n">
         <v>260</v>
       </c>
-      <c r="D5">
+      <c r="D5" s="0" t="n">
         <v>255</v>
       </c>
-      <c r="G5">
+      <c r="G5" s="0" t="n">
         <v>290</v>
       </c>
-      <c r="H5">
+      <c r="H5" s="0" t="n">
         <v>235</v>
       </c>
     </row>
-    <row r="6" spans="1:10">
-      <c r="A6" s="5">
+    <row r="6" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A6" s="1" t="n">
         <v>44618</v>
       </c>
-      <c r="C6">
+      <c r="C6" s="0" t="n">
         <v>325</v>
       </c>
-      <c r="D6">
+      <c r="D6" s="0" t="n">
         <v>595</v>
       </c>
-      <c r="E6">
+      <c r="E6" s="0" t="n">
         <v>200</v>
       </c>
-      <c r="F6">
+      <c r="F6" s="0" t="n">
         <v>170</v>
       </c>
-      <c r="G6">
+      <c r="G6" s="0" t="n">
         <v>390</v>
       </c>
-      <c r="H6">
+      <c r="H6" s="0" t="n">
         <v>520</v>
       </c>
     </row>
-    <row r="7" spans="1:10">
-      <c r="A7" s="5">
+    <row r="7" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A7" s="1" t="n">
         <v>44627</v>
       </c>
-      <c r="C7">
+      <c r="C7" s="0" t="n">
         <v>65</v>
       </c>
-      <c r="D7">
+      <c r="D7" s="0" t="n">
         <v>435</v>
       </c>
-      <c r="G7">
+      <c r="G7" s="0" t="n">
         <v>215</v>
       </c>
-      <c r="H7">
+      <c r="H7" s="0" t="n">
         <v>305</v>
       </c>
     </row>
-    <row r="8" spans="1:10">
-      <c r="A8" s="5">
+    <row r="8" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A8" s="1" t="n">
         <v>44632</v>
       </c>
-      <c r="B8">
+      <c r="B8" s="0" t="n">
         <v>570</v>
       </c>
-      <c r="C8">
+      <c r="C8" s="0" t="n">
         <v>285</v>
       </c>
-      <c r="D8">
+      <c r="D8" s="0" t="n">
         <v>555</v>
       </c>
-      <c r="E8">
+      <c r="E8" s="0" t="n">
         <v>205</v>
       </c>
-      <c r="F8">
+      <c r="F8" s="0" t="n">
         <v>330</v>
       </c>
-      <c r="G8">
+      <c r="G8" s="0" t="n">
         <v>280</v>
       </c>
-      <c r="H8">
+      <c r="H8" s="0" t="n">
         <v>375</v>
       </c>
     </row>
-    <row r="9" spans="1:10">
-      <c r="A9" s="5">
+    <row r="9" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A9" s="1" t="n">
         <v>44635</v>
       </c>
-      <c r="B9">
+      <c r="B9" s="0" t="n">
         <v>240</v>
       </c>
-      <c r="C9">
+      <c r="C9" s="0" t="n">
         <v>295</v>
       </c>
-      <c r="D9">
+      <c r="D9" s="0" t="n">
         <v>525</v>
       </c>
-      <c r="E9">
+      <c r="E9" s="0" t="n">
         <v>645</v>
       </c>
-      <c r="F9">
+      <c r="F9" s="0" t="n">
         <v>130</v>
       </c>
-      <c r="G9">
+      <c r="G9" s="0" t="n">
         <v>325</v>
       </c>
-      <c r="H9">
+      <c r="H9" s="0" t="n">
         <v>495</v>
       </c>
     </row>
-    <row r="10" spans="1:10">
-      <c r="A10" s="5">
+    <row r="10" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A10" s="1" t="n">
         <v>44636</v>
       </c>
-      <c r="B10">
+      <c r="B10" s="0" t="n">
         <v>300</v>
       </c>
-      <c r="C10">
+      <c r="C10" s="0" t="n">
         <v>400</v>
       </c>
-      <c r="D10">
+      <c r="D10" s="0" t="n">
         <v>210</v>
       </c>
-      <c r="E10">
+      <c r="E10" s="0" t="n">
         <v>525</v>
       </c>
-      <c r="F10">
+      <c r="F10" s="0" t="n">
         <v>545</v>
       </c>
-      <c r="G10">
+      <c r="G10" s="0" t="n">
         <v>100</v>
       </c>
-      <c r="H10">
+      <c r="H10" s="0" t="n">
         <v>425</v>
       </c>
     </row>
-    <row r="11" spans="1:10">
-      <c r="A11" s="5">
+    <row r="11" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A11" s="1" t="n">
         <v>44637</v>
       </c>
-      <c r="B11">
+      <c r="B11" s="0" t="n">
         <v>405</v>
       </c>
-      <c r="C11">
+      <c r="C11" s="0" t="n">
         <v>405</v>
       </c>
-      <c r="D11">
+      <c r="D11" s="0" t="n">
         <v>515</v>
       </c>
-      <c r="E11">
+      <c r="E11" s="0" t="n">
         <v>175</v>
       </c>
-      <c r="F11">
+      <c r="F11" s="0" t="n">
         <v>370</v>
       </c>
-      <c r="G11">
+      <c r="G11" s="0" t="n">
         <v>155</v>
       </c>
-      <c r="H11">
+      <c r="H11" s="0" t="n">
         <v>435</v>
       </c>
     </row>
-    <row r="12" spans="1:10">
-      <c r="A12" s="5">
+    <row r="12" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A12" s="1" t="n">
         <v>44666</v>
       </c>
-      <c r="C12">
+      <c r="C12" s="0" t="n">
         <v>295</v>
       </c>
-      <c r="D12">
+      <c r="D12" s="0" t="n">
         <v>610</v>
       </c>
-      <c r="E12">
+      <c r="E12" s="0" t="n">
         <v>240</v>
       </c>
-      <c r="F12">
+      <c r="F12" s="0" t="n">
         <v>425</v>
       </c>
-      <c r="G12">
+      <c r="G12" s="0" t="n">
         <v>455</v>
       </c>
-      <c r="H12">
+      <c r="H12" s="0" t="n">
         <v>460</v>
       </c>
     </row>
-    <row r="13" spans="1:10">
-      <c r="A13" s="5">
+    <row r="13" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A13" s="1" t="n">
         <v>44667</v>
       </c>
-      <c r="B13">
+      <c r="B13" s="0" t="n">
         <v>245</v>
       </c>
-      <c r="C13">
+      <c r="C13" s="0" t="n">
         <v>400</v>
       </c>
-      <c r="D13">
+      <c r="D13" s="0" t="n">
         <v>525</v>
       </c>
-      <c r="E13">
+      <c r="E13" s="0" t="n">
         <v>295</v>
       </c>
-      <c r="F13">
+      <c r="F13" s="0" t="n">
         <v>580</v>
       </c>
-      <c r="G13">
+      <c r="G13" s="0" t="n">
         <v>415</v>
       </c>
-      <c r="H13">
+      <c r="H13" s="0" t="n">
         <v>220</v>
       </c>
     </row>
-    <row r="14" spans="1:10">
-      <c r="A14" s="5">
+    <row r="14" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A14" s="1" t="n">
         <v>44681</v>
       </c>
-      <c r="B14">
+      <c r="B14" s="0" t="n">
         <v>335</v>
       </c>
-      <c r="C14">
+      <c r="C14" s="0" t="n">
         <v>280</v>
       </c>
-      <c r="D14">
+      <c r="D14" s="0" t="n">
         <v>435</v>
       </c>
-      <c r="E14">
+      <c r="E14" s="0" t="n">
         <v>260</v>
       </c>
-      <c r="G14">
+      <c r="G14" s="0" t="n">
         <v>365</v>
       </c>
-      <c r="H14">
+      <c r="H14" s="0" t="n">
         <v>410</v>
       </c>
     </row>
-    <row r="15" spans="1:10">
-      <c r="A15" s="5">
+    <row r="15" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A15" s="1" t="n">
         <v>44688</v>
       </c>
-      <c r="C15">
+      <c r="C15" s="0" t="n">
         <v>300</v>
       </c>
-      <c r="E15">
+      <c r="E15" s="0" t="n">
         <v>375</v>
       </c>
-      <c r="F15">
+      <c r="F15" s="0" t="n">
         <v>35</v>
       </c>
-      <c r="G15">
+      <c r="G15" s="0" t="n">
         <v>195</v>
       </c>
-      <c r="H15">
+      <c r="H15" s="0" t="n">
         <v>210</v>
       </c>
     </row>
-    <row r="16" spans="1:10">
-      <c r="A16" s="5">
+    <row r="16" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A16" s="1" t="n">
         <v>44695</v>
       </c>
-      <c r="E16">
+      <c r="E16" s="0" t="n">
         <v>270</v>
       </c>
-      <c r="F16">
+      <c r="F16" s="0" t="n">
         <v>495</v>
       </c>
-      <c r="G16">
+      <c r="G16" s="0" t="n">
         <v>80</v>
       </c>
-      <c r="H16">
+      <c r="H16" s="0" t="n">
         <v>385</v>
       </c>
     </row>
-    <row r="17" spans="1:8">
-      <c r="A17" s="5">
+    <row r="17" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A17" s="1" t="n">
         <v>44842</v>
       </c>
-      <c r="B17">
+      <c r="B17" s="0" t="n">
         <v>490</v>
       </c>
-      <c r="C17">
+      <c r="C17" s="0" t="n">
         <v>150</v>
       </c>
-      <c r="D17">
+      <c r="D17" s="0" t="n">
         <v>505</v>
       </c>
-      <c r="G17">
+      <c r="G17" s="0" t="n">
         <v>255</v>
       </c>
-      <c r="H17">
+      <c r="H17" s="0" t="n">
         <v>80</v>
       </c>
     </row>
-    <row r="18" spans="1:8">
-      <c r="A18" s="5">
+    <row r="18" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A18" s="1" t="n">
         <v>44849</v>
       </c>
-      <c r="C18">
+      <c r="C18" s="0" t="n">
         <v>415</v>
       </c>
-      <c r="E18">
+      <c r="E18" s="0" t="n">
         <v>155</v>
       </c>
-      <c r="F18">
+      <c r="F18" s="0" t="n">
         <v>305</v>
       </c>
-      <c r="G18">
+      <c r="G18" s="0" t="n">
         <v>145</v>
       </c>
-      <c r="H18">
+      <c r="H18" s="0" t="n">
         <v>450</v>
       </c>
     </row>
-    <row r="19" spans="1:8">
-      <c r="A19" s="5">
+    <row r="19" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A19" s="1" t="n">
         <v>44877</v>
       </c>
-      <c r="C19">
+      <c r="C19" s="0" t="n">
         <v>215</v>
       </c>
-      <c r="E19">
+      <c r="E19" s="0" t="n">
         <v>310</v>
       </c>
-      <c r="F19">
+      <c r="F19" s="0" t="n">
         <v>385</v>
       </c>
-      <c r="G19">
+      <c r="G19" s="0" t="n">
         <v>190</v>
       </c>
-      <c r="H19">
+      <c r="H19" s="0" t="n">
         <v>120</v>
       </c>
     </row>
-    <row r="20" spans="1:8">
-      <c r="A20" s="5">
+    <row r="20" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A20" s="1" t="n">
         <v>44884</v>
       </c>
-      <c r="B20">
+      <c r="B20" s="0" t="n">
         <v>205</v>
       </c>
-      <c r="C20">
+      <c r="C20" s="0" t="n">
         <v>265</v>
       </c>
-      <c r="G20">
+      <c r="G20" s="0" t="n">
         <v>265</v>
       </c>
-      <c r="H20">
+      <c r="H20" s="0" t="n">
         <v>185</v>
       </c>
     </row>
-    <row r="21" spans="1:8">
-      <c r="A21" s="5">
+    <row r="21" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A21" s="1" t="n">
         <v>44884</v>
       </c>
-      <c r="B21">
+      <c r="B21" s="0" t="n">
         <v>400</v>
       </c>
-      <c r="C21">
+      <c r="C21" s="0" t="n">
         <v>420</v>
       </c>
-      <c r="G21">
+      <c r="G21" s="0" t="n">
         <v>120</v>
       </c>
-      <c r="H21">
+      <c r="H21" s="0" t="n">
         <v>200</v>
       </c>
     </row>
-    <row r="22" spans="1:8">
-      <c r="A22" s="5">
+    <row r="22" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A22" s="1" t="n">
         <v>44905</v>
       </c>
-      <c r="B22">
+      <c r="B22" s="0" t="n">
         <v>180</v>
       </c>
-      <c r="C22">
+      <c r="C22" s="0" t="n">
         <v>170</v>
       </c>
-      <c r="E22">
+      <c r="E22" s="0" t="n">
         <v>115</v>
       </c>
-      <c r="F22">
+      <c r="F22" s="0" t="n">
         <v>515</v>
       </c>
     </row>
-    <row r="23" spans="1:8">
-      <c r="A23" s="5">
+    <row r="23" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A23" s="1" t="n">
         <v>44919</v>
       </c>
-      <c r="B23">
+      <c r="B23" s="0" t="n">
         <v>390</v>
       </c>
-      <c r="C23">
+      <c r="C23" s="0" t="n">
         <v>320</v>
       </c>
-      <c r="D23">
+      <c r="D23" s="0" t="n">
         <v>315</v>
       </c>
-      <c r="E23">
+      <c r="E23" s="0" t="n">
         <v>325</v>
       </c>
-      <c r="F23">
+      <c r="F23" s="0" t="n">
         <v>270</v>
       </c>
-      <c r="G23">
+      <c r="G23" s="0" t="n">
         <v>380</v>
       </c>
-      <c r="H23">
+      <c r="H23" s="0" t="n">
         <v>385</v>
       </c>
     </row>
-    <row r="24" spans="1:8">
-      <c r="A24" s="5">
+    <row r="24" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A24" s="1" t="n">
         <v>44920</v>
       </c>
-      <c r="B24">
+      <c r="B24" s="0" t="n">
         <v>350</v>
       </c>
-      <c r="C24">
+      <c r="C24" s="0" t="n">
         <v>490</v>
       </c>
-      <c r="D24">
+      <c r="D24" s="0" t="n">
         <v>130</v>
       </c>
-      <c r="E24">
+      <c r="E24" s="0" t="n">
         <v>430</v>
       </c>
-      <c r="F24">
+      <c r="F24" s="0" t="n">
         <v>285</v>
       </c>
-      <c r="G24">
+      <c r="G24" s="0" t="n">
         <v>340</v>
       </c>
-      <c r="H24">
+      <c r="H24" s="0" t="n">
         <v>590</v>
       </c>
     </row>
-    <row r="25" spans="1:8">
-      <c r="A25" s="5">
+    <row r="25" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A25" s="1" t="n">
         <v>44921</v>
       </c>
-      <c r="B25">
+      <c r="B25" s="0" t="n">
         <v>145</v>
       </c>
-      <c r="C25">
+      <c r="C25" s="0" t="n">
         <v>285</v>
       </c>
-      <c r="D25">
+      <c r="D25" s="0" t="n">
         <v>390</v>
       </c>
-      <c r="E25">
+      <c r="E25" s="0" t="n">
         <v>505</v>
       </c>
-      <c r="F25">
+      <c r="F25" s="0" t="n">
         <v>485</v>
       </c>
-      <c r="G25">
+      <c r="G25" s="0" t="n">
         <v>280</v>
       </c>
-      <c r="H25">
+      <c r="H25" s="0" t="n">
         <v>380</v>
       </c>
     </row>
-    <row r="26" spans="1:8">
-      <c r="A26" s="5">
+    <row r="26" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A26" s="1" t="n">
         <v>44923</v>
       </c>
-      <c r="B26">
+      <c r="B26" s="0" t="n">
         <v>435</v>
       </c>
-      <c r="C26">
+      <c r="C26" s="0" t="n">
         <v>255</v>
       </c>
-      <c r="D26">
+      <c r="D26" s="0" t="n">
         <v>405</v>
       </c>
-      <c r="G26">
+      <c r="G26" s="0" t="n">
         <v>440</v>
       </c>
-      <c r="H26">
+      <c r="H26" s="0" t="n">
         <v>370</v>
       </c>
     </row>
-    <row r="27" spans="1:8">
-      <c r="A27" s="5">
+    <row r="27" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A27" s="1" t="n">
         <v>44924</v>
       </c>
-      <c r="B27">
+      <c r="B27" s="0" t="n">
         <v>425</v>
       </c>
-      <c r="C27">
+      <c r="C27" s="0" t="n">
         <v>200</v>
       </c>
-      <c r="D27">
+      <c r="D27" s="0" t="n">
         <v>520</v>
       </c>
-      <c r="E27">
+      <c r="E27" s="0" t="n">
         <v>365</v>
       </c>
-      <c r="F27">
+      <c r="F27" s="0" t="n">
         <v>275</v>
       </c>
-      <c r="G27">
+      <c r="G27" s="0" t="n">
         <v>305</v>
       </c>
-      <c r="H27">
+      <c r="H27" s="0" t="n">
         <v>390</v>
       </c>
     </row>
-    <row r="28" spans="1:8">
-      <c r="A28" s="5">
+    <row r="28" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A28" s="1" t="n">
         <v>44925</v>
       </c>
-      <c r="B28">
+      <c r="B28" s="0" t="n">
         <v>215</v>
       </c>
-      <c r="C28">
+      <c r="C28" s="0" t="n">
         <v>485</v>
       </c>
-      <c r="D28">
+      <c r="D28" s="0" t="n">
         <v>520</v>
       </c>
-      <c r="E28">
+      <c r="E28" s="0" t="n">
         <v>435</v>
       </c>
-      <c r="F28">
+      <c r="F28" s="0" t="n">
         <v>80</v>
       </c>
-      <c r="G28">
+      <c r="G28" s="0" t="n">
         <v>305</v>
       </c>
-      <c r="H28">
+      <c r="H28" s="0" t="n">
         <v>580</v>
       </c>
     </row>
-    <row r="29" spans="1:8">
-      <c r="A29" s="5">
+    <row r="29" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A29" s="1" t="n">
         <v>44926</v>
       </c>
-      <c r="C29">
+      <c r="C29" s="0" t="n">
         <v>185</v>
       </c>
-      <c r="D29">
+      <c r="D29" s="0" t="n">
         <v>405</v>
       </c>
-      <c r="E29">
+      <c r="E29" s="0" t="n">
         <v>345</v>
       </c>
-      <c r="F29">
+      <c r="F29" s="0" t="n">
         <v>140</v>
       </c>
-      <c r="G29">
+      <c r="G29" s="0" t="n">
         <v>300</v>
       </c>
-      <c r="H29">
+      <c r="H29" s="0" t="n">
         <v>475</v>
       </c>
     </row>
-    <row r="30" spans="1:8">
-      <c r="A30" s="5">
+    <row r="30" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A30" s="1" t="n">
         <v>44926</v>
       </c>
-      <c r="C30">
+      <c r="C30" s="0" t="n">
         <v>290</v>
       </c>
-      <c r="D30">
+      <c r="D30" s="0" t="n">
         <v>325</v>
       </c>
-      <c r="E30">
+      <c r="E30" s="0" t="n">
         <v>190</v>
       </c>
-      <c r="F30">
+      <c r="F30" s="0" t="n">
         <v>90</v>
       </c>
-      <c r="G30">
+      <c r="G30" s="0" t="n">
         <v>310</v>
       </c>
-      <c r="H30">
+      <c r="H30" s="0" t="n">
         <v>630</v>
       </c>
     </row>
-    <row r="31" spans="1:8">
-      <c r="A31" s="5">
+    <row r="31" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A31" s="1" t="n">
         <v>44927</v>
       </c>
-      <c r="B31">
+      <c r="B31" s="0" t="n">
         <v>315</v>
       </c>
-      <c r="C31">
+      <c r="C31" s="0" t="n">
         <v>215</v>
       </c>
-      <c r="D31">
+      <c r="D31" s="0" t="n">
         <v>675</v>
       </c>
-      <c r="E31">
+      <c r="E31" s="0" t="n">
         <v>430</v>
       </c>
-      <c r="F31">
+      <c r="F31" s="0" t="n">
         <v>405</v>
       </c>
-      <c r="G31">
+      <c r="G31" s="0" t="n">
         <v>310</v>
       </c>
-      <c r="H31">
+      <c r="H31" s="0" t="n">
         <v>340</v>
       </c>
     </row>
-    <row r="32" spans="1:8">
-      <c r="A32" s="5">
+    <row r="32" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A32" s="1" t="n">
         <v>44927</v>
       </c>
-      <c r="C32">
+      <c r="C32" s="0" t="n">
         <v>250</v>
       </c>
-      <c r="E32">
+      <c r="E32" s="0" t="n">
         <v>330</v>
       </c>
-      <c r="F32">
+      <c r="F32" s="0" t="n">
         <v>240</v>
       </c>
-      <c r="H32">
+      <c r="H32" s="0" t="n">
         <v>615</v>
       </c>
     </row>
-    <row r="33" spans="1:8">
-      <c r="A33" s="5">
+    <row r="33" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A33" s="1" t="n">
         <v>44947</v>
       </c>
-      <c r="B33">
+      <c r="B33" s="0" t="n">
         <v>220</v>
       </c>
-      <c r="C33">
+      <c r="C33" s="0" t="n">
         <v>165</v>
       </c>
-      <c r="E33">
+      <c r="E33" s="0" t="n">
         <v>185</v>
       </c>
-      <c r="F33">
+      <c r="F33" s="0" t="n">
         <v>145</v>
       </c>
-      <c r="G33">
+      <c r="G33" s="0" t="n">
         <v>275</v>
       </c>
-      <c r="H33">
+      <c r="H33" s="0" t="n">
         <v>285</v>
       </c>
     </row>
-    <row r="34" spans="1:8">
-      <c r="A34" s="5">
+    <row r="34" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A34" s="1" t="n">
         <v>44947</v>
       </c>
-      <c r="B34">
+      <c r="B34" s="0" t="n">
         <v>245</v>
       </c>
-      <c r="E34">
+      <c r="E34" s="0" t="n">
         <v>205</v>
       </c>
-      <c r="F34">
+      <c r="F34" s="0" t="n">
         <v>375</v>
       </c>
-      <c r="G34">
+      <c r="G34" s="0" t="n">
         <v>580</v>
       </c>
-      <c r="H34">
+      <c r="H34" s="0" t="n">
         <v>375</v>
       </c>
     </row>
-    <row r="35" spans="1:8">
-      <c r="A35" s="5">
+    <row r="35" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A35" s="1" t="n">
         <v>44952</v>
       </c>
-      <c r="E35">
+      <c r="E35" s="0" t="n">
         <v>220</v>
       </c>
-      <c r="F35">
+      <c r="F35" s="0" t="n">
         <v>140</v>
       </c>
-      <c r="G35">
+      <c r="G35" s="0" t="n">
         <v>460</v>
       </c>
-      <c r="H35">
+      <c r="H35" s="0" t="n">
         <v>325</v>
       </c>
     </row>
-    <row r="36" spans="1:8">
-      <c r="A36" s="5">
+    <row r="36" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A36" s="1" t="n">
         <v>44952</v>
       </c>
-      <c r="E36">
+      <c r="E36" s="0" t="n">
         <v>250</v>
       </c>
-      <c r="F36">
+      <c r="F36" s="0" t="n">
         <v>280</v>
       </c>
-      <c r="G36">
+      <c r="G36" s="0" t="n">
         <v>130</v>
       </c>
-      <c r="H36">
+      <c r="H36" s="0" t="n">
         <v>285</v>
       </c>
     </row>
-    <row r="37" spans="1:8">
-      <c r="A37" s="5">
+    <row r="37" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A37" s="1" t="n">
         <v>44953</v>
       </c>
-      <c r="E37">
+      <c r="E37" s="0" t="n">
         <v>205</v>
       </c>
-      <c r="F37">
+      <c r="F37" s="0" t="n">
         <v>265</v>
       </c>
-      <c r="G37">
+      <c r="G37" s="0" t="n">
         <v>445</v>
       </c>
-      <c r="H37">
+      <c r="H37" s="0" t="n">
         <v>140</v>
       </c>
     </row>
-    <row r="38" spans="1:8">
-      <c r="A38" s="5">
+    <row r="38" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A38" s="1" t="n">
         <v>44953</v>
       </c>
-      <c r="E38">
+      <c r="E38" s="0" t="n">
         <v>255</v>
       </c>
-      <c r="F38">
+      <c r="F38" s="0" t="n">
         <v>330</v>
       </c>
-      <c r="G38">
+      <c r="G38" s="0" t="n">
         <v>310</v>
       </c>
-      <c r="H38">
+      <c r="H38" s="0" t="n">
         <v>50</v>
       </c>
     </row>
-    <row r="39" spans="1:8">
-      <c r="A39" s="5">
+    <row r="39" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A39" s="1" t="n">
         <v>44957</v>
       </c>
-      <c r="E39">
+      <c r="E39" s="0" t="n">
         <v>355</v>
       </c>
-      <c r="F39">
+      <c r="F39" s="0" t="n">
         <v>130</v>
       </c>
-      <c r="G39">
+      <c r="G39" s="0" t="n">
         <v>165</v>
       </c>
-      <c r="H39">
+      <c r="H39" s="0" t="n">
         <v>310</v>
       </c>
     </row>
-    <row r="40" spans="1:8">
-      <c r="A40" s="5">
+    <row r="40" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A40" s="1" t="n">
         <v>44958</v>
       </c>
-      <c r="E40">
+      <c r="E40" s="0" t="n">
         <v>270</v>
       </c>
-      <c r="F40">
+      <c r="F40" s="0" t="n">
         <v>425</v>
       </c>
-      <c r="G40">
+      <c r="G40" s="0" t="n">
         <v>75</v>
       </c>
-      <c r="H40">
+      <c r="H40" s="0" t="n">
         <v>420</v>
       </c>
     </row>
-    <row r="41" spans="1:8">
-      <c r="A41" s="5">
+    <row r="41" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A41" s="1" t="n">
         <v>44959</v>
       </c>
-      <c r="E41">
+      <c r="E41" s="0" t="n">
         <v>320</v>
       </c>
-      <c r="F41">
+      <c r="F41" s="0" t="n">
         <v>175</v>
       </c>
-      <c r="G41">
+      <c r="G41" s="0" t="n">
         <v>220</v>
       </c>
-      <c r="H41">
+      <c r="H41" s="0" t="n">
         <v>235</v>
       </c>
     </row>
-    <row r="42" spans="1:8">
-      <c r="A42" s="5">
+    <row r="42" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A42" s="1" t="n">
         <v>44959</v>
       </c>
-      <c r="E42">
+      <c r="E42" s="0" t="n">
         <v>280</v>
       </c>
-      <c r="F42">
+      <c r="F42" s="0" t="n">
         <v>280</v>
       </c>
-      <c r="G42">
+      <c r="G42" s="0" t="n">
         <v>215</v>
       </c>
-      <c r="H42">
+      <c r="H42" s="0" t="n">
         <v>115</v>
       </c>
     </row>
-    <row r="43" spans="1:8">
-      <c r="A43" s="5">
+    <row r="43" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A43" s="1" t="n">
         <v>44960</v>
       </c>
-      <c r="E43">
+      <c r="E43" s="0" t="n">
         <v>115</v>
       </c>
-      <c r="F43">
+      <c r="F43" s="0" t="n">
         <v>250</v>
       </c>
-      <c r="G43">
+      <c r="G43" s="0" t="n">
         <v>370</v>
       </c>
-      <c r="H43">
+      <c r="H43" s="0" t="n">
         <v>230</v>
       </c>
     </row>
-    <row r="44" spans="1:8">
-      <c r="A44" s="5">
+    <row r="44" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A44" s="1" t="n">
         <v>44961</v>
       </c>
-      <c r="E44">
+      <c r="E44" s="0" t="n">
         <v>75</v>
       </c>
-      <c r="F44">
+      <c r="F44" s="0" t="n">
         <v>220</v>
       </c>
-      <c r="G44">
+      <c r="G44" s="0" t="n">
         <v>245</v>
       </c>
-      <c r="H44">
+      <c r="H44" s="0" t="n">
         <v>425</v>
       </c>
     </row>
-    <row r="45" spans="1:8">
-      <c r="A45" s="5">
+    <row r="45" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A45" s="1" t="n">
         <v>44961</v>
       </c>
-      <c r="E45">
+      <c r="E45" s="0" t="n">
         <v>165</v>
       </c>
-      <c r="F45">
+      <c r="F45" s="0" t="n">
         <v>130</v>
       </c>
-      <c r="G45">
+      <c r="G45" s="0" t="n">
         <v>150</v>
       </c>
-      <c r="H45">
+      <c r="H45" s="0" t="n">
         <v>285</v>
       </c>
     </row>
-    <row r="46" spans="1:8">
-      <c r="A46" s="5">
+    <row r="46" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A46" s="1" t="n">
         <v>44962</v>
       </c>
-      <c r="E46">
+      <c r="E46" s="0" t="n">
         <v>385</v>
       </c>
-      <c r="F46">
+      <c r="F46" s="0" t="n">
         <v>320</v>
       </c>
-      <c r="G46">
+      <c r="G46" s="0" t="n">
         <v>240</v>
       </c>
-      <c r="H46">
+      <c r="H46" s="0" t="n">
         <v>325</v>
       </c>
     </row>
-    <row r="47" spans="1:8">
-      <c r="A47" s="5">
+    <row r="47" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A47" s="1" t="n">
         <v>44996</v>
       </c>
-      <c r="B47">
+      <c r="B47" s="0" t="n">
         <v>370</v>
       </c>
-      <c r="C47">
+      <c r="C47" s="0" t="n">
         <v>355</v>
       </c>
-      <c r="D47">
+      <c r="D47" s="0" t="n">
         <v>290</v>
       </c>
-      <c r="E47">
+      <c r="E47" s="0" t="n">
         <v>210</v>
       </c>
-      <c r="F47">
+      <c r="F47" s="0" t="n">
         <v>325</v>
       </c>
-      <c r="G47">
+      <c r="G47" s="0" t="n">
         <v>390</v>
       </c>
-      <c r="H47">
+      <c r="H47" s="0" t="n">
         <v>340</v>
       </c>
     </row>
-    <row r="48" spans="1:8">
-      <c r="A48" s="5">
+    <row r="48" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A48" s="1" t="n">
         <v>44982</v>
       </c>
-      <c r="B48">
+      <c r="B48" s="0" t="n">
         <v>160</v>
       </c>
-      <c r="C48">
+      <c r="C48" s="0" t="n">
         <v>240</v>
       </c>
-      <c r="E48">
+      <c r="E48" s="0" t="n">
         <v>245</v>
       </c>
-      <c r="F48">
+      <c r="F48" s="0" t="n">
         <v>315</v>
       </c>
     </row>
-    <row r="49" spans="1:8">
-      <c r="A49" s="5">
+    <row r="49" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A49" s="1" t="n">
         <v>44982</v>
       </c>
-      <c r="B49">
+      <c r="B49" s="0" t="n">
         <v>265</v>
       </c>
-      <c r="C49">
+      <c r="C49" s="0" t="n">
         <v>180</v>
       </c>
-      <c r="E49">
+      <c r="E49" s="0" t="n">
         <v>60</v>
       </c>
-      <c r="F49">
+      <c r="F49" s="0" t="n">
         <v>175</v>
       </c>
     </row>
-    <row r="50" spans="1:8">
-      <c r="A50" s="5">
+    <row r="50" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A50" s="1" t="n">
         <v>44982</v>
       </c>
-      <c r="B50">
+      <c r="B50" s="0" t="n">
         <v>290</v>
       </c>
-      <c r="C50">
+      <c r="C50" s="0" t="n">
         <v>385</v>
       </c>
-      <c r="E50">
+      <c r="E50" s="0" t="n">
         <v>145</v>
       </c>
-      <c r="F50">
+      <c r="F50" s="0" t="n">
         <v>365</v>
       </c>
     </row>
-    <row r="51" spans="1:8">
-      <c r="A51" s="5">
+    <row r="51" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A51" s="1" t="n">
         <v>44989</v>
       </c>
-      <c r="C51">
+      <c r="C51" s="0" t="n">
         <v>220</v>
       </c>
-      <c r="E51">
+      <c r="E51" s="0" t="n">
         <v>160</v>
       </c>
-      <c r="F51">
+      <c r="F51" s="0" t="n">
         <v>140</v>
       </c>
     </row>
-    <row r="52" spans="1:8">
-      <c r="A52" s="5">
+    <row r="52" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A52" s="1" t="n">
         <v>44989</v>
       </c>
-      <c r="C52">
+      <c r="C52" s="0" t="n">
         <v>260</v>
       </c>
-      <c r="E52">
+      <c r="E52" s="0" t="n">
         <v>45</v>
       </c>
-      <c r="F52">
+      <c r="F52" s="0" t="n">
         <v>495</v>
       </c>
     </row>
-    <row r="53" spans="1:8">
-      <c r="A53" s="5">
+    <row r="53" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A53" s="1" t="n">
         <v>44989</v>
       </c>
-      <c r="C53">
+      <c r="C53" s="0" t="n">
         <v>280</v>
       </c>
-      <c r="E53">
+      <c r="E53" s="0" t="n">
         <v>160</v>
       </c>
-      <c r="F53">
+      <c r="F53" s="0" t="n">
         <v>80</v>
       </c>
     </row>
-    <row r="54" spans="1:8">
-      <c r="A54" s="5">
+    <row r="54" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A54" s="1" t="n">
         <v>44996</v>
       </c>
-      <c r="B54">
+      <c r="B54" s="0" t="n">
         <v>370</v>
       </c>
-      <c r="C54">
+      <c r="C54" s="0" t="n">
         <v>355</v>
       </c>
-      <c r="D54">
+      <c r="D54" s="0" t="n">
         <v>290</v>
       </c>
-      <c r="E54">
+      <c r="E54" s="0" t="n">
         <v>210</v>
       </c>
-      <c r="F54">
+      <c r="F54" s="0" t="n">
         <v>325</v>
       </c>
-      <c r="G54">
+      <c r="G54" s="0" t="n">
         <v>390</v>
       </c>
-      <c r="H54">
+      <c r="H54" s="0" t="n">
         <v>340</v>
       </c>
     </row>
-    <row r="55" spans="1:8">
-      <c r="A55" s="5">
+    <row r="55" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A55" s="1" t="n">
         <v>44996</v>
       </c>
-      <c r="B55">
+      <c r="B55" s="0" t="n">
         <v>285</v>
       </c>
-      <c r="C55">
+      <c r="C55" s="0" t="n">
         <v>445</v>
       </c>
-      <c r="D55">
+      <c r="D55" s="0" t="n">
         <v>355</v>
       </c>
-      <c r="E55">
+      <c r="E55" s="0" t="n">
         <v>325</v>
       </c>
-      <c r="F55">
+      <c r="F55" s="0" t="n">
         <v>465</v>
       </c>
-      <c r="G55">
+      <c r="G55" s="0" t="n">
         <v>420</v>
       </c>
-      <c r="H55">
+      <c r="H55" s="0" t="n">
         <v>490</v>
       </c>
     </row>
-    <row r="56" spans="1:8">
-      <c r="A56" s="5">
+    <row r="56" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A56" s="1" t="n">
         <v>44998</v>
       </c>
-      <c r="B56">
+      <c r="B56" s="0" t="n">
         <v>420</v>
       </c>
-      <c r="C56">
+      <c r="C56" s="0" t="n">
         <v>335</v>
       </c>
-      <c r="D56">
+      <c r="D56" s="0" t="n">
         <v>510</v>
       </c>
-      <c r="E56">
+      <c r="E56" s="0" t="n">
         <v>120</v>
       </c>
-      <c r="F56">
+      <c r="F56" s="0" t="n">
         <v>480</v>
       </c>
-      <c r="G56">
+      <c r="G56" s="0" t="n">
         <v>470</v>
       </c>
-      <c r="H56">
+      <c r="H56" s="0" t="n">
         <v>595</v>
       </c>
     </row>
-    <row r="57" spans="1:8">
-      <c r="A57" s="5">
+    <row r="57" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A57" s="1" t="n">
         <v>44999</v>
       </c>
-      <c r="B57">
+      <c r="B57" s="0" t="n">
         <v>270</v>
       </c>
-      <c r="C57">
+      <c r="C57" s="0" t="n">
         <v>445</v>
       </c>
-      <c r="D57">
+      <c r="D57" s="0" t="n">
         <v>425</v>
       </c>
-      <c r="E57">
+      <c r="E57" s="0" t="n">
         <v>365</v>
       </c>
-      <c r="F57">
+      <c r="F57" s="0" t="n">
         <v>210</v>
       </c>
-      <c r="H57">
+      <c r="H57" s="0" t="n">
         <v>250</v>
       </c>
     </row>
-    <row r="58" spans="1:8">
-      <c r="A58" s="5">
+    <row r="58" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A58" s="1" t="n">
         <v>45010</v>
       </c>
-      <c r="B58">
+      <c r="B58" s="0" t="n">
         <v>410</v>
       </c>
-      <c r="C58">
+      <c r="C58" s="0" t="n">
         <v>125</v>
       </c>
-      <c r="E58">
+      <c r="E58" s="0" t="n">
         <v>345</v>
       </c>
-      <c r="F58">
+      <c r="F58" s="0" t="n">
         <v>40</v>
       </c>
     </row>
-    <row r="59" spans="1:8">
-      <c r="A59" s="5">
+    <row r="59" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A59" s="1" t="n">
         <v>45017</v>
       </c>
-      <c r="B59">
+      <c r="B59" s="0" t="n">
         <v>230</v>
       </c>
-      <c r="C59">
+      <c r="C59" s="0" t="n">
         <v>210</v>
       </c>
-      <c r="E59">
+      <c r="E59" s="0" t="n">
         <v>410</v>
       </c>
-      <c r="F59">
+      <c r="F59" s="0" t="n">
         <v>160</v>
       </c>
     </row>
-    <row r="60" spans="1:8">
-      <c r="A60" s="5">
+    <row r="60" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A60" s="1" t="n">
         <v>45017</v>
       </c>
-      <c r="B60">
+      <c r="B60" s="0" t="n">
         <v>210</v>
       </c>
-      <c r="C60">
+      <c r="C60" s="0" t="n">
         <v>150</v>
       </c>
-      <c r="E60">
+      <c r="E60" s="0" t="n">
         <v>430</v>
       </c>
-      <c r="F60">
+      <c r="F60" s="0" t="n">
         <v>160</v>
       </c>
     </row>
-    <row r="61" spans="1:8">
-      <c r="A61" s="5">
+    <row r="61" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A61" s="1" t="n">
         <v>45038</v>
       </c>
-      <c r="E61">
+      <c r="E61" s="0" t="n">
         <v>185</v>
       </c>
-      <c r="F61">
+      <c r="F61" s="0" t="n">
         <v>300</v>
       </c>
-      <c r="G61">
+      <c r="G61" s="0" t="n">
         <v>305</v>
       </c>
-      <c r="H61">
+      <c r="H61" s="0" t="n">
         <v>135</v>
       </c>
     </row>
-    <row r="62" spans="1:8">
-      <c r="A62" s="5">
+    <row r="62" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A62" s="1" t="n">
         <v>45045</v>
       </c>
-      <c r="B62">
+      <c r="B62" s="0" t="n">
         <v>390</v>
       </c>
-      <c r="C62">
+      <c r="C62" s="0" t="n">
         <v>200</v>
       </c>
-      <c r="E62">
+      <c r="E62" s="0" t="n">
         <v>225</v>
       </c>
-      <c r="F62">
+      <c r="F62" s="0" t="n">
         <v>150</v>
       </c>
-      <c r="G62">
+      <c r="G62" s="0" t="n">
         <v>155</v>
       </c>
-      <c r="H62">
+      <c r="H62" s="0" t="n">
         <v>515</v>
       </c>
     </row>
-    <row r="63" spans="1:8">
-      <c r="A63" s="5">
+    <row r="63" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A63" s="1" t="n">
         <v>45052</v>
       </c>
-      <c r="C63">
+      <c r="C63" s="0" t="n">
         <v>355</v>
       </c>
-      <c r="E63">
+      <c r="E63" s="0" t="n">
         <v>170</v>
       </c>
-      <c r="F63">
+      <c r="F63" s="0" t="n">
         <v>360</v>
       </c>
-      <c r="G63">
+      <c r="G63" s="0" t="n">
         <v>215</v>
       </c>
-      <c r="H63">
+      <c r="H63" s="0" t="n">
         <v>185</v>
       </c>
     </row>
-    <row r="64" spans="1:8">
-      <c r="A64" s="5">
+    <row r="64" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A64" s="1" t="n">
         <v>45066</v>
       </c>
-      <c r="B64">
+      <c r="B64" s="0" t="n">
         <v>315</v>
       </c>
-      <c r="C64">
+      <c r="C64" s="0" t="n">
         <v>370</v>
       </c>
-      <c r="D64">
+      <c r="D64" s="0" t="n">
         <v>340</v>
       </c>
-      <c r="E64">
+      <c r="E64" s="0" t="n">
         <v>160</v>
       </c>
-      <c r="F64">
+      <c r="F64" s="0" t="n">
         <v>525</v>
       </c>
-      <c r="G64">
+      <c r="G64" s="0" t="n">
         <v>340</v>
       </c>
-      <c r="H64">
+      <c r="H64" s="0" t="n">
         <v>490</v>
       </c>
     </row>
-    <row r="65" spans="1:8">
-      <c r="A65" s="5">
+    <row r="65" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A65" s="1" t="n">
         <v>45067</v>
       </c>
-      <c r="B65">
+      <c r="B65" s="0" t="n">
         <v>125</v>
       </c>
-      <c r="C65">
+      <c r="C65" s="0" t="n">
         <v>210</v>
       </c>
-      <c r="D65">
+      <c r="D65" s="0" t="n">
         <v>515</v>
       </c>
-      <c r="G65">
+      <c r="G65" s="0" t="n">
         <v>225</v>
       </c>
-      <c r="H65">
+      <c r="H65" s="0" t="n">
         <v>285</v>
       </c>
     </row>
-    <row r="66" spans="1:8">
-      <c r="A66" s="5">
+    <row r="66" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A66" s="1" t="n">
         <v>45068</v>
       </c>
-      <c r="B66">
+      <c r="B66" s="0" t="n">
         <v>300</v>
       </c>
-      <c r="C66">
+      <c r="C66" s="0" t="n">
         <v>425</v>
       </c>
-      <c r="D66">
+      <c r="D66" s="0" t="n">
         <v>280</v>
       </c>
-      <c r="G66">
+      <c r="G66" s="0" t="n">
         <v>300</v>
       </c>
-      <c r="H66">
+      <c r="H66" s="0" t="n">
         <v>485</v>
       </c>
     </row>
-    <row r="67" spans="1:8">
-      <c r="A67" s="5">
+    <row r="67" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A67" s="1" t="n">
         <v>45094</v>
       </c>
-      <c r="C67">
+      <c r="C67" s="0" t="n">
         <v>295</v>
       </c>
-      <c r="D67">
+      <c r="D67" s="0" t="n">
         <v>450</v>
       </c>
-      <c r="E67">
+      <c r="E67" s="0" t="n">
         <v>505</v>
       </c>
-      <c r="F67">
+      <c r="F67" s="0" t="n">
         <v>310</v>
       </c>
-      <c r="G67">
+      <c r="G67" s="0" t="n">
         <v>85</v>
       </c>
-      <c r="H67">
+      <c r="H67" s="0" t="n">
         <v>165</v>
       </c>
     </row>
-    <row r="68" spans="1:8">
-      <c r="A68" s="5">
+    <row r="68" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A68" s="1" t="n">
         <v>45101</v>
       </c>
-      <c r="C68">
+      <c r="C68" s="0" t="n">
         <v>290</v>
       </c>
-      <c r="E68">
+      <c r="E68" s="0" t="n">
         <v>330</v>
       </c>
-      <c r="F68">
+      <c r="F68" s="0" t="n">
         <v>275</v>
       </c>
-      <c r="G68">
+      <c r="G68" s="0" t="n">
         <v>190</v>
       </c>
-      <c r="H68">
+      <c r="H68" s="0" t="n">
         <v>255</v>
       </c>
     </row>
-    <row r="69" spans="1:8">
-      <c r="A69" s="5">
+    <row r="69" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A69" s="1" t="n">
         <v>45101</v>
       </c>
-      <c r="C69">
+      <c r="C69" s="0" t="n">
         <v>245</v>
       </c>
-      <c r="E69">
+      <c r="E69" s="0" t="n">
         <v>275</v>
       </c>
-      <c r="F69">
+      <c r="F69" s="0" t="n">
         <v>545</v>
       </c>
-      <c r="G69">
+      <c r="G69" s="0" t="n">
         <v>350</v>
       </c>
-      <c r="H69">
+      <c r="H69" s="0" t="n">
         <v>130</v>
       </c>
     </row>
-    <row r="70" spans="1:8">
-      <c r="A70" s="5">
+    <row r="70" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A70" s="1" t="n">
         <v>45115</v>
       </c>
-      <c r="E70">
+      <c r="E70" s="0" t="n">
         <v>170</v>
       </c>
-      <c r="F70">
+      <c r="F70" s="0" t="n">
         <v>315</v>
       </c>
-      <c r="G70">
+      <c r="G70" s="0" t="n">
         <v>275</v>
       </c>
-      <c r="H70">
+      <c r="H70" s="0" t="n">
         <v>305</v>
       </c>
     </row>
-    <row r="71" spans="1:8">
-      <c r="A71" s="5">
+    <row r="71" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A71" s="1" t="n">
         <v>45115</v>
       </c>
-      <c r="E71">
+      <c r="E71" s="0" t="n">
         <v>180</v>
       </c>
-      <c r="F71">
+      <c r="F71" s="0" t="n">
         <v>255</v>
       </c>
-      <c r="G71">
+      <c r="G71" s="0" t="n">
         <v>295</v>
       </c>
-      <c r="H71">
+      <c r="H71" s="0" t="n">
         <v>140</v>
       </c>
     </row>
-    <row r="72" spans="1:8">
-      <c r="A72" s="5">
+    <row r="72" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A72" s="1" t="n">
         <v>45122</v>
       </c>
-      <c r="B72">
+      <c r="B72" s="0" t="n">
         <v>380</v>
       </c>
-      <c r="C72">
+      <c r="C72" s="0" t="n">
         <v>300</v>
       </c>
-      <c r="D72">
+      <c r="D72" s="0" t="n">
         <v>245</v>
       </c>
-      <c r="G72">
+      <c r="G72" s="0" t="n">
         <v>255</v>
       </c>
-      <c r="H72">
+      <c r="H72" s="0" t="n">
         <v>300</v>
       </c>
     </row>
-    <row r="73" spans="1:8">
-      <c r="A73" s="5">
+    <row r="73" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A73" s="1" t="n">
         <v>45129</v>
       </c>
-      <c r="C73">
+      <c r="C73" s="0" t="n">
         <v>195</v>
       </c>
-      <c r="D73">
+      <c r="D73" s="0" t="n">
         <v>390</v>
       </c>
-      <c r="E73">
+      <c r="E73" s="0" t="n">
         <v>390</v>
       </c>
-      <c r="F73">
+      <c r="F73" s="0" t="n">
         <v>550</v>
       </c>
-      <c r="G73">
+      <c r="G73" s="0" t="n">
         <v>500</v>
       </c>
-      <c r="H73">
+      <c r="H73" s="0" t="n">
         <v>200</v>
       </c>
     </row>
-    <row r="74" spans="1:8">
-      <c r="A74" s="5">
+    <row r="74" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A74" s="1" t="n">
         <v>45129</v>
       </c>
-      <c r="C74">
+      <c r="C74" s="0" t="n">
         <v>280</v>
       </c>
-      <c r="D74">
+      <c r="D74" s="0" t="n">
         <v>200</v>
       </c>
-      <c r="E74">
+      <c r="E74" s="0" t="n">
         <v>190</v>
       </c>
-      <c r="F74">
+      <c r="F74" s="0" t="n">
         <v>265</v>
       </c>
-      <c r="G74">
+      <c r="G74" s="0" t="n">
         <v>410</v>
       </c>
-      <c r="H74">
+      <c r="H74" s="0" t="n">
         <v>175</v>
       </c>
     </row>
-    <row r="75" spans="1:8">
-      <c r="A75" s="5">
+    <row r="75" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A75" s="1" t="n">
         <v>45136</v>
       </c>
-      <c r="E75">
+      <c r="E75" s="0" t="n">
         <v>110</v>
       </c>
-      <c r="F75">
+      <c r="F75" s="0" t="n">
         <v>340</v>
       </c>
-      <c r="G75">
+      <c r="G75" s="0" t="n">
         <v>215</v>
       </c>
-      <c r="H75">
+      <c r="H75" s="0" t="n">
         <v>270</v>
       </c>
     </row>
-    <row r="76" spans="1:8">
-      <c r="A76" s="5">
+    <row r="76" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A76" s="1" t="n">
         <v>45144</v>
       </c>
-      <c r="D76">
+      <c r="D76" s="0" t="n">
         <v>340</v>
       </c>
-      <c r="E76">
+      <c r="E76" s="0" t="n">
         <v>285</v>
       </c>
-      <c r="F76">
+      <c r="F76" s="0" t="n">
         <v>200</v>
       </c>
-      <c r="G76">
+      <c r="G76" s="0" t="n">
         <v>250</v>
       </c>
-      <c r="H76">
+      <c r="H76" s="0" t="n">
         <v>270</v>
       </c>
     </row>
-    <row r="77" spans="1:8">
-      <c r="A77" s="5">
+    <row r="77" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A77" s="1" t="n">
         <v>45150</v>
       </c>
-      <c r="C77">
+      <c r="C77" s="0" t="n">
         <v>450</v>
       </c>
-      <c r="D77">
+      <c r="D77" s="0" t="n">
         <v>290</v>
       </c>
-      <c r="E77">
+      <c r="E77" s="0" t="n">
         <v>390</v>
       </c>
-      <c r="F77">
+      <c r="F77" s="0" t="n">
         <v>455</v>
       </c>
-      <c r="G77">
+      <c r="G77" s="0" t="n">
         <v>270</v>
       </c>
-      <c r="H77">
+      <c r="H77" s="0" t="n">
         <v>205</v>
       </c>
     </row>
-    <row r="78" spans="1:8">
-      <c r="A78" s="5">
+    <row r="78" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A78" s="1" t="n">
         <v>45151</v>
       </c>
-      <c r="C78">
+      <c r="C78" s="0" t="n">
         <v>420</v>
       </c>
-      <c r="D78">
+      <c r="D78" s="0" t="n">
         <v>395</v>
       </c>
-      <c r="E78">
+      <c r="E78" s="0" t="n">
         <v>300</v>
       </c>
-      <c r="F78">
+      <c r="F78" s="0" t="n">
         <v>215</v>
       </c>
-      <c r="G78">
+      <c r="G78" s="0" t="n">
         <v>400</v>
       </c>
-      <c r="H78">
+      <c r="H78" s="0" t="n">
         <v>355</v>
       </c>
     </row>
-    <row r="79" spans="1:8">
-      <c r="A79" s="5">
+    <row r="79" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A79" s="1" t="n">
         <v>45157</v>
       </c>
-      <c r="B79">
+      <c r="B79" s="0" t="n">
         <v>185</v>
       </c>
-      <c r="E79">
+      <c r="E79" s="0" t="n">
         <v>90</v>
       </c>
-      <c r="F79">
+      <c r="F79" s="0" t="n">
         <v>290</v>
       </c>
-      <c r="G79">
+      <c r="G79" s="0" t="n">
         <v>210</v>
       </c>
-      <c r="H79">
+      <c r="H79" s="0" t="n">
         <v>155</v>
       </c>
     </row>
-    <row r="80" spans="1:8">
-      <c r="A80" s="5">
+    <row r="80" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A80" s="1" t="n">
         <v>45178</v>
       </c>
-      <c r="B80">
+      <c r="B80" s="0" t="n">
         <v>380</v>
       </c>
-      <c r="C80">
+      <c r="C80" s="0" t="n">
         <v>515</v>
       </c>
-      <c r="E80">
+      <c r="E80" s="0" t="n">
         <v>480</v>
       </c>
-      <c r="G80">
+      <c r="G80" s="0" t="n">
         <v>210</v>
       </c>
-      <c r="H80">
+      <c r="H80" s="0" t="n">
         <v>60</v>
       </c>
     </row>
-    <row r="81" spans="1:8">
-      <c r="A81" s="5">
+    <row r="81" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A81" s="1" t="n">
         <v>45179</v>
       </c>
-      <c r="C81">
+      <c r="C81" s="0" t="n">
         <v>260</v>
       </c>
-      <c r="E81">
+      <c r="E81" s="0" t="n">
         <v>310</v>
       </c>
-      <c r="F81">
+      <c r="F81" s="0" t="n">
         <v>80</v>
       </c>
-      <c r="G81">
+      <c r="G81" s="0" t="n">
         <v>355</v>
       </c>
-      <c r="H81">
+      <c r="H81" s="0" t="n">
         <v>215</v>
       </c>
     </row>
-    <row r="82" spans="1:8">
-      <c r="A82" s="5">
+    <row r="82" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A82" s="1" t="n">
         <v>45213</v>
       </c>
-      <c r="B82">
+      <c r="B82" s="0" t="n">
         <v>365</v>
       </c>
-      <c r="C82">
+      <c r="C82" s="0" t="n">
         <v>155</v>
       </c>
-      <c r="E82">
+      <c r="E82" s="0" t="n">
         <v>260</v>
       </c>
-      <c r="F82">
+      <c r="F82" s="0" t="n">
         <v>340</v>
       </c>
-      <c r="G82">
+      <c r="G82" s="0" t="n">
         <v>255</v>
       </c>
-      <c r="H82">
+      <c r="H82" s="0" t="n">
         <v>315</v>
       </c>
     </row>
-    <row r="83" spans="1:8">
-      <c r="A83" s="5">
+    <row r="83" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A83" s="1" t="n">
         <v>45213</v>
       </c>
-      <c r="C83">
+      <c r="C83" s="0" t="n">
         <v>345</v>
       </c>
-      <c r="E83">
+      <c r="E83" s="0" t="n">
         <v>265</v>
       </c>
-      <c r="F83">
+      <c r="F83" s="0" t="n">
         <v>260</v>
       </c>
-      <c r="G83">
+      <c r="G83" s="0" t="n">
         <v>275</v>
       </c>
-      <c r="H83">
+      <c r="H83" s="0" t="n">
         <v>360</v>
       </c>
     </row>
-    <row r="84" spans="1:8">
-      <c r="A84" s="5">
+    <row r="84" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A84" s="1" t="n">
         <v>45227</v>
       </c>
-      <c r="C84">
+      <c r="C84" s="0" t="n">
         <v>285</v>
       </c>
-      <c r="D84">
+      <c r="D84" s="0" t="n">
         <v>350</v>
       </c>
-      <c r="E84">
+      <c r="E84" s="0" t="n">
         <v>70</v>
       </c>
-      <c r="F84">
+      <c r="F84" s="0" t="n">
         <v>220</v>
       </c>
-      <c r="G84">
+      <c r="G84" s="0" t="n">
         <v>305</v>
       </c>
     </row>
-    <row r="85" spans="1:8">
-      <c r="A85" s="5">
+    <row r="85" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A85" s="1" t="n">
         <v>45248</v>
       </c>
-      <c r="B85">
+      <c r="B85" s="0" t="n">
         <v>230</v>
       </c>
-      <c r="C85">
+      <c r="C85" s="0" t="n">
         <v>365</v>
       </c>
-      <c r="E85">
+      <c r="E85" s="0" t="n">
         <v>35</v>
       </c>
-      <c r="F85">
+      <c r="F85" s="0" t="n">
         <v>200</v>
       </c>
     </row>
-    <row r="86" spans="1:8">
-      <c r="A86" s="5">
+    <row r="86" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A86" s="1" t="n">
         <v>45255</v>
       </c>
-      <c r="B86">
+      <c r="B86" s="0" t="n">
         <v>265</v>
       </c>
-      <c r="C86">
+      <c r="C86" s="0" t="n">
         <v>195</v>
       </c>
-      <c r="E86">
+      <c r="E86" s="0" t="n">
         <v>215</v>
       </c>
-      <c r="F86">
+      <c r="F86" s="0" t="n">
         <v>235</v>
       </c>
     </row>
-    <row r="87" spans="1:8">
-      <c r="A87" s="5">
+    <row r="87" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A87" s="1" t="n">
         <v>45255</v>
       </c>
-      <c r="B87">
+      <c r="B87" s="0" t="n">
         <v>315</v>
       </c>
-      <c r="C87">
+      <c r="C87" s="0" t="n">
         <v>210</v>
       </c>
-      <c r="E87">
+      <c r="E87" s="0" t="n">
         <v>50</v>
       </c>
-      <c r="F87">
+      <c r="F87" s="0" t="n">
         <v>300</v>
       </c>
     </row>
-    <row r="88" spans="1:8">
-      <c r="A88" s="5">
+    <row r="88" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A88" s="1" t="n">
         <v>45263</v>
       </c>
-      <c r="B88">
+      <c r="B88" s="0" t="n">
         <v>210</v>
       </c>
-      <c r="C88">
+      <c r="C88" s="0" t="n">
         <v>155</v>
       </c>
-      <c r="E88">
+      <c r="E88" s="0" t="n">
         <v>165</v>
       </c>
-      <c r="F88">
+      <c r="F88" s="0" t="n">
         <v>70</v>
       </c>
     </row>
-    <row r="89" spans="1:8">
-      <c r="A89" s="5">
+    <row r="89" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A89" s="1" t="n">
         <v>45263</v>
       </c>
-      <c r="B89">
+      <c r="B89" s="0" t="n">
         <v>230</v>
       </c>
-      <c r="C89">
+      <c r="C89" s="0" t="n">
         <v>205</v>
       </c>
-      <c r="E89">
+      <c r="E89" s="0" t="n">
         <v>230</v>
       </c>
-      <c r="F89">
+      <c r="F89" s="0" t="n">
         <v>230</v>
       </c>
     </row>
-    <row r="90" spans="1:8">
-      <c r="A90" s="5">
+    <row r="90" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A90" s="1" t="n">
         <v>45269</v>
       </c>
-      <c r="B90">
+      <c r="B90" s="0" t="n">
         <v>475</v>
       </c>
-      <c r="C90">
+      <c r="C90" s="0" t="n">
         <v>115</v>
       </c>
-      <c r="E90">
+      <c r="E90" s="0" t="n">
         <v>105</v>
       </c>
-      <c r="F90">
+      <c r="F90" s="0" t="n">
         <v>310</v>
       </c>
     </row>
-    <row r="91" spans="1:8">
-      <c r="A91" s="5">
+    <row r="91" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A91" s="1" t="n">
         <v>45269</v>
       </c>
-      <c r="B91">
+      <c r="B91" s="0" t="n">
         <v>150</v>
       </c>
-      <c r="C91">
+      <c r="C91" s="0" t="n">
         <v>200</v>
       </c>
-      <c r="E91">
+      <c r="E91" s="0" t="n">
         <v>350</v>
       </c>
-      <c r="F91">
+      <c r="F91" s="0" t="n">
         <v>195</v>
       </c>
     </row>
-    <row r="92" spans="1:8">
-      <c r="A92" s="5">
+    <row r="92" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A92" s="1" t="n">
         <v>45269</v>
       </c>
-      <c r="B92">
+      <c r="B92" s="0" t="n">
         <v>150</v>
       </c>
-      <c r="C92">
+      <c r="C92" s="0" t="n">
         <v>395</v>
       </c>
-      <c r="E92">
+      <c r="E92" s="0" t="n">
         <v>190</v>
       </c>
-      <c r="F92">
+      <c r="F92" s="0" t="n">
         <v>240</v>
       </c>
     </row>
-    <row r="93" spans="1:8">
-      <c r="A93" s="5">
+    <row r="93" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A93" s="1" t="n">
         <v>45283</v>
       </c>
-      <c r="E93">
+      <c r="E93" s="0" t="n">
         <v>300</v>
       </c>
-      <c r="F93">
+      <c r="F93" s="0" t="n">
         <v>425</v>
       </c>
-      <c r="G93">
+      <c r="G93" s="0" t="n">
         <v>430</v>
       </c>
-      <c r="H93">
+      <c r="H93" s="0" t="n">
         <v>245</v>
       </c>
     </row>
-    <row r="94" spans="1:8">
-      <c r="A94" s="5">
+    <row r="94" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A94" s="1" t="n">
         <v>45283</v>
       </c>
-      <c r="E94">
+      <c r="E94" s="0" t="n">
         <v>115</v>
       </c>
-      <c r="F94">
+      <c r="F94" s="0" t="n">
         <v>220</v>
       </c>
-      <c r="G94">
+      <c r="G94" s="0" t="n">
         <v>280</v>
       </c>
-      <c r="H94">
+      <c r="H94" s="0" t="n">
         <v>245</v>
       </c>
     </row>
-    <row r="95" spans="1:8">
-      <c r="A95" s="5">
+    <row r="95" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A95" s="1" t="n">
         <v>45283</v>
       </c>
-      <c r="E95">
+      <c r="E95" s="0" t="n">
         <v>140</v>
       </c>
-      <c r="F95">
+      <c r="F95" s="0" t="n">
         <v>345</v>
       </c>
-      <c r="G95">
+      <c r="G95" s="0" t="n">
         <v>355</v>
       </c>
-      <c r="H95">
+      <c r="H95" s="0" t="n">
         <v>150</v>
       </c>
     </row>
-    <row r="96" spans="1:8">
-      <c r="A96" s="5">
+    <row r="96" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A96" s="1" t="n">
         <v>45284</v>
       </c>
-      <c r="B96">
+      <c r="B96" s="0" t="n">
         <v>245</v>
       </c>
-      <c r="C96">
+      <c r="C96" s="0" t="n">
         <v>475</v>
       </c>
-      <c r="D96">
+      <c r="D96" s="0" t="n">
         <v>280</v>
       </c>
-      <c r="E96">
+      <c r="E96" s="0" t="n">
         <v>185</v>
       </c>
-      <c r="F96">
+      <c r="F96" s="0" t="n">
         <v>425</v>
       </c>
-      <c r="G96">
+      <c r="G96" s="0" t="n">
         <v>330</v>
       </c>
-      <c r="H96">
+      <c r="H96" s="0" t="n">
         <v>505</v>
       </c>
     </row>
-    <row r="97" spans="1:8">
-      <c r="A97" s="5">
+    <row r="97" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A97" s="1" t="n">
         <v>45285</v>
       </c>
-      <c r="B97">
+      <c r="B97" s="0" t="n">
         <v>490</v>
       </c>
-      <c r="C97">
+      <c r="C97" s="0" t="n">
         <v>210</v>
       </c>
-      <c r="D97">
+      <c r="D97" s="0" t="n">
         <v>435</v>
       </c>
-      <c r="E97">
+      <c r="E97" s="0" t="n">
         <v>185</v>
       </c>
-      <c r="F97">
+      <c r="F97" s="0" t="n">
         <v>400</v>
       </c>
-      <c r="G97">
+      <c r="G97" s="0" t="n">
         <v>125</v>
       </c>
-      <c r="H97">
+      <c r="H97" s="0" t="n">
         <v>410</v>
       </c>
     </row>
-    <row r="98" spans="1:8">
-      <c r="A98" s="5">
+    <row r="98" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A98" s="1" t="n">
         <v>45285</v>
       </c>
-      <c r="B98">
+      <c r="B98" s="0" t="n">
         <v>330</v>
       </c>
-      <c r="C98">
+      <c r="C98" s="0" t="n">
         <v>285</v>
       </c>
-      <c r="D98">
+      <c r="D98" s="0" t="n">
         <v>435</v>
       </c>
-      <c r="E98">
+      <c r="E98" s="0" t="n">
         <v>230</v>
       </c>
-      <c r="F98">
+      <c r="F98" s="0" t="n">
         <v>355</v>
       </c>
-      <c r="G98">
+      <c r="G98" s="0" t="n">
         <v>125</v>
       </c>
-      <c r="H98">
+      <c r="H98" s="0" t="n">
         <v>545</v>
       </c>
     </row>
-    <row r="99" spans="1:8">
-      <c r="A99" s="5">
+    <row r="99" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A99" s="1" t="n">
         <v>45286</v>
       </c>
-      <c r="C99">
+      <c r="C99" s="0" t="n">
         <v>285</v>
       </c>
-      <c r="E99">
+      <c r="E99" s="0" t="n">
         <v>180</v>
       </c>
-      <c r="F99">
+      <c r="F99" s="0" t="n">
         <v>365</v>
       </c>
-      <c r="G99">
+      <c r="G99" s="0" t="n">
         <v>440</v>
       </c>
-      <c r="H99">
+      <c r="H99" s="0" t="n">
         <v>75</v>
       </c>
     </row>
-    <row r="100" spans="1:8">
-      <c r="A100" s="5">
+    <row r="100" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A100" s="1" t="n">
         <v>45286</v>
       </c>
-      <c r="B100">
+      <c r="B100" s="0" t="n">
         <v>225</v>
       </c>
-      <c r="C100">
+      <c r="C100" s="0" t="n">
         <v>360</v>
       </c>
-      <c r="D100">
+      <c r="D100" s="0" t="n">
         <v>320</v>
       </c>
-      <c r="E100">
+      <c r="E100" s="0" t="n">
         <v>270</v>
       </c>
-      <c r="F100">
+      <c r="F100" s="0" t="n">
         <v>125</v>
       </c>
-      <c r="G100">
+      <c r="G100" s="0" t="n">
         <v>285</v>
       </c>
-      <c r="H100">
+      <c r="H100" s="0" t="n">
         <v>520</v>
       </c>
     </row>
-    <row r="101" spans="1:8">
-      <c r="A101" s="5">
+    <row r="101" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A101" s="1" t="n">
         <v>45290</v>
       </c>
-      <c r="B101">
+      <c r="B101" s="0" t="n">
         <v>435</v>
       </c>
-      <c r="C101">
+      <c r="C101" s="0" t="n">
         <v>150</v>
       </c>
-      <c r="D101">
+      <c r="D101" s="0" t="n">
         <v>410</v>
       </c>
-      <c r="E101">
+      <c r="E101" s="0" t="n">
         <v>180</v>
       </c>
-      <c r="F101">
+      <c r="F101" s="0" t="n">
         <v>85</v>
       </c>
-      <c r="G101">
+      <c r="G101" s="0" t="n">
         <v>330</v>
       </c>
-      <c r="H101">
+      <c r="H101" s="0" t="n">
         <v>300</v>
       </c>
     </row>
-    <row r="102" spans="1:8">
-      <c r="A102" s="5">
+    <row r="102" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A102" s="1" t="n">
         <v>45291</v>
       </c>
-      <c r="C102">
+      <c r="C102" s="0" t="n">
         <v>485</v>
       </c>
-      <c r="E102">
+      <c r="E102" s="0" t="n">
         <v>240</v>
       </c>
-      <c r="F102">
+      <c r="F102" s="0" t="n">
         <v>110</v>
       </c>
-      <c r="G102">
+      <c r="G102" s="0" t="n">
         <v>450</v>
       </c>
-      <c r="H102">
+      <c r="H102" s="0" t="n">
         <v>220</v>
       </c>
     </row>
-    <row r="103" spans="1:8">
-      <c r="A103" s="5">
+    <row r="103" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A103" s="1" t="n">
         <v>45297</v>
       </c>
-      <c r="B103">
+      <c r="B103" s="0" t="n">
         <v>375</v>
       </c>
-      <c r="C103">
+      <c r="C103" s="0" t="n">
         <v>425</v>
       </c>
-      <c r="E103">
+      <c r="E103" s="0" t="n">
         <v>385</v>
       </c>
-      <c r="F103">
+      <c r="F103" s="0" t="n">
         <v>185</v>
       </c>
-      <c r="G103">
+      <c r="G103" s="0" t="n">
         <v>220</v>
       </c>
-      <c r="H103">
+      <c r="H103" s="0" t="n">
         <v>450</v>
       </c>
     </row>
-    <row r="104" spans="1:8">
-      <c r="A104" s="5">
+    <row r="104" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A104" s="1" t="n">
         <v>45297</v>
       </c>
-      <c r="B104">
+      <c r="B104" s="0" t="n">
         <v>335</v>
       </c>
-      <c r="C104">
+      <c r="C104" s="0" t="n">
         <v>415</v>
       </c>
-      <c r="E104">
+      <c r="E104" s="0" t="n">
         <v>290</v>
       </c>
-      <c r="F104">
+      <c r="F104" s="0" t="n">
         <v>270</v>
       </c>
-      <c r="G104">
+      <c r="G104" s="0" t="n">
         <v>300</v>
       </c>
-      <c r="H104">
+      <c r="H104" s="0" t="n">
         <v>505</v>
       </c>
     </row>
-    <row r="105" spans="1:8">
-      <c r="A105" s="5">
+    <row r="105" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A105" s="1" t="n">
         <v>45304</v>
       </c>
-      <c r="B105">
+      <c r="B105" s="0" t="n">
         <v>65</v>
       </c>
-      <c r="E105">
+      <c r="E105" s="0" t="n">
         <v>395</v>
       </c>
-      <c r="F105">
+      <c r="F105" s="0" t="n">
         <v>260</v>
       </c>
-      <c r="G105">
+      <c r="G105" s="0" t="n">
         <v>415</v>
       </c>
-      <c r="H105">
+      <c r="H105" s="0" t="n">
         <v>225</v>
       </c>
     </row>
-    <row r="106" spans="1:8">
-      <c r="A106" s="5">
+    <row r="106" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A106" s="1" t="n">
         <v>45304</v>
       </c>
-      <c r="B106">
+      <c r="B106" s="0" t="n">
         <v>370</v>
       </c>
-      <c r="C106">
+      <c r="C106" s="0" t="n">
         <v>635</v>
       </c>
-      <c r="E106">
+      <c r="E106" s="0" t="n">
         <v>430</v>
       </c>
-      <c r="F106">
+      <c r="F106" s="0" t="n">
         <v>570</v>
       </c>
-      <c r="G106">
+      <c r="G106" s="0" t="n">
         <v>400</v>
       </c>
-      <c r="H106">
+      <c r="H106" s="0" t="n">
         <v>135</v>
       </c>
     </row>
-    <row r="107" spans="1:8">
-      <c r="A107" s="5">
+    <row r="107" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A107" s="1" t="n">
         <v>45318</v>
       </c>
-      <c r="B107">
+      <c r="B107" s="0" t="n">
         <v>305</v>
       </c>
-      <c r="C107">
+      <c r="C107" s="0" t="n">
         <v>195</v>
       </c>
-      <c r="E107">
+      <c r="E107" s="0" t="n">
         <v>315</v>
       </c>
-      <c r="F107">
+      <c r="F107" s="0" t="n">
         <v>365</v>
       </c>
     </row>
-    <row r="108" spans="1:8">
-      <c r="A108" s="5">
+    <row r="108" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A108" s="1" t="n">
         <v>45318</v>
       </c>
-      <c r="B108">
+      <c r="B108" s="0" t="n">
         <v>145</v>
       </c>
-      <c r="C108">
+      <c r="C108" s="0" t="n">
         <v>280</v>
       </c>
-      <c r="E108">
+      <c r="E108" s="0" t="n">
         <v>220</v>
       </c>
-      <c r="F108">
+      <c r="F108" s="0" t="n">
         <v>320</v>
       </c>
     </row>
-    <row r="109" spans="1:8">
-      <c r="A109" s="5">
+    <row r="109" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A109" s="1" t="n">
         <v>45325</v>
       </c>
-      <c r="B109">
+      <c r="B109" s="0" t="n">
         <v>100</v>
       </c>
-      <c r="C109">
+      <c r="C109" s="0" t="n">
         <v>70</v>
       </c>
-      <c r="E109">
+      <c r="E109" s="0" t="n">
         <v>320</v>
       </c>
-      <c r="F109">
+      <c r="F109" s="0" t="n">
         <v>270</v>
       </c>
     </row>
-    <row r="110" spans="1:8">
-      <c r="A110" s="5">
+    <row r="110" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A110" s="1" t="n">
         <v>45325</v>
       </c>
-      <c r="B110">
+      <c r="B110" s="0" t="n">
         <v>375</v>
       </c>
-      <c r="C110">
+      <c r="C110" s="0" t="n">
         <v>215</v>
       </c>
-      <c r="E110">
+      <c r="E110" s="0" t="n">
         <v>150</v>
       </c>
-      <c r="F110">
+      <c r="F110" s="0" t="n">
         <v>370</v>
       </c>
     </row>
-    <row r="111" spans="1:8">
-      <c r="A111" s="5">
+    <row r="111" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A111" s="1" t="n">
         <v>45346</v>
       </c>
-      <c r="B111">
+      <c r="B111" s="0" t="n">
         <v>335</v>
       </c>
-      <c r="C111">
+      <c r="C111" s="0" t="n">
         <v>155</v>
       </c>
-      <c r="E111">
+      <c r="E111" s="0" t="n">
         <v>240</v>
       </c>
-      <c r="F111">
+      <c r="F111" s="0" t="n">
         <v>305</v>
       </c>
     </row>
-    <row r="112" spans="1:8">
-      <c r="A112" s="5">
+    <row r="112" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A112" s="1" t="n">
         <v>45346</v>
       </c>
-      <c r="B112">
+      <c r="B112" s="0" t="n">
         <v>400</v>
       </c>
-      <c r="C112">
+      <c r="C112" s="0" t="n">
         <v>65</v>
       </c>
-      <c r="E112">
+      <c r="E112" s="0" t="n">
         <v>385</v>
       </c>
-      <c r="F112">
+      <c r="F112" s="0" t="n">
         <v>315</v>
       </c>
     </row>
-    <row r="113" spans="1:8">
-      <c r="A113" s="5">
+    <row r="113" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A113" s="1" t="n">
         <v>45356</v>
       </c>
-      <c r="C113">
+      <c r="C113" s="0" t="n">
         <v>375</v>
       </c>
-      <c r="D113">
+      <c r="D113" s="0" t="n">
         <v>365</v>
       </c>
-      <c r="E113">
+      <c r="E113" s="0" t="n">
         <v>215</v>
       </c>
-      <c r="F113">
+      <c r="F113" s="0" t="n">
         <v>65</v>
       </c>
-      <c r="G113">
+      <c r="G113" s="0" t="n">
         <v>325</v>
       </c>
-      <c r="H113">
+      <c r="H113" s="0" t="n">
         <v>475</v>
       </c>
     </row>
-    <row r="114" spans="1:8">
-      <c r="A114" s="5">
+    <row r="114" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A114" s="1" t="n">
         <v>45357</v>
       </c>
-      <c r="C114">
+      <c r="C114" s="0" t="n">
         <v>490</v>
       </c>
-      <c r="E114">
+      <c r="E114" s="0" t="n">
         <v>315</v>
       </c>
-      <c r="F114">
+      <c r="F114" s="0" t="n">
         <v>285</v>
       </c>
-      <c r="G114">
+      <c r="G114" s="0" t="n">
         <v>350</v>
       </c>
-      <c r="H114">
+      <c r="H114" s="0" t="n">
         <v>230</v>
       </c>
     </row>
-    <row r="115" spans="1:8">
-      <c r="A115" s="5">
+    <row r="115" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A115" s="1" t="n">
         <v>45358</v>
       </c>
-      <c r="C115">
+      <c r="C115" s="0" t="n">
         <v>315</v>
       </c>
-      <c r="E115">
+      <c r="E115" s="0" t="n">
         <v>240</v>
       </c>
-      <c r="F115">
+      <c r="F115" s="0" t="n">
         <v>265</v>
       </c>
-      <c r="G115">
+      <c r="G115" s="0" t="n">
         <v>395</v>
       </c>
-      <c r="H115">
+      <c r="H115" s="0" t="n">
         <v>235</v>
       </c>
     </row>
-    <row r="116" spans="1:8">
-      <c r="A116" s="5">
+    <row r="116" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A116" s="1" t="n">
         <v>45358</v>
       </c>
-      <c r="C116">
+      <c r="C116" s="0" t="n">
         <v>195</v>
       </c>
-      <c r="E116">
+      <c r="E116" s="0" t="n">
         <v>305</v>
       </c>
-      <c r="F116">
+      <c r="F116" s="0" t="n">
         <v>315</v>
       </c>
-      <c r="G116">
+      <c r="G116" s="0" t="n">
         <v>285</v>
       </c>
-      <c r="H116">
+      <c r="H116" s="0" t="n">
         <v>590</v>
       </c>
     </row>
-    <row r="117" spans="1:8">
-      <c r="A117" s="5">
+    <row r="117" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A117" s="1" t="n">
         <v>45374</v>
       </c>
-      <c r="B117">
+      <c r="B117" s="0" t="n">
         <v>200</v>
       </c>
-      <c r="C117">
+      <c r="C117" s="0" t="n">
         <v>515</v>
       </c>
-      <c r="E117">
+      <c r="E117" s="0" t="n">
         <v>380</v>
       </c>
-      <c r="F117">
+      <c r="F117" s="0" t="n">
         <v>135</v>
       </c>
     </row>
-    <row r="118" spans="1:8">
-      <c r="A118" s="5">
+    <row r="118" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A118" s="1" t="n">
         <v>45374</v>
       </c>
-      <c r="B118">
+      <c r="B118" s="0" t="n">
         <v>155</v>
       </c>
-      <c r="C118">
+      <c r="C118" s="0" t="n">
         <v>220</v>
       </c>
-      <c r="E118">
+      <c r="E118" s="0" t="n">
         <v>155</v>
       </c>
-      <c r="F118">
+      <c r="F118" s="0" t="n">
         <v>355</v>
       </c>
     </row>
-    <row r="119" spans="1:8">
-      <c r="A119" s="5">
+    <row r="119" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A119" s="1" t="n">
         <v>45388</v>
       </c>
-      <c r="B119">
+      <c r="B119" s="0" t="n">
         <v>260</v>
       </c>
-      <c r="C119">
+      <c r="C119" s="0" t="n">
         <v>280</v>
       </c>
-      <c r="E119">
+      <c r="E119" s="0" t="n">
         <v>245</v>
       </c>
-      <c r="F119">
+      <c r="F119" s="0" t="n">
         <v>225</v>
       </c>
     </row>
-    <row r="120" spans="1:8">
-      <c r="A120" s="5">
+    <row r="120" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A120" s="1" t="n">
         <v>45402</v>
       </c>
-      <c r="C120">
+      <c r="C120" s="0" t="n">
         <v>365</v>
       </c>
-      <c r="E120">
+      <c r="E120" s="0" t="n">
         <v>415</v>
       </c>
-      <c r="F120">
+      <c r="F120" s="0" t="n">
         <v>390</v>
       </c>
-      <c r="G120">
+      <c r="G120" s="0" t="n">
         <v>355</v>
       </c>
-      <c r="H120">
+      <c r="H120" s="0" t="n">
         <v>185</v>
       </c>
     </row>
-    <row r="121" spans="1:8">
-      <c r="A121" s="5">
+    <row r="121" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A121" s="1" t="n">
         <v>45409</v>
       </c>
-      <c r="B121">
+      <c r="B121" s="0" t="n">
         <v>260</v>
       </c>
-      <c r="C121">
+      <c r="C121" s="0" t="n">
         <v>250</v>
       </c>
-      <c r="G121">
+      <c r="G121" s="0" t="n">
         <v>250</v>
       </c>
-      <c r="H121">
+      <c r="H121" s="0" t="n">
         <v>415</v>
       </c>
     </row>
-    <row r="122" spans="1:8">
-      <c r="A122" s="5">
+    <row r="122" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A122" s="1" t="n">
         <v>45416</v>
       </c>
-      <c r="C122">
+      <c r="C122" s="0" t="n">
         <v>270</v>
       </c>
-      <c r="E122">
+      <c r="E122" s="0" t="n">
         <v>95</v>
       </c>
-      <c r="F122">
+      <c r="F122" s="0" t="n">
         <v>405</v>
       </c>
-      <c r="G122">
+      <c r="G122" s="0" t="n">
         <v>225</v>
       </c>
-      <c r="H122">
+      <c r="H122" s="0" t="n">
         <v>290</v>
       </c>
     </row>
-    <row r="123" spans="1:8">
-      <c r="A123" s="5">
+    <row r="123" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A123" s="1" t="n">
         <v>45416</v>
       </c>
-      <c r="C123">
+      <c r="C123" s="0" t="n">
         <v>265</v>
       </c>
-      <c r="E123">
+      <c r="E123" s="0" t="n">
         <v>470</v>
       </c>
-      <c r="F123">
+      <c r="F123" s="0" t="n">
         <v>330</v>
       </c>
-      <c r="G123">
+      <c r="G123" s="0" t="n">
         <v>125</v>
       </c>
-      <c r="H123">
+      <c r="H123" s="0" t="n">
         <v>280</v>
       </c>
     </row>
-    <row r="124" spans="1:8">
-      <c r="A124" s="5">
+    <row r="124" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A124" s="1" t="n">
         <v>45423</v>
       </c>
-      <c r="E124">
+      <c r="E124" s="0" t="n">
         <v>185</v>
       </c>
-      <c r="F124">
+      <c r="F124" s="0" t="n">
         <v>260</v>
       </c>
-      <c r="G124">
+      <c r="G124" s="0" t="n">
         <v>375</v>
       </c>
-      <c r="H124">
+      <c r="H124" s="0" t="n">
         <v>525</v>
       </c>
     </row>
-    <row r="125" spans="1:8">
-      <c r="A125" s="5">
+    <row r="125" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A125" s="1" t="n">
         <v>45423</v>
       </c>
-      <c r="E125">
+      <c r="E125" s="0" t="n">
         <v>355</v>
       </c>
-      <c r="F125">
+      <c r="F125" s="0" t="n">
         <v>110</v>
       </c>
-      <c r="G125">
+      <c r="G125" s="0" t="n">
         <v>270</v>
       </c>
-      <c r="H125">
+      <c r="H125" s="0" t="n">
         <v>150</v>
       </c>
     </row>
-    <row r="126" spans="1:8">
-      <c r="A126" s="5">
+    <row r="126" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A126" s="1" t="n">
         <v>45437</v>
       </c>
-      <c r="C126">
+      <c r="C126" s="0" t="n">
         <v>385</v>
       </c>
-      <c r="E126">
+      <c r="E126" s="0" t="n">
         <v>190</v>
       </c>
-      <c r="F126">
+      <c r="F126" s="0" t="n">
         <v>365</v>
       </c>
-      <c r="G126">
+      <c r="G126" s="0" t="n">
         <v>360</v>
       </c>
-      <c r="H126">
+      <c r="H126" s="0" t="n">
         <v>240</v>
       </c>
     </row>
-    <row r="127" spans="1:8">
-      <c r="A127" s="5">
+    <row r="127" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A127" s="1" t="n">
         <v>45437</v>
       </c>
-      <c r="C127">
+      <c r="C127" s="0" t="n">
         <v>310</v>
       </c>
-      <c r="E127">
+      <c r="E127" s="0" t="n">
         <v>255</v>
       </c>
-      <c r="F127">
+      <c r="F127" s="0" t="n">
         <v>335</v>
       </c>
-      <c r="G127">
+      <c r="G127" s="0" t="n">
         <v>480</v>
       </c>
-      <c r="H127">
+      <c r="H127" s="0" t="n">
         <v>300</v>
       </c>
     </row>
-    <row r="128" spans="1:8">
-      <c r="A128" s="5">
+    <row r="128" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A128" s="1" t="n">
         <v>45444</v>
       </c>
-      <c r="C128">
+      <c r="C128" s="0" t="n">
         <v>535</v>
       </c>
-      <c r="E128">
+      <c r="E128" s="0" t="n">
         <v>110</v>
       </c>
-      <c r="F128">
+      <c r="F128" s="0" t="n">
         <v>275</v>
       </c>
-      <c r="G128">
+      <c r="G128" s="0" t="n">
         <v>375</v>
       </c>
-      <c r="H128">
+      <c r="H128" s="0" t="n">
         <v>240</v>
       </c>
     </row>
-    <row r="129" spans="1:971">
-      <c r="A129" s="5">
+    <row r="129" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A129" s="1" t="n">
         <v>45451</v>
       </c>
-      <c r="E129">
+      <c r="E129" s="0" t="n">
         <v>295</v>
       </c>
-      <c r="F129">
+      <c r="F129" s="0" t="n">
         <v>285</v>
       </c>
-      <c r="G129">
+      <c r="G129" s="0" t="n">
         <v>210</v>
       </c>
-      <c r="H129">
+      <c r="H129" s="0" t="n">
         <v>305</v>
       </c>
     </row>
-    <row r="130" spans="1:971">
-      <c r="A130" s="5">
+    <row r="130" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A130" s="1" t="n">
         <v>45465</v>
       </c>
-      <c r="E130">
+      <c r="E130" s="0" t="n">
         <v>340</v>
       </c>
-      <c r="F130">
+      <c r="F130" s="0" t="n">
         <v>135</v>
       </c>
-      <c r="G130">
+      <c r="G130" s="0" t="n">
         <v>260</v>
       </c>
-      <c r="H130">
+      <c r="H130" s="0" t="n">
         <v>365</v>
       </c>
     </row>
-    <row r="131" spans="1:971">
-      <c r="A131" s="5">
+    <row r="131" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A131" s="1" t="n">
         <v>45501</v>
       </c>
-      <c r="C131">
+      <c r="C131" s="0" t="n">
         <v>340</v>
       </c>
-      <c r="E131">
+      <c r="E131" s="0" t="n">
         <v>195</v>
       </c>
-      <c r="F131">
+      <c r="F131" s="0" t="n">
         <v>210</v>
       </c>
-      <c r="G131">
+      <c r="G131" s="0" t="n">
         <v>185</v>
       </c>
-      <c r="H131">
+      <c r="H131" s="0" t="n">
         <v>575</v>
       </c>
     </row>
-    <row r="132" spans="1:971">
-      <c r="A132" s="5">
+    <row r="132" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A132" s="1" t="n">
         <v>45507</v>
       </c>
-      <c r="C132">
+      <c r="C132" s="0" t="n">
         <v>160</v>
       </c>
-      <c r="E132">
+      <c r="E132" s="0" t="n">
         <v>190</v>
       </c>
-      <c r="F132">
+      <c r="F132" s="0" t="n">
         <v>370</v>
       </c>
-      <c r="G132">
+      <c r="G132" s="0" t="n">
         <v>300</v>
       </c>
-      <c r="H132">
+      <c r="H132" s="0" t="n">
         <v>135</v>
       </c>
     </row>
-    <row r="133" spans="1:971">
-      <c r="A133" s="5">
+    <row r="133" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A133" s="1" t="n">
         <v>45559</v>
       </c>
-      <c r="C133">
+      <c r="C133" s="0" t="n">
         <v>415</v>
       </c>
-      <c r="E133">
+      <c r="E133" s="0" t="n">
         <v>35</v>
       </c>
-      <c r="F133">
+      <c r="F133" s="0" t="n">
         <v>345</v>
       </c>
-      <c r="G133">
+      <c r="G133" s="0" t="n">
         <v>315</v>
       </c>
-      <c r="H133">
+      <c r="H133" s="0" t="n">
         <v>585</v>
       </c>
-      <c r="I133" s="1"/>
-      <c r="K133" s="1"/>
-      <c r="S133" s="1"/>
-      <c r="AA133" s="1"/>
-      <c r="AI133" s="1"/>
-      <c r="AQ133" s="1"/>
-      <c r="AY133" s="1"/>
-      <c r="BG133" s="1"/>
-      <c r="BO133" s="1"/>
-      <c r="BW133" s="1"/>
-      <c r="CE133" s="1"/>
-      <c r="CM133" s="1"/>
-      <c r="CU133" s="1"/>
-      <c r="DC133" s="1"/>
-      <c r="DK133" s="1"/>
-      <c r="DS133" s="1"/>
-      <c r="EA133" s="1"/>
-      <c r="EI133" s="1"/>
-      <c r="EQ133" s="1"/>
-      <c r="EY133" s="1"/>
-      <c r="FG133" s="1"/>
-      <c r="FO133" s="1"/>
-      <c r="FW133" s="1"/>
-      <c r="GE133" s="1"/>
-      <c r="GM133" s="1"/>
-      <c r="GU133" s="1"/>
-      <c r="HC133" s="1"/>
-      <c r="HK133" s="1"/>
-      <c r="HS133" s="1"/>
-      <c r="IA133" s="1"/>
-      <c r="II133" s="1"/>
-      <c r="IQ133" s="1"/>
-      <c r="IY133" s="1"/>
-      <c r="JG133" s="1"/>
-      <c r="JO133" s="1"/>
-      <c r="JW133" s="1"/>
-      <c r="KE133" s="1"/>
-      <c r="KM133" s="1"/>
-      <c r="KU133" s="1"/>
-      <c r="LC133" s="1"/>
-      <c r="LK133" s="1"/>
-      <c r="LS133" s="1"/>
-      <c r="MA133" s="1"/>
-      <c r="MI133" s="1"/>
-      <c r="MQ133" s="1"/>
-      <c r="MY133" s="1"/>
-      <c r="NG133" s="1"/>
-      <c r="NO133" s="1"/>
-      <c r="NW133" s="1"/>
-      <c r="OE133" s="1"/>
-      <c r="OM133" s="1"/>
-      <c r="OU133" s="1"/>
-      <c r="PC133" s="1"/>
-      <c r="PK133" s="1"/>
-      <c r="PS133" s="1"/>
-      <c r="QA133" s="1"/>
-      <c r="QI133" s="1"/>
-      <c r="QQ133" s="1"/>
-      <c r="QY133" s="1"/>
-      <c r="RG133" s="1"/>
-      <c r="RO133" s="1"/>
-      <c r="RW133" s="1"/>
-      <c r="SE133" s="1"/>
-      <c r="SM133" s="1"/>
-      <c r="SU133" s="1"/>
-      <c r="TC133" s="1"/>
-      <c r="TK133" s="1"/>
-      <c r="TS133" s="1"/>
-      <c r="UA133" s="1"/>
-      <c r="UI133" s="1"/>
-      <c r="UQ133" s="1"/>
-      <c r="UY133" s="1"/>
-      <c r="VG133" s="1"/>
-      <c r="VO133" s="1"/>
-      <c r="VW133" s="1"/>
-      <c r="WE133" s="1"/>
-      <c r="WM133" s="1"/>
-      <c r="WU133" s="1"/>
-      <c r="XC133" s="1"/>
-      <c r="XK133" s="1"/>
-      <c r="XS133" s="1"/>
-      <c r="YA133" s="1"/>
-      <c r="YI133" s="1"/>
-      <c r="YQ133" s="1"/>
-      <c r="YY133" s="1"/>
-      <c r="ZG133" s="1"/>
-      <c r="ZO133" s="1"/>
-      <c r="ZW133" s="1"/>
-      <c r="AAE133" s="1"/>
-      <c r="AAM133" s="1"/>
-      <c r="AAU133" s="1"/>
-      <c r="ABC133" s="1"/>
-      <c r="ABK133" s="1"/>
-      <c r="ABS133" s="1"/>
-      <c r="ACA133" s="1"/>
-      <c r="ACI133" s="1"/>
-      <c r="ACQ133" s="1"/>
-      <c r="ACY133" s="1"/>
-      <c r="ADG133" s="1"/>
-      <c r="ADO133" s="1"/>
-      <c r="ADW133" s="1"/>
-      <c r="AEE133" s="1"/>
-      <c r="AEM133" s="1"/>
-      <c r="AEU133" s="1"/>
-      <c r="AFC133" s="1"/>
-      <c r="AFK133" s="1"/>
-      <c r="AFS133" s="1"/>
-      <c r="AGA133" s="1"/>
-      <c r="AGI133" s="1"/>
-      <c r="AGQ133" s="1"/>
-      <c r="AGY133" s="1"/>
-      <c r="AHG133" s="1"/>
-      <c r="AHO133" s="1"/>
-      <c r="AHW133" s="1"/>
-      <c r="AIE133" s="1"/>
-      <c r="AIM133" s="1"/>
-      <c r="AIU133" s="1"/>
-      <c r="AJC133" s="1"/>
-      <c r="AJK133" s="1"/>
-      <c r="AJS133" s="1"/>
-      <c r="AKA133" s="1"/>
-      <c r="AKI133" s="1"/>
-    </row>
-    <row r="134" spans="1:971">
-      <c r="A134" s="5">
+      <c r="I133" s="7"/>
+      <c r="K133" s="7"/>
+      <c r="S133" s="7"/>
+      <c r="AA133" s="7"/>
+      <c r="AI133" s="7"/>
+      <c r="AQ133" s="7"/>
+      <c r="AY133" s="7"/>
+      <c r="BG133" s="7"/>
+      <c r="BO133" s="7"/>
+      <c r="BW133" s="7"/>
+      <c r="CE133" s="7"/>
+      <c r="CM133" s="7"/>
+      <c r="CU133" s="7"/>
+      <c r="DC133" s="7"/>
+      <c r="DK133" s="7"/>
+      <c r="DS133" s="7"/>
+      <c r="EA133" s="7"/>
+      <c r="EI133" s="7"/>
+      <c r="EQ133" s="7"/>
+      <c r="EY133" s="7"/>
+      <c r="FG133" s="7"/>
+      <c r="FO133" s="7"/>
+      <c r="FW133" s="7"/>
+      <c r="GE133" s="7"/>
+      <c r="GM133" s="7"/>
+      <c r="GU133" s="7"/>
+      <c r="HC133" s="7"/>
+      <c r="HK133" s="7"/>
+      <c r="HS133" s="7"/>
+      <c r="IA133" s="7"/>
+      <c r="II133" s="7"/>
+      <c r="IQ133" s="7"/>
+      <c r="IY133" s="7"/>
+      <c r="JG133" s="7"/>
+      <c r="JO133" s="7"/>
+      <c r="JW133" s="7"/>
+      <c r="KE133" s="7"/>
+      <c r="KM133" s="7"/>
+      <c r="KU133" s="7"/>
+      <c r="LC133" s="7"/>
+      <c r="LK133" s="7"/>
+      <c r="LS133" s="7"/>
+      <c r="MA133" s="7"/>
+      <c r="MI133" s="7"/>
+      <c r="MQ133" s="7"/>
+      <c r="MY133" s="7"/>
+      <c r="NG133" s="7"/>
+      <c r="NO133" s="7"/>
+      <c r="NW133" s="7"/>
+      <c r="OE133" s="7"/>
+      <c r="OM133" s="7"/>
+      <c r="OU133" s="7"/>
+      <c r="PC133" s="7"/>
+      <c r="PK133" s="7"/>
+      <c r="PS133" s="7"/>
+      <c r="QA133" s="7"/>
+      <c r="QI133" s="7"/>
+      <c r="QQ133" s="7"/>
+      <c r="QY133" s="7"/>
+      <c r="RG133" s="7"/>
+      <c r="RO133" s="7"/>
+      <c r="RW133" s="7"/>
+      <c r="SE133" s="7"/>
+      <c r="SM133" s="7"/>
+      <c r="SU133" s="7"/>
+      <c r="TC133" s="7"/>
+      <c r="TK133" s="7"/>
+      <c r="TS133" s="7"/>
+      <c r="UA133" s="7"/>
+      <c r="UI133" s="7"/>
+      <c r="UQ133" s="7"/>
+      <c r="UY133" s="7"/>
+      <c r="VG133" s="7"/>
+      <c r="VO133" s="7"/>
+      <c r="VW133" s="7"/>
+      <c r="WE133" s="7"/>
+      <c r="WM133" s="7"/>
+      <c r="WU133" s="7"/>
+      <c r="XC133" s="7"/>
+      <c r="XK133" s="7"/>
+      <c r="XS133" s="7"/>
+      <c r="YA133" s="7"/>
+      <c r="YI133" s="7"/>
+      <c r="YQ133" s="7"/>
+      <c r="YY133" s="7"/>
+      <c r="ZG133" s="7"/>
+      <c r="ZO133" s="7"/>
+      <c r="ZW133" s="7"/>
+      <c r="AAE133" s="7"/>
+      <c r="AAM133" s="7"/>
+      <c r="AAU133" s="7"/>
+      <c r="ABC133" s="7"/>
+      <c r="ABK133" s="7"/>
+      <c r="ABS133" s="7"/>
+      <c r="ACA133" s="7"/>
+      <c r="ACI133" s="7"/>
+      <c r="ACQ133" s="7"/>
+      <c r="ACY133" s="7"/>
+      <c r="ADG133" s="7"/>
+      <c r="ADO133" s="7"/>
+      <c r="ADW133" s="7"/>
+      <c r="AEE133" s="7"/>
+      <c r="AEM133" s="7"/>
+      <c r="AEU133" s="7"/>
+      <c r="AFC133" s="7"/>
+      <c r="AFK133" s="7"/>
+      <c r="AFS133" s="7"/>
+      <c r="AGA133" s="7"/>
+      <c r="AGI133" s="7"/>
+      <c r="AGQ133" s="7"/>
+      <c r="AGY133" s="7"/>
+      <c r="AHG133" s="7"/>
+      <c r="AHO133" s="7"/>
+      <c r="AHW133" s="7"/>
+      <c r="AIE133" s="7"/>
+      <c r="AIM133" s="7"/>
+      <c r="AIU133" s="7"/>
+      <c r="AJC133" s="7"/>
+      <c r="AJK133" s="7"/>
+      <c r="AJS133" s="7"/>
+      <c r="AKA133" s="7"/>
+      <c r="AKI133" s="7"/>
+    </row>
+    <row r="134" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A134" s="1" t="n">
         <v>45514</v>
       </c>
-      <c r="E134">
+      <c r="E134" s="0" t="n">
         <v>425</v>
       </c>
-      <c r="F134">
+      <c r="F134" s="0" t="n">
         <v>365</v>
       </c>
-      <c r="G134">
+      <c r="G134" s="0" t="n">
         <v>50</v>
       </c>
-      <c r="H134">
+      <c r="H134" s="0" t="n">
         <v>455</v>
       </c>
     </row>
-    <row r="135" spans="1:971">
-      <c r="A135" s="5">
+    <row r="135" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A135" s="1" t="n">
         <v>45521</v>
       </c>
-      <c r="B135">
+      <c r="B135" s="0" t="n">
         <v>275</v>
       </c>
-      <c r="C135">
+      <c r="C135" s="0" t="n">
         <v>345</v>
       </c>
-      <c r="G135">
+      <c r="G135" s="0" t="n">
         <v>190</v>
       </c>
-      <c r="H135">
+      <c r="H135" s="0" t="n">
         <v>240</v>
       </c>
     </row>
-    <row r="136" spans="1:971">
-      <c r="A136" s="5">
+    <row r="136" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A136" s="1" t="n">
         <v>45559</v>
       </c>
-      <c r="C136">
+      <c r="C136" s="0" t="n">
         <v>415</v>
       </c>
-      <c r="E136">
+      <c r="E136" s="0" t="n">
         <v>35</v>
       </c>
-      <c r="F136">
+      <c r="F136" s="0" t="n">
         <v>345</v>
       </c>
-      <c r="G136">
+      <c r="G136" s="0" t="n">
         <v>315</v>
       </c>
-      <c r="H136">
+      <c r="H136" s="0" t="n">
         <v>585</v>
       </c>
     </row>
-    <row r="137" spans="1:971">
-      <c r="A137" s="5">
+    <row r="137" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A137" s="1" t="n">
         <v>45535</v>
       </c>
-      <c r="B137">
+      <c r="B137" s="0" t="n">
         <v>165</v>
       </c>
-      <c r="C137">
+      <c r="C137" s="0" t="n">
         <v>60</v>
       </c>
-      <c r="G137">
+      <c r="G137" s="0" t="n">
         <v>205</v>
       </c>
-      <c r="H137">
+      <c r="H137" s="0" t="n">
         <v>400</v>
       </c>
     </row>
-    <row r="138" spans="1:971">
-      <c r="A138" s="5">
+    <row r="138" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A138" s="1" t="n">
         <v>45542</v>
       </c>
-      <c r="E138">
+      <c r="E138" s="0" t="n">
         <v>155</v>
       </c>
-      <c r="F138">
+      <c r="F138" s="0" t="n">
         <v>370</v>
       </c>
-      <c r="G138">
+      <c r="G138" s="0" t="n">
         <v>345</v>
       </c>
-      <c r="H138">
+      <c r="H138" s="0" t="n">
         <v>160</v>
       </c>
     </row>
-    <row r="139" spans="1:971">
-      <c r="A139" s="5">
+    <row r="139" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A139" s="1" t="n">
         <v>45550</v>
       </c>
-      <c r="E139">
+      <c r="E139" s="0" t="n">
         <v>120</v>
       </c>
-      <c r="F139">
+      <c r="F139" s="0" t="n">
         <v>295</v>
       </c>
-      <c r="G139">
+      <c r="G139" s="0" t="n">
         <v>250</v>
       </c>
-      <c r="H139">
+      <c r="H139" s="0" t="n">
         <v>35</v>
       </c>
     </row>
-    <row r="140" spans="1:971">
-      <c r="A140" s="5">
+    <row r="140" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A140" s="1" t="n">
         <v>45556</v>
       </c>
-      <c r="B140">
+      <c r="B140" s="0" t="n">
         <v>15</v>
       </c>
-      <c r="C140">
+      <c r="C140" s="0" t="n">
         <v>140</v>
       </c>
-      <c r="G140">
+      <c r="G140" s="0" t="n">
         <v>100</v>
       </c>
-      <c r="H140">
+      <c r="H140" s="0" t="n">
         <v>190</v>
       </c>
     </row>
-    <row r="141" spans="1:971">
-      <c r="A141" s="5">
+    <row r="141" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A141" s="1" t="n">
         <v>45563</v>
       </c>
-      <c r="C141">
+      <c r="C141" s="0" t="n">
         <v>255</v>
       </c>
-      <c r="E141">
+      <c r="E141" s="0" t="n">
         <v>240</v>
       </c>
-      <c r="F141">
+      <c r="F141" s="0" t="n">
         <v>265</v>
       </c>
-      <c r="G141">
+      <c r="G141" s="0" t="n">
         <v>250</v>
       </c>
-      <c r="H141">
+      <c r="H141" s="0" t="n">
         <v>365</v>
       </c>
     </row>
-    <row r="142" spans="1:971">
-      <c r="A142" s="5">
+    <row r="142" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A142" s="1" t="n">
         <v>45570</v>
       </c>
-      <c r="E142">
+      <c r="E142" s="0" t="n">
         <v>55</v>
       </c>
-      <c r="F142">
+      <c r="F142" s="0" t="n">
         <v>270</v>
       </c>
-      <c r="G142">
+      <c r="G142" s="0" t="n">
         <v>285</v>
       </c>
-      <c r="H142">
+      <c r="H142" s="0" t="n">
         <v>315</v>
       </c>
     </row>
-    <row r="143" spans="1:971">
-      <c r="A143" s="5">
+    <row r="143" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A143" s="1" t="n">
         <v>45570</v>
       </c>
-      <c r="E143">
+      <c r="E143" s="0" t="n">
         <v>250</v>
       </c>
-      <c r="F143">
+      <c r="F143" s="0" t="n">
         <v>305</v>
       </c>
-      <c r="G143">
+      <c r="G143" s="0" t="n">
         <v>145</v>
       </c>
-      <c r="H143">
+      <c r="H143" s="0" t="n">
         <v>310</v>
       </c>
     </row>
-    <row r="144" spans="1:971">
-      <c r="A144" s="5">
+    <row r="144" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A144" s="1" t="n">
         <v>45570</v>
       </c>
-      <c r="E144">
+      <c r="E144" s="0" t="n">
         <v>390</v>
       </c>
-      <c r="F144">
+      <c r="F144" s="0" t="n">
         <v>185</v>
       </c>
-      <c r="G144">
+      <c r="G144" s="0" t="n">
         <v>110</v>
       </c>
-      <c r="H144">
+      <c r="H144" s="0" t="n">
         <v>355</v>
       </c>
     </row>
-    <row r="145" spans="1:8">
-      <c r="A145" s="5">
+    <row r="145" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A145" s="1" t="n">
         <v>45577</v>
       </c>
-      <c r="E145">
+      <c r="E145" s="0" t="n">
         <v>400</v>
       </c>
-      <c r="F145">
+      <c r="F145" s="0" t="n">
         <v>120</v>
       </c>
-      <c r="G145">
+      <c r="G145" s="0" t="n">
         <v>125</v>
       </c>
-      <c r="H145">
+      <c r="H145" s="0" t="n">
         <v>195</v>
       </c>
     </row>
-    <row r="146" spans="1:8">
-      <c r="A146" s="5">
+    <row r="146" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A146" s="1" t="n">
         <v>45591</v>
       </c>
-      <c r="E146">
+      <c r="E146" s="0" t="n">
         <v>165</v>
       </c>
-      <c r="F146">
+      <c r="F146" s="0" t="n">
         <v>345</v>
       </c>
-      <c r="G146">
+      <c r="G146" s="0" t="n">
         <v>235</v>
       </c>
-      <c r="H146">
+      <c r="H146" s="0" t="n">
         <v>340</v>
       </c>
     </row>
-    <row r="147" spans="1:8">
-      <c r="A147" s="5">
+    <row r="147" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A147" s="1" t="n">
         <v>45619</v>
       </c>
-      <c r="B147">
+      <c r="B147" s="0" t="n">
         <v>90</v>
       </c>
-      <c r="C147">
+      <c r="C147" s="0" t="n">
         <v>435</v>
       </c>
-      <c r="E147">
+      <c r="E147" s="0" t="n">
         <v>135</v>
       </c>
-      <c r="F147">
+      <c r="F147" s="0" t="n">
         <v>70</v>
       </c>
     </row>
-    <row r="148" spans="1:8">
-      <c r="A148" s="5">
+    <row r="148" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A148" s="1" t="n">
         <v>45631</v>
       </c>
-      <c r="B148">
+      <c r="B148" s="0" t="n">
         <v>215</v>
       </c>
-      <c r="C148">
+      <c r="C148" s="0" t="n">
         <v>200</v>
       </c>
-      <c r="E148">
+      <c r="E148" s="0" t="n">
         <v>220</v>
       </c>
-      <c r="F148">
+      <c r="F148" s="0" t="n">
         <v>295</v>
       </c>
     </row>
-    <row r="149" spans="1:8">
-      <c r="A149" s="5">
+    <row r="149" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A149" s="1" t="n">
         <v>45647</v>
       </c>
-      <c r="C149">
+      <c r="C149" s="0" t="n">
         <v>375</v>
       </c>
-      <c r="E149">
+      <c r="E149" s="0" t="n">
         <v>115</v>
       </c>
-      <c r="F149">
+      <c r="F149" s="0" t="n">
         <v>350</v>
       </c>
-      <c r="G149">
+      <c r="G149" s="0" t="n">
         <v>430</v>
       </c>
-      <c r="H149">
+      <c r="H149" s="0" t="n">
         <v>110</v>
       </c>
     </row>
-    <row r="150" spans="1:8">
-      <c r="A150" s="5">
+    <row r="150" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A150" s="1" t="n">
         <v>45647</v>
       </c>
-      <c r="E150">
+      <c r="E150" s="0" t="n">
         <v>210</v>
       </c>
-      <c r="F150">
+      <c r="F150" s="0" t="n">
         <v>430</v>
       </c>
-      <c r="G150">
+      <c r="G150" s="0" t="n">
         <v>390</v>
       </c>
-      <c r="H150">
+      <c r="H150" s="0" t="n">
         <v>300</v>
       </c>
     </row>
-    <row r="151" spans="1:8">
-      <c r="A151" s="5">
+    <row r="151" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A151" s="1" t="n">
         <v>45650</v>
       </c>
-      <c r="B151">
+      <c r="B151" s="0" t="n">
         <v>160</v>
       </c>
-      <c r="C151">
+      <c r="C151" s="0" t="n">
         <v>465</v>
       </c>
-      <c r="E151">
+      <c r="E151" s="0" t="n">
         <v>220</v>
       </c>
-      <c r="F151">
+      <c r="F151" s="0" t="n">
         <v>330</v>
       </c>
-      <c r="G151">
+      <c r="G151" s="0" t="n">
         <v>345</v>
       </c>
-      <c r="H151">
+      <c r="H151" s="0" t="n">
         <v>395</v>
       </c>
     </row>
-    <row r="152" spans="1:8">
-      <c r="A152" s="5">
+    <row r="152" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A152" s="1" t="n">
         <v>45650</v>
       </c>
-      <c r="C152">
+      <c r="C152" s="0" t="n">
         <v>250</v>
       </c>
-      <c r="E152">
+      <c r="E152" s="0" t="n">
         <v>315</v>
       </c>
-      <c r="F152">
+      <c r="F152" s="0" t="n">
         <v>310</v>
       </c>
-      <c r="G152">
+      <c r="G152" s="0" t="n">
         <v>290</v>
       </c>
-      <c r="H152">
+      <c r="H152" s="0" t="n">
         <v>415</v>
       </c>
     </row>
-    <row r="153" spans="1:8">
-      <c r="A153" s="5">
+    <row r="153" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A153" s="1" t="n">
         <v>45651</v>
       </c>
-      <c r="B153">
+      <c r="B153" s="0" t="n">
         <v>410</v>
       </c>
-      <c r="C153">
+      <c r="C153" s="0" t="n">
         <v>170</v>
       </c>
-      <c r="E153">
+      <c r="E153" s="0" t="n">
         <v>190</v>
       </c>
-      <c r="F153">
+      <c r="F153" s="0" t="n">
         <v>455</v>
       </c>
-      <c r="G153">
+      <c r="G153" s="0" t="n">
         <v>465</v>
       </c>
-      <c r="H153">
+      <c r="H153" s="0" t="n">
         <v>250</v>
       </c>
     </row>
-    <row r="154" spans="1:8">
-      <c r="A154" s="5">
+    <row r="154" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A154" s="1" t="n">
         <v>45651</v>
       </c>
-      <c r="C154">
+      <c r="C154" s="0" t="n">
         <v>145</v>
       </c>
-      <c r="E154">
+      <c r="E154" s="0" t="n">
         <v>325</v>
       </c>
-      <c r="F154">
+      <c r="F154" s="0" t="n">
         <v>255</v>
       </c>
-      <c r="G154">
+      <c r="G154" s="0" t="n">
         <v>345</v>
       </c>
-      <c r="H154">
+      <c r="H154" s="0" t="n">
         <v>320</v>
       </c>
     </row>
-    <row r="155" spans="1:8">
-      <c r="A155" s="5">
+    <row r="155" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A155" s="1" t="n">
         <v>45652</v>
       </c>
-      <c r="B155">
+      <c r="B155" s="0" t="n">
         <v>285</v>
       </c>
-      <c r="C155">
+      <c r="C155" s="0" t="n">
         <v>180</v>
       </c>
-      <c r="E155">
+      <c r="E155" s="0" t="n">
         <v>360</v>
       </c>
-      <c r="F155">
+      <c r="F155" s="0" t="n">
         <v>375</v>
       </c>
-      <c r="G155">
+      <c r="G155" s="0" t="n">
         <v>280</v>
       </c>
-      <c r="H155">
+      <c r="H155" s="0" t="n">
         <v>545</v>
       </c>
     </row>
-    <row r="156" spans="1:8">
-      <c r="A156" s="5">
+    <row r="156" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A156" s="1" t="n">
         <v>45652</v>
       </c>
-      <c r="C156">
+      <c r="C156" s="0" t="n">
         <v>35</v>
       </c>
-      <c r="E156">
+      <c r="E156" s="0" t="n">
         <v>345</v>
       </c>
-      <c r="F156">
+      <c r="F156" s="0" t="n">
         <v>325</v>
       </c>
-      <c r="G156">
+      <c r="G156" s="0" t="n">
         <v>240</v>
       </c>
-      <c r="H156">
+      <c r="H156" s="0" t="n">
         <v>460</v>
       </c>
     </row>
-    <row r="157" spans="1:8">
-      <c r="A157" s="5">
+    <row r="157" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A157" s="1" t="n">
         <v>45654</v>
       </c>
-      <c r="B157">
+      <c r="B157" s="0" t="n">
         <v>395</v>
       </c>
-      <c r="C157">
+      <c r="C157" s="0" t="n">
         <v>360</v>
       </c>
-      <c r="D157">
+      <c r="D157" s="0" t="n">
         <v>415</v>
       </c>
-      <c r="E157">
+      <c r="E157" s="0" t="n">
         <v>165</v>
       </c>
-      <c r="F157">
+      <c r="F157" s="0" t="n">
         <v>395</v>
       </c>
-      <c r="G157">
+      <c r="G157" s="0" t="n">
         <v>245</v>
       </c>
-      <c r="H157">
+      <c r="H157" s="0" t="n">
         <v>230</v>
       </c>
     </row>
-    <row r="158" spans="1:8">
-      <c r="A158" s="5">
+    <row r="158" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A158" s="1" t="n">
         <v>45654</v>
       </c>
-      <c r="C158">
+      <c r="C158" s="0" t="n">
         <v>165</v>
       </c>
-      <c r="D158">
+      <c r="D158" s="0" t="n">
         <v>380</v>
       </c>
-      <c r="E158">
+      <c r="E158" s="0" t="n">
         <v>345</v>
       </c>
-      <c r="F158">
+      <c r="F158" s="0" t="n">
         <v>290</v>
       </c>
-      <c r="G158">
+      <c r="G158" s="0" t="n">
         <v>150</v>
       </c>
-      <c r="H158">
+      <c r="H158" s="0" t="n">
         <v>260</v>
       </c>
     </row>
-    <row r="159" spans="1:8">
-      <c r="A159" s="5">
+    <row r="159" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A159" s="1" t="n">
         <v>45655</v>
       </c>
-      <c r="B159">
+      <c r="B159" s="0" t="n">
         <v>175</v>
       </c>
-      <c r="C159">
+      <c r="C159" s="0" t="n">
         <v>330</v>
       </c>
-      <c r="D159">
+      <c r="D159" s="0" t="n">
         <v>255</v>
       </c>
-      <c r="G159">
+      <c r="G159" s="0" t="n">
         <v>295</v>
       </c>
-      <c r="H159">
+      <c r="H159" s="0" t="n">
         <v>265</v>
       </c>
     </row>
-    <row r="160" spans="1:8">
-      <c r="A160" s="5">
+    <row r="160" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A160" s="1" t="n">
         <v>45657</v>
       </c>
-      <c r="C160">
+      <c r="C160" s="0" t="n">
         <v>185</v>
       </c>
-      <c r="D160">
+      <c r="D160" s="0" t="n">
         <v>235</v>
       </c>
-      <c r="E160">
+      <c r="E160" s="0" t="n">
         <v>325</v>
       </c>
-      <c r="F160">
+      <c r="F160" s="0" t="n">
         <v>258</v>
       </c>
-      <c r="G160">
+      <c r="G160" s="0" t="n">
         <v>325</v>
       </c>
-      <c r="H160">
+      <c r="H160" s="0" t="n">
         <v>465</v>
       </c>
     </row>
-    <row r="161" spans="1:8">
-      <c r="A161" s="5">
+    <row r="161" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A161" s="1" t="n">
         <v>45657</v>
       </c>
-      <c r="C161">
+      <c r="C161" s="0" t="n">
         <v>55</v>
       </c>
-      <c r="D161">
+      <c r="D161" s="0" t="n">
         <v>275</v>
       </c>
-      <c r="E161">
+      <c r="E161" s="0" t="n">
         <v>405</v>
       </c>
-      <c r="F161">
+      <c r="F161" s="0" t="n">
         <v>215</v>
       </c>
-      <c r="G161">
+      <c r="G161" s="0" t="n">
         <v>455</v>
       </c>
-      <c r="H161">
+      <c r="H161" s="0" t="n">
         <v>190</v>
       </c>
     </row>
-    <row r="162" spans="1:8">
-      <c r="A162" s="5">
+    <row r="162" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A162" s="1" t="n">
         <v>45658</v>
       </c>
-      <c r="B162">
+      <c r="B162" s="0" t="n">
         <v>140</v>
       </c>
-      <c r="C162">
+      <c r="C162" s="0" t="n">
         <v>240</v>
       </c>
-      <c r="D162">
+      <c r="D162" s="0" t="n">
         <v>285</v>
       </c>
-      <c r="E162">
+      <c r="E162" s="0" t="n">
         <v>285</v>
       </c>
-      <c r="F162">
+      <c r="F162" s="0" t="n">
         <v>260</v>
       </c>
-      <c r="G162">
+      <c r="G162" s="0" t="n">
         <v>545</v>
       </c>
-      <c r="H162">
+      <c r="H162" s="0" t="n">
         <v>570</v>
       </c>
     </row>
-    <row r="163" spans="1:8">
-      <c r="A163" s="5">
+    <row r="163" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A163" s="1" t="n">
         <v>45661</v>
       </c>
-      <c r="B163">
+      <c r="B163" s="0" t="n">
         <v>325</v>
       </c>
-      <c r="C163">
+      <c r="C163" s="0" t="n">
         <v>260</v>
       </c>
-      <c r="D163">
+      <c r="D163" s="0" t="n">
         <v>290</v>
       </c>
-      <c r="E163">
+      <c r="E163" s="0" t="n">
         <v>510</v>
       </c>
-      <c r="F163">
+      <c r="F163" s="0" t="n">
         <v>475</v>
       </c>
-      <c r="G163">
+      <c r="G163" s="0" t="n">
         <v>435</v>
       </c>
-      <c r="H163">
+      <c r="H163" s="0" t="n">
         <v>645</v>
       </c>
     </row>
-    <row r="164" spans="1:8">
-      <c r="A164" s="5">
+    <row r="164" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A164" s="1" t="n">
         <v>45668</v>
       </c>
-      <c r="B164">
+      <c r="B164" s="0" t="n">
         <v>115</v>
       </c>
-      <c r="E164">
+      <c r="E164" s="0" t="n">
         <v>170</v>
       </c>
-      <c r="F164">
+      <c r="F164" s="0" t="n">
         <v>545</v>
       </c>
     </row>
-    <row r="165" spans="1:8">
-      <c r="A165" s="5">
+    <row r="165" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A165" s="1" t="n">
         <v>45675</v>
       </c>
-      <c r="B165">
+      <c r="B165" s="0" t="n">
         <v>280</v>
       </c>
-      <c r="C165">
+      <c r="C165" s="0" t="n">
         <v>365</v>
       </c>
-      <c r="E165">
+      <c r="E165" s="0" t="n">
         <v>325</v>
       </c>
-      <c r="F165">
+      <c r="F165" s="0" t="n">
         <v>45</v>
       </c>
     </row>
-    <row r="166" spans="1:8">
-      <c r="A166" s="5">
+    <row r="166" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A166" s="1" t="n">
         <v>45675</v>
       </c>
-      <c r="C166">
+      <c r="C166" s="0" t="n">
         <v>235</v>
       </c>
-      <c r="E166">
+      <c r="E166" s="0" t="n">
         <v>140</v>
       </c>
-      <c r="F166">
+      <c r="F166" s="0" t="n">
         <v>150</v>
       </c>
     </row>
-    <row r="167" spans="1:8">
-      <c r="A167" s="5">
+    <row r="167" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A167" s="1" t="n">
         <v>45682</v>
       </c>
-      <c r="B167">
+      <c r="B167" s="0" t="n">
         <v>165</v>
       </c>
-      <c r="C167">
+      <c r="C167" s="0" t="n">
         <v>265</v>
       </c>
-      <c r="E167">
+      <c r="E167" s="0" t="n">
         <v>220</v>
       </c>
-      <c r="F167">
+      <c r="F167" s="0" t="n">
         <v>265</v>
       </c>
     </row>
-    <row r="168" spans="1:8">
-      <c r="A168" s="5">
+    <row r="168" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A168" s="1" t="n">
         <v>45682</v>
       </c>
-      <c r="C168">
+      <c r="C168" s="0" t="n">
         <v>445</v>
       </c>
-      <c r="E168">
+      <c r="E168" s="0" t="n">
         <v>240</v>
       </c>
-      <c r="F168">
+      <c r="F168" s="0" t="n">
         <v>300</v>
       </c>
     </row>
-    <row r="169" spans="1:8">
-      <c r="A169" s="5">
+    <row r="169" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A169" s="1" t="n">
         <v>45689</v>
       </c>
-      <c r="B169">
+      <c r="B169" s="0" t="n">
         <v>145</v>
       </c>
-      <c r="C169">
+      <c r="C169" s="0" t="n">
         <v>285</v>
       </c>
-      <c r="D169">
+      <c r="D169" s="0" t="n">
         <v>150</v>
       </c>
-      <c r="E169">
+      <c r="E169" s="0" t="n">
         <v>300</v>
       </c>
-      <c r="F169">
+      <c r="F169" s="0" t="n">
         <v>305</v>
       </c>
     </row>
-    <row r="170" spans="1:8">
-      <c r="A170" s="5">
+    <row r="170" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A170" s="1" t="n">
         <v>45696</v>
       </c>
-      <c r="C170">
+      <c r="C170" s="0" t="n">
         <v>135</v>
       </c>
-      <c r="E170">
+      <c r="E170" s="0" t="n">
         <v>110</v>
       </c>
-      <c r="F170">
+      <c r="F170" s="0" t="n">
         <v>175</v>
       </c>
     </row>
-    <row r="171" spans="1:8">
-      <c r="A171" s="5">
+    <row r="171" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A171" s="1" t="n">
         <v>45696</v>
       </c>
-      <c r="C171">
+      <c r="C171" s="0" t="n">
         <v>65</v>
       </c>
-      <c r="E171">
+      <c r="E171" s="0" t="n">
         <v>205</v>
       </c>
-      <c r="F171">
+      <c r="F171" s="0" t="n">
         <v>205</v>
       </c>
     </row>
-    <row r="172" spans="1:8">
-      <c r="A172" s="5">
+    <row r="172" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A172" s="1" t="n">
         <v>45696</v>
       </c>
-      <c r="C172">
+      <c r="C172" s="0" t="n">
         <v>190</v>
       </c>
-      <c r="E172">
+      <c r="E172" s="0" t="n">
         <v>305</v>
       </c>
-      <c r="F172">
+      <c r="F172" s="0" t="n">
         <v>115</v>
       </c>
     </row>
-    <row r="173" spans="1:8">
-      <c r="A173" s="5">
+    <row r="173" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A173" s="1" t="n">
         <v>45705</v>
       </c>
-      <c r="C173">
+      <c r="C173" s="0" t="n">
         <v>220</v>
       </c>
-      <c r="E173">
+      <c r="E173" s="0" t="n">
         <v>125</v>
       </c>
-      <c r="F173">
+      <c r="F173" s="0" t="n">
         <v>105</v>
       </c>
     </row>
-    <row r="174" spans="1:8">
-      <c r="A174" s="5">
+    <row r="174" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A174" s="1" t="n">
         <v>45737</v>
       </c>
-      <c r="E174">
+      <c r="E174" s="0" t="n">
         <v>145</v>
       </c>
-      <c r="F174">
+      <c r="F174" s="0" t="n">
         <v>245</v>
       </c>
-      <c r="G174">
+      <c r="G174" s="0" t="n">
         <v>385</v>
       </c>
-      <c r="H174">
+      <c r="H174" s="0" t="n">
         <v>65</v>
       </c>
     </row>
-    <row r="175" spans="1:8">
-      <c r="A175" s="5">
+    <row r="175" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A175" s="1" t="n">
         <v>45740</v>
       </c>
-      <c r="E175">
+      <c r="E175" s="0" t="n">
         <v>135</v>
       </c>
-      <c r="F175">
+      <c r="F175" s="0" t="n">
         <v>280</v>
       </c>
-      <c r="G175">
+      <c r="G175" s="0" t="n">
         <v>110</v>
       </c>
-      <c r="H175">
+      <c r="H175" s="0" t="n">
         <v>220</v>
       </c>
     </row>
-    <row r="176" spans="1:8">
-      <c r="A176" s="5">
+    <row r="176" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A176" s="1" t="n">
         <v>45746</v>
       </c>
-      <c r="E176">
+      <c r="E176" s="0" t="n">
         <v>300</v>
       </c>
-      <c r="F176">
+      <c r="F176" s="0" t="n">
         <v>260</v>
       </c>
-      <c r="G176">
+      <c r="G176" s="0" t="n">
         <v>195</v>
       </c>
-      <c r="H176">
+      <c r="H176" s="0" t="n">
         <v>260</v>
       </c>
     </row>
-    <row r="177" spans="1:8">
-      <c r="A177" s="5">
+    <row r="177" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A177" s="1" t="n">
         <v>45752</v>
       </c>
-      <c r="B177">
+      <c r="B177" s="0" t="n">
         <v>335</v>
       </c>
-      <c r="E177">
+      <c r="E177" s="0" t="n">
         <v>405</v>
       </c>
-      <c r="F177">
+      <c r="F177" s="0" t="n">
         <v>265</v>
       </c>
-      <c r="G177">
+      <c r="G177" s="0" t="n">
         <v>175</v>
       </c>
-      <c r="H177">
+      <c r="H177" s="0" t="n">
         <v>605</v>
       </c>
     </row>
-    <row r="178" spans="1:8">
-      <c r="A178" s="5">
+    <row r="178" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A178" s="1" t="n">
         <v>45752</v>
       </c>
-      <c r="E178">
+      <c r="E178" s="0" t="n">
         <v>255</v>
       </c>
-      <c r="F178">
+      <c r="F178" s="0" t="n">
         <v>185</v>
       </c>
-      <c r="G178">
+      <c r="G178" s="0" t="n">
         <v>250</v>
       </c>
-      <c r="H178">
+      <c r="H178" s="0" t="n">
         <v>450</v>
       </c>
     </row>
-    <row r="179" spans="1:8">
-      <c r="A179" s="5">
+    <row r="179" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A179" s="1" t="n">
         <v>45759</v>
       </c>
-      <c r="E179">
+      <c r="E179" s="0" t="n">
         <v>135</v>
       </c>
-      <c r="F179">
+      <c r="F179" s="0" t="n">
         <v>315</v>
       </c>
-      <c r="G179">
+      <c r="G179" s="0" t="n">
         <v>170</v>
       </c>
-      <c r="H179">
+      <c r="H179" s="0" t="n">
         <v>285</v>
       </c>
     </row>
-    <row r="180" spans="1:8">
-      <c r="A180" s="5">
+    <row r="180" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A180" s="1" t="n">
         <v>45773</v>
       </c>
-      <c r="C180">
+      <c r="C180" s="0" t="n">
         <v>320</v>
       </c>
-      <c r="E180">
+      <c r="E180" s="0" t="n">
         <v>280</v>
       </c>
-      <c r="F180">
+      <c r="F180" s="0" t="n">
         <v>120</v>
       </c>
-      <c r="G180">
+      <c r="G180" s="0" t="n">
         <v>235</v>
       </c>
-      <c r="H180">
+      <c r="H180" s="0" t="n">
         <v>395</v>
       </c>
     </row>
-    <row r="181" spans="1:8">
-      <c r="A181" s="5">
+    <row r="181" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A181" s="1" t="n">
         <v>45780</v>
       </c>
-      <c r="E181">
+      <c r="E181" s="0" t="n">
         <v>200</v>
       </c>
-      <c r="F181">
+      <c r="F181" s="0" t="n">
         <v>395</v>
       </c>
-      <c r="G181">
+      <c r="G181" s="0" t="n">
         <v>200</v>
       </c>
-      <c r="H181">
+      <c r="H181" s="0" t="n">
         <v>390</v>
       </c>
     </row>
-    <row r="182" spans="1:8">
-      <c r="A182" s="5">
+    <row r="182" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A182" s="1" t="n">
         <v>45780</v>
       </c>
-      <c r="E182">
+      <c r="E182" s="0" t="n">
         <v>220</v>
       </c>
-      <c r="F182">
+      <c r="F182" s="0" t="n">
         <v>115</v>
       </c>
-      <c r="G182">
+      <c r="G182" s="0" t="n">
         <v>435</v>
       </c>
-      <c r="H182">
+      <c r="H182" s="0" t="n">
         <v>280</v>
       </c>
     </row>
-    <row r="183" spans="1:8">
-      <c r="A183" s="5">
+    <row r="183" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A183" s="1" t="n">
         <v>45801</v>
       </c>
-      <c r="E183">
+      <c r="E183" s="0" t="n">
         <v>355</v>
       </c>
-      <c r="F183">
+      <c r="F183" s="0" t="n">
         <v>115</v>
       </c>
-      <c r="G183">
+      <c r="G183" s="0" t="n">
         <v>220</v>
       </c>
-      <c r="H183">
+      <c r="H183" s="0" t="n">
         <v>150</v>
       </c>
     </row>
-    <row r="184" spans="1:8">
-      <c r="A184" s="5">
+    <row r="184" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A184" s="1" t="n">
         <v>45801</v>
       </c>
-      <c r="E184">
+      <c r="E184" s="0" t="n">
         <v>250</v>
       </c>
-      <c r="F184">
+      <c r="F184" s="0" t="n">
         <v>215</v>
       </c>
-      <c r="G184">
+      <c r="G184" s="0" t="n">
         <v>130</v>
       </c>
-      <c r="H184">
+      <c r="H184" s="0" t="n">
         <v>235</v>
       </c>
     </row>
-    <row r="185" spans="1:8">
-      <c r="A185" s="5">
+    <row r="185" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A185" s="1" t="n">
         <v>45801</v>
       </c>
-      <c r="E185">
+      <c r="E185" s="0" t="n">
         <v>95</v>
       </c>
-      <c r="F185">
+      <c r="F185" s="0" t="n">
         <v>200</v>
       </c>
-      <c r="G185">
+      <c r="G185" s="0" t="n">
         <v>150</v>
       </c>
-      <c r="H185">
+      <c r="H185" s="0" t="n">
         <v>140</v>
       </c>
     </row>
-    <row r="186" spans="1:8">
-      <c r="A186" s="5">
+    <row r="186" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A186" s="1" t="n">
         <v>45808</v>
       </c>
-      <c r="C186">
+      <c r="C186" s="0" t="n">
         <v>410</v>
       </c>
-      <c r="D186">
+      <c r="D186" s="0" t="n">
         <v>190</v>
       </c>
-      <c r="E186">
+      <c r="E186" s="0" t="n">
         <v>290</v>
       </c>
-      <c r="F186">
+      <c r="F186" s="0" t="n">
         <v>210</v>
       </c>
-      <c r="G186">
+      <c r="G186" s="0" t="n">
         <v>215</v>
       </c>
-      <c r="H186">
+      <c r="H186" s="0" t="n">
         <v>345</v>
       </c>
     </row>
-    <row r="187" spans="1:8">
-      <c r="A187" s="5">
+    <row r="187" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A187" s="1" t="n">
         <v>45815</v>
       </c>
-      <c r="B187">
+      <c r="B187" s="0" t="n">
         <v>170</v>
       </c>
-      <c r="C187">
+      <c r="C187" s="0" t="n">
         <v>160</v>
       </c>
-      <c r="G187">
+      <c r="G187" s="0" t="n">
         <v>50</v>
       </c>
-      <c r="H187">
+      <c r="H187" s="0" t="n">
         <v>310</v>
       </c>
     </row>
-    <row r="188" spans="1:8">
-      <c r="A188" s="5">
+    <row r="188" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A188" s="1" t="n">
         <v>45836</v>
       </c>
-      <c r="B188">
+      <c r="B188" s="0" t="n">
         <v>210</v>
       </c>
-      <c r="C188">
+      <c r="C188" s="0" t="n">
         <v>145</v>
       </c>
-      <c r="D188">
+      <c r="D188" s="0" t="n">
         <v>320</v>
       </c>
-      <c r="G188">
+      <c r="G188" s="0" t="n">
         <v>340</v>
       </c>
-      <c r="H188">
+      <c r="H188" s="0" t="n">
         <v>290</v>
       </c>
     </row>
-    <row r="189" spans="1:8">
-      <c r="A189" s="5">
+    <row r="189" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A189" s="1" t="n">
         <v>45843</v>
       </c>
-      <c r="E189">
+      <c r="E189" s="0" t="n">
         <v>245</v>
       </c>
-      <c r="F189">
+      <c r="F189" s="0" t="n">
         <v>145</v>
       </c>
-      <c r="G189">
+      <c r="G189" s="0" t="n">
         <v>310</v>
       </c>
-      <c r="H189">
+      <c r="H189" s="0" t="n">
         <v>280</v>
       </c>
     </row>
-    <row r="190" spans="1:8">
-      <c r="A190" s="5">
+    <row r="190" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A190" s="1" t="n">
         <v>45843</v>
       </c>
-      <c r="E190">
+      <c r="E190" s="0" t="n">
         <v>300</v>
       </c>
-      <c r="F190">
+      <c r="F190" s="0" t="n">
         <v>100</v>
       </c>
-      <c r="G190">
+      <c r="G190" s="0" t="n">
         <v>310</v>
       </c>
-      <c r="H190">
+      <c r="H190" s="0" t="n">
         <v>210</v>
       </c>
     </row>
-    <row r="191" spans="1:8">
-      <c r="A191" s="5">
+    <row r="191" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A191" s="1" t="n">
         <v>45850</v>
       </c>
-      <c r="E191">
+      <c r="E191" s="0" t="n">
         <v>365</v>
       </c>
-      <c r="F191">
+      <c r="F191" s="0" t="n">
         <v>125</v>
       </c>
-      <c r="G191">
+      <c r="G191" s="0" t="n">
         <v>245</v>
       </c>
-      <c r="H191">
+      <c r="H191" s="0" t="n">
         <v>80</v>
       </c>
     </row>
-    <row r="192" spans="1:8">
-      <c r="A192" s="5">
+    <row r="192" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A192" s="1" t="n">
         <v>45850</v>
       </c>
-      <c r="E192">
+      <c r="E192" s="0" t="n">
         <v>355</v>
       </c>
-      <c r="F192">
+      <c r="F192" s="0" t="n">
         <v>320</v>
       </c>
-      <c r="G192">
+      <c r="G192" s="0" t="n">
         <v>210</v>
       </c>
-      <c r="H192">
+      <c r="H192" s="0" t="n">
         <v>170</v>
       </c>
     </row>
-    <row r="193" spans="1:8">
-      <c r="A193" s="5">
+    <row r="193" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A193" s="1" t="n">
         <v>45857</v>
       </c>
-      <c r="E193">
+      <c r="E193" s="0" t="n">
         <v>235</v>
       </c>
-      <c r="F193">
+      <c r="F193" s="0" t="n">
         <v>355</v>
       </c>
-      <c r="G193">
+      <c r="G193" s="0" t="n">
         <v>265</v>
       </c>
-      <c r="H193">
+      <c r="H193" s="0" t="n">
         <v>305</v>
       </c>
     </row>
-    <row r="194" spans="1:8">
-      <c r="A194" s="5">
+    <row r="194" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A194" s="1" t="n">
         <v>45886</v>
       </c>
-      <c r="E194">
+      <c r="E194" s="0" t="n">
         <v>265</v>
       </c>
-      <c r="F194">
+      <c r="F194" s="0" t="n">
         <v>330</v>
       </c>
-      <c r="G194">
+      <c r="G194" s="0" t="n">
         <v>250</v>
       </c>
-      <c r="H194">
+      <c r="H194" s="0" t="n">
         <v>250</v>
       </c>
     </row>
-    <row r="195" spans="1:8">
-      <c r="A195" s="5">
+    <row r="195" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A195" s="1" t="n">
         <v>45892</v>
       </c>
-      <c r="B195">
+      <c r="B195" s="0" t="n">
         <v>480</v>
       </c>
-      <c r="E195">
+      <c r="E195" s="0" t="n">
         <v>195</v>
       </c>
-      <c r="F195">
+      <c r="F195" s="0" t="n">
         <v>25</v>
       </c>
-      <c r="G195">
+      <c r="G195" s="0" t="n">
         <v>460</v>
       </c>
-      <c r="H195">
+      <c r="H195" s="0" t="n">
         <v>400</v>
       </c>
     </row>
-    <row r="196" spans="1:8">
-      <c r="A196" s="5">
+    <row r="196" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A196" s="1" t="n">
         <v>45892</v>
       </c>
-      <c r="E196">
+      <c r="E196" s="0" t="n">
         <v>250</v>
       </c>
-      <c r="F196">
+      <c r="F196" s="0" t="n">
         <v>75</v>
       </c>
-      <c r="G196">
+      <c r="G196" s="0" t="n">
         <v>380</v>
       </c>
-      <c r="H196">
+      <c r="H196" s="0" t="n">
         <v>260</v>
       </c>
     </row>
-    <row r="197" spans="1:8">
-      <c r="A197" s="5">
+    <row r="197" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A197" s="1" t="n">
         <v>45899</v>
       </c>
-      <c r="B197">
+      <c r="B197" s="0" t="n">
         <v>275</v>
       </c>
-      <c r="C197">
+      <c r="C197" s="0" t="n">
         <v>280</v>
       </c>
-      <c r="G197">
+      <c r="G197" s="0" t="n">
         <v>135</v>
       </c>
-      <c r="H197">
+      <c r="H197" s="0" t="n">
         <v>220</v>
       </c>
     </row>
-    <row r="198" spans="1:8">
-      <c r="A198" s="8">
+    <row r="198" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A198" s="8" t="n">
         <v>45906</v>
       </c>
-      <c r="B198">
+      <c r="B198" s="0" t="n">
         <v>280</v>
       </c>
-      <c r="C198">
+      <c r="C198" s="0" t="n">
         <v>140</v>
       </c>
-      <c r="E198">
+      <c r="E198" s="0" t="n">
         <v>635</v>
       </c>
-      <c r="F198">
+      <c r="F198" s="0" t="n">
         <v>305</v>
       </c>
-      <c r="G198">
+      <c r="G198" s="0" t="n">
         <v>420</v>
       </c>
-      <c r="H198">
+      <c r="H198" s="0" t="n">
         <v>320</v>
       </c>
     </row>
-    <row r="199" spans="1:8">
-      <c r="A199" s="8">
+    <row r="199" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A199" s="8" t="n">
         <v>45906</v>
       </c>
-      <c r="C199">
+      <c r="C199" s="0" t="n">
         <v>260</v>
       </c>
-      <c r="E199">
+      <c r="E199" s="0" t="n">
         <v>180</v>
       </c>
-      <c r="F199">
+      <c r="F199" s="0" t="n">
         <v>530</v>
       </c>
-      <c r="G199">
+      <c r="G199" s="0" t="n">
         <v>370</v>
       </c>
-      <c r="H199">
+      <c r="H199" s="0" t="n">
         <v>70</v>
       </c>
     </row>
-    <row r="200" spans="1:8">
-      <c r="A200" s="8">
+    <row r="200" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A200" s="8" t="n">
         <v>45913</v>
       </c>
-      <c r="B200">
+      <c r="B200" s="0" t="n">
         <v>320</v>
       </c>
-      <c r="G200">
+      <c r="G200" s="0" t="n">
         <v>100</v>
       </c>
-      <c r="H200">
+      <c r="H200" s="0" t="n">
         <v>490</v>
       </c>
     </row>
-    <row r="201" spans="1:8">
-      <c r="A201" s="8">
+    <row r="201" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A201" s="8" t="n">
         <v>45913</v>
       </c>
-      <c r="C201">
+      <c r="C201" s="0" t="n">
         <v>255</v>
       </c>
-      <c r="E201">
+      <c r="E201" s="0" t="n">
         <v>300</v>
       </c>
-      <c r="F201">
+      <c r="F201" s="0" t="n">
         <v>305</v>
       </c>
-      <c r="G201">
+      <c r="G201" s="0" t="n">
         <v>395</v>
       </c>
-      <c r="H201">
+      <c r="H201" s="0" t="n">
         <v>435</v>
       </c>
     </row>
-    <row r="202" spans="1:8">
-      <c r="A202" s="8">
+    <row r="202" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A202" s="8" t="n">
         <v>45920</v>
       </c>
-      <c r="E202">
+      <c r="E202" s="0" t="n">
         <v>270</v>
       </c>
-      <c r="F202">
+      <c r="F202" s="0" t="n">
         <v>235</v>
       </c>
-      <c r="G202">
+      <c r="G202" s="0" t="n">
         <v>350</v>
       </c>
-      <c r="H202">
+      <c r="H202" s="0" t="n">
         <v>175</v>
       </c>
     </row>
-    <row r="203" spans="1:8">
-      <c r="A203" s="8">
+    <row r="203" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A203" s="8" t="n">
         <v>45928</v>
       </c>
-      <c r="E203">
+      <c r="E203" s="0" t="n">
         <v>250</v>
       </c>
-      <c r="F203">
+      <c r="F203" s="0" t="n">
         <v>145</v>
       </c>
-      <c r="G203">
+      <c r="G203" s="0" t="n">
         <v>250</v>
       </c>
-      <c r="H203">
+      <c r="H203" s="0" t="n">
         <v>215</v>
       </c>
     </row>
-    <row r="204" spans="1:8">
-      <c r="A204" s="8">
+    <row r="204" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A204" s="8" t="n">
         <v>45930</v>
       </c>
-      <c r="E204">
+      <c r="E204" s="0" t="n">
         <v>285</v>
       </c>
-      <c r="F204">
+      <c r="F204" s="0" t="n">
         <v>185</v>
       </c>
-      <c r="G204">
+      <c r="G204" s="0" t="n">
         <v>110</v>
       </c>
-      <c r="H204">
+      <c r="H204" s="0" t="n">
         <v>305</v>
       </c>
     </row>
-    <row r="205" spans="1:8">
-      <c r="A205" s="8">
+    <row r="205" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A205" s="8" t="n">
         <v>45932</v>
       </c>
-      <c r="E205">
+      <c r="E205" s="0" t="n">
         <v>450</v>
       </c>
-      <c r="F205">
+      <c r="F205" s="0" t="n">
         <v>335</v>
       </c>
-      <c r="G205">
+      <c r="G205" s="0" t="n">
         <v>120</v>
       </c>
-      <c r="H205">
+      <c r="H205" s="0" t="n">
         <v>290</v>
       </c>
     </row>
-    <row r="206" spans="1:8">
-      <c r="A206" s="8">
+    <row r="206" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A206" s="8" t="n">
         <v>45933</v>
       </c>
-      <c r="E206">
+      <c r="E206" s="0" t="n">
         <v>145</v>
       </c>
-      <c r="F206">
+      <c r="F206" s="0" t="n">
         <v>435</v>
       </c>
-      <c r="G206">
+      <c r="G206" s="0" t="n">
         <v>225</v>
       </c>
-      <c r="H206">
+      <c r="H206" s="0" t="n">
         <v>230</v>
       </c>
     </row>
-    <row r="207" spans="1:8">
-      <c r="A207" s="8">
+    <row r="207" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A207" s="8" t="n">
         <v>45934</v>
       </c>
-      <c r="E207">
+      <c r="E207" s="0" t="n">
         <v>205</v>
       </c>
-      <c r="F207">
+      <c r="F207" s="0" t="n">
         <v>130</v>
       </c>
-      <c r="G207">
+      <c r="G207" s="0" t="n">
         <v>240</v>
       </c>
-      <c r="H207">
+      <c r="H207" s="0" t="n">
         <v>110</v>
       </c>
     </row>
-    <row r="208" spans="1:8">
-      <c r="A208" s="8">
+    <row r="208" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A208" s="8" t="n">
         <v>45935</v>
       </c>
-      <c r="E208">
+      <c r="E208" s="0" t="n">
         <v>300</v>
       </c>
-      <c r="F208">
+      <c r="F208" s="0" t="n">
         <v>230</v>
       </c>
-      <c r="G208">
+      <c r="G208" s="0" t="n">
         <v>205</v>
       </c>
-      <c r="H208">
+      <c r="H208" s="0" t="n">
         <v>420</v>
       </c>
     </row>
-    <row r="209" spans="1:8">
-      <c r="A209" s="8">
+    <row r="209" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A209" s="8" t="n">
         <v>45935</v>
       </c>
-      <c r="E209">
+      <c r="E209" s="0" t="n">
         <v>245</v>
       </c>
-      <c r="F209">
+      <c r="F209" s="0" t="n">
         <v>145</v>
       </c>
-      <c r="G209">
+      <c r="G209" s="0" t="n">
         <v>240</v>
       </c>
-      <c r="H209">
+      <c r="H209" s="0" t="n">
         <v>140</v>
       </c>
     </row>
-    <row r="210" spans="1:8">
-      <c r="A210" s="8">
+    <row r="210" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A210" s="8" t="n">
         <v>45935</v>
       </c>
-      <c r="E210">
+      <c r="E210" s="0" t="n">
         <v>125</v>
       </c>
-      <c r="F210">
+      <c r="F210" s="0" t="n">
         <v>320</v>
       </c>
-      <c r="G210">
+      <c r="G210" s="0" t="n">
         <v>340</v>
       </c>
-      <c r="H210">
+      <c r="H210" s="0" t="n">
         <v>360</v>
       </c>
     </row>
-    <row r="211" spans="1:8">
-      <c r="A211" s="8">
+    <row r="211" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A211" s="8" t="n">
         <v>45936</v>
       </c>
-      <c r="E211">
+      <c r="E211" s="0" t="n">
         <v>95</v>
       </c>
-      <c r="F211">
+      <c r="F211" s="0" t="n">
         <v>220</v>
       </c>
-      <c r="G211">
+      <c r="G211" s="0" t="n">
         <v>240</v>
       </c>
-      <c r="H211">
+      <c r="H211" s="0" t="n">
         <v>165</v>
       </c>
     </row>
-    <row r="212" spans="1:8">
-      <c r="A212" s="8">
+    <row r="212" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A212" s="8" t="n">
         <v>45940</v>
       </c>
-      <c r="C212">
+      <c r="C212" s="0" t="n">
         <v>275</v>
       </c>
-      <c r="D212">
+      <c r="D212" s="0" t="n">
         <v>125</v>
       </c>
-      <c r="E212">
+      <c r="E212" s="0" t="n">
         <v>340</v>
       </c>
-      <c r="F212">
+      <c r="F212" s="0" t="n">
         <v>85</v>
       </c>
-      <c r="G212">
+      <c r="G212" s="0" t="n">
         <v>540</v>
       </c>
-      <c r="H212">
+      <c r="H212" s="0" t="n">
         <v>395</v>
       </c>
     </row>
-    <row r="213" spans="1:8">
-      <c r="A213" s="8">
+    <row r="213" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A213" s="8" t="n">
         <v>45942</v>
       </c>
-      <c r="C213">
+      <c r="C213" s="0" t="n">
         <v>410</v>
       </c>
-      <c r="D213">
+      <c r="D213" s="0" t="n">
         <v>105</v>
       </c>
-      <c r="G213">
+      <c r="G213" s="0" t="n">
         <v>230</v>
       </c>
-      <c r="H213">
+      <c r="H213" s="0" t="n">
         <v>285</v>
       </c>
     </row>
-    <row r="214" spans="1:8">
-      <c r="A214" s="8">
+    <row r="214" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A214" s="8" t="n">
         <v>45942</v>
       </c>
-      <c r="C214">
+      <c r="C214" s="0" t="n">
         <v>90</v>
       </c>
-      <c r="D214">
+      <c r="D214" s="0" t="n">
         <v>265</v>
       </c>
-      <c r="G214">
+      <c r="G214" s="0" t="n">
         <v>265</v>
       </c>
-      <c r="H214">
+      <c r="H214" s="0" t="n">
         <v>275</v>
       </c>
     </row>
-    <row r="215" spans="1:8">
-      <c r="A215" s="8">
+    <row r="215" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A215" s="8" t="n">
         <v>45948</v>
       </c>
-      <c r="E215">
+      <c r="E215" s="0" t="n">
         <v>355</v>
       </c>
-      <c r="F215">
+      <c r="F215" s="0" t="n">
         <v>55</v>
       </c>
-      <c r="G215">
+      <c r="G215" s="0" t="n">
         <v>290</v>
       </c>
-      <c r="H215">
+      <c r="H215" s="0" t="n">
         <v>335</v>
       </c>
     </row>
-    <row r="216" spans="1:8">
-      <c r="A216" s="8">
+    <row r="216" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A216" s="8" t="n">
         <v>45948</v>
       </c>
-      <c r="E216">
+      <c r="E216" s="0" t="n">
         <v>85</v>
       </c>
-      <c r="F216">
+      <c r="F216" s="0" t="n">
         <v>245</v>
       </c>
-      <c r="G216">
+      <c r="G216" s="0" t="n">
         <v>430</v>
       </c>
-      <c r="H216">
+      <c r="H216" s="0" t="n">
         <v>230</v>
       </c>
     </row>
-    <row r="217" spans="1:8">
-      <c r="A217" s="8">
+    <row r="217" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A217" s="8" t="n">
         <v>45955</v>
       </c>
-      <c r="C217">
+      <c r="C217" s="0" t="n">
         <v>135</v>
       </c>
-      <c r="E217">
+      <c r="E217" s="0" t="n">
         <v>225</v>
       </c>
-      <c r="F217">
+      <c r="F217" s="0" t="n">
         <v>145</v>
       </c>
-      <c r="H217">
+      <c r="H217" s="0" t="n">
         <v>130</v>
       </c>
     </row>
-    <row r="218" spans="1:8">
-      <c r="A218" s="8">
+    <row r="218" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A218" s="8" t="n">
         <v>45962</v>
       </c>
-      <c r="C218">
+      <c r="C218" s="0" t="n">
         <v>155</v>
       </c>
-      <c r="E218">
+      <c r="E218" s="0" t="n">
         <v>345</v>
       </c>
-      <c r="F218">
+      <c r="F218" s="0" t="n">
         <v>195</v>
       </c>
-      <c r="G218">
+      <c r="G218" s="0" t="n">
         <v>285</v>
       </c>
-      <c r="H218">
+      <c r="H218" s="0" t="n">
         <v>310</v>
       </c>
     </row>
-    <row r="219" spans="1:8">
-      <c r="A219" s="5">
+    <row r="219" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A219" s="1" t="n">
         <v>45969</v>
       </c>
-      <c r="C219">
+      <c r="C219" s="0" t="n">
         <v>420</v>
       </c>
-      <c r="D219">
+      <c r="D219" s="0" t="n">
         <v>200</v>
       </c>
-      <c r="E219">
+      <c r="E219" s="0" t="n">
         <v>485</v>
       </c>
-      <c r="F219">
+      <c r="F219" s="0" t="n">
         <v>175</v>
       </c>
-      <c r="G219">
+      <c r="G219" s="0" t="n">
         <v>305</v>
       </c>
-      <c r="H219">
+      <c r="H219" s="0" t="n">
         <v>475</v>
       </c>
     </row>
-    <row r="220" spans="1:8">
-      <c r="A220" s="8">
+    <row r="220" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A220" s="8" t="n">
         <v>45983</v>
       </c>
-      <c r="B220">
+      <c r="B220" s="0" t="n">
         <v>50</v>
       </c>
-      <c r="C220">
+      <c r="C220" s="0" t="n">
         <v>140</v>
       </c>
-      <c r="E220">
+      <c r="E220" s="0" t="n">
         <v>245</v>
       </c>
-      <c r="F220">
+      <c r="F220" s="0" t="n">
         <v>340</v>
       </c>
     </row>
-    <row r="221" spans="1:8">
-      <c r="A221" s="8">
+    <row r="221" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A221" s="8" t="n">
         <v>45983</v>
       </c>
-      <c r="B221">
+      <c r="B221" s="0" t="n">
         <v>435</v>
       </c>
-      <c r="C221">
+      <c r="C221" s="0" t="n">
         <v>180</v>
       </c>
-      <c r="E221">
+      <c r="E221" s="0" t="n">
         <v>160</v>
       </c>
-      <c r="F221">
+      <c r="F221" s="0" t="n">
         <v>80</v>
       </c>
     </row>
-    <row r="222" spans="1:8">
-      <c r="A222" s="8">
+    <row r="222" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A222" s="8" t="n">
         <v>45990</v>
       </c>
-      <c r="C222">
+      <c r="C222" s="0" t="n">
         <v>355</v>
       </c>
-      <c r="E222">
+      <c r="E222" s="0" t="n">
         <v>135</v>
       </c>
-      <c r="F222">
+      <c r="F222" s="0" t="n">
         <v>135</v>
       </c>
     </row>
-    <row r="223" spans="1:8">
-      <c r="A223" s="8">
+    <row r="223" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A223" s="8" t="n">
         <v>45990</v>
       </c>
-      <c r="C223">
+      <c r="C223" s="0" t="n">
         <v>120</v>
       </c>
-      <c r="E223">
+      <c r="E223" s="0" t="n">
         <v>185</v>
       </c>
-      <c r="F223">
+      <c r="F223" s="0" t="n">
         <v>380</v>
       </c>
     </row>
-    <row r="224" spans="1:8">
-      <c r="A224" s="8">
+    <row r="224" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A224" s="8" t="n">
         <v>45990</v>
       </c>
-      <c r="C224">
+      <c r="C224" s="0" t="n">
         <v>260</v>
       </c>
-      <c r="E224">
+      <c r="E224" s="0" t="n">
         <v>95</v>
       </c>
-      <c r="F224">
+      <c r="F224" s="0" t="n">
         <v>230</v>
       </c>
     </row>
-    <row r="225" spans="1:8">
-      <c r="A225" s="8">
+    <row r="225" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A225" s="8" t="n">
         <v>45990</v>
       </c>
-      <c r="C225">
+      <c r="C225" s="0" t="n">
         <v>125</v>
       </c>
-      <c r="E225">
+      <c r="E225" s="0" t="n">
         <v>240</v>
       </c>
-      <c r="F225">
+      <c r="F225" s="0" t="n">
         <v>130</v>
       </c>
     </row>
-    <row r="226" spans="1:8">
-      <c r="A226" s="8">
+    <row r="226" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A226" s="8" t="n">
         <v>45997</v>
       </c>
-      <c r="B226">
+      <c r="B226" s="0" t="n">
         <v>175</v>
       </c>
-      <c r="C226">
+      <c r="C226" s="0" t="n">
         <v>275</v>
       </c>
-      <c r="E226">
+      <c r="E226" s="0" t="n">
         <v>105</v>
       </c>
-      <c r="F226">
+      <c r="F226" s="0" t="n">
         <v>240</v>
       </c>
     </row>
-    <row r="227" spans="1:8">
-      <c r="A227" s="8">
+    <row r="227" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A227" s="8" t="n">
         <v>45997</v>
       </c>
-      <c r="B227">
+      <c r="B227" s="0" t="n">
         <v>60</v>
       </c>
-      <c r="C227">
+      <c r="C227" s="0" t="n">
         <v>235</v>
       </c>
-      <c r="E227">
+      <c r="E227" s="0" t="n">
         <v>340</v>
       </c>
-      <c r="F227">
+      <c r="F227" s="0" t="n">
         <v>260</v>
       </c>
     </row>
-    <row r="228" spans="1:8">
-      <c r="A228" s="8">
+    <row r="228" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A228" s="8" t="n">
         <v>45997</v>
       </c>
-      <c r="B228">
+      <c r="B228" s="0" t="n">
         <v>370</v>
       </c>
-      <c r="C228">
+      <c r="C228" s="0" t="n">
         <v>415</v>
       </c>
-      <c r="E228">
+      <c r="E228" s="0" t="n">
         <v>230</v>
       </c>
-      <c r="F228">
+      <c r="F228" s="0" t="n">
         <v>370</v>
       </c>
     </row>
-    <row r="229" spans="1:8">
-      <c r="A229" s="5">
+    <row r="229" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A229" s="1" t="n">
         <v>46005</v>
       </c>
-      <c r="E229">
+      <c r="E229" s="0" t="n">
         <v>215</v>
       </c>
-      <c r="F229">
+      <c r="F229" s="0" t="n">
         <v>110</v>
       </c>
-      <c r="G229">
+      <c r="G229" s="0" t="n">
         <v>370</v>
       </c>
-      <c r="H229">
+      <c r="H229" s="0" t="n">
         <v>275</v>
       </c>
     </row>
-    <row r="230" spans="1:8">
-      <c r="A230" s="5">
+    <row r="230" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A230" s="1" t="n">
         <v>46005</v>
       </c>
-      <c r="E230">
+      <c r="E230" s="0" t="n">
         <v>325</v>
       </c>
-      <c r="F230">
+      <c r="F230" s="0" t="n">
         <v>285</v>
       </c>
-      <c r="G230">
+      <c r="G230" s="0" t="n">
         <v>270</v>
       </c>
-      <c r="H230">
+      <c r="H230" s="0" t="n">
         <v>215</v>
       </c>
     </row>
-    <row r="231" spans="1:8">
-      <c r="A231" s="5">
+    <row r="231" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A231" s="1" t="n">
         <v>46012</v>
       </c>
-      <c r="C231">
+      <c r="C231" s="0" t="n">
         <v>245</v>
       </c>
-      <c r="E231">
+      <c r="E231" s="0" t="n">
         <v>185</v>
       </c>
-      <c r="F231">
+      <c r="F231" s="0" t="n">
         <v>255</v>
       </c>
-      <c r="G231">
+      <c r="G231" s="0" t="n">
         <v>275</v>
       </c>
-      <c r="H231">
+      <c r="H231" s="0" t="n">
         <v>365</v>
       </c>
     </row>
-    <row r="232" spans="1:8">
-      <c r="A232" s="5">
+    <row r="232" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A232" s="1" t="n">
         <v>46012</v>
       </c>
-      <c r="E232">
+      <c r="E232" s="0" t="n">
         <v>345</v>
       </c>
-      <c r="F232">
+      <c r="F232" s="0" t="n">
         <v>90</v>
       </c>
-      <c r="G232">
+      <c r="G232" s="0" t="n">
         <v>180</v>
       </c>
-      <c r="H232">
+      <c r="H232" s="0" t="n">
         <v>145</v>
       </c>
     </row>
-    <row r="233" spans="1:8">
-      <c r="A233" s="5">
+    <row r="233" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A233" s="1" t="n">
         <v>46012</v>
       </c>
-      <c r="E233">
+      <c r="E233" s="0" t="n">
         <v>210</v>
       </c>
-      <c r="F233">
+      <c r="F233" s="0" t="n">
         <v>170</v>
       </c>
-      <c r="G233">
+      <c r="G233" s="0" t="n">
         <v>190</v>
       </c>
-      <c r="H233">
+      <c r="H233" s="0" t="n">
         <v>225</v>
       </c>
     </row>
-    <row r="234" spans="1:8">
-      <c r="A234" s="5">
+    <row r="234" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A234" s="1" t="n">
         <v>46015</v>
       </c>
-      <c r="B234">
+      <c r="B234" s="0" t="n">
         <v>135</v>
       </c>
-      <c r="C234">
+      <c r="C234" s="0" t="n">
         <v>285</v>
       </c>
-      <c r="E234">
+      <c r="E234" s="0" t="n">
         <v>185</v>
       </c>
-      <c r="F234">
+      <c r="F234" s="0" t="n">
         <v>405</v>
       </c>
-      <c r="G234">
+      <c r="G234" s="0" t="n">
         <v>450</v>
       </c>
-      <c r="H234">
+      <c r="H234" s="0" t="n">
         <v>345</v>
       </c>
     </row>
-    <row r="235" spans="1:8">
-      <c r="A235" s="5">
+    <row r="235" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A235" s="1" t="n">
         <v>46016</v>
       </c>
-      <c r="B235">
+      <c r="B235" s="0" t="n">
         <v>465</v>
       </c>
-      <c r="C235">
+      <c r="C235" s="0" t="n">
         <v>270</v>
       </c>
-      <c r="E235">
+      <c r="E235" s="0" t="n">
         <v>200</v>
       </c>
-      <c r="F235">
+      <c r="F235" s="0" t="n">
         <v>445</v>
       </c>
-      <c r="G235">
+      <c r="G235" s="0" t="n">
         <v>380</v>
       </c>
-      <c r="H235">
+      <c r="H235" s="0" t="n">
         <v>565</v>
       </c>
     </row>
-    <row r="236" spans="1:8">
-      <c r="A236" s="5">
+    <row r="236" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A236" s="1" t="n">
         <v>46020</v>
       </c>
-      <c r="B236">
+      <c r="B236" s="0" t="n">
         <v>405</v>
       </c>
-      <c r="C236">
+      <c r="C236" s="0" t="n">
         <v>370</v>
       </c>
-      <c r="D236">
+      <c r="D236" s="0" t="n">
         <v>385</v>
       </c>
-      <c r="E236">
+      <c r="E236" s="0" t="n">
         <v>185</v>
       </c>
-      <c r="F236">
+      <c r="F236" s="0" t="n">
         <v>430</v>
       </c>
-      <c r="H236">
+      <c r="H236" s="0" t="n">
         <v>270</v>
       </c>
     </row>
-    <row r="237" spans="1:8">
-      <c r="A237" s="5">
+    <row r="237" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A237" s="1" t="n">
         <v>46032</v>
       </c>
-      <c r="B237">
+      <c r="B237" s="0" t="n">
         <v>340</v>
       </c>
-      <c r="E237">
+      <c r="E237" s="0" t="n">
         <v>65</v>
       </c>
-      <c r="F237">
+      <c r="F237" s="0" t="n">
         <v>255</v>
       </c>
     </row>
-    <row r="238" spans="1:8">
-      <c r="A238" s="5">
+    <row r="238" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A238" s="1" t="n">
         <v>46032</v>
       </c>
-      <c r="B238">
+      <c r="B238" s="0" t="n">
         <v>245</v>
       </c>
-      <c r="E238">
+      <c r="E238" s="0" t="n">
         <v>210</v>
       </c>
-      <c r="F238">
+      <c r="F238" s="0" t="n">
         <v>190</v>
       </c>
     </row>
-    <row r="239" spans="1:8">
-      <c r="A239" s="5">
+    <row r="239" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A239" s="1" t="n">
         <v>46039</v>
       </c>
-      <c r="B239">
+      <c r="B239" s="0" t="n">
         <v>135</v>
       </c>
-      <c r="C239">
+      <c r="C239" s="0" t="n">
         <v>145</v>
       </c>
-      <c r="E239">
+      <c r="E239" s="0" t="n">
         <v>120</v>
       </c>
-      <c r="F239">
+      <c r="F239" s="0" t="n">
         <v>70</v>
       </c>
     </row>
-    <row r="240" spans="1:8">
-      <c r="A240" s="5">
+    <row r="240" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A240" s="1" t="n">
         <v>46039</v>
       </c>
-      <c r="B240">
+      <c r="B240" s="0" t="n">
         <v>180</v>
       </c>
-      <c r="C240">
+      <c r="C240" s="0" t="n">
         <v>140</v>
       </c>
-      <c r="E240">
+      <c r="E240" s="0" t="n">
         <v>145</v>
       </c>
-      <c r="F240">
+      <c r="F240" s="0" t="n">
         <v>425</v>
       </c>
     </row>
-    <row r="241" spans="1:8">
-      <c r="A241" s="5">
+    <row r="241" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A241" s="1" t="n">
         <v>46039</v>
       </c>
-      <c r="B241">
+      <c r="B241" s="0" t="n">
         <v>285</v>
       </c>
-      <c r="C241">
+      <c r="C241" s="0" t="n">
         <v>245</v>
       </c>
-      <c r="E241">
+      <c r="E241" s="0" t="n">
         <v>105</v>
       </c>
-      <c r="F241">
+      <c r="F241" s="0" t="n">
         <v>130</v>
       </c>
     </row>
-    <row r="242" spans="1:8">
-      <c r="A242" s="5">
+    <row r="242" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A242" s="1" t="n">
         <v>46067</v>
       </c>
-      <c r="B242">
+      <c r="B242" s="0" t="n">
         <v>325</v>
       </c>
-      <c r="C242">
+      <c r="C242" s="0" t="n">
         <v>225</v>
       </c>
-      <c r="D242">
+      <c r="D242" s="0" t="n">
         <v>250</v>
       </c>
-      <c r="E242">
+      <c r="E242" s="0" t="n">
         <v>420</v>
       </c>
-      <c r="F242">
+      <c r="F242" s="0" t="n">
         <v>340</v>
       </c>
     </row>
-    <row r="243" spans="1:8">
-      <c r="A243" s="5">
+    <row r="243" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A243" s="1" t="n">
         <v>46067</v>
       </c>
-      <c r="C243">
+      <c r="C243" s="0" t="n">
         <v>205</v>
       </c>
-      <c r="D243">
+      <c r="D243" s="0" t="n">
         <v>240</v>
       </c>
-      <c r="E243">
+      <c r="E243" s="0" t="n">
         <v>385</v>
       </c>
-      <c r="F243">
+      <c r="F243" s="0" t="n">
         <v>170</v>
       </c>
     </row>
-    <row r="244" spans="1:8">
-      <c r="A244" s="5">
+    <row r="244" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A244" s="1" t="n">
         <v>46067</v>
       </c>
-      <c r="B244">
+      <c r="B244" s="0" t="n">
         <v>305</v>
       </c>
-      <c r="C244">
+      <c r="C244" s="0" t="n">
         <v>45</v>
       </c>
-      <c r="E244">
+      <c r="E244" s="0" t="n">
         <v>230</v>
       </c>
-      <c r="F244">
+      <c r="F244" s="0" t="n">
         <v>290</v>
       </c>
     </row>
-    <row r="245" spans="1:8">
-      <c r="A245" s="5">
+    <row r="245" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A245" s="1" t="n">
         <v>46067</v>
       </c>
-      <c r="B245">
+      <c r="B245" s="0" t="n">
         <v>285</v>
       </c>
-      <c r="C245">
+      <c r="C245" s="0" t="n">
         <v>60</v>
       </c>
-      <c r="E245">
+      <c r="E245" s="0" t="n">
         <v>225</v>
       </c>
-      <c r="F245">
+      <c r="F245" s="0" t="n">
         <v>270</v>
       </c>
     </row>
-    <row r="246" spans="1:8">
-      <c r="A246" s="5">
+    <row r="246" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A246" s="1" t="n">
         <v>46074</v>
       </c>
-      <c r="B246">
+      <c r="B246" s="0" t="n">
         <v>95</v>
       </c>
-      <c r="C246">
+      <c r="C246" s="0" t="n">
         <v>340</v>
       </c>
-      <c r="E246">
+      <c r="E246" s="0" t="n">
         <v>215</v>
       </c>
-      <c r="F246">
+      <c r="F246" s="0" t="n">
         <v>260</v>
       </c>
     </row>
-    <row r="247" spans="1:8">
-      <c r="A247" s="5">
+    <row r="247" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A247" s="1" t="n">
         <v>46074</v>
       </c>
-      <c r="B247">
+      <c r="B247" s="0" t="n">
         <v>250</v>
       </c>
-      <c r="C247">
+      <c r="C247" s="0" t="n">
         <v>285</v>
       </c>
-      <c r="E247">
+      <c r="E247" s="0" t="n">
         <v>260</v>
       </c>
-      <c r="F247">
+      <c r="F247" s="0" t="n">
         <v>280</v>
       </c>
     </row>
-    <row r="248" spans="1:8">
-      <c r="A248" s="5">
+    <row r="248" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A248" s="1" t="n">
         <v>46081</v>
       </c>
-      <c r="B248">
+      <c r="B248" s="0" t="n">
         <v>180</v>
       </c>
-      <c r="E248">
+      <c r="E248" s="0" t="n">
         <v>355</v>
       </c>
-      <c r="F248">
+      <c r="F248" s="0" t="n">
         <v>120</v>
       </c>
     </row>
-    <row r="249" spans="1:8">
-      <c r="A249" s="5">
+    <row r="249" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A249" s="1" t="n">
         <v>46081</v>
       </c>
-      <c r="B249">
+      <c r="B249" s="0" t="n">
         <v>360</v>
       </c>
-      <c r="E249">
+      <c r="E249" s="0" t="n">
         <v>140</v>
       </c>
-      <c r="F249">
+      <c r="F249" s="0" t="n">
         <v>260</v>
       </c>
     </row>
-    <row r="250" spans="1:8">
-      <c r="A250" s="5">
+    <row r="250" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A250" s="1" t="n">
         <v>46109</v>
       </c>
-      <c r="B250">
+      <c r="B250" s="0" t="n">
         <v>610</v>
       </c>
-      <c r="C250">
+      <c r="C250" s="0" t="n">
         <v>345</v>
       </c>
-      <c r="E250">
+      <c r="E250" s="0" t="n">
         <v>75</v>
       </c>
-      <c r="F250">
+      <c r="F250" s="0" t="n">
         <v>170</v>
       </c>
     </row>
-    <row r="251" spans="1:8">
-      <c r="A251" s="5">
+    <row r="251" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A251" s="1" t="n">
         <v>46115</v>
       </c>
-      <c r="B251">
+      <c r="B251" s="0" t="n">
         <v>165</v>
       </c>
-      <c r="C251">
+      <c r="C251" s="0" t="n">
         <v>225</v>
       </c>
-      <c r="G251">
+      <c r="G251" s="0" t="n">
         <v>190</v>
       </c>
-      <c r="H251">
+      <c r="H251" s="0" t="n">
         <v>235</v>
       </c>
     </row>
-    <row r="252" spans="1:8">
-      <c r="A252" s="5">
+    <row r="252" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A252" s="1" t="n">
         <v>46123</v>
       </c>
-      <c r="B252">
+      <c r="B252" s="0" t="n">
         <v>275</v>
       </c>
-      <c r="C252">
+      <c r="C252" s="0" t="n">
         <v>290</v>
       </c>
-      <c r="E252">
+      <c r="E252" s="0" t="n">
         <v>295</v>
       </c>
-      <c r="F252">
+      <c r="F252" s="0" t="n">
         <v>300</v>
       </c>
-      <c r="G252">
+      <c r="G252" s="0" t="n">
         <v>335</v>
       </c>
-      <c r="H252">
+      <c r="H252" s="0" t="n">
         <v>280</v>
       </c>
     </row>
-    <row r="253" spans="1:8">
-      <c r="A253" s="5">
+    <row r="253" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A253" s="1" t="n">
         <v>46130</v>
       </c>
-      <c r="E253">
+      <c r="E253" s="0" t="n">
         <v>455</v>
       </c>
-      <c r="F253">
+      <c r="F253" s="0" t="n">
         <v>335</v>
       </c>
-      <c r="G253">
+      <c r="G253" s="0" t="n">
         <v>155</v>
       </c>
-      <c r="H253">
+      <c r="H253" s="0" t="n">
         <v>230</v>
       </c>
     </row>
-    <row r="254" spans="1:8">
-      <c r="A254" s="5">
+    <row r="254" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A254" s="1" t="n">
         <v>46137</v>
       </c>
-      <c r="E254">
+      <c r="E254" s="0" t="n">
         <v>340</v>
       </c>
-      <c r="F254">
+      <c r="F254" s="0" t="n">
         <v>440</v>
       </c>
-      <c r="G254">
+      <c r="G254" s="0" t="n">
         <v>260</v>
       </c>
-      <c r="H254">
+      <c r="H254" s="0" t="n">
         <v>420</v>
       </c>
     </row>
-    <row r="255" spans="1:8">
-      <c r="A255" s="5">
+    <row r="255" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A255" s="1" t="n">
         <v>46144</v>
       </c>
-      <c r="C255">
+      <c r="C255" s="0" t="n">
         <v>165</v>
       </c>
-      <c r="E255">
+      <c r="E255" s="0" t="n">
         <v>215</v>
       </c>
-      <c r="F255">
+      <c r="F255" s="0" t="n">
         <v>490</v>
       </c>
-      <c r="G255">
+      <c r="G255" s="0" t="n">
         <v>150</v>
       </c>
-      <c r="H255">
+      <c r="H255" s="0" t="n">
         <v>365</v>
       </c>
     </row>
-    <row r="256" spans="1:8">
-      <c r="A256" s="5">
+    <row r="256" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A256" s="1" t="n">
         <v>46151</v>
       </c>
-      <c r="C256">
+      <c r="C256" s="0" t="n">
         <v>475</v>
       </c>
-      <c r="D256">
+      <c r="D256" s="0" t="n">
         <v>300</v>
       </c>
-      <c r="E256">
+      <c r="E256" s="0" t="n">
         <v>240</v>
       </c>
-      <c r="F256">
+      <c r="F256" s="0" t="n">
         <v>355</v>
       </c>
-      <c r="G256">
+      <c r="G256" s="0" t="n">
         <v>440</v>
       </c>
-      <c r="H256">
+      <c r="H256" s="0" t="n">
         <v>390</v>
       </c>
     </row>
-    <row r="257" spans="1:8">
-      <c r="A257" s="5">
+    <row r="257" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A257" s="1" t="n">
         <v>46151</v>
       </c>
-      <c r="C257">
+      <c r="C257" s="0" t="n">
         <v>95</v>
       </c>
-      <c r="D257">
+      <c r="D257" s="0" t="n">
         <v>370</v>
       </c>
-      <c r="E257">
+      <c r="E257" s="0" t="n">
         <v>415</v>
       </c>
-      <c r="F257">
+      <c r="F257" s="0" t="n">
         <v>610</v>
       </c>
-      <c r="G257">
+      <c r="G257" s="0" t="n">
         <v>335</v>
       </c>
-      <c r="H257">
+      <c r="H257" s="0" t="n">
         <v>335</v>
       </c>
     </row>
-    <row r="258" spans="1:8">
-      <c r="A258" s="5">
+    <row r="258" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A258" s="1" t="n">
         <v>46165</v>
       </c>
-      <c r="E258">
+      <c r="E258" s="0" t="n">
         <v>310</v>
       </c>
-      <c r="F258">
+      <c r="F258" s="0" t="n">
         <v>180</v>
       </c>
-      <c r="G258">
+      <c r="G258" s="0" t="n">
         <v>175</v>
       </c>
-      <c r="H258">
+      <c r="H258" s="0" t="n">
         <v>220</v>
       </c>
     </row>
-    <row r="259" spans="1:8">
-      <c r="A259" s="5">
+    <row r="259" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A259" s="1" t="n">
         <v>46165</v>
       </c>
-      <c r="E259">
+      <c r="E259" s="0" t="n">
         <v>100</v>
       </c>
-      <c r="F259">
+      <c r="F259" s="0" t="n">
         <v>480</v>
       </c>
-      <c r="G259">
+      <c r="G259" s="0" t="n">
         <v>120</v>
       </c>
-      <c r="H259">
+      <c r="H259" s="0" t="n">
         <v>180</v>
       </c>
     </row>
-    <row r="260" spans="1:8">
-      <c r="A260" s="5">
+    <row r="260" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A260" s="1" t="n">
         <v>46172</v>
       </c>
-      <c r="B260">
+      <c r="B260" s="0" t="n">
         <v>245</v>
       </c>
-      <c r="C260">
+      <c r="C260" s="0" t="n">
         <v>465</v>
       </c>
-      <c r="E260">
+      <c r="E260" s="0" t="n">
         <v>370</v>
       </c>
-      <c r="F260">
+      <c r="F260" s="0" t="n">
         <v>80</v>
       </c>
-      <c r="G260">
+      <c r="G260" s="0" t="n">
         <v>310</v>
       </c>
-      <c r="H260">
+      <c r="H260" s="0" t="n">
         <v>275</v>
       </c>
     </row>
-    <row r="261" spans="1:8">
-      <c r="A261" s="5">
+    <row r="261" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A261" s="1" t="n">
         <v>46172</v>
       </c>
-      <c r="C261">
+      <c r="C261" s="0" t="n">
         <v>40</v>
       </c>
-      <c r="E261">
+      <c r="E261" s="0" t="n">
         <v>200</v>
       </c>
-      <c r="F261">
+      <c r="F261" s="0" t="n">
         <v>390</v>
       </c>
-      <c r="G261">
+      <c r="G261" s="0" t="n">
         <v>235</v>
       </c>
-      <c r="H261">
+      <c r="H261" s="0" t="n">
         <v>350</v>
       </c>
     </row>
-    <row r="262" spans="1:8">
-      <c r="A262" s="5">
+    <row r="262" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A262" s="1" t="n">
         <v>46179</v>
       </c>
-      <c r="C262">
+      <c r="C262" s="0" t="n">
         <v>180</v>
       </c>
-      <c r="E262">
+      <c r="E262" s="0" t="n">
         <v>475</v>
       </c>
-      <c r="F262">
+      <c r="F262" s="0" t="n">
         <v>410</v>
       </c>
-      <c r="G262">
+      <c r="G262" s="0" t="n">
         <v>300</v>
       </c>
-      <c r="H262">
+      <c r="H262" s="0" t="n">
         <v>195</v>
       </c>
     </row>
-    <row r="263" spans="1:8">
-      <c r="A263" s="5">
+    <row r="263" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A263" s="1" t="n">
         <v>46186</v>
       </c>
-      <c r="E263">
+      <c r="E263" s="0" t="n">
         <v>398</v>
       </c>
-      <c r="F263">
+      <c r="F263" s="0" t="n">
         <v>490</v>
       </c>
-      <c r="G263">
+      <c r="G263" s="0" t="n">
         <v>210</v>
       </c>
-      <c r="H263">
+      <c r="H263" s="0" t="n">
         <v>305</v>
       </c>
     </row>
-    <row r="264" spans="1:8">
-      <c r="A264" s="5">
+    <row r="264" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A264" s="1" t="n">
         <v>46186</v>
       </c>
-      <c r="E264">
+      <c r="E264" s="0" t="n">
         <v>235</v>
       </c>
-      <c r="F264">
+      <c r="F264" s="0" t="n">
         <v>250</v>
       </c>
-      <c r="G264">
+      <c r="G264" s="0" t="n">
         <v>315</v>
       </c>
-      <c r="H264">
+      <c r="H264" s="0" t="n">
         <v>325</v>
       </c>
     </row>
-    <row r="265" spans="1:8">
-      <c r="A265" s="5">
+    <row r="265" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A265" s="1" t="n">
         <v>46186</v>
       </c>
-      <c r="E265">
+      <c r="E265" s="0" t="n">
         <v>245</v>
       </c>
-      <c r="F265">
+      <c r="F265" s="0" t="n">
         <v>180</v>
       </c>
-      <c r="G265">
+      <c r="G265" s="0" t="n">
         <v>190</v>
       </c>
-      <c r="H265">
+      <c r="H265" s="0" t="n">
         <v>295</v>
       </c>
     </row>
-    <row r="266" spans="1:8">
-      <c r="A266" s="5">
+    <row r="266" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A266" s="1" t="n">
         <v>46193</v>
       </c>
-      <c r="E266">
+      <c r="E266" s="0" t="n">
         <v>145</v>
       </c>
-      <c r="F266">
+      <c r="F266" s="0" t="n">
         <v>125</v>
       </c>
-      <c r="G266">
+      <c r="G266" s="0" t="n">
         <v>280</v>
       </c>
-      <c r="H266">
+      <c r="H266" s="0" t="n">
         <v>240</v>
       </c>
     </row>
-    <row r="267" spans="1:8">
-      <c r="A267" s="5">
+    <row r="267" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A267" s="1" t="n">
         <v>46194</v>
       </c>
-      <c r="E267">
+      <c r="E267" s="0" t="n">
         <v>345</v>
       </c>
-      <c r="F267">
+      <c r="F267" s="0" t="n">
         <v>185</v>
       </c>
-      <c r="G267">
+      <c r="G267" s="0" t="n">
         <v>115</v>
       </c>
-      <c r="H267">
+      <c r="H267" s="0" t="n">
         <v>300</v>
       </c>
     </row>
-    <row r="268" spans="1:8">
-      <c r="A268" s="5">
+    <row r="268" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A268" s="1" t="n">
         <v>46207</v>
       </c>
-      <c r="E268">
+      <c r="E268" s="0" t="n">
         <v>275</v>
       </c>
-      <c r="F268">
+      <c r="F268" s="0" t="n">
         <v>150</v>
       </c>
-      <c r="G268">
+      <c r="G268" s="0" t="n">
         <v>300</v>
       </c>
-      <c r="H268">
+      <c r="H268" s="0" t="n">
         <v>175</v>
       </c>
     </row>
-    <row r="269" spans="1:8">
-      <c r="A269" s="5">
+    <row r="269" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A269" s="1" t="n">
         <v>46207</v>
       </c>
-      <c r="E269">
+      <c r="E269" s="0" t="n">
         <v>180</v>
       </c>
-      <c r="F269">
+      <c r="F269" s="0" t="n">
         <v>360</v>
       </c>
-      <c r="G269">
+      <c r="G269" s="0" t="n">
         <v>190</v>
       </c>
-      <c r="H269">
+      <c r="H269" s="0" t="n">
         <v>435</v>
       </c>
     </row>
-    <row r="270" spans="1:8">
-      <c r="A270" s="5">
+    <row r="270" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A270" s="1" t="n">
         <v>46214</v>
       </c>
-      <c r="E270">
+      <c r="E270" s="0" t="n">
         <v>285</v>
       </c>
-      <c r="F270">
+      <c r="F270" s="0" t="n">
         <v>105</v>
       </c>
-      <c r="G270">
+      <c r="G270" s="0" t="n">
         <v>410</v>
       </c>
-      <c r="H270">
+      <c r="H270" s="0" t="n">
         <v>380</v>
       </c>
     </row>
-    <row r="271" spans="1:8">
-      <c r="A271" s="5">
+    <row r="271" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A271" s="1" t="n">
         <v>46214</v>
       </c>
-      <c r="E271">
+      <c r="E271" s="0" t="n">
         <v>85</v>
       </c>
-      <c r="F271">
+      <c r="F271" s="0" t="n">
         <v>240</v>
       </c>
-      <c r="G271">
+      <c r="G271" s="0" t="n">
         <v>245</v>
       </c>
-      <c r="H271">
+      <c r="H271" s="0" t="n">
         <v>335</v>
       </c>
     </row>
-    <row r="272" spans="1:8">
-      <c r="A272" s="5">
+    <row r="272" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A272" s="1" t="n">
         <v>46220</v>
       </c>
-      <c r="C272">
+      <c r="C272" s="0" t="n">
         <v>40</v>
       </c>
-      <c r="D272">
+      <c r="D272" s="0" t="n">
         <v>370</v>
       </c>
-      <c r="G272">
+      <c r="G272" s="0" t="n">
         <v>320</v>
       </c>
-      <c r="H272">
+      <c r="H272" s="0" t="n">
         <v>175</v>
       </c>
     </row>
-    <row r="273" spans="1:8">
-      <c r="A273" s="5">
+    <row r="273" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A273" s="1" t="n">
         <v>46230</v>
       </c>
-      <c r="C273">
+      <c r="C273" s="0" t="n">
         <v>415</v>
       </c>
-      <c r="E273">
+      <c r="E273" s="0" t="n">
         <v>240</v>
       </c>
-      <c r="F273">
+      <c r="F273" s="0" t="n">
         <v>290</v>
       </c>
-      <c r="G273">
+      <c r="G273" s="0" t="n">
         <v>315</v>
       </c>
-      <c r="H273">
+      <c r="H273" s="0" t="n">
         <v>125</v>
       </c>
     </row>
-    <row r="274" spans="1:8">
-      <c r="A274" s="5">
+    <row r="274" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A274" s="1" t="n">
         <v>46230</v>
       </c>
-      <c r="C274">
+      <c r="C274" s="0" t="n">
         <v>200</v>
       </c>
-      <c r="E274">
+      <c r="E274" s="0" t="n">
         <v>160</v>
       </c>
-      <c r="F274">
+      <c r="F274" s="0" t="n">
         <v>500</v>
       </c>
-      <c r="G274">
+      <c r="G274" s="0" t="n">
         <v>360</v>
       </c>
-      <c r="H274">
+      <c r="H274" s="0" t="n">
         <v>185</v>
       </c>
     </row>
-    <row r="275" spans="1:8">
-      <c r="A275" s="5">
+    <row r="275" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A275" s="1" t="n">
         <v>46235</v>
       </c>
-      <c r="E275">
+      <c r="E275" s="0" t="n">
         <v>45</v>
       </c>
-      <c r="F275">
+      <c r="F275" s="0" t="n">
         <v>320</v>
       </c>
-      <c r="G275">
+      <c r="G275" s="0" t="n">
         <v>380</v>
       </c>
-      <c r="H275">
+      <c r="H275" s="0" t="n">
         <v>380</v>
       </c>
     </row>
-    <row r="276" spans="1:8">
-      <c r="A276" s="5">
+    <row r="276" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A276" s="1" t="n">
         <v>46235</v>
       </c>
-      <c r="E276">
+      <c r="E276" s="0" t="n">
         <v>225</v>
       </c>
-      <c r="F276">
+      <c r="F276" s="0" t="n">
         <v>135</v>
       </c>
-      <c r="G276">
+      <c r="G276" s="0" t="n">
         <v>285</v>
       </c>
-      <c r="H276">
+      <c r="H276" s="0" t="n">
         <v>40</v>
       </c>
     </row>
-    <row r="277" spans="1:8">
-      <c r="A277" s="5">
+    <row r="277" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A277" s="1" t="n">
         <v>46236</v>
       </c>
-      <c r="E277">
+      <c r="E277" s="0" t="n">
         <v>270</v>
       </c>
-      <c r="F277">
+      <c r="F277" s="0" t="n">
         <v>330</v>
       </c>
-      <c r="G277">
+      <c r="G277" s="0" t="n">
         <v>330</v>
       </c>
-      <c r="H277">
+      <c r="H277" s="0" t="n">
         <v>540</v>
       </c>
     </row>
-    <row r="278" spans="1:8">
-      <c r="A278" s="5">
+    <row r="278" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A278" s="1" t="n">
         <v>46256</v>
       </c>
-      <c r="C278">
+      <c r="C278" s="0" t="n">
         <v>200</v>
       </c>
-      <c r="E278">
+      <c r="E278" s="0" t="n">
         <v>305</v>
       </c>
-      <c r="F278">
+      <c r="F278" s="0" t="n">
         <v>420</v>
       </c>
-      <c r="G278">
+      <c r="G278" s="0" t="n">
         <v>130</v>
       </c>
-      <c r="H278">
+      <c r="H278" s="0" t="n">
         <v>175</v>
       </c>
     </row>
-    <row r="279" spans="1:8">
-      <c r="A279" s="5">
+    <row r="279" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A279" s="1" t="n">
         <v>46256</v>
       </c>
-      <c r="C279">
+      <c r="C279" s="0" t="n">
         <v>220</v>
       </c>
-      <c r="E279">
+      <c r="E279" s="0" t="n">
         <v>390</v>
       </c>
-      <c r="F279">
+      <c r="F279" s="0" t="n">
         <v>425</v>
       </c>
-      <c r="G279">
+      <c r="G279" s="0" t="n">
         <v>215</v>
       </c>
-      <c r="H279">
+      <c r="H279" s="0" t="n">
         <v>355</v>
       </c>
     </row>
-    <row r="280" spans="1:8">
-      <c r="A280" s="5">
+    <row r="280" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A280" s="1" t="n">
         <v>46267</v>
       </c>
-      <c r="E280">
+      <c r="E280" s="0" t="n">
         <v>240</v>
       </c>
-      <c r="F280">
+      <c r="F280" s="0" t="n">
         <v>310</v>
       </c>
-      <c r="G280">
+      <c r="G280" s="0" t="n">
         <v>260</v>
       </c>
-      <c r="H280">
+      <c r="H280" s="0" t="n">
         <v>315</v>
       </c>
     </row>
-    <row r="281" spans="1:8">
-      <c r="A281" s="5">
+    <row r="281" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A281" s="1" t="n">
         <v>46271</v>
       </c>
-      <c r="E281">
+      <c r="E281" s="0" t="n">
         <v>25</v>
       </c>
-      <c r="F281">
+      <c r="F281" s="0" t="n">
         <v>395</v>
       </c>
-      <c r="G281">
+      <c r="G281" s="0" t="n">
         <v>290</v>
       </c>
-      <c r="H281">
+      <c r="H281" s="0" t="n">
         <v>385</v>
       </c>
     </row>
-    <row r="282" spans="1:8">
-      <c r="A282" s="5">
+    <row r="282" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A282" s="1" t="n">
         <v>46272</v>
       </c>
-      <c r="E282">
+      <c r="E282" s="0" t="n">
         <v>320</v>
       </c>
-      <c r="F282">
+      <c r="F282" s="0" t="n">
         <v>420</v>
       </c>
-      <c r="G282">
+      <c r="G282" s="0" t="n">
         <v>245</v>
       </c>
-      <c r="H282">
+      <c r="H282" s="0" t="n">
         <v>70</v>
       </c>
     </row>
-    <row r="283" spans="1:8">
-      <c r="A283" s="5">
+    <row r="283" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A283" s="1" t="n">
         <v>46273</v>
       </c>
-      <c r="E283">
+      <c r="E283" s="0" t="n">
         <v>275</v>
       </c>
-      <c r="F283">
+      <c r="F283" s="0" t="n">
         <v>365</v>
       </c>
-      <c r="G283">
+      <c r="G283" s="0" t="n">
         <v>135</v>
       </c>
-      <c r="H283">
+      <c r="H283" s="0" t="n">
         <v>435</v>
       </c>
     </row>
-    <row r="284" spans="1:8">
-      <c r="A284" s="5">
+    <row r="284" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A284" s="1" t="n">
         <v>46274</v>
       </c>
-      <c r="E284">
+      <c r="E284" s="0" t="n">
         <v>80</v>
       </c>
-      <c r="F284">
+      <c r="F284" s="0" t="n">
         <v>340</v>
       </c>
-      <c r="G284">
+      <c r="G284" s="0" t="n">
         <v>230</v>
       </c>
-      <c r="H284">
+      <c r="H284" s="0" t="n">
         <v>305</v>
       </c>
     </row>
-    <row r="285" spans="1:8">
-      <c r="A285" s="5">
+    <row r="285" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A285" s="1" t="n">
         <v>46275</v>
       </c>
-      <c r="E285">
+      <c r="E285" s="0" t="n">
         <v>320</v>
       </c>
-      <c r="F285">
+      <c r="F285" s="0" t="n">
         <v>450</v>
       </c>
-      <c r="G285">
+      <c r="G285" s="0" t="n">
         <v>75</v>
       </c>
-      <c r="H285">
+      <c r="H285" s="0" t="n">
         <v>150</v>
       </c>
     </row>
-    <row r="286" spans="1:8">
-      <c r="A286" s="5">
+    <row r="286" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A286" s="1" t="n">
         <v>46276</v>
       </c>
-      <c r="E286">
+      <c r="E286" s="0" t="n">
         <v>225</v>
       </c>
-      <c r="F286">
+      <c r="F286" s="0" t="n">
         <v>425</v>
       </c>
-      <c r="G286">
+      <c r="G286" s="0" t="n">
         <v>100</v>
       </c>
-      <c r="H286">
+      <c r="H286" s="0" t="n">
         <v>250</v>
       </c>
     </row>
-    <row r="287" spans="1:8">
-      <c r="A287" s="5">
+    <row r="287" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A287" s="1" t="n">
         <v>46277</v>
       </c>
-      <c r="E287">
+      <c r="E287" s="0" t="n">
         <v>345</v>
       </c>
-      <c r="F287">
+      <c r="F287" s="0" t="n">
         <v>310</v>
       </c>
-      <c r="G287">
+      <c r="G287" s="0" t="n">
         <v>215</v>
       </c>
-      <c r="H287">
+      <c r="H287" s="0" t="n">
         <v>245</v>
       </c>
     </row>
-    <row r="288" spans="1:8">
-      <c r="A288" s="5">
+    <row r="288" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A288" s="1" t="n">
         <v>46291</v>
       </c>
-      <c r="E288">
+      <c r="E288" s="0" t="n">
         <v>210</v>
       </c>
-      <c r="F288">
+      <c r="F288" s="0" t="n">
         <v>160</v>
       </c>
-      <c r="G288">
+      <c r="G288" s="0" t="n">
         <v>250</v>
       </c>
-      <c r="H288">
+      <c r="H288" s="0" t="n">
         <v>225</v>
       </c>
     </row>
-    <row r="289" spans="1:8">
-      <c r="A289" s="5">
+    <row r="289" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A289" s="1" t="n">
         <v>46298</v>
       </c>
-      <c r="E289">
+      <c r="E289" s="0" t="n">
         <v>180</v>
       </c>
-      <c r="F289">
+      <c r="F289" s="0" t="n">
         <v>115</v>
       </c>
-      <c r="G289">
+      <c r="G289" s="0" t="n">
         <v>105</v>
       </c>
-      <c r="H289">
+      <c r="H289" s="0" t="n">
         <v>360</v>
+      </c>
+    </row>
+    <row r="290" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A290" s="1" t="n">
+        <v>46305</v>
+      </c>
+      <c r="C290" s="0" t="n">
+        <v>175</v>
+      </c>
+      <c r="D290" s="0" t="n">
+        <v>265</v>
+      </c>
+      <c r="G290" s="0" t="n">
+        <v>60</v>
+      </c>
+      <c r="H290" s="0" t="n">
+        <v>380</v>
+      </c>
+    </row>
+    <row r="291" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A291" s="1" t="n">
+        <v>46312</v>
+      </c>
+      <c r="C291" s="0" t="n">
+        <v>205</v>
+      </c>
+      <c r="E291" s="0" t="n">
+        <v>395</v>
+      </c>
+      <c r="F291" s="0" t="n">
+        <v>230</v>
+      </c>
+      <c r="G291" s="0" t="n">
+        <v>320</v>
+      </c>
+      <c r="H291" s="0" t="n">
+        <v>395</v>
       </c>
     </row>
   </sheetData>
   <conditionalFormatting sqref="J134:J1048576 J1:J132">
-    <cfRule type="colorScale" priority="21">
+    <cfRule type="colorScale" priority="2">
       <colorScale>
-        <cfvo type="min"/>
+        <cfvo type="min" val="0"/>
         <cfvo type="percentile" val="50"/>
-        <cfvo type="max"/>
+        <cfvo type="max" val="0"/>
         <color rgb="FF63BE7B"/>
         <color rgb="FFFFEB84"/>
         <color rgb="FFF8696B"/>
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup orientation="portrait" horizontalDpi="0" verticalDpi="0" r:id="rId1"/>
+  <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.511811023622047" footer="0.511811023622047"/>
+  <pageSetup paperSize="1" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" horizontalDpi="300" verticalDpi="300" copies="1"/>
+  <headerFooter differentFirst="false" differentOddEven="false">
+    <oddHeader/>
+    <oddFooter/>
+  </headerFooter>
 </worksheet>
 </file>
--- a/docs/Cottage Rummy Data File.xlsx
+++ b/docs/Cottage Rummy Data File.xlsx
@@ -129,40 +129,44 @@
     <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
   </cellStyleXfs>
-  <cellXfs count="9">
+  <cellXfs count="10">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="165" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="165" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="right" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="166" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="166" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="right" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -363,97 +367,97 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:AKI291"/>
+  <dimension ref="A1:AKI292"/>
   <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="14.25" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="10.29"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="10" min="10" style="0" width="15.71"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="10" min="10" style="2" width="15.71"/>
   </cols>
   <sheetData>
-    <row r="1" s="4" customFormat="true" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A1" s="2" t="s">
+    <row r="1" s="5" customFormat="true" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A1" s="3" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="3" t="s">
+      <c r="B1" s="4" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="3" t="s">
+      <c r="C1" s="4" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="3" t="s">
+      <c r="D1" s="4" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="3" t="s">
+      <c r="E1" s="4" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="3" t="s">
+      <c r="F1" s="4" t="s">
         <v>5</v>
       </c>
-      <c r="G1" s="3" t="s">
+      <c r="G1" s="4" t="s">
         <v>6</v>
       </c>
-      <c r="H1" s="3" t="s">
+      <c r="H1" s="4" t="s">
         <v>7</v>
       </c>
-      <c r="J1" s="3"/>
-    </row>
-    <row r="2" s="4" customFormat="true" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A2" s="5" t="n">
+      <c r="J1" s="4"/>
+    </row>
+    <row r="2" s="5" customFormat="true" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A2" s="6" t="n">
         <v>44580</v>
       </c>
-      <c r="B2" s="6" t="n">
+      <c r="B2" s="7" t="n">
         <v>225</v>
       </c>
-      <c r="C2" s="6" t="n">
+      <c r="C2" s="7" t="n">
         <v>390</v>
       </c>
-      <c r="D2" s="6"/>
-      <c r="E2" s="6"/>
-      <c r="F2" s="6"/>
-      <c r="G2" s="6" t="n">
+      <c r="D2" s="7"/>
+      <c r="E2" s="7"/>
+      <c r="F2" s="7"/>
+      <c r="G2" s="7" t="n">
         <v>290</v>
       </c>
-      <c r="H2" s="6" t="n">
+      <c r="H2" s="7" t="n">
         <v>5</v>
       </c>
     </row>
-    <row r="3" s="4" customFormat="true" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A3" s="5" t="n">
+    <row r="3" s="5" customFormat="true" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A3" s="6" t="n">
         <v>44580</v>
       </c>
-      <c r="B3" s="6"/>
-      <c r="C3" s="6" t="n">
+      <c r="B3" s="7"/>
+      <c r="C3" s="7" t="n">
         <v>155</v>
       </c>
-      <c r="D3" s="6" t="n">
+      <c r="D3" s="7" t="n">
         <v>185</v>
       </c>
-      <c r="E3" s="6"/>
-      <c r="F3" s="6"/>
-      <c r="G3" s="6" t="n">
+      <c r="E3" s="7"/>
+      <c r="F3" s="7"/>
+      <c r="G3" s="7" t="n">
         <v>310</v>
       </c>
-      <c r="H3" s="6" t="n">
+      <c r="H3" s="7" t="n">
         <v>295</v>
       </c>
     </row>
-    <row r="4" s="4" customFormat="true" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A4" s="5" t="n">
+    <row r="4" s="5" customFormat="true" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A4" s="6" t="n">
         <v>44580</v>
       </c>
-      <c r="B4" s="6"/>
-      <c r="C4" s="6" t="n">
+      <c r="B4" s="7"/>
+      <c r="C4" s="7" t="n">
         <v>380</v>
       </c>
-      <c r="D4" s="6" t="n">
+      <c r="D4" s="7" t="n">
         <v>100</v>
       </c>
-      <c r="E4" s="6"/>
-      <c r="F4" s="6"/>
-      <c r="G4" s="6" t="n">
+      <c r="E4" s="7"/>
+      <c r="F4" s="7"/>
+      <c r="G4" s="7" t="n">
         <v>215</v>
       </c>
-      <c r="H4" s="6" t="n">
+      <c r="H4" s="7" t="n">
         <v>195</v>
       </c>
     </row>
@@ -461,19 +465,19 @@
       <c r="A5" s="1" t="n">
         <v>44617</v>
       </c>
-      <c r="B5" s="0" t="n">
+      <c r="B5" s="2" t="n">
         <v>310</v>
       </c>
-      <c r="C5" s="0" t="n">
+      <c r="C5" s="2" t="n">
         <v>260</v>
       </c>
-      <c r="D5" s="0" t="n">
+      <c r="D5" s="2" t="n">
         <v>255</v>
       </c>
-      <c r="G5" s="0" t="n">
+      <c r="G5" s="2" t="n">
         <v>290</v>
       </c>
-      <c r="H5" s="0" t="n">
+      <c r="H5" s="2" t="n">
         <v>235</v>
       </c>
     </row>
@@ -481,22 +485,22 @@
       <c r="A6" s="1" t="n">
         <v>44618</v>
       </c>
-      <c r="C6" s="0" t="n">
+      <c r="C6" s="2" t="n">
         <v>325</v>
       </c>
-      <c r="D6" s="0" t="n">
+      <c r="D6" s="2" t="n">
         <v>595</v>
       </c>
-      <c r="E6" s="0" t="n">
+      <c r="E6" s="2" t="n">
         <v>200</v>
       </c>
-      <c r="F6" s="0" t="n">
+      <c r="F6" s="2" t="n">
         <v>170</v>
       </c>
-      <c r="G6" s="0" t="n">
+      <c r="G6" s="2" t="n">
         <v>390</v>
       </c>
-      <c r="H6" s="0" t="n">
+      <c r="H6" s="2" t="n">
         <v>520</v>
       </c>
     </row>
@@ -504,16 +508,16 @@
       <c r="A7" s="1" t="n">
         <v>44627</v>
       </c>
-      <c r="C7" s="0" t="n">
+      <c r="C7" s="2" t="n">
         <v>65</v>
       </c>
-      <c r="D7" s="0" t="n">
+      <c r="D7" s="2" t="n">
         <v>435</v>
       </c>
-      <c r="G7" s="0" t="n">
+      <c r="G7" s="2" t="n">
         <v>215</v>
       </c>
-      <c r="H7" s="0" t="n">
+      <c r="H7" s="2" t="n">
         <v>305</v>
       </c>
     </row>
@@ -521,25 +525,25 @@
       <c r="A8" s="1" t="n">
         <v>44632</v>
       </c>
-      <c r="B8" s="0" t="n">
+      <c r="B8" s="2" t="n">
         <v>570</v>
       </c>
-      <c r="C8" s="0" t="n">
+      <c r="C8" s="2" t="n">
         <v>285</v>
       </c>
-      <c r="D8" s="0" t="n">
+      <c r="D8" s="2" t="n">
         <v>555</v>
       </c>
-      <c r="E8" s="0" t="n">
+      <c r="E8" s="2" t="n">
         <v>205</v>
       </c>
-      <c r="F8" s="0" t="n">
+      <c r="F8" s="2" t="n">
         <v>330</v>
       </c>
-      <c r="G8" s="0" t="n">
+      <c r="G8" s="2" t="n">
         <v>280</v>
       </c>
-      <c r="H8" s="0" t="n">
+      <c r="H8" s="2" t="n">
         <v>375</v>
       </c>
     </row>
@@ -547,25 +551,25 @@
       <c r="A9" s="1" t="n">
         <v>44635</v>
       </c>
-      <c r="B9" s="0" t="n">
+      <c r="B9" s="2" t="n">
         <v>240</v>
       </c>
-      <c r="C9" s="0" t="n">
+      <c r="C9" s="2" t="n">
         <v>295</v>
       </c>
-      <c r="D9" s="0" t="n">
+      <c r="D9" s="2" t="n">
         <v>525</v>
       </c>
-      <c r="E9" s="0" t="n">
+      <c r="E9" s="2" t="n">
         <v>645</v>
       </c>
-      <c r="F9" s="0" t="n">
+      <c r="F9" s="2" t="n">
         <v>130</v>
       </c>
-      <c r="G9" s="0" t="n">
+      <c r="G9" s="2" t="n">
         <v>325</v>
       </c>
-      <c r="H9" s="0" t="n">
+      <c r="H9" s="2" t="n">
         <v>495</v>
       </c>
     </row>
@@ -573,25 +577,25 @@
       <c r="A10" s="1" t="n">
         <v>44636</v>
       </c>
-      <c r="B10" s="0" t="n">
+      <c r="B10" s="2" t="n">
         <v>300</v>
       </c>
-      <c r="C10" s="0" t="n">
+      <c r="C10" s="2" t="n">
         <v>400</v>
       </c>
-      <c r="D10" s="0" t="n">
+      <c r="D10" s="2" t="n">
         <v>210</v>
       </c>
-      <c r="E10" s="0" t="n">
+      <c r="E10" s="2" t="n">
         <v>525</v>
       </c>
-      <c r="F10" s="0" t="n">
+      <c r="F10" s="2" t="n">
         <v>545</v>
       </c>
-      <c r="G10" s="0" t="n">
+      <c r="G10" s="2" t="n">
         <v>100</v>
       </c>
-      <c r="H10" s="0" t="n">
+      <c r="H10" s="2" t="n">
         <v>425</v>
       </c>
     </row>
@@ -599,25 +603,25 @@
       <c r="A11" s="1" t="n">
         <v>44637</v>
       </c>
-      <c r="B11" s="0" t="n">
+      <c r="B11" s="2" t="n">
         <v>405</v>
       </c>
-      <c r="C11" s="0" t="n">
+      <c r="C11" s="2" t="n">
         <v>405</v>
       </c>
-      <c r="D11" s="0" t="n">
+      <c r="D11" s="2" t="n">
         <v>515</v>
       </c>
-      <c r="E11" s="0" t="n">
+      <c r="E11" s="2" t="n">
         <v>175</v>
       </c>
-      <c r="F11" s="0" t="n">
+      <c r="F11" s="2" t="n">
         <v>370</v>
       </c>
-      <c r="G11" s="0" t="n">
+      <c r="G11" s="2" t="n">
         <v>155</v>
       </c>
-      <c r="H11" s="0" t="n">
+      <c r="H11" s="2" t="n">
         <v>435</v>
       </c>
     </row>
@@ -625,22 +629,22 @@
       <c r="A12" s="1" t="n">
         <v>44666</v>
       </c>
-      <c r="C12" s="0" t="n">
+      <c r="C12" s="2" t="n">
         <v>295</v>
       </c>
-      <c r="D12" s="0" t="n">
+      <c r="D12" s="2" t="n">
         <v>610</v>
       </c>
-      <c r="E12" s="0" t="n">
+      <c r="E12" s="2" t="n">
         <v>240</v>
       </c>
-      <c r="F12" s="0" t="n">
+      <c r="F12" s="2" t="n">
         <v>425</v>
       </c>
-      <c r="G12" s="0" t="n">
+      <c r="G12" s="2" t="n">
         <v>455</v>
       </c>
-      <c r="H12" s="0" t="n">
+      <c r="H12" s="2" t="n">
         <v>460</v>
       </c>
     </row>
@@ -648,25 +652,25 @@
       <c r="A13" s="1" t="n">
         <v>44667</v>
       </c>
-      <c r="B13" s="0" t="n">
+      <c r="B13" s="2" t="n">
         <v>245</v>
       </c>
-      <c r="C13" s="0" t="n">
+      <c r="C13" s="2" t="n">
         <v>400</v>
       </c>
-      <c r="D13" s="0" t="n">
+      <c r="D13" s="2" t="n">
         <v>525</v>
       </c>
-      <c r="E13" s="0" t="n">
+      <c r="E13" s="2" t="n">
         <v>295</v>
       </c>
-      <c r="F13" s="0" t="n">
+      <c r="F13" s="2" t="n">
         <v>580</v>
       </c>
-      <c r="G13" s="0" t="n">
+      <c r="G13" s="2" t="n">
         <v>415</v>
       </c>
-      <c r="H13" s="0" t="n">
+      <c r="H13" s="2" t="n">
         <v>220</v>
       </c>
     </row>
@@ -674,22 +678,22 @@
       <c r="A14" s="1" t="n">
         <v>44681</v>
       </c>
-      <c r="B14" s="0" t="n">
+      <c r="B14" s="2" t="n">
         <v>335</v>
       </c>
-      <c r="C14" s="0" t="n">
+      <c r="C14" s="2" t="n">
         <v>280</v>
       </c>
-      <c r="D14" s="0" t="n">
+      <c r="D14" s="2" t="n">
         <v>435</v>
       </c>
-      <c r="E14" s="0" t="n">
+      <c r="E14" s="2" t="n">
         <v>260</v>
       </c>
-      <c r="G14" s="0" t="n">
+      <c r="G14" s="2" t="n">
         <v>365</v>
       </c>
-      <c r="H14" s="0" t="n">
+      <c r="H14" s="2" t="n">
         <v>410</v>
       </c>
     </row>
@@ -697,19 +701,19 @@
       <c r="A15" s="1" t="n">
         <v>44688</v>
       </c>
-      <c r="C15" s="0" t="n">
+      <c r="C15" s="2" t="n">
         <v>300</v>
       </c>
-      <c r="E15" s="0" t="n">
+      <c r="E15" s="2" t="n">
         <v>375</v>
       </c>
-      <c r="F15" s="0" t="n">
+      <c r="F15" s="2" t="n">
         <v>35</v>
       </c>
-      <c r="G15" s="0" t="n">
+      <c r="G15" s="2" t="n">
         <v>195</v>
       </c>
-      <c r="H15" s="0" t="n">
+      <c r="H15" s="2" t="n">
         <v>210</v>
       </c>
     </row>
@@ -717,16 +721,16 @@
       <c r="A16" s="1" t="n">
         <v>44695</v>
       </c>
-      <c r="E16" s="0" t="n">
+      <c r="E16" s="2" t="n">
         <v>270</v>
       </c>
-      <c r="F16" s="0" t="n">
+      <c r="F16" s="2" t="n">
         <v>495</v>
       </c>
-      <c r="G16" s="0" t="n">
+      <c r="G16" s="2" t="n">
         <v>80</v>
       </c>
-      <c r="H16" s="0" t="n">
+      <c r="H16" s="2" t="n">
         <v>385</v>
       </c>
     </row>
@@ -734,19 +738,19 @@
       <c r="A17" s="1" t="n">
         <v>44842</v>
       </c>
-      <c r="B17" s="0" t="n">
+      <c r="B17" s="2" t="n">
         <v>490</v>
       </c>
-      <c r="C17" s="0" t="n">
+      <c r="C17" s="2" t="n">
         <v>150</v>
       </c>
-      <c r="D17" s="0" t="n">
+      <c r="D17" s="2" t="n">
         <v>505</v>
       </c>
-      <c r="G17" s="0" t="n">
+      <c r="G17" s="2" t="n">
         <v>255</v>
       </c>
-      <c r="H17" s="0" t="n">
+      <c r="H17" s="2" t="n">
         <v>80</v>
       </c>
     </row>
@@ -754,19 +758,19 @@
       <c r="A18" s="1" t="n">
         <v>44849</v>
       </c>
-      <c r="C18" s="0" t="n">
+      <c r="C18" s="2" t="n">
         <v>415</v>
       </c>
-      <c r="E18" s="0" t="n">
+      <c r="E18" s="2" t="n">
         <v>155</v>
       </c>
-      <c r="F18" s="0" t="n">
+      <c r="F18" s="2" t="n">
         <v>305</v>
       </c>
-      <c r="G18" s="0" t="n">
+      <c r="G18" s="2" t="n">
         <v>145</v>
       </c>
-      <c r="H18" s="0" t="n">
+      <c r="H18" s="2" t="n">
         <v>450</v>
       </c>
     </row>
@@ -774,19 +778,19 @@
       <c r="A19" s="1" t="n">
         <v>44877</v>
       </c>
-      <c r="C19" s="0" t="n">
+      <c r="C19" s="2" t="n">
         <v>215</v>
       </c>
-      <c r="E19" s="0" t="n">
+      <c r="E19" s="2" t="n">
         <v>310</v>
       </c>
-      <c r="F19" s="0" t="n">
+      <c r="F19" s="2" t="n">
         <v>385</v>
       </c>
-      <c r="G19" s="0" t="n">
+      <c r="G19" s="2" t="n">
         <v>190</v>
       </c>
-      <c r="H19" s="0" t="n">
+      <c r="H19" s="2" t="n">
         <v>120</v>
       </c>
     </row>
@@ -794,16 +798,16 @@
       <c r="A20" s="1" t="n">
         <v>44884</v>
       </c>
-      <c r="B20" s="0" t="n">
+      <c r="B20" s="2" t="n">
         <v>205</v>
       </c>
-      <c r="C20" s="0" t="n">
+      <c r="C20" s="2" t="n">
         <v>265</v>
       </c>
-      <c r="G20" s="0" t="n">
+      <c r="G20" s="2" t="n">
         <v>265</v>
       </c>
-      <c r="H20" s="0" t="n">
+      <c r="H20" s="2" t="n">
         <v>185</v>
       </c>
     </row>
@@ -811,16 +815,16 @@
       <c r="A21" s="1" t="n">
         <v>44884</v>
       </c>
-      <c r="B21" s="0" t="n">
+      <c r="B21" s="2" t="n">
         <v>400</v>
       </c>
-      <c r="C21" s="0" t="n">
+      <c r="C21" s="2" t="n">
         <v>420</v>
       </c>
-      <c r="G21" s="0" t="n">
+      <c r="G21" s="2" t="n">
         <v>120</v>
       </c>
-      <c r="H21" s="0" t="n">
+      <c r="H21" s="2" t="n">
         <v>200</v>
       </c>
     </row>
@@ -828,16 +832,16 @@
       <c r="A22" s="1" t="n">
         <v>44905</v>
       </c>
-      <c r="B22" s="0" t="n">
+      <c r="B22" s="2" t="n">
         <v>180</v>
       </c>
-      <c r="C22" s="0" t="n">
+      <c r="C22" s="2" t="n">
         <v>170</v>
       </c>
-      <c r="E22" s="0" t="n">
+      <c r="E22" s="2" t="n">
         <v>115</v>
       </c>
-      <c r="F22" s="0" t="n">
+      <c r="F22" s="2" t="n">
         <v>515</v>
       </c>
     </row>
@@ -845,25 +849,25 @@
       <c r="A23" s="1" t="n">
         <v>44919</v>
       </c>
-      <c r="B23" s="0" t="n">
+      <c r="B23" s="2" t="n">
         <v>390</v>
       </c>
-      <c r="C23" s="0" t="n">
+      <c r="C23" s="2" t="n">
         <v>320</v>
       </c>
-      <c r="D23" s="0" t="n">
+      <c r="D23" s="2" t="n">
         <v>315</v>
       </c>
-      <c r="E23" s="0" t="n">
+      <c r="E23" s="2" t="n">
         <v>325</v>
       </c>
-      <c r="F23" s="0" t="n">
+      <c r="F23" s="2" t="n">
         <v>270</v>
       </c>
-      <c r="G23" s="0" t="n">
+      <c r="G23" s="2" t="n">
         <v>380</v>
       </c>
-      <c r="H23" s="0" t="n">
+      <c r="H23" s="2" t="n">
         <v>385</v>
       </c>
     </row>
@@ -871,25 +875,25 @@
       <c r="A24" s="1" t="n">
         <v>44920</v>
       </c>
-      <c r="B24" s="0" t="n">
+      <c r="B24" s="2" t="n">
         <v>350</v>
       </c>
-      <c r="C24" s="0" t="n">
+      <c r="C24" s="2" t="n">
         <v>490</v>
       </c>
-      <c r="D24" s="0" t="n">
+      <c r="D24" s="2" t="n">
         <v>130</v>
       </c>
-      <c r="E24" s="0" t="n">
+      <c r="E24" s="2" t="n">
         <v>430</v>
       </c>
-      <c r="F24" s="0" t="n">
+      <c r="F24" s="2" t="n">
         <v>285</v>
       </c>
-      <c r="G24" s="0" t="n">
+      <c r="G24" s="2" t="n">
         <v>340</v>
       </c>
-      <c r="H24" s="0" t="n">
+      <c r="H24" s="2" t="n">
         <v>590</v>
       </c>
     </row>
@@ -897,25 +901,25 @@
       <c r="A25" s="1" t="n">
         <v>44921</v>
       </c>
-      <c r="B25" s="0" t="n">
+      <c r="B25" s="2" t="n">
         <v>145</v>
       </c>
-      <c r="C25" s="0" t="n">
+      <c r="C25" s="2" t="n">
         <v>285</v>
       </c>
-      <c r="D25" s="0" t="n">
+      <c r="D25" s="2" t="n">
         <v>390</v>
       </c>
-      <c r="E25" s="0" t="n">
+      <c r="E25" s="2" t="n">
         <v>505</v>
       </c>
-      <c r="F25" s="0" t="n">
+      <c r="F25" s="2" t="n">
         <v>485</v>
       </c>
-      <c r="G25" s="0" t="n">
+      <c r="G25" s="2" t="n">
         <v>280</v>
       </c>
-      <c r="H25" s="0" t="n">
+      <c r="H25" s="2" t="n">
         <v>380</v>
       </c>
     </row>
@@ -923,19 +927,19 @@
       <c r="A26" s="1" t="n">
         <v>44923</v>
       </c>
-      <c r="B26" s="0" t="n">
+      <c r="B26" s="2" t="n">
         <v>435</v>
       </c>
-      <c r="C26" s="0" t="n">
+      <c r="C26" s="2" t="n">
         <v>255</v>
       </c>
-      <c r="D26" s="0" t="n">
+      <c r="D26" s="2" t="n">
         <v>405</v>
       </c>
-      <c r="G26" s="0" t="n">
+      <c r="G26" s="2" t="n">
         <v>440</v>
       </c>
-      <c r="H26" s="0" t="n">
+      <c r="H26" s="2" t="n">
         <v>370</v>
       </c>
     </row>
@@ -943,25 +947,25 @@
       <c r="A27" s="1" t="n">
         <v>44924</v>
       </c>
-      <c r="B27" s="0" t="n">
+      <c r="B27" s="2" t="n">
         <v>425</v>
       </c>
-      <c r="C27" s="0" t="n">
+      <c r="C27" s="2" t="n">
         <v>200</v>
       </c>
-      <c r="D27" s="0" t="n">
+      <c r="D27" s="2" t="n">
         <v>520</v>
       </c>
-      <c r="E27" s="0" t="n">
+      <c r="E27" s="2" t="n">
         <v>365</v>
       </c>
-      <c r="F27" s="0" t="n">
+      <c r="F27" s="2" t="n">
         <v>275</v>
       </c>
-      <c r="G27" s="0" t="n">
+      <c r="G27" s="2" t="n">
         <v>305</v>
       </c>
-      <c r="H27" s="0" t="n">
+      <c r="H27" s="2" t="n">
         <v>390</v>
       </c>
     </row>
@@ -969,25 +973,25 @@
       <c r="A28" s="1" t="n">
         <v>44925</v>
       </c>
-      <c r="B28" s="0" t="n">
+      <c r="B28" s="2" t="n">
         <v>215</v>
       </c>
-      <c r="C28" s="0" t="n">
+      <c r="C28" s="2" t="n">
         <v>485</v>
       </c>
-      <c r="D28" s="0" t="n">
+      <c r="D28" s="2" t="n">
         <v>520</v>
       </c>
-      <c r="E28" s="0" t="n">
+      <c r="E28" s="2" t="n">
         <v>435</v>
       </c>
-      <c r="F28" s="0" t="n">
+      <c r="F28" s="2" t="n">
         <v>80</v>
       </c>
-      <c r="G28" s="0" t="n">
+      <c r="G28" s="2" t="n">
         <v>305</v>
       </c>
-      <c r="H28" s="0" t="n">
+      <c r="H28" s="2" t="n">
         <v>580</v>
       </c>
     </row>
@@ -995,22 +999,22 @@
       <c r="A29" s="1" t="n">
         <v>44926</v>
       </c>
-      <c r="C29" s="0" t="n">
+      <c r="C29" s="2" t="n">
         <v>185</v>
       </c>
-      <c r="D29" s="0" t="n">
+      <c r="D29" s="2" t="n">
         <v>405</v>
       </c>
-      <c r="E29" s="0" t="n">
+      <c r="E29" s="2" t="n">
         <v>345</v>
       </c>
-      <c r="F29" s="0" t="n">
+      <c r="F29" s="2" t="n">
         <v>140</v>
       </c>
-      <c r="G29" s="0" t="n">
+      <c r="G29" s="2" t="n">
         <v>300</v>
       </c>
-      <c r="H29" s="0" t="n">
+      <c r="H29" s="2" t="n">
         <v>475</v>
       </c>
     </row>
@@ -1018,22 +1022,22 @@
       <c r="A30" s="1" t="n">
         <v>44926</v>
       </c>
-      <c r="C30" s="0" t="n">
+      <c r="C30" s="2" t="n">
         <v>290</v>
       </c>
-      <c r="D30" s="0" t="n">
+      <c r="D30" s="2" t="n">
         <v>325</v>
       </c>
-      <c r="E30" s="0" t="n">
+      <c r="E30" s="2" t="n">
         <v>190</v>
       </c>
-      <c r="F30" s="0" t="n">
+      <c r="F30" s="2" t="n">
         <v>90</v>
       </c>
-      <c r="G30" s="0" t="n">
+      <c r="G30" s="2" t="n">
         <v>310</v>
       </c>
-      <c r="H30" s="0" t="n">
+      <c r="H30" s="2" t="n">
         <v>630</v>
       </c>
     </row>
@@ -1041,25 +1045,25 @@
       <c r="A31" s="1" t="n">
         <v>44927</v>
       </c>
-      <c r="B31" s="0" t="n">
+      <c r="B31" s="2" t="n">
         <v>315</v>
       </c>
-      <c r="C31" s="0" t="n">
+      <c r="C31" s="2" t="n">
         <v>215</v>
       </c>
-      <c r="D31" s="0" t="n">
+      <c r="D31" s="2" t="n">
         <v>675</v>
       </c>
-      <c r="E31" s="0" t="n">
+      <c r="E31" s="2" t="n">
         <v>430</v>
       </c>
-      <c r="F31" s="0" t="n">
+      <c r="F31" s="2" t="n">
         <v>405</v>
       </c>
-      <c r="G31" s="0" t="n">
+      <c r="G31" s="2" t="n">
         <v>310</v>
       </c>
-      <c r="H31" s="0" t="n">
+      <c r="H31" s="2" t="n">
         <v>340</v>
       </c>
     </row>
@@ -1067,16 +1071,16 @@
       <c r="A32" s="1" t="n">
         <v>44927</v>
       </c>
-      <c r="C32" s="0" t="n">
+      <c r="C32" s="2" t="n">
         <v>250</v>
       </c>
-      <c r="E32" s="0" t="n">
+      <c r="E32" s="2" t="n">
         <v>330</v>
       </c>
-      <c r="F32" s="0" t="n">
+      <c r="F32" s="2" t="n">
         <v>240</v>
       </c>
-      <c r="H32" s="0" t="n">
+      <c r="H32" s="2" t="n">
         <v>615</v>
       </c>
     </row>
@@ -1084,22 +1088,22 @@
       <c r="A33" s="1" t="n">
         <v>44947</v>
       </c>
-      <c r="B33" s="0" t="n">
+      <c r="B33" s="2" t="n">
         <v>220</v>
       </c>
-      <c r="C33" s="0" t="n">
+      <c r="C33" s="2" t="n">
         <v>165</v>
       </c>
-      <c r="E33" s="0" t="n">
+      <c r="E33" s="2" t="n">
         <v>185</v>
       </c>
-      <c r="F33" s="0" t="n">
+      <c r="F33" s="2" t="n">
         <v>145</v>
       </c>
-      <c r="G33" s="0" t="n">
+      <c r="G33" s="2" t="n">
         <v>275</v>
       </c>
-      <c r="H33" s="0" t="n">
+      <c r="H33" s="2" t="n">
         <v>285</v>
       </c>
     </row>
@@ -1107,19 +1111,19 @@
       <c r="A34" s="1" t="n">
         <v>44947</v>
       </c>
-      <c r="B34" s="0" t="n">
+      <c r="B34" s="2" t="n">
         <v>245</v>
       </c>
-      <c r="E34" s="0" t="n">
+      <c r="E34" s="2" t="n">
         <v>205</v>
       </c>
-      <c r="F34" s="0" t="n">
+      <c r="F34" s="2" t="n">
         <v>375</v>
       </c>
-      <c r="G34" s="0" t="n">
+      <c r="G34" s="2" t="n">
         <v>580</v>
       </c>
-      <c r="H34" s="0" t="n">
+      <c r="H34" s="2" t="n">
         <v>375</v>
       </c>
     </row>
@@ -1127,16 +1131,16 @@
       <c r="A35" s="1" t="n">
         <v>44952</v>
       </c>
-      <c r="E35" s="0" t="n">
+      <c r="E35" s="2" t="n">
         <v>220</v>
       </c>
-      <c r="F35" s="0" t="n">
+      <c r="F35" s="2" t="n">
         <v>140</v>
       </c>
-      <c r="G35" s="0" t="n">
+      <c r="G35" s="2" t="n">
         <v>460</v>
       </c>
-      <c r="H35" s="0" t="n">
+      <c r="H35" s="2" t="n">
         <v>325</v>
       </c>
     </row>
@@ -1144,16 +1148,16 @@
       <c r="A36" s="1" t="n">
         <v>44952</v>
       </c>
-      <c r="E36" s="0" t="n">
+      <c r="E36" s="2" t="n">
         <v>250</v>
       </c>
-      <c r="F36" s="0" t="n">
+      <c r="F36" s="2" t="n">
         <v>280</v>
       </c>
-      <c r="G36" s="0" t="n">
+      <c r="G36" s="2" t="n">
         <v>130</v>
       </c>
-      <c r="H36" s="0" t="n">
+      <c r="H36" s="2" t="n">
         <v>285</v>
       </c>
     </row>
@@ -1161,16 +1165,16 @@
       <c r="A37" s="1" t="n">
         <v>44953</v>
       </c>
-      <c r="E37" s="0" t="n">
+      <c r="E37" s="2" t="n">
         <v>205</v>
       </c>
-      <c r="F37" s="0" t="n">
+      <c r="F37" s="2" t="n">
         <v>265</v>
       </c>
-      <c r="G37" s="0" t="n">
+      <c r="G37" s="2" t="n">
         <v>445</v>
       </c>
-      <c r="H37" s="0" t="n">
+      <c r="H37" s="2" t="n">
         <v>140</v>
       </c>
     </row>
@@ -1178,16 +1182,16 @@
       <c r="A38" s="1" t="n">
         <v>44953</v>
       </c>
-      <c r="E38" s="0" t="n">
+      <c r="E38" s="2" t="n">
         <v>255</v>
       </c>
-      <c r="F38" s="0" t="n">
+      <c r="F38" s="2" t="n">
         <v>330</v>
       </c>
-      <c r="G38" s="0" t="n">
+      <c r="G38" s="2" t="n">
         <v>310</v>
       </c>
-      <c r="H38" s="0" t="n">
+      <c r="H38" s="2" t="n">
         <v>50</v>
       </c>
     </row>
@@ -1195,16 +1199,16 @@
       <c r="A39" s="1" t="n">
         <v>44957</v>
       </c>
-      <c r="E39" s="0" t="n">
+      <c r="E39" s="2" t="n">
         <v>355</v>
       </c>
-      <c r="F39" s="0" t="n">
+      <c r="F39" s="2" t="n">
         <v>130</v>
       </c>
-      <c r="G39" s="0" t="n">
+      <c r="G39" s="2" t="n">
         <v>165</v>
       </c>
-      <c r="H39" s="0" t="n">
+      <c r="H39" s="2" t="n">
         <v>310</v>
       </c>
     </row>
@@ -1212,16 +1216,16 @@
       <c r="A40" s="1" t="n">
         <v>44958</v>
       </c>
-      <c r="E40" s="0" t="n">
+      <c r="E40" s="2" t="n">
         <v>270</v>
       </c>
-      <c r="F40" s="0" t="n">
+      <c r="F40" s="2" t="n">
         <v>425</v>
       </c>
-      <c r="G40" s="0" t="n">
+      <c r="G40" s="2" t="n">
         <v>75</v>
       </c>
-      <c r="H40" s="0" t="n">
+      <c r="H40" s="2" t="n">
         <v>420</v>
       </c>
     </row>
@@ -1229,16 +1233,16 @@
       <c r="A41" s="1" t="n">
         <v>44959</v>
       </c>
-      <c r="E41" s="0" t="n">
+      <c r="E41" s="2" t="n">
         <v>320</v>
       </c>
-      <c r="F41" s="0" t="n">
+      <c r="F41" s="2" t="n">
         <v>175</v>
       </c>
-      <c r="G41" s="0" t="n">
+      <c r="G41" s="2" t="n">
         <v>220</v>
       </c>
-      <c r="H41" s="0" t="n">
+      <c r="H41" s="2" t="n">
         <v>235</v>
       </c>
     </row>
@@ -1246,16 +1250,16 @@
       <c r="A42" s="1" t="n">
         <v>44959</v>
       </c>
-      <c r="E42" s="0" t="n">
+      <c r="E42" s="2" t="n">
         <v>280</v>
       </c>
-      <c r="F42" s="0" t="n">
+      <c r="F42" s="2" t="n">
         <v>280</v>
       </c>
-      <c r="G42" s="0" t="n">
+      <c r="G42" s="2" t="n">
         <v>215</v>
       </c>
-      <c r="H42" s="0" t="n">
+      <c r="H42" s="2" t="n">
         <v>115</v>
       </c>
     </row>
@@ -1263,16 +1267,16 @@
       <c r="A43" s="1" t="n">
         <v>44960</v>
       </c>
-      <c r="E43" s="0" t="n">
+      <c r="E43" s="2" t="n">
         <v>115</v>
       </c>
-      <c r="F43" s="0" t="n">
+      <c r="F43" s="2" t="n">
         <v>250</v>
       </c>
-      <c r="G43" s="0" t="n">
+      <c r="G43" s="2" t="n">
         <v>370</v>
       </c>
-      <c r="H43" s="0" t="n">
+      <c r="H43" s="2" t="n">
         <v>230</v>
       </c>
     </row>
@@ -1280,16 +1284,16 @@
       <c r="A44" s="1" t="n">
         <v>44961</v>
       </c>
-      <c r="E44" s="0" t="n">
+      <c r="E44" s="2" t="n">
         <v>75</v>
       </c>
-      <c r="F44" s="0" t="n">
+      <c r="F44" s="2" t="n">
         <v>220</v>
       </c>
-      <c r="G44" s="0" t="n">
+      <c r="G44" s="2" t="n">
         <v>245</v>
       </c>
-      <c r="H44" s="0" t="n">
+      <c r="H44" s="2" t="n">
         <v>425</v>
       </c>
     </row>
@@ -1297,16 +1301,16 @@
       <c r="A45" s="1" t="n">
         <v>44961</v>
       </c>
-      <c r="E45" s="0" t="n">
+      <c r="E45" s="2" t="n">
         <v>165</v>
       </c>
-      <c r="F45" s="0" t="n">
+      <c r="F45" s="2" t="n">
         <v>130</v>
       </c>
-      <c r="G45" s="0" t="n">
+      <c r="G45" s="2" t="n">
         <v>150</v>
       </c>
-      <c r="H45" s="0" t="n">
+      <c r="H45" s="2" t="n">
         <v>285</v>
       </c>
     </row>
@@ -1314,16 +1318,16 @@
       <c r="A46" s="1" t="n">
         <v>44962</v>
       </c>
-      <c r="E46" s="0" t="n">
+      <c r="E46" s="2" t="n">
         <v>385</v>
       </c>
-      <c r="F46" s="0" t="n">
+      <c r="F46" s="2" t="n">
         <v>320</v>
       </c>
-      <c r="G46" s="0" t="n">
+      <c r="G46" s="2" t="n">
         <v>240</v>
       </c>
-      <c r="H46" s="0" t="n">
+      <c r="H46" s="2" t="n">
         <v>325</v>
       </c>
     </row>
@@ -1331,25 +1335,25 @@
       <c r="A47" s="1" t="n">
         <v>44996</v>
       </c>
-      <c r="B47" s="0" t="n">
+      <c r="B47" s="2" t="n">
         <v>370</v>
       </c>
-      <c r="C47" s="0" t="n">
+      <c r="C47" s="2" t="n">
         <v>355</v>
       </c>
-      <c r="D47" s="0" t="n">
+      <c r="D47" s="2" t="n">
         <v>290</v>
       </c>
-      <c r="E47" s="0" t="n">
+      <c r="E47" s="2" t="n">
         <v>210</v>
       </c>
-      <c r="F47" s="0" t="n">
+      <c r="F47" s="2" t="n">
         <v>325</v>
       </c>
-      <c r="G47" s="0" t="n">
+      <c r="G47" s="2" t="n">
         <v>390</v>
       </c>
-      <c r="H47" s="0" t="n">
+      <c r="H47" s="2" t="n">
         <v>340</v>
       </c>
     </row>
@@ -1357,16 +1361,16 @@
       <c r="A48" s="1" t="n">
         <v>44982</v>
       </c>
-      <c r="B48" s="0" t="n">
+      <c r="B48" s="2" t="n">
         <v>160</v>
       </c>
-      <c r="C48" s="0" t="n">
+      <c r="C48" s="2" t="n">
         <v>240</v>
       </c>
-      <c r="E48" s="0" t="n">
+      <c r="E48" s="2" t="n">
         <v>245</v>
       </c>
-      <c r="F48" s="0" t="n">
+      <c r="F48" s="2" t="n">
         <v>315</v>
       </c>
     </row>
@@ -1374,16 +1378,16 @@
       <c r="A49" s="1" t="n">
         <v>44982</v>
       </c>
-      <c r="B49" s="0" t="n">
+      <c r="B49" s="2" t="n">
         <v>265</v>
       </c>
-      <c r="C49" s="0" t="n">
+      <c r="C49" s="2" t="n">
         <v>180</v>
       </c>
-      <c r="E49" s="0" t="n">
+      <c r="E49" s="2" t="n">
         <v>60</v>
       </c>
-      <c r="F49" s="0" t="n">
+      <c r="F49" s="2" t="n">
         <v>175</v>
       </c>
     </row>
@@ -1391,16 +1395,16 @@
       <c r="A50" s="1" t="n">
         <v>44982</v>
       </c>
-      <c r="B50" s="0" t="n">
+      <c r="B50" s="2" t="n">
         <v>290</v>
       </c>
-      <c r="C50" s="0" t="n">
+      <c r="C50" s="2" t="n">
         <v>385</v>
       </c>
-      <c r="E50" s="0" t="n">
+      <c r="E50" s="2" t="n">
         <v>145</v>
       </c>
-      <c r="F50" s="0" t="n">
+      <c r="F50" s="2" t="n">
         <v>365</v>
       </c>
     </row>
@@ -1408,13 +1412,13 @@
       <c r="A51" s="1" t="n">
         <v>44989</v>
       </c>
-      <c r="C51" s="0" t="n">
+      <c r="C51" s="2" t="n">
         <v>220</v>
       </c>
-      <c r="E51" s="0" t="n">
+      <c r="E51" s="2" t="n">
         <v>160</v>
       </c>
-      <c r="F51" s="0" t="n">
+      <c r="F51" s="2" t="n">
         <v>140</v>
       </c>
     </row>
@@ -1422,13 +1426,13 @@
       <c r="A52" s="1" t="n">
         <v>44989</v>
       </c>
-      <c r="C52" s="0" t="n">
+      <c r="C52" s="2" t="n">
         <v>260</v>
       </c>
-      <c r="E52" s="0" t="n">
+      <c r="E52" s="2" t="n">
         <v>45</v>
       </c>
-      <c r="F52" s="0" t="n">
+      <c r="F52" s="2" t="n">
         <v>495</v>
       </c>
     </row>
@@ -1436,13 +1440,13 @@
       <c r="A53" s="1" t="n">
         <v>44989</v>
       </c>
-      <c r="C53" s="0" t="n">
+      <c r="C53" s="2" t="n">
         <v>280</v>
       </c>
-      <c r="E53" s="0" t="n">
+      <c r="E53" s="2" t="n">
         <v>160</v>
       </c>
-      <c r="F53" s="0" t="n">
+      <c r="F53" s="2" t="n">
         <v>80</v>
       </c>
     </row>
@@ -1450,25 +1454,25 @@
       <c r="A54" s="1" t="n">
         <v>44996</v>
       </c>
-      <c r="B54" s="0" t="n">
+      <c r="B54" s="2" t="n">
         <v>370</v>
       </c>
-      <c r="C54" s="0" t="n">
+      <c r="C54" s="2" t="n">
         <v>355</v>
       </c>
-      <c r="D54" s="0" t="n">
+      <c r="D54" s="2" t="n">
         <v>290</v>
       </c>
-      <c r="E54" s="0" t="n">
+      <c r="E54" s="2" t="n">
         <v>210</v>
       </c>
-      <c r="F54" s="0" t="n">
+      <c r="F54" s="2" t="n">
         <v>325</v>
       </c>
-      <c r="G54" s="0" t="n">
+      <c r="G54" s="2" t="n">
         <v>390</v>
       </c>
-      <c r="H54" s="0" t="n">
+      <c r="H54" s="2" t="n">
         <v>340</v>
       </c>
     </row>
@@ -1476,25 +1480,25 @@
       <c r="A55" s="1" t="n">
         <v>44996</v>
       </c>
-      <c r="B55" s="0" t="n">
+      <c r="B55" s="2" t="n">
         <v>285</v>
       </c>
-      <c r="C55" s="0" t="n">
+      <c r="C55" s="2" t="n">
         <v>445</v>
       </c>
-      <c r="D55" s="0" t="n">
+      <c r="D55" s="2" t="n">
         <v>355</v>
       </c>
-      <c r="E55" s="0" t="n">
+      <c r="E55" s="2" t="n">
         <v>325</v>
       </c>
-      <c r="F55" s="0" t="n">
+      <c r="F55" s="2" t="n">
         <v>465</v>
       </c>
-      <c r="G55" s="0" t="n">
+      <c r="G55" s="2" t="n">
         <v>420</v>
       </c>
-      <c r="H55" s="0" t="n">
+      <c r="H55" s="2" t="n">
         <v>490</v>
       </c>
     </row>
@@ -1502,25 +1506,25 @@
       <c r="A56" s="1" t="n">
         <v>44998</v>
       </c>
-      <c r="B56" s="0" t="n">
+      <c r="B56" s="2" t="n">
         <v>420</v>
       </c>
-      <c r="C56" s="0" t="n">
+      <c r="C56" s="2" t="n">
         <v>335</v>
       </c>
-      <c r="D56" s="0" t="n">
+      <c r="D56" s="2" t="n">
         <v>510</v>
       </c>
-      <c r="E56" s="0" t="n">
+      <c r="E56" s="2" t="n">
         <v>120</v>
       </c>
-      <c r="F56" s="0" t="n">
+      <c r="F56" s="2" t="n">
         <v>480</v>
       </c>
-      <c r="G56" s="0" t="n">
+      <c r="G56" s="2" t="n">
         <v>470</v>
       </c>
-      <c r="H56" s="0" t="n">
+      <c r="H56" s="2" t="n">
         <v>595</v>
       </c>
     </row>
@@ -1528,22 +1532,22 @@
       <c r="A57" s="1" t="n">
         <v>44999</v>
       </c>
-      <c r="B57" s="0" t="n">
+      <c r="B57" s="2" t="n">
         <v>270</v>
       </c>
-      <c r="C57" s="0" t="n">
+      <c r="C57" s="2" t="n">
         <v>445</v>
       </c>
-      <c r="D57" s="0" t="n">
+      <c r="D57" s="2" t="n">
         <v>425</v>
       </c>
-      <c r="E57" s="0" t="n">
+      <c r="E57" s="2" t="n">
         <v>365</v>
       </c>
-      <c r="F57" s="0" t="n">
+      <c r="F57" s="2" t="n">
         <v>210</v>
       </c>
-      <c r="H57" s="0" t="n">
+      <c r="H57" s="2" t="n">
         <v>250</v>
       </c>
     </row>
@@ -1551,16 +1555,16 @@
       <c r="A58" s="1" t="n">
         <v>45010</v>
       </c>
-      <c r="B58" s="0" t="n">
+      <c r="B58" s="2" t="n">
         <v>410</v>
       </c>
-      <c r="C58" s="0" t="n">
+      <c r="C58" s="2" t="n">
         <v>125</v>
       </c>
-      <c r="E58" s="0" t="n">
+      <c r="E58" s="2" t="n">
         <v>345</v>
       </c>
-      <c r="F58" s="0" t="n">
+      <c r="F58" s="2" t="n">
         <v>40</v>
       </c>
     </row>
@@ -1568,16 +1572,16 @@
       <c r="A59" s="1" t="n">
         <v>45017</v>
       </c>
-      <c r="B59" s="0" t="n">
+      <c r="B59" s="2" t="n">
         <v>230</v>
       </c>
-      <c r="C59" s="0" t="n">
+      <c r="C59" s="2" t="n">
         <v>210</v>
       </c>
-      <c r="E59" s="0" t="n">
+      <c r="E59" s="2" t="n">
         <v>410</v>
       </c>
-      <c r="F59" s="0" t="n">
+      <c r="F59" s="2" t="n">
         <v>160</v>
       </c>
     </row>
@@ -1585,16 +1589,16 @@
       <c r="A60" s="1" t="n">
         <v>45017</v>
       </c>
-      <c r="B60" s="0" t="n">
+      <c r="B60" s="2" t="n">
         <v>210</v>
       </c>
-      <c r="C60" s="0" t="n">
+      <c r="C60" s="2" t="n">
         <v>150</v>
       </c>
-      <c r="E60" s="0" t="n">
+      <c r="E60" s="2" t="n">
         <v>430</v>
       </c>
-      <c r="F60" s="0" t="n">
+      <c r="F60" s="2" t="n">
         <v>160</v>
       </c>
     </row>
@@ -1602,16 +1606,16 @@
       <c r="A61" s="1" t="n">
         <v>45038</v>
       </c>
-      <c r="E61" s="0" t="n">
+      <c r="E61" s="2" t="n">
         <v>185</v>
       </c>
-      <c r="F61" s="0" t="n">
+      <c r="F61" s="2" t="n">
         <v>300</v>
       </c>
-      <c r="G61" s="0" t="n">
+      <c r="G61" s="2" t="n">
         <v>305</v>
       </c>
-      <c r="H61" s="0" t="n">
+      <c r="H61" s="2" t="n">
         <v>135</v>
       </c>
     </row>
@@ -1619,22 +1623,22 @@
       <c r="A62" s="1" t="n">
         <v>45045</v>
       </c>
-      <c r="B62" s="0" t="n">
+      <c r="B62" s="2" t="n">
         <v>390</v>
       </c>
-      <c r="C62" s="0" t="n">
+      <c r="C62" s="2" t="n">
         <v>200</v>
       </c>
-      <c r="E62" s="0" t="n">
+      <c r="E62" s="2" t="n">
         <v>225</v>
       </c>
-      <c r="F62" s="0" t="n">
+      <c r="F62" s="2" t="n">
         <v>150</v>
       </c>
-      <c r="G62" s="0" t="n">
+      <c r="G62" s="2" t="n">
         <v>155</v>
       </c>
-      <c r="H62" s="0" t="n">
+      <c r="H62" s="2" t="n">
         <v>515</v>
       </c>
     </row>
@@ -1642,19 +1646,19 @@
       <c r="A63" s="1" t="n">
         <v>45052</v>
       </c>
-      <c r="C63" s="0" t="n">
+      <c r="C63" s="2" t="n">
         <v>355</v>
       </c>
-      <c r="E63" s="0" t="n">
+      <c r="E63" s="2" t="n">
         <v>170</v>
       </c>
-      <c r="F63" s="0" t="n">
+      <c r="F63" s="2" t="n">
         <v>360</v>
       </c>
-      <c r="G63" s="0" t="n">
+      <c r="G63" s="2" t="n">
         <v>215</v>
       </c>
-      <c r="H63" s="0" t="n">
+      <c r="H63" s="2" t="n">
         <v>185</v>
       </c>
     </row>
@@ -1662,25 +1666,25 @@
       <c r="A64" s="1" t="n">
         <v>45066</v>
       </c>
-      <c r="B64" s="0" t="n">
+      <c r="B64" s="2" t="n">
         <v>315</v>
       </c>
-      <c r="C64" s="0" t="n">
+      <c r="C64" s="2" t="n">
         <v>370</v>
       </c>
-      <c r="D64" s="0" t="n">
+      <c r="D64" s="2" t="n">
         <v>340</v>
       </c>
-      <c r="E64" s="0" t="n">
+      <c r="E64" s="2" t="n">
         <v>160</v>
       </c>
-      <c r="F64" s="0" t="n">
+      <c r="F64" s="2" t="n">
         <v>525</v>
       </c>
-      <c r="G64" s="0" t="n">
+      <c r="G64" s="2" t="n">
         <v>340</v>
       </c>
-      <c r="H64" s="0" t="n">
+      <c r="H64" s="2" t="n">
         <v>490</v>
       </c>
     </row>
@@ -1688,19 +1692,19 @@
       <c r="A65" s="1" t="n">
         <v>45067</v>
       </c>
-      <c r="B65" s="0" t="n">
+      <c r="B65" s="2" t="n">
         <v>125</v>
       </c>
-      <c r="C65" s="0" t="n">
+      <c r="C65" s="2" t="n">
         <v>210</v>
       </c>
-      <c r="D65" s="0" t="n">
+      <c r="D65" s="2" t="n">
         <v>515</v>
       </c>
-      <c r="G65" s="0" t="n">
+      <c r="G65" s="2" t="n">
         <v>225</v>
       </c>
-      <c r="H65" s="0" t="n">
+      <c r="H65" s="2" t="n">
         <v>285</v>
       </c>
     </row>
@@ -1708,19 +1712,19 @@
       <c r="A66" s="1" t="n">
         <v>45068</v>
       </c>
-      <c r="B66" s="0" t="n">
+      <c r="B66" s="2" t="n">
         <v>300</v>
       </c>
-      <c r="C66" s="0" t="n">
+      <c r="C66" s="2" t="n">
         <v>425</v>
       </c>
-      <c r="D66" s="0" t="n">
+      <c r="D66" s="2" t="n">
         <v>280</v>
       </c>
-      <c r="G66" s="0" t="n">
+      <c r="G66" s="2" t="n">
         <v>300</v>
       </c>
-      <c r="H66" s="0" t="n">
+      <c r="H66" s="2" t="n">
         <v>485</v>
       </c>
     </row>
@@ -1728,22 +1732,22 @@
       <c r="A67" s="1" t="n">
         <v>45094</v>
       </c>
-      <c r="C67" s="0" t="n">
+      <c r="C67" s="2" t="n">
         <v>295</v>
       </c>
-      <c r="D67" s="0" t="n">
+      <c r="D67" s="2" t="n">
         <v>450</v>
       </c>
-      <c r="E67" s="0" t="n">
+      <c r="E67" s="2" t="n">
         <v>505</v>
       </c>
-      <c r="F67" s="0" t="n">
+      <c r="F67" s="2" t="n">
         <v>310</v>
       </c>
-      <c r="G67" s="0" t="n">
+      <c r="G67" s="2" t="n">
         <v>85</v>
       </c>
-      <c r="H67" s="0" t="n">
+      <c r="H67" s="2" t="n">
         <v>165</v>
       </c>
     </row>
@@ -1751,19 +1755,19 @@
       <c r="A68" s="1" t="n">
         <v>45101</v>
       </c>
-      <c r="C68" s="0" t="n">
+      <c r="C68" s="2" t="n">
         <v>290</v>
       </c>
-      <c r="E68" s="0" t="n">
+      <c r="E68" s="2" t="n">
         <v>330</v>
       </c>
-      <c r="F68" s="0" t="n">
+      <c r="F68" s="2" t="n">
         <v>275</v>
       </c>
-      <c r="G68" s="0" t="n">
+      <c r="G68" s="2" t="n">
         <v>190</v>
       </c>
-      <c r="H68" s="0" t="n">
+      <c r="H68" s="2" t="n">
         <v>255</v>
       </c>
     </row>
@@ -1771,19 +1775,19 @@
       <c r="A69" s="1" t="n">
         <v>45101</v>
       </c>
-      <c r="C69" s="0" t="n">
+      <c r="C69" s="2" t="n">
         <v>245</v>
       </c>
-      <c r="E69" s="0" t="n">
+      <c r="E69" s="2" t="n">
         <v>275</v>
       </c>
-      <c r="F69" s="0" t="n">
+      <c r="F69" s="2" t="n">
         <v>545</v>
       </c>
-      <c r="G69" s="0" t="n">
+      <c r="G69" s="2" t="n">
         <v>350</v>
       </c>
-      <c r="H69" s="0" t="n">
+      <c r="H69" s="2" t="n">
         <v>130</v>
       </c>
     </row>
@@ -1791,16 +1795,16 @@
       <c r="A70" s="1" t="n">
         <v>45115</v>
       </c>
-      <c r="E70" s="0" t="n">
+      <c r="E70" s="2" t="n">
         <v>170</v>
       </c>
-      <c r="F70" s="0" t="n">
+      <c r="F70" s="2" t="n">
         <v>315</v>
       </c>
-      <c r="G70" s="0" t="n">
+      <c r="G70" s="2" t="n">
         <v>275</v>
       </c>
-      <c r="H70" s="0" t="n">
+      <c r="H70" s="2" t="n">
         <v>305</v>
       </c>
     </row>
@@ -1808,16 +1812,16 @@
       <c r="A71" s="1" t="n">
         <v>45115</v>
       </c>
-      <c r="E71" s="0" t="n">
+      <c r="E71" s="2" t="n">
         <v>180</v>
       </c>
-      <c r="F71" s="0" t="n">
+      <c r="F71" s="2" t="n">
         <v>255</v>
       </c>
-      <c r="G71" s="0" t="n">
+      <c r="G71" s="2" t="n">
         <v>295</v>
       </c>
-      <c r="H71" s="0" t="n">
+      <c r="H71" s="2" t="n">
         <v>140</v>
       </c>
     </row>
@@ -1825,19 +1829,19 @@
       <c r="A72" s="1" t="n">
         <v>45122</v>
       </c>
-      <c r="B72" s="0" t="n">
+      <c r="B72" s="2" t="n">
         <v>380</v>
       </c>
-      <c r="C72" s="0" t="n">
+      <c r="C72" s="2" t="n">
         <v>300</v>
       </c>
-      <c r="D72" s="0" t="n">
+      <c r="D72" s="2" t="n">
         <v>245</v>
       </c>
-      <c r="G72" s="0" t="n">
+      <c r="G72" s="2" t="n">
         <v>255</v>
       </c>
-      <c r="H72" s="0" t="n">
+      <c r="H72" s="2" t="n">
         <v>300</v>
       </c>
     </row>
@@ -1845,22 +1849,22 @@
       <c r="A73" s="1" t="n">
         <v>45129</v>
       </c>
-      <c r="C73" s="0" t="n">
+      <c r="C73" s="2" t="n">
         <v>195</v>
       </c>
-      <c r="D73" s="0" t="n">
+      <c r="D73" s="2" t="n">
         <v>390</v>
       </c>
-      <c r="E73" s="0" t="n">
+      <c r="E73" s="2" t="n">
         <v>390</v>
       </c>
-      <c r="F73" s="0" t="n">
+      <c r="F73" s="2" t="n">
         <v>550</v>
       </c>
-      <c r="G73" s="0" t="n">
+      <c r="G73" s="2" t="n">
         <v>500</v>
       </c>
-      <c r="H73" s="0" t="n">
+      <c r="H73" s="2" t="n">
         <v>200</v>
       </c>
     </row>
@@ -1868,22 +1872,22 @@
       <c r="A74" s="1" t="n">
         <v>45129</v>
       </c>
-      <c r="C74" s="0" t="n">
+      <c r="C74" s="2" t="n">
         <v>280</v>
       </c>
-      <c r="D74" s="0" t="n">
+      <c r="D74" s="2" t="n">
         <v>200</v>
       </c>
-      <c r="E74" s="0" t="n">
+      <c r="E74" s="2" t="n">
         <v>190</v>
       </c>
-      <c r="F74" s="0" t="n">
+      <c r="F74" s="2" t="n">
         <v>265</v>
       </c>
-      <c r="G74" s="0" t="n">
+      <c r="G74" s="2" t="n">
         <v>410</v>
       </c>
-      <c r="H74" s="0" t="n">
+      <c r="H74" s="2" t="n">
         <v>175</v>
       </c>
     </row>
@@ -1891,16 +1895,16 @@
       <c r="A75" s="1" t="n">
         <v>45136</v>
       </c>
-      <c r="E75" s="0" t="n">
+      <c r="E75" s="2" t="n">
         <v>110</v>
       </c>
-      <c r="F75" s="0" t="n">
+      <c r="F75" s="2" t="n">
         <v>340</v>
       </c>
-      <c r="G75" s="0" t="n">
+      <c r="G75" s="2" t="n">
         <v>215</v>
       </c>
-      <c r="H75" s="0" t="n">
+      <c r="H75" s="2" t="n">
         <v>270</v>
       </c>
     </row>
@@ -1908,19 +1912,19 @@
       <c r="A76" s="1" t="n">
         <v>45144</v>
       </c>
-      <c r="D76" s="0" t="n">
+      <c r="D76" s="2" t="n">
         <v>340</v>
       </c>
-      <c r="E76" s="0" t="n">
+      <c r="E76" s="2" t="n">
         <v>285</v>
       </c>
-      <c r="F76" s="0" t="n">
+      <c r="F76" s="2" t="n">
         <v>200</v>
       </c>
-      <c r="G76" s="0" t="n">
+      <c r="G76" s="2" t="n">
         <v>250</v>
       </c>
-      <c r="H76" s="0" t="n">
+      <c r="H76" s="2" t="n">
         <v>270</v>
       </c>
     </row>
@@ -1928,22 +1932,22 @@
       <c r="A77" s="1" t="n">
         <v>45150</v>
       </c>
-      <c r="C77" s="0" t="n">
+      <c r="C77" s="2" t="n">
         <v>450</v>
       </c>
-      <c r="D77" s="0" t="n">
+      <c r="D77" s="2" t="n">
         <v>290</v>
       </c>
-      <c r="E77" s="0" t="n">
+      <c r="E77" s="2" t="n">
         <v>390</v>
       </c>
-      <c r="F77" s="0" t="n">
+      <c r="F77" s="2" t="n">
         <v>455</v>
       </c>
-      <c r="G77" s="0" t="n">
+      <c r="G77" s="2" t="n">
         <v>270</v>
       </c>
-      <c r="H77" s="0" t="n">
+      <c r="H77" s="2" t="n">
         <v>205</v>
       </c>
     </row>
@@ -1951,22 +1955,22 @@
       <c r="A78" s="1" t="n">
         <v>45151</v>
       </c>
-      <c r="C78" s="0" t="n">
+      <c r="C78" s="2" t="n">
         <v>420</v>
       </c>
-      <c r="D78" s="0" t="n">
+      <c r="D78" s="2" t="n">
         <v>395</v>
       </c>
-      <c r="E78" s="0" t="n">
+      <c r="E78" s="2" t="n">
         <v>300</v>
       </c>
-      <c r="F78" s="0" t="n">
+      <c r="F78" s="2" t="n">
         <v>215</v>
       </c>
-      <c r="G78" s="0" t="n">
+      <c r="G78" s="2" t="n">
         <v>400</v>
       </c>
-      <c r="H78" s="0" t="n">
+      <c r="H78" s="2" t="n">
         <v>355</v>
       </c>
     </row>
@@ -1974,19 +1978,19 @@
       <c r="A79" s="1" t="n">
         <v>45157</v>
       </c>
-      <c r="B79" s="0" t="n">
+      <c r="B79" s="2" t="n">
         <v>185</v>
       </c>
-      <c r="E79" s="0" t="n">
+      <c r="E79" s="2" t="n">
         <v>90</v>
       </c>
-      <c r="F79" s="0" t="n">
+      <c r="F79" s="2" t="n">
         <v>290</v>
       </c>
-      <c r="G79" s="0" t="n">
+      <c r="G79" s="2" t="n">
         <v>210</v>
       </c>
-      <c r="H79" s="0" t="n">
+      <c r="H79" s="2" t="n">
         <v>155</v>
       </c>
     </row>
@@ -1994,19 +1998,19 @@
       <c r="A80" s="1" t="n">
         <v>45178</v>
       </c>
-      <c r="B80" s="0" t="n">
+      <c r="B80" s="2" t="n">
         <v>380</v>
       </c>
-      <c r="C80" s="0" t="n">
+      <c r="C80" s="2" t="n">
         <v>515</v>
       </c>
-      <c r="E80" s="0" t="n">
+      <c r="E80" s="2" t="n">
         <v>480</v>
       </c>
-      <c r="G80" s="0" t="n">
+      <c r="G80" s="2" t="n">
         <v>210</v>
       </c>
-      <c r="H80" s="0" t="n">
+      <c r="H80" s="2" t="n">
         <v>60</v>
       </c>
     </row>
@@ -2014,19 +2018,19 @@
       <c r="A81" s="1" t="n">
         <v>45179</v>
       </c>
-      <c r="C81" s="0" t="n">
+      <c r="C81" s="2" t="n">
         <v>260</v>
       </c>
-      <c r="E81" s="0" t="n">
+      <c r="E81" s="2" t="n">
         <v>310</v>
       </c>
-      <c r="F81" s="0" t="n">
+      <c r="F81" s="2" t="n">
         <v>80</v>
       </c>
-      <c r="G81" s="0" t="n">
+      <c r="G81" s="2" t="n">
         <v>355</v>
       </c>
-      <c r="H81" s="0" t="n">
+      <c r="H81" s="2" t="n">
         <v>215</v>
       </c>
     </row>
@@ -2034,22 +2038,22 @@
       <c r="A82" s="1" t="n">
         <v>45213</v>
       </c>
-      <c r="B82" s="0" t="n">
+      <c r="B82" s="2" t="n">
         <v>365</v>
       </c>
-      <c r="C82" s="0" t="n">
+      <c r="C82" s="2" t="n">
         <v>155</v>
       </c>
-      <c r="E82" s="0" t="n">
+      <c r="E82" s="2" t="n">
         <v>260</v>
       </c>
-      <c r="F82" s="0" t="n">
+      <c r="F82" s="2" t="n">
         <v>340</v>
       </c>
-      <c r="G82" s="0" t="n">
+      <c r="G82" s="2" t="n">
         <v>255</v>
       </c>
-      <c r="H82" s="0" t="n">
+      <c r="H82" s="2" t="n">
         <v>315</v>
       </c>
     </row>
@@ -2057,19 +2061,19 @@
       <c r="A83" s="1" t="n">
         <v>45213</v>
       </c>
-      <c r="C83" s="0" t="n">
+      <c r="C83" s="2" t="n">
         <v>345</v>
       </c>
-      <c r="E83" s="0" t="n">
+      <c r="E83" s="2" t="n">
         <v>265</v>
       </c>
-      <c r="F83" s="0" t="n">
+      <c r="F83" s="2" t="n">
         <v>260</v>
       </c>
-      <c r="G83" s="0" t="n">
+      <c r="G83" s="2" t="n">
         <v>275</v>
       </c>
-      <c r="H83" s="0" t="n">
+      <c r="H83" s="2" t="n">
         <v>360</v>
       </c>
     </row>
@@ -2077,19 +2081,19 @@
       <c r="A84" s="1" t="n">
         <v>45227</v>
       </c>
-      <c r="C84" s="0" t="n">
+      <c r="C84" s="2" t="n">
         <v>285</v>
       </c>
-      <c r="D84" s="0" t="n">
+      <c r="D84" s="2" t="n">
         <v>350</v>
       </c>
-      <c r="E84" s="0" t="n">
+      <c r="E84" s="2" t="n">
         <v>70</v>
       </c>
-      <c r="F84" s="0" t="n">
+      <c r="F84" s="2" t="n">
         <v>220</v>
       </c>
-      <c r="G84" s="0" t="n">
+      <c r="G84" s="2" t="n">
         <v>305</v>
       </c>
     </row>
@@ -2097,16 +2101,16 @@
       <c r="A85" s="1" t="n">
         <v>45248</v>
       </c>
-      <c r="B85" s="0" t="n">
+      <c r="B85" s="2" t="n">
         <v>230</v>
       </c>
-      <c r="C85" s="0" t="n">
+      <c r="C85" s="2" t="n">
         <v>365</v>
       </c>
-      <c r="E85" s="0" t="n">
+      <c r="E85" s="2" t="n">
         <v>35</v>
       </c>
-      <c r="F85" s="0" t="n">
+      <c r="F85" s="2" t="n">
         <v>200</v>
       </c>
     </row>
@@ -2114,16 +2118,16 @@
       <c r="A86" s="1" t="n">
         <v>45255</v>
       </c>
-      <c r="B86" s="0" t="n">
+      <c r="B86" s="2" t="n">
         <v>265</v>
       </c>
-      <c r="C86" s="0" t="n">
+      <c r="C86" s="2" t="n">
         <v>195</v>
       </c>
-      <c r="E86" s="0" t="n">
+      <c r="E86" s="2" t="n">
         <v>215</v>
       </c>
-      <c r="F86" s="0" t="n">
+      <c r="F86" s="2" t="n">
         <v>235</v>
       </c>
     </row>
@@ -2131,16 +2135,16 @@
       <c r="A87" s="1" t="n">
         <v>45255</v>
       </c>
-      <c r="B87" s="0" t="n">
+      <c r="B87" s="2" t="n">
         <v>315</v>
       </c>
-      <c r="C87" s="0" t="n">
+      <c r="C87" s="2" t="n">
         <v>210</v>
       </c>
-      <c r="E87" s="0" t="n">
+      <c r="E87" s="2" t="n">
         <v>50</v>
       </c>
-      <c r="F87" s="0" t="n">
+      <c r="F87" s="2" t="n">
         <v>300</v>
       </c>
     </row>
@@ -2148,16 +2152,16 @@
       <c r="A88" s="1" t="n">
         <v>45263</v>
       </c>
-      <c r="B88" s="0" t="n">
+      <c r="B88" s="2" t="n">
         <v>210</v>
       </c>
-      <c r="C88" s="0" t="n">
+      <c r="C88" s="2" t="n">
         <v>155</v>
       </c>
-      <c r="E88" s="0" t="n">
+      <c r="E88" s="2" t="n">
         <v>165</v>
       </c>
-      <c r="F88" s="0" t="n">
+      <c r="F88" s="2" t="n">
         <v>70</v>
       </c>
     </row>
@@ -2165,16 +2169,16 @@
       <c r="A89" s="1" t="n">
         <v>45263</v>
       </c>
-      <c r="B89" s="0" t="n">
+      <c r="B89" s="2" t="n">
         <v>230</v>
       </c>
-      <c r="C89" s="0" t="n">
+      <c r="C89" s="2" t="n">
         <v>205</v>
       </c>
-      <c r="E89" s="0" t="n">
+      <c r="E89" s="2" t="n">
         <v>230</v>
       </c>
-      <c r="F89" s="0" t="n">
+      <c r="F89" s="2" t="n">
         <v>230</v>
       </c>
     </row>
@@ -2182,16 +2186,16 @@
       <c r="A90" s="1" t="n">
         <v>45269</v>
       </c>
-      <c r="B90" s="0" t="n">
+      <c r="B90" s="2" t="n">
         <v>475</v>
       </c>
-      <c r="C90" s="0" t="n">
+      <c r="C90" s="2" t="n">
         <v>115</v>
       </c>
-      <c r="E90" s="0" t="n">
+      <c r="E90" s="2" t="n">
         <v>105</v>
       </c>
-      <c r="F90" s="0" t="n">
+      <c r="F90" s="2" t="n">
         <v>310</v>
       </c>
     </row>
@@ -2199,16 +2203,16 @@
       <c r="A91" s="1" t="n">
         <v>45269</v>
       </c>
-      <c r="B91" s="0" t="n">
+      <c r="B91" s="2" t="n">
         <v>150</v>
       </c>
-      <c r="C91" s="0" t="n">
+      <c r="C91" s="2" t="n">
         <v>200</v>
       </c>
-      <c r="E91" s="0" t="n">
+      <c r="E91" s="2" t="n">
         <v>350</v>
       </c>
-      <c r="F91" s="0" t="n">
+      <c r="F91" s="2" t="n">
         <v>195</v>
       </c>
     </row>
@@ -2216,16 +2220,16 @@
       <c r="A92" s="1" t="n">
         <v>45269</v>
       </c>
-      <c r="B92" s="0" t="n">
+      <c r="B92" s="2" t="n">
         <v>150</v>
       </c>
-      <c r="C92" s="0" t="n">
+      <c r="C92" s="2" t="n">
         <v>395</v>
       </c>
-      <c r="E92" s="0" t="n">
+      <c r="E92" s="2" t="n">
         <v>190</v>
       </c>
-      <c r="F92" s="0" t="n">
+      <c r="F92" s="2" t="n">
         <v>240</v>
       </c>
     </row>
@@ -2233,16 +2237,16 @@
       <c r="A93" s="1" t="n">
         <v>45283</v>
       </c>
-      <c r="E93" s="0" t="n">
+      <c r="E93" s="2" t="n">
         <v>300</v>
       </c>
-      <c r="F93" s="0" t="n">
+      <c r="F93" s="2" t="n">
         <v>425</v>
       </c>
-      <c r="G93" s="0" t="n">
+      <c r="G93" s="2" t="n">
         <v>430</v>
       </c>
-      <c r="H93" s="0" t="n">
+      <c r="H93" s="2" t="n">
         <v>245</v>
       </c>
     </row>
@@ -2250,16 +2254,16 @@
       <c r="A94" s="1" t="n">
         <v>45283</v>
       </c>
-      <c r="E94" s="0" t="n">
+      <c r="E94" s="2" t="n">
         <v>115</v>
       </c>
-      <c r="F94" s="0" t="n">
+      <c r="F94" s="2" t="n">
         <v>220</v>
       </c>
-      <c r="G94" s="0" t="n">
+      <c r="G94" s="2" t="n">
         <v>280</v>
       </c>
-      <c r="H94" s="0" t="n">
+      <c r="H94" s="2" t="n">
         <v>245</v>
       </c>
     </row>
@@ -2267,16 +2271,16 @@
       <c r="A95" s="1" t="n">
         <v>45283</v>
       </c>
-      <c r="E95" s="0" t="n">
+      <c r="E95" s="2" t="n">
         <v>140</v>
       </c>
-      <c r="F95" s="0" t="n">
+      <c r="F95" s="2" t="n">
         <v>345</v>
       </c>
-      <c r="G95" s="0" t="n">
+      <c r="G95" s="2" t="n">
         <v>355</v>
       </c>
-      <c r="H95" s="0" t="n">
+      <c r="H95" s="2" t="n">
         <v>150</v>
       </c>
     </row>
@@ -2284,25 +2288,25 @@
       <c r="A96" s="1" t="n">
         <v>45284</v>
       </c>
-      <c r="B96" s="0" t="n">
+      <c r="B96" s="2" t="n">
         <v>245</v>
       </c>
-      <c r="C96" s="0" t="n">
+      <c r="C96" s="2" t="n">
         <v>475</v>
       </c>
-      <c r="D96" s="0" t="n">
+      <c r="D96" s="2" t="n">
         <v>280</v>
       </c>
-      <c r="E96" s="0" t="n">
+      <c r="E96" s="2" t="n">
         <v>185</v>
       </c>
-      <c r="F96" s="0" t="n">
+      <c r="F96" s="2" t="n">
         <v>425</v>
       </c>
-      <c r="G96" s="0" t="n">
+      <c r="G96" s="2" t="n">
         <v>330</v>
       </c>
-      <c r="H96" s="0" t="n">
+      <c r="H96" s="2" t="n">
         <v>505</v>
       </c>
     </row>
@@ -2310,25 +2314,25 @@
       <c r="A97" s="1" t="n">
         <v>45285</v>
       </c>
-      <c r="B97" s="0" t="n">
+      <c r="B97" s="2" t="n">
         <v>490</v>
       </c>
-      <c r="C97" s="0" t="n">
+      <c r="C97" s="2" t="n">
         <v>210</v>
       </c>
-      <c r="D97" s="0" t="n">
+      <c r="D97" s="2" t="n">
         <v>435</v>
       </c>
-      <c r="E97" s="0" t="n">
+      <c r="E97" s="2" t="n">
         <v>185</v>
       </c>
-      <c r="F97" s="0" t="n">
+      <c r="F97" s="2" t="n">
         <v>400</v>
       </c>
-      <c r="G97" s="0" t="n">
+      <c r="G97" s="2" t="n">
         <v>125</v>
       </c>
-      <c r="H97" s="0" t="n">
+      <c r="H97" s="2" t="n">
         <v>410</v>
       </c>
     </row>
@@ -2336,25 +2340,25 @@
       <c r="A98" s="1" t="n">
         <v>45285</v>
       </c>
-      <c r="B98" s="0" t="n">
+      <c r="B98" s="2" t="n">
         <v>330</v>
       </c>
-      <c r="C98" s="0" t="n">
+      <c r="C98" s="2" t="n">
         <v>285</v>
       </c>
-      <c r="D98" s="0" t="n">
+      <c r="D98" s="2" t="n">
         <v>435</v>
       </c>
-      <c r="E98" s="0" t="n">
+      <c r="E98" s="2" t="n">
         <v>230</v>
       </c>
-      <c r="F98" s="0" t="n">
+      <c r="F98" s="2" t="n">
         <v>355</v>
       </c>
-      <c r="G98" s="0" t="n">
+      <c r="G98" s="2" t="n">
         <v>125</v>
       </c>
-      <c r="H98" s="0" t="n">
+      <c r="H98" s="2" t="n">
         <v>545</v>
       </c>
     </row>
@@ -2362,19 +2366,19 @@
       <c r="A99" s="1" t="n">
         <v>45286</v>
       </c>
-      <c r="C99" s="0" t="n">
+      <c r="C99" s="2" t="n">
         <v>285</v>
       </c>
-      <c r="E99" s="0" t="n">
+      <c r="E99" s="2" t="n">
         <v>180</v>
       </c>
-      <c r="F99" s="0" t="n">
+      <c r="F99" s="2" t="n">
         <v>365</v>
       </c>
-      <c r="G99" s="0" t="n">
+      <c r="G99" s="2" t="n">
         <v>440</v>
       </c>
-      <c r="H99" s="0" t="n">
+      <c r="H99" s="2" t="n">
         <v>75</v>
       </c>
     </row>
@@ -2382,25 +2386,25 @@
       <c r="A100" s="1" t="n">
         <v>45286</v>
       </c>
-      <c r="B100" s="0" t="n">
+      <c r="B100" s="2" t="n">
         <v>225</v>
       </c>
-      <c r="C100" s="0" t="n">
+      <c r="C100" s="2" t="n">
         <v>360</v>
       </c>
-      <c r="D100" s="0" t="n">
+      <c r="D100" s="2" t="n">
         <v>320</v>
       </c>
-      <c r="E100" s="0" t="n">
+      <c r="E100" s="2" t="n">
         <v>270</v>
       </c>
-      <c r="F100" s="0" t="n">
+      <c r="F100" s="2" t="n">
         <v>125</v>
       </c>
-      <c r="G100" s="0" t="n">
+      <c r="G100" s="2" t="n">
         <v>285</v>
       </c>
-      <c r="H100" s="0" t="n">
+      <c r="H100" s="2" t="n">
         <v>520</v>
       </c>
     </row>
@@ -2408,25 +2412,25 @@
       <c r="A101" s="1" t="n">
         <v>45290</v>
       </c>
-      <c r="B101" s="0" t="n">
+      <c r="B101" s="2" t="n">
         <v>435</v>
       </c>
-      <c r="C101" s="0" t="n">
+      <c r="C101" s="2" t="n">
         <v>150</v>
       </c>
-      <c r="D101" s="0" t="n">
+      <c r="D101" s="2" t="n">
         <v>410</v>
       </c>
-      <c r="E101" s="0" t="n">
+      <c r="E101" s="2" t="n">
         <v>180</v>
       </c>
-      <c r="F101" s="0" t="n">
+      <c r="F101" s="2" t="n">
         <v>85</v>
       </c>
-      <c r="G101" s="0" t="n">
+      <c r="G101" s="2" t="n">
         <v>330</v>
       </c>
-      <c r="H101" s="0" t="n">
+      <c r="H101" s="2" t="n">
         <v>300</v>
       </c>
     </row>
@@ -2434,19 +2438,19 @@
       <c r="A102" s="1" t="n">
         <v>45291</v>
       </c>
-      <c r="C102" s="0" t="n">
+      <c r="C102" s="2" t="n">
         <v>485</v>
       </c>
-      <c r="E102" s="0" t="n">
+      <c r="E102" s="2" t="n">
         <v>240</v>
       </c>
-      <c r="F102" s="0" t="n">
+      <c r="F102" s="2" t="n">
         <v>110</v>
       </c>
-      <c r="G102" s="0" t="n">
+      <c r="G102" s="2" t="n">
         <v>450</v>
       </c>
-      <c r="H102" s="0" t="n">
+      <c r="H102" s="2" t="n">
         <v>220</v>
       </c>
     </row>
@@ -2454,22 +2458,22 @@
       <c r="A103" s="1" t="n">
         <v>45297</v>
       </c>
-      <c r="B103" s="0" t="n">
+      <c r="B103" s="2" t="n">
         <v>375</v>
       </c>
-      <c r="C103" s="0" t="n">
+      <c r="C103" s="2" t="n">
         <v>425</v>
       </c>
-      <c r="E103" s="0" t="n">
+      <c r="E103" s="2" t="n">
         <v>385</v>
       </c>
-      <c r="F103" s="0" t="n">
+      <c r="F103" s="2" t="n">
         <v>185</v>
       </c>
-      <c r="G103" s="0" t="n">
+      <c r="G103" s="2" t="n">
         <v>220</v>
       </c>
-      <c r="H103" s="0" t="n">
+      <c r="H103" s="2" t="n">
         <v>450</v>
       </c>
     </row>
@@ -2477,22 +2481,22 @@
       <c r="A104" s="1" t="n">
         <v>45297</v>
       </c>
-      <c r="B104" s="0" t="n">
+      <c r="B104" s="2" t="n">
         <v>335</v>
       </c>
-      <c r="C104" s="0" t="n">
+      <c r="C104" s="2" t="n">
         <v>415</v>
       </c>
-      <c r="E104" s="0" t="n">
+      <c r="E104" s="2" t="n">
         <v>290</v>
       </c>
-      <c r="F104" s="0" t="n">
+      <c r="F104" s="2" t="n">
         <v>270</v>
       </c>
-      <c r="G104" s="0" t="n">
+      <c r="G104" s="2" t="n">
         <v>300</v>
       </c>
-      <c r="H104" s="0" t="n">
+      <c r="H104" s="2" t="n">
         <v>505</v>
       </c>
     </row>
@@ -2500,19 +2504,19 @@
       <c r="A105" s="1" t="n">
         <v>45304</v>
       </c>
-      <c r="B105" s="0" t="n">
+      <c r="B105" s="2" t="n">
         <v>65</v>
       </c>
-      <c r="E105" s="0" t="n">
+      <c r="E105" s="2" t="n">
         <v>395</v>
       </c>
-      <c r="F105" s="0" t="n">
+      <c r="F105" s="2" t="n">
         <v>260</v>
       </c>
-      <c r="G105" s="0" t="n">
+      <c r="G105" s="2" t="n">
         <v>415</v>
       </c>
-      <c r="H105" s="0" t="n">
+      <c r="H105" s="2" t="n">
         <v>225</v>
       </c>
     </row>
@@ -2520,22 +2524,22 @@
       <c r="A106" s="1" t="n">
         <v>45304</v>
       </c>
-      <c r="B106" s="0" t="n">
+      <c r="B106" s="2" t="n">
         <v>370</v>
       </c>
-      <c r="C106" s="0" t="n">
+      <c r="C106" s="2" t="n">
         <v>635</v>
       </c>
-      <c r="E106" s="0" t="n">
+      <c r="E106" s="2" t="n">
         <v>430</v>
       </c>
-      <c r="F106" s="0" t="n">
+      <c r="F106" s="2" t="n">
         <v>570</v>
       </c>
-      <c r="G106" s="0" t="n">
+      <c r="G106" s="2" t="n">
         <v>400</v>
       </c>
-      <c r="H106" s="0" t="n">
+      <c r="H106" s="2" t="n">
         <v>135</v>
       </c>
     </row>
@@ -2543,16 +2547,16 @@
       <c r="A107" s="1" t="n">
         <v>45318</v>
       </c>
-      <c r="B107" s="0" t="n">
+      <c r="B107" s="2" t="n">
         <v>305</v>
       </c>
-      <c r="C107" s="0" t="n">
+      <c r="C107" s="2" t="n">
         <v>195</v>
       </c>
-      <c r="E107" s="0" t="n">
+      <c r="E107" s="2" t="n">
         <v>315</v>
       </c>
-      <c r="F107" s="0" t="n">
+      <c r="F107" s="2" t="n">
         <v>365</v>
       </c>
     </row>
@@ -2560,16 +2564,16 @@
       <c r="A108" s="1" t="n">
         <v>45318</v>
       </c>
-      <c r="B108" s="0" t="n">
+      <c r="B108" s="2" t="n">
         <v>145</v>
       </c>
-      <c r="C108" s="0" t="n">
+      <c r="C108" s="2" t="n">
         <v>280</v>
       </c>
-      <c r="E108" s="0" t="n">
+      <c r="E108" s="2" t="n">
         <v>220</v>
       </c>
-      <c r="F108" s="0" t="n">
+      <c r="F108" s="2" t="n">
         <v>320</v>
       </c>
     </row>
@@ -2577,16 +2581,16 @@
       <c r="A109" s="1" t="n">
         <v>45325</v>
       </c>
-      <c r="B109" s="0" t="n">
+      <c r="B109" s="2" t="n">
         <v>100</v>
       </c>
-      <c r="C109" s="0" t="n">
+      <c r="C109" s="2" t="n">
         <v>70</v>
       </c>
-      <c r="E109" s="0" t="n">
+      <c r="E109" s="2" t="n">
         <v>320</v>
       </c>
-      <c r="F109" s="0" t="n">
+      <c r="F109" s="2" t="n">
         <v>270</v>
       </c>
     </row>
@@ -2594,16 +2598,16 @@
       <c r="A110" s="1" t="n">
         <v>45325</v>
       </c>
-      <c r="B110" s="0" t="n">
+      <c r="B110" s="2" t="n">
         <v>375</v>
       </c>
-      <c r="C110" s="0" t="n">
+      <c r="C110" s="2" t="n">
         <v>215</v>
       </c>
-      <c r="E110" s="0" t="n">
+      <c r="E110" s="2" t="n">
         <v>150</v>
       </c>
-      <c r="F110" s="0" t="n">
+      <c r="F110" s="2" t="n">
         <v>370</v>
       </c>
     </row>
@@ -2611,16 +2615,16 @@
       <c r="A111" s="1" t="n">
         <v>45346</v>
       </c>
-      <c r="B111" s="0" t="n">
+      <c r="B111" s="2" t="n">
         <v>335</v>
       </c>
-      <c r="C111" s="0" t="n">
+      <c r="C111" s="2" t="n">
         <v>155</v>
       </c>
-      <c r="E111" s="0" t="n">
+      <c r="E111" s="2" t="n">
         <v>240</v>
       </c>
-      <c r="F111" s="0" t="n">
+      <c r="F111" s="2" t="n">
         <v>305</v>
       </c>
     </row>
@@ -2628,16 +2632,16 @@
       <c r="A112" s="1" t="n">
         <v>45346</v>
       </c>
-      <c r="B112" s="0" t="n">
+      <c r="B112" s="2" t="n">
         <v>400</v>
       </c>
-      <c r="C112" s="0" t="n">
+      <c r="C112" s="2" t="n">
         <v>65</v>
       </c>
-      <c r="E112" s="0" t="n">
+      <c r="E112" s="2" t="n">
         <v>385</v>
       </c>
-      <c r="F112" s="0" t="n">
+      <c r="F112" s="2" t="n">
         <v>315</v>
       </c>
     </row>
@@ -2645,22 +2649,22 @@
       <c r="A113" s="1" t="n">
         <v>45356</v>
       </c>
-      <c r="C113" s="0" t="n">
+      <c r="C113" s="2" t="n">
         <v>375</v>
       </c>
-      <c r="D113" s="0" t="n">
+      <c r="D113" s="2" t="n">
         <v>365</v>
       </c>
-      <c r="E113" s="0" t="n">
+      <c r="E113" s="2" t="n">
         <v>215</v>
       </c>
-      <c r="F113" s="0" t="n">
+      <c r="F113" s="2" t="n">
         <v>65</v>
       </c>
-      <c r="G113" s="0" t="n">
+      <c r="G113" s="2" t="n">
         <v>325</v>
       </c>
-      <c r="H113" s="0" t="n">
+      <c r="H113" s="2" t="n">
         <v>475</v>
       </c>
     </row>
@@ -2668,19 +2672,19 @@
       <c r="A114" s="1" t="n">
         <v>45357</v>
       </c>
-      <c r="C114" s="0" t="n">
+      <c r="C114" s="2" t="n">
         <v>490</v>
       </c>
-      <c r="E114" s="0" t="n">
+      <c r="E114" s="2" t="n">
         <v>315</v>
       </c>
-      <c r="F114" s="0" t="n">
+      <c r="F114" s="2" t="n">
         <v>285</v>
       </c>
-      <c r="G114" s="0" t="n">
+      <c r="G114" s="2" t="n">
         <v>350</v>
       </c>
-      <c r="H114" s="0" t="n">
+      <c r="H114" s="2" t="n">
         <v>230</v>
       </c>
     </row>
@@ -2688,19 +2692,19 @@
       <c r="A115" s="1" t="n">
         <v>45358</v>
       </c>
-      <c r="C115" s="0" t="n">
+      <c r="C115" s="2" t="n">
         <v>315</v>
       </c>
-      <c r="E115" s="0" t="n">
+      <c r="E115" s="2" t="n">
         <v>240</v>
       </c>
-      <c r="F115" s="0" t="n">
+      <c r="F115" s="2" t="n">
         <v>265</v>
       </c>
-      <c r="G115" s="0" t="n">
+      <c r="G115" s="2" t="n">
         <v>395</v>
       </c>
-      <c r="H115" s="0" t="n">
+      <c r="H115" s="2" t="n">
         <v>235</v>
       </c>
     </row>
@@ -2708,19 +2712,19 @@
       <c r="A116" s="1" t="n">
         <v>45358</v>
       </c>
-      <c r="C116" s="0" t="n">
+      <c r="C116" s="2" t="n">
         <v>195</v>
       </c>
-      <c r="E116" s="0" t="n">
+      <c r="E116" s="2" t="n">
         <v>305</v>
       </c>
-      <c r="F116" s="0" t="n">
+      <c r="F116" s="2" t="n">
         <v>315</v>
       </c>
-      <c r="G116" s="0" t="n">
+      <c r="G116" s="2" t="n">
         <v>285</v>
       </c>
-      <c r="H116" s="0" t="n">
+      <c r="H116" s="2" t="n">
         <v>590</v>
       </c>
     </row>
@@ -2728,16 +2732,16 @@
       <c r="A117" s="1" t="n">
         <v>45374</v>
       </c>
-      <c r="B117" s="0" t="n">
+      <c r="B117" s="2" t="n">
         <v>200</v>
       </c>
-      <c r="C117" s="0" t="n">
+      <c r="C117" s="2" t="n">
         <v>515</v>
       </c>
-      <c r="E117" s="0" t="n">
+      <c r="E117" s="2" t="n">
         <v>380</v>
       </c>
-      <c r="F117" s="0" t="n">
+      <c r="F117" s="2" t="n">
         <v>135</v>
       </c>
     </row>
@@ -2745,16 +2749,16 @@
       <c r="A118" s="1" t="n">
         <v>45374</v>
       </c>
-      <c r="B118" s="0" t="n">
+      <c r="B118" s="2" t="n">
         <v>155</v>
       </c>
-      <c r="C118" s="0" t="n">
+      <c r="C118" s="2" t="n">
         <v>220</v>
       </c>
-      <c r="E118" s="0" t="n">
+      <c r="E118" s="2" t="n">
         <v>155</v>
       </c>
-      <c r="F118" s="0" t="n">
+      <c r="F118" s="2" t="n">
         <v>355</v>
       </c>
     </row>
@@ -2762,16 +2766,16 @@
       <c r="A119" s="1" t="n">
         <v>45388</v>
       </c>
-      <c r="B119" s="0" t="n">
+      <c r="B119" s="2" t="n">
         <v>260</v>
       </c>
-      <c r="C119" s="0" t="n">
+      <c r="C119" s="2" t="n">
         <v>280</v>
       </c>
-      <c r="E119" s="0" t="n">
+      <c r="E119" s="2" t="n">
         <v>245</v>
       </c>
-      <c r="F119" s="0" t="n">
+      <c r="F119" s="2" t="n">
         <v>225</v>
       </c>
     </row>
@@ -2779,19 +2783,19 @@
       <c r="A120" s="1" t="n">
         <v>45402</v>
       </c>
-      <c r="C120" s="0" t="n">
+      <c r="C120" s="2" t="n">
         <v>365</v>
       </c>
-      <c r="E120" s="0" t="n">
+      <c r="E120" s="2" t="n">
         <v>415</v>
       </c>
-      <c r="F120" s="0" t="n">
+      <c r="F120" s="2" t="n">
         <v>390</v>
       </c>
-      <c r="G120" s="0" t="n">
+      <c r="G120" s="2" t="n">
         <v>355</v>
       </c>
-      <c r="H120" s="0" t="n">
+      <c r="H120" s="2" t="n">
         <v>185</v>
       </c>
     </row>
@@ -2799,16 +2803,16 @@
       <c r="A121" s="1" t="n">
         <v>45409</v>
       </c>
-      <c r="B121" s="0" t="n">
+      <c r="B121" s="2" t="n">
         <v>260</v>
       </c>
-      <c r="C121" s="0" t="n">
+      <c r="C121" s="2" t="n">
         <v>250</v>
       </c>
-      <c r="G121" s="0" t="n">
+      <c r="G121" s="2" t="n">
         <v>250</v>
       </c>
-      <c r="H121" s="0" t="n">
+      <c r="H121" s="2" t="n">
         <v>415</v>
       </c>
     </row>
@@ -2816,19 +2820,19 @@
       <c r="A122" s="1" t="n">
         <v>45416</v>
       </c>
-      <c r="C122" s="0" t="n">
+      <c r="C122" s="2" t="n">
         <v>270</v>
       </c>
-      <c r="E122" s="0" t="n">
+      <c r="E122" s="2" t="n">
         <v>95</v>
       </c>
-      <c r="F122" s="0" t="n">
+      <c r="F122" s="2" t="n">
         <v>405</v>
       </c>
-      <c r="G122" s="0" t="n">
+      <c r="G122" s="2" t="n">
         <v>225</v>
       </c>
-      <c r="H122" s="0" t="n">
+      <c r="H122" s="2" t="n">
         <v>290</v>
       </c>
     </row>
@@ -2836,19 +2840,19 @@
       <c r="A123" s="1" t="n">
         <v>45416</v>
       </c>
-      <c r="C123" s="0" t="n">
+      <c r="C123" s="2" t="n">
         <v>265</v>
       </c>
-      <c r="E123" s="0" t="n">
+      <c r="E123" s="2" t="n">
         <v>470</v>
       </c>
-      <c r="F123" s="0" t="n">
+      <c r="F123" s="2" t="n">
         <v>330</v>
       </c>
-      <c r="G123" s="0" t="n">
+      <c r="G123" s="2" t="n">
         <v>125</v>
       </c>
-      <c r="H123" s="0" t="n">
+      <c r="H123" s="2" t="n">
         <v>280</v>
       </c>
     </row>
@@ -2856,16 +2860,16 @@
       <c r="A124" s="1" t="n">
         <v>45423</v>
       </c>
-      <c r="E124" s="0" t="n">
+      <c r="E124" s="2" t="n">
         <v>185</v>
       </c>
-      <c r="F124" s="0" t="n">
+      <c r="F124" s="2" t="n">
         <v>260</v>
       </c>
-      <c r="G124" s="0" t="n">
+      <c r="G124" s="2" t="n">
         <v>375</v>
       </c>
-      <c r="H124" s="0" t="n">
+      <c r="H124" s="2" t="n">
         <v>525</v>
       </c>
     </row>
@@ -2873,16 +2877,16 @@
       <c r="A125" s="1" t="n">
         <v>45423</v>
       </c>
-      <c r="E125" s="0" t="n">
+      <c r="E125" s="2" t="n">
         <v>355</v>
       </c>
-      <c r="F125" s="0" t="n">
+      <c r="F125" s="2" t="n">
         <v>110</v>
       </c>
-      <c r="G125" s="0" t="n">
+      <c r="G125" s="2" t="n">
         <v>270</v>
       </c>
-      <c r="H125" s="0" t="n">
+      <c r="H125" s="2" t="n">
         <v>150</v>
       </c>
     </row>
@@ -2890,19 +2894,19 @@
       <c r="A126" s="1" t="n">
         <v>45437</v>
       </c>
-      <c r="C126" s="0" t="n">
+      <c r="C126" s="2" t="n">
         <v>385</v>
       </c>
-      <c r="E126" s="0" t="n">
+      <c r="E126" s="2" t="n">
         <v>190</v>
       </c>
-      <c r="F126" s="0" t="n">
+      <c r="F126" s="2" t="n">
         <v>365</v>
       </c>
-      <c r="G126" s="0" t="n">
+      <c r="G126" s="2" t="n">
         <v>360</v>
       </c>
-      <c r="H126" s="0" t="n">
+      <c r="H126" s="2" t="n">
         <v>240</v>
       </c>
     </row>
@@ -2910,19 +2914,19 @@
       <c r="A127" s="1" t="n">
         <v>45437</v>
       </c>
-      <c r="C127" s="0" t="n">
+      <c r="C127" s="2" t="n">
         <v>310</v>
       </c>
-      <c r="E127" s="0" t="n">
+      <c r="E127" s="2" t="n">
         <v>255</v>
       </c>
-      <c r="F127" s="0" t="n">
+      <c r="F127" s="2" t="n">
         <v>335</v>
       </c>
-      <c r="G127" s="0" t="n">
+      <c r="G127" s="2" t="n">
         <v>480</v>
       </c>
-      <c r="H127" s="0" t="n">
+      <c r="H127" s="2" t="n">
         <v>300</v>
       </c>
     </row>
@@ -2930,19 +2934,19 @@
       <c r="A128" s="1" t="n">
         <v>45444</v>
       </c>
-      <c r="C128" s="0" t="n">
+      <c r="C128" s="2" t="n">
         <v>535</v>
       </c>
-      <c r="E128" s="0" t="n">
+      <c r="E128" s="2" t="n">
         <v>110</v>
       </c>
-      <c r="F128" s="0" t="n">
+      <c r="F128" s="2" t="n">
         <v>275</v>
       </c>
-      <c r="G128" s="0" t="n">
+      <c r="G128" s="2" t="n">
         <v>375</v>
       </c>
-      <c r="H128" s="0" t="n">
+      <c r="H128" s="2" t="n">
         <v>240</v>
       </c>
     </row>
@@ -2950,16 +2954,16 @@
       <c r="A129" s="1" t="n">
         <v>45451</v>
       </c>
-      <c r="E129" s="0" t="n">
+      <c r="E129" s="2" t="n">
         <v>295</v>
       </c>
-      <c r="F129" s="0" t="n">
+      <c r="F129" s="2" t="n">
         <v>285</v>
       </c>
-      <c r="G129" s="0" t="n">
+      <c r="G129" s="2" t="n">
         <v>210</v>
       </c>
-      <c r="H129" s="0" t="n">
+      <c r="H129" s="2" t="n">
         <v>305</v>
       </c>
     </row>
@@ -2967,16 +2971,16 @@
       <c r="A130" s="1" t="n">
         <v>45465</v>
       </c>
-      <c r="E130" s="0" t="n">
+      <c r="E130" s="2" t="n">
         <v>340</v>
       </c>
-      <c r="F130" s="0" t="n">
+      <c r="F130" s="2" t="n">
         <v>135</v>
       </c>
-      <c r="G130" s="0" t="n">
+      <c r="G130" s="2" t="n">
         <v>260</v>
       </c>
-      <c r="H130" s="0" t="n">
+      <c r="H130" s="2" t="n">
         <v>365</v>
       </c>
     </row>
@@ -2984,19 +2988,19 @@
       <c r="A131" s="1" t="n">
         <v>45501</v>
       </c>
-      <c r="C131" s="0" t="n">
+      <c r="C131" s="2" t="n">
         <v>340</v>
       </c>
-      <c r="E131" s="0" t="n">
+      <c r="E131" s="2" t="n">
         <v>195</v>
       </c>
-      <c r="F131" s="0" t="n">
+      <c r="F131" s="2" t="n">
         <v>210</v>
       </c>
-      <c r="G131" s="0" t="n">
+      <c r="G131" s="2" t="n">
         <v>185</v>
       </c>
-      <c r="H131" s="0" t="n">
+      <c r="H131" s="2" t="n">
         <v>575</v>
       </c>
     </row>
@@ -3004,19 +3008,19 @@
       <c r="A132" s="1" t="n">
         <v>45507</v>
       </c>
-      <c r="C132" s="0" t="n">
+      <c r="C132" s="2" t="n">
         <v>160</v>
       </c>
-      <c r="E132" s="0" t="n">
+      <c r="E132" s="2" t="n">
         <v>190</v>
       </c>
-      <c r="F132" s="0" t="n">
+      <c r="F132" s="2" t="n">
         <v>370</v>
       </c>
-      <c r="G132" s="0" t="n">
+      <c r="G132" s="2" t="n">
         <v>300</v>
       </c>
-      <c r="H132" s="0" t="n">
+      <c r="H132" s="2" t="n">
         <v>135</v>
       </c>
     </row>
@@ -3024,158 +3028,158 @@
       <c r="A133" s="1" t="n">
         <v>45559</v>
       </c>
-      <c r="C133" s="0" t="n">
+      <c r="C133" s="2" t="n">
         <v>415</v>
       </c>
-      <c r="E133" s="0" t="n">
+      <c r="E133" s="2" t="n">
         <v>35</v>
       </c>
-      <c r="F133" s="0" t="n">
+      <c r="F133" s="2" t="n">
         <v>345</v>
       </c>
-      <c r="G133" s="0" t="n">
+      <c r="G133" s="2" t="n">
         <v>315</v>
       </c>
-      <c r="H133" s="0" t="n">
+      <c r="H133" s="2" t="n">
         <v>585</v>
       </c>
-      <c r="I133" s="7"/>
-      <c r="K133" s="7"/>
-      <c r="S133" s="7"/>
-      <c r="AA133" s="7"/>
-      <c r="AI133" s="7"/>
-      <c r="AQ133" s="7"/>
-      <c r="AY133" s="7"/>
-      <c r="BG133" s="7"/>
-      <c r="BO133" s="7"/>
-      <c r="BW133" s="7"/>
-      <c r="CE133" s="7"/>
-      <c r="CM133" s="7"/>
-      <c r="CU133" s="7"/>
-      <c r="DC133" s="7"/>
-      <c r="DK133" s="7"/>
-      <c r="DS133" s="7"/>
-      <c r="EA133" s="7"/>
-      <c r="EI133" s="7"/>
-      <c r="EQ133" s="7"/>
-      <c r="EY133" s="7"/>
-      <c r="FG133" s="7"/>
-      <c r="FO133" s="7"/>
-      <c r="FW133" s="7"/>
-      <c r="GE133" s="7"/>
-      <c r="GM133" s="7"/>
-      <c r="GU133" s="7"/>
-      <c r="HC133" s="7"/>
-      <c r="HK133" s="7"/>
-      <c r="HS133" s="7"/>
-      <c r="IA133" s="7"/>
-      <c r="II133" s="7"/>
-      <c r="IQ133" s="7"/>
-      <c r="IY133" s="7"/>
-      <c r="JG133" s="7"/>
-      <c r="JO133" s="7"/>
-      <c r="JW133" s="7"/>
-      <c r="KE133" s="7"/>
-      <c r="KM133" s="7"/>
-      <c r="KU133" s="7"/>
-      <c r="LC133" s="7"/>
-      <c r="LK133" s="7"/>
-      <c r="LS133" s="7"/>
-      <c r="MA133" s="7"/>
-      <c r="MI133" s="7"/>
-      <c r="MQ133" s="7"/>
-      <c r="MY133" s="7"/>
-      <c r="NG133" s="7"/>
-      <c r="NO133" s="7"/>
-      <c r="NW133" s="7"/>
-      <c r="OE133" s="7"/>
-      <c r="OM133" s="7"/>
-      <c r="OU133" s="7"/>
-      <c r="PC133" s="7"/>
-      <c r="PK133" s="7"/>
-      <c r="PS133" s="7"/>
-      <c r="QA133" s="7"/>
-      <c r="QI133" s="7"/>
-      <c r="QQ133" s="7"/>
-      <c r="QY133" s="7"/>
-      <c r="RG133" s="7"/>
-      <c r="RO133" s="7"/>
-      <c r="RW133" s="7"/>
-      <c r="SE133" s="7"/>
-      <c r="SM133" s="7"/>
-      <c r="SU133" s="7"/>
-      <c r="TC133" s="7"/>
-      <c r="TK133" s="7"/>
-      <c r="TS133" s="7"/>
-      <c r="UA133" s="7"/>
-      <c r="UI133" s="7"/>
-      <c r="UQ133" s="7"/>
-      <c r="UY133" s="7"/>
-      <c r="VG133" s="7"/>
-      <c r="VO133" s="7"/>
-      <c r="VW133" s="7"/>
-      <c r="WE133" s="7"/>
-      <c r="WM133" s="7"/>
-      <c r="WU133" s="7"/>
-      <c r="XC133" s="7"/>
-      <c r="XK133" s="7"/>
-      <c r="XS133" s="7"/>
-      <c r="YA133" s="7"/>
-      <c r="YI133" s="7"/>
-      <c r="YQ133" s="7"/>
-      <c r="YY133" s="7"/>
-      <c r="ZG133" s="7"/>
-      <c r="ZO133" s="7"/>
-      <c r="ZW133" s="7"/>
-      <c r="AAE133" s="7"/>
-      <c r="AAM133" s="7"/>
-      <c r="AAU133" s="7"/>
-      <c r="ABC133" s="7"/>
-      <c r="ABK133" s="7"/>
-      <c r="ABS133" s="7"/>
-      <c r="ACA133" s="7"/>
-      <c r="ACI133" s="7"/>
-      <c r="ACQ133" s="7"/>
-      <c r="ACY133" s="7"/>
-      <c r="ADG133" s="7"/>
-      <c r="ADO133" s="7"/>
-      <c r="ADW133" s="7"/>
-      <c r="AEE133" s="7"/>
-      <c r="AEM133" s="7"/>
-      <c r="AEU133" s="7"/>
-      <c r="AFC133" s="7"/>
-      <c r="AFK133" s="7"/>
-      <c r="AFS133" s="7"/>
-      <c r="AGA133" s="7"/>
-      <c r="AGI133" s="7"/>
-      <c r="AGQ133" s="7"/>
-      <c r="AGY133" s="7"/>
-      <c r="AHG133" s="7"/>
-      <c r="AHO133" s="7"/>
-      <c r="AHW133" s="7"/>
-      <c r="AIE133" s="7"/>
-      <c r="AIM133" s="7"/>
-      <c r="AIU133" s="7"/>
-      <c r="AJC133" s="7"/>
-      <c r="AJK133" s="7"/>
-      <c r="AJS133" s="7"/>
-      <c r="AKA133" s="7"/>
-      <c r="AKI133" s="7"/>
+      <c r="I133" s="8"/>
+      <c r="K133" s="8"/>
+      <c r="S133" s="8"/>
+      <c r="AA133" s="8"/>
+      <c r="AI133" s="8"/>
+      <c r="AQ133" s="8"/>
+      <c r="AY133" s="8"/>
+      <c r="BG133" s="8"/>
+      <c r="BO133" s="8"/>
+      <c r="BW133" s="8"/>
+      <c r="CE133" s="8"/>
+      <c r="CM133" s="8"/>
+      <c r="CU133" s="8"/>
+      <c r="DC133" s="8"/>
+      <c r="DK133" s="8"/>
+      <c r="DS133" s="8"/>
+      <c r="EA133" s="8"/>
+      <c r="EI133" s="8"/>
+      <c r="EQ133" s="8"/>
+      <c r="EY133" s="8"/>
+      <c r="FG133" s="8"/>
+      <c r="FO133" s="8"/>
+      <c r="FW133" s="8"/>
+      <c r="GE133" s="8"/>
+      <c r="GM133" s="8"/>
+      <c r="GU133" s="8"/>
+      <c r="HC133" s="8"/>
+      <c r="HK133" s="8"/>
+      <c r="HS133" s="8"/>
+      <c r="IA133" s="8"/>
+      <c r="II133" s="8"/>
+      <c r="IQ133" s="8"/>
+      <c r="IY133" s="8"/>
+      <c r="JG133" s="8"/>
+      <c r="JO133" s="8"/>
+      <c r="JW133" s="8"/>
+      <c r="KE133" s="8"/>
+      <c r="KM133" s="8"/>
+      <c r="KU133" s="8"/>
+      <c r="LC133" s="8"/>
+      <c r="LK133" s="8"/>
+      <c r="LS133" s="8"/>
+      <c r="MA133" s="8"/>
+      <c r="MI133" s="8"/>
+      <c r="MQ133" s="8"/>
+      <c r="MY133" s="8"/>
+      <c r="NG133" s="8"/>
+      <c r="NO133" s="8"/>
+      <c r="NW133" s="8"/>
+      <c r="OE133" s="8"/>
+      <c r="OM133" s="8"/>
+      <c r="OU133" s="8"/>
+      <c r="PC133" s="8"/>
+      <c r="PK133" s="8"/>
+      <c r="PS133" s="8"/>
+      <c r="QA133" s="8"/>
+      <c r="QI133" s="8"/>
+      <c r="QQ133" s="8"/>
+      <c r="QY133" s="8"/>
+      <c r="RG133" s="8"/>
+      <c r="RO133" s="8"/>
+      <c r="RW133" s="8"/>
+      <c r="SE133" s="8"/>
+      <c r="SM133" s="8"/>
+      <c r="SU133" s="8"/>
+      <c r="TC133" s="8"/>
+      <c r="TK133" s="8"/>
+      <c r="TS133" s="8"/>
+      <c r="UA133" s="8"/>
+      <c r="UI133" s="8"/>
+      <c r="UQ133" s="8"/>
+      <c r="UY133" s="8"/>
+      <c r="VG133" s="8"/>
+      <c r="VO133" s="8"/>
+      <c r="VW133" s="8"/>
+      <c r="WE133" s="8"/>
+      <c r="WM133" s="8"/>
+      <c r="WU133" s="8"/>
+      <c r="XC133" s="8"/>
+      <c r="XK133" s="8"/>
+      <c r="XS133" s="8"/>
+      <c r="YA133" s="8"/>
+      <c r="YI133" s="8"/>
+      <c r="YQ133" s="8"/>
+      <c r="YY133" s="8"/>
+      <c r="ZG133" s="8"/>
+      <c r="ZO133" s="8"/>
+      <c r="ZW133" s="8"/>
+      <c r="AAE133" s="8"/>
+      <c r="AAM133" s="8"/>
+      <c r="AAU133" s="8"/>
+      <c r="ABC133" s="8"/>
+      <c r="ABK133" s="8"/>
+      <c r="ABS133" s="8"/>
+      <c r="ACA133" s="8"/>
+      <c r="ACI133" s="8"/>
+      <c r="ACQ133" s="8"/>
+      <c r="ACY133" s="8"/>
+      <c r="ADG133" s="8"/>
+      <c r="ADO133" s="8"/>
+      <c r="ADW133" s="8"/>
+      <c r="AEE133" s="8"/>
+      <c r="AEM133" s="8"/>
+      <c r="AEU133" s="8"/>
+      <c r="AFC133" s="8"/>
+      <c r="AFK133" s="8"/>
+      <c r="AFS133" s="8"/>
+      <c r="AGA133" s="8"/>
+      <c r="AGI133" s="8"/>
+      <c r="AGQ133" s="8"/>
+      <c r="AGY133" s="8"/>
+      <c r="AHG133" s="8"/>
+      <c r="AHO133" s="8"/>
+      <c r="AHW133" s="8"/>
+      <c r="AIE133" s="8"/>
+      <c r="AIM133" s="8"/>
+      <c r="AIU133" s="8"/>
+      <c r="AJC133" s="8"/>
+      <c r="AJK133" s="8"/>
+      <c r="AJS133" s="8"/>
+      <c r="AKA133" s="8"/>
+      <c r="AKI133" s="8"/>
     </row>
     <row r="134" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A134" s="1" t="n">
         <v>45514</v>
       </c>
-      <c r="E134" s="0" t="n">
+      <c r="E134" s="2" t="n">
         <v>425</v>
       </c>
-      <c r="F134" s="0" t="n">
+      <c r="F134" s="2" t="n">
         <v>365</v>
       </c>
-      <c r="G134" s="0" t="n">
+      <c r="G134" s="2" t="n">
         <v>50</v>
       </c>
-      <c r="H134" s="0" t="n">
+      <c r="H134" s="2" t="n">
         <v>455</v>
       </c>
     </row>
@@ -3183,16 +3187,16 @@
       <c r="A135" s="1" t="n">
         <v>45521</v>
       </c>
-      <c r="B135" s="0" t="n">
+      <c r="B135" s="2" t="n">
         <v>275</v>
       </c>
-      <c r="C135" s="0" t="n">
+      <c r="C135" s="2" t="n">
         <v>345</v>
       </c>
-      <c r="G135" s="0" t="n">
+      <c r="G135" s="2" t="n">
         <v>190</v>
       </c>
-      <c r="H135" s="0" t="n">
+      <c r="H135" s="2" t="n">
         <v>240</v>
       </c>
     </row>
@@ -3200,19 +3204,19 @@
       <c r="A136" s="1" t="n">
         <v>45559</v>
       </c>
-      <c r="C136" s="0" t="n">
+      <c r="C136" s="2" t="n">
         <v>415</v>
       </c>
-      <c r="E136" s="0" t="n">
+      <c r="E136" s="2" t="n">
         <v>35</v>
       </c>
-      <c r="F136" s="0" t="n">
+      <c r="F136" s="2" t="n">
         <v>345</v>
       </c>
-      <c r="G136" s="0" t="n">
+      <c r="G136" s="2" t="n">
         <v>315</v>
       </c>
-      <c r="H136" s="0" t="n">
+      <c r="H136" s="2" t="n">
         <v>585</v>
       </c>
     </row>
@@ -3220,16 +3224,16 @@
       <c r="A137" s="1" t="n">
         <v>45535</v>
       </c>
-      <c r="B137" s="0" t="n">
+      <c r="B137" s="2" t="n">
         <v>165</v>
       </c>
-      <c r="C137" s="0" t="n">
+      <c r="C137" s="2" t="n">
         <v>60</v>
       </c>
-      <c r="G137" s="0" t="n">
+      <c r="G137" s="2" t="n">
         <v>205</v>
       </c>
-      <c r="H137" s="0" t="n">
+      <c r="H137" s="2" t="n">
         <v>400</v>
       </c>
     </row>
@@ -3237,16 +3241,16 @@
       <c r="A138" s="1" t="n">
         <v>45542</v>
       </c>
-      <c r="E138" s="0" t="n">
+      <c r="E138" s="2" t="n">
         <v>155</v>
       </c>
-      <c r="F138" s="0" t="n">
+      <c r="F138" s="2" t="n">
         <v>370</v>
       </c>
-      <c r="G138" s="0" t="n">
+      <c r="G138" s="2" t="n">
         <v>345</v>
       </c>
-      <c r="H138" s="0" t="n">
+      <c r="H138" s="2" t="n">
         <v>160</v>
       </c>
     </row>
@@ -3254,16 +3258,16 @@
       <c r="A139" s="1" t="n">
         <v>45550</v>
       </c>
-      <c r="E139" s="0" t="n">
+      <c r="E139" s="2" t="n">
         <v>120</v>
       </c>
-      <c r="F139" s="0" t="n">
+      <c r="F139" s="2" t="n">
         <v>295</v>
       </c>
-      <c r="G139" s="0" t="n">
+      <c r="G139" s="2" t="n">
         <v>250</v>
       </c>
-      <c r="H139" s="0" t="n">
+      <c r="H139" s="2" t="n">
         <v>35</v>
       </c>
     </row>
@@ -3271,16 +3275,16 @@
       <c r="A140" s="1" t="n">
         <v>45556</v>
       </c>
-      <c r="B140" s="0" t="n">
+      <c r="B140" s="2" t="n">
         <v>15</v>
       </c>
-      <c r="C140" s="0" t="n">
+      <c r="C140" s="2" t="n">
         <v>140</v>
       </c>
-      <c r="G140" s="0" t="n">
+      <c r="G140" s="2" t="n">
         <v>100</v>
       </c>
-      <c r="H140" s="0" t="n">
+      <c r="H140" s="2" t="n">
         <v>190</v>
       </c>
     </row>
@@ -3288,19 +3292,19 @@
       <c r="A141" s="1" t="n">
         <v>45563</v>
       </c>
-      <c r="C141" s="0" t="n">
+      <c r="C141" s="2" t="n">
         <v>255</v>
       </c>
-      <c r="E141" s="0" t="n">
+      <c r="E141" s="2" t="n">
         <v>240</v>
       </c>
-      <c r="F141" s="0" t="n">
+      <c r="F141" s="2" t="n">
         <v>265</v>
       </c>
-      <c r="G141" s="0" t="n">
+      <c r="G141" s="2" t="n">
         <v>250</v>
       </c>
-      <c r="H141" s="0" t="n">
+      <c r="H141" s="2" t="n">
         <v>365</v>
       </c>
     </row>
@@ -3308,16 +3312,16 @@
       <c r="A142" s="1" t="n">
         <v>45570</v>
       </c>
-      <c r="E142" s="0" t="n">
+      <c r="E142" s="2" t="n">
         <v>55</v>
       </c>
-      <c r="F142" s="0" t="n">
+      <c r="F142" s="2" t="n">
         <v>270</v>
       </c>
-      <c r="G142" s="0" t="n">
+      <c r="G142" s="2" t="n">
         <v>285</v>
       </c>
-      <c r="H142" s="0" t="n">
+      <c r="H142" s="2" t="n">
         <v>315</v>
       </c>
     </row>
@@ -3325,16 +3329,16 @@
       <c r="A143" s="1" t="n">
         <v>45570</v>
       </c>
-      <c r="E143" s="0" t="n">
+      <c r="E143" s="2" t="n">
         <v>250</v>
       </c>
-      <c r="F143" s="0" t="n">
+      <c r="F143" s="2" t="n">
         <v>305</v>
       </c>
-      <c r="G143" s="0" t="n">
+      <c r="G143" s="2" t="n">
         <v>145</v>
       </c>
-      <c r="H143" s="0" t="n">
+      <c r="H143" s="2" t="n">
         <v>310</v>
       </c>
     </row>
@@ -3342,16 +3346,16 @@
       <c r="A144" s="1" t="n">
         <v>45570</v>
       </c>
-      <c r="E144" s="0" t="n">
+      <c r="E144" s="2" t="n">
         <v>390</v>
       </c>
-      <c r="F144" s="0" t="n">
+      <c r="F144" s="2" t="n">
         <v>185</v>
       </c>
-      <c r="G144" s="0" t="n">
+      <c r="G144" s="2" t="n">
         <v>110</v>
       </c>
-      <c r="H144" s="0" t="n">
+      <c r="H144" s="2" t="n">
         <v>355</v>
       </c>
     </row>
@@ -3359,16 +3363,16 @@
       <c r="A145" s="1" t="n">
         <v>45577</v>
       </c>
-      <c r="E145" s="0" t="n">
+      <c r="E145" s="2" t="n">
         <v>400</v>
       </c>
-      <c r="F145" s="0" t="n">
+      <c r="F145" s="2" t="n">
         <v>120</v>
       </c>
-      <c r="G145" s="0" t="n">
+      <c r="G145" s="2" t="n">
         <v>125</v>
       </c>
-      <c r="H145" s="0" t="n">
+      <c r="H145" s="2" t="n">
         <v>195</v>
       </c>
     </row>
@@ -3376,16 +3380,16 @@
       <c r="A146" s="1" t="n">
         <v>45591</v>
       </c>
-      <c r="E146" s="0" t="n">
+      <c r="E146" s="2" t="n">
         <v>165</v>
       </c>
-      <c r="F146" s="0" t="n">
+      <c r="F146" s="2" t="n">
         <v>345</v>
       </c>
-      <c r="G146" s="0" t="n">
+      <c r="G146" s="2" t="n">
         <v>235</v>
       </c>
-      <c r="H146" s="0" t="n">
+      <c r="H146" s="2" t="n">
         <v>340</v>
       </c>
     </row>
@@ -3393,16 +3397,16 @@
       <c r="A147" s="1" t="n">
         <v>45619</v>
       </c>
-      <c r="B147" s="0" t="n">
+      <c r="B147" s="2" t="n">
         <v>90</v>
       </c>
-      <c r="C147" s="0" t="n">
+      <c r="C147" s="2" t="n">
         <v>435</v>
       </c>
-      <c r="E147" s="0" t="n">
+      <c r="E147" s="2" t="n">
         <v>135</v>
       </c>
-      <c r="F147" s="0" t="n">
+      <c r="F147" s="2" t="n">
         <v>70</v>
       </c>
     </row>
@@ -3410,16 +3414,16 @@
       <c r="A148" s="1" t="n">
         <v>45631</v>
       </c>
-      <c r="B148" s="0" t="n">
+      <c r="B148" s="2" t="n">
         <v>215</v>
       </c>
-      <c r="C148" s="0" t="n">
+      <c r="C148" s="2" t="n">
         <v>200</v>
       </c>
-      <c r="E148" s="0" t="n">
+      <c r="E148" s="2" t="n">
         <v>220</v>
       </c>
-      <c r="F148" s="0" t="n">
+      <c r="F148" s="2" t="n">
         <v>295</v>
       </c>
     </row>
@@ -3427,19 +3431,19 @@
       <c r="A149" s="1" t="n">
         <v>45647</v>
       </c>
-      <c r="C149" s="0" t="n">
+      <c r="C149" s="2" t="n">
         <v>375</v>
       </c>
-      <c r="E149" s="0" t="n">
+      <c r="E149" s="2" t="n">
         <v>115</v>
       </c>
-      <c r="F149" s="0" t="n">
+      <c r="F149" s="2" t="n">
         <v>350</v>
       </c>
-      <c r="G149" s="0" t="n">
+      <c r="G149" s="2" t="n">
         <v>430</v>
       </c>
-      <c r="H149" s="0" t="n">
+      <c r="H149" s="2" t="n">
         <v>110</v>
       </c>
     </row>
@@ -3447,16 +3451,16 @@
       <c r="A150" s="1" t="n">
         <v>45647</v>
       </c>
-      <c r="E150" s="0" t="n">
+      <c r="E150" s="2" t="n">
         <v>210</v>
       </c>
-      <c r="F150" s="0" t="n">
+      <c r="F150" s="2" t="n">
         <v>430</v>
       </c>
-      <c r="G150" s="0" t="n">
+      <c r="G150" s="2" t="n">
         <v>390</v>
       </c>
-      <c r="H150" s="0" t="n">
+      <c r="H150" s="2" t="n">
         <v>300</v>
       </c>
     </row>
@@ -3464,22 +3468,22 @@
       <c r="A151" s="1" t="n">
         <v>45650</v>
       </c>
-      <c r="B151" s="0" t="n">
+      <c r="B151" s="2" t="n">
         <v>160</v>
       </c>
-      <c r="C151" s="0" t="n">
+      <c r="C151" s="2" t="n">
         <v>465</v>
       </c>
-      <c r="E151" s="0" t="n">
+      <c r="E151" s="2" t="n">
         <v>220</v>
       </c>
-      <c r="F151" s="0" t="n">
+      <c r="F151" s="2" t="n">
         <v>330</v>
       </c>
-      <c r="G151" s="0" t="n">
+      <c r="G151" s="2" t="n">
         <v>345</v>
       </c>
-      <c r="H151" s="0" t="n">
+      <c r="H151" s="2" t="n">
         <v>395</v>
       </c>
     </row>
@@ -3487,19 +3491,19 @@
       <c r="A152" s="1" t="n">
         <v>45650</v>
       </c>
-      <c r="C152" s="0" t="n">
+      <c r="C152" s="2" t="n">
         <v>250</v>
       </c>
-      <c r="E152" s="0" t="n">
+      <c r="E152" s="2" t="n">
         <v>315</v>
       </c>
-      <c r="F152" s="0" t="n">
+      <c r="F152" s="2" t="n">
         <v>310</v>
       </c>
-      <c r="G152" s="0" t="n">
+      <c r="G152" s="2" t="n">
         <v>290</v>
       </c>
-      <c r="H152" s="0" t="n">
+      <c r="H152" s="2" t="n">
         <v>415</v>
       </c>
     </row>
@@ -3507,22 +3511,22 @@
       <c r="A153" s="1" t="n">
         <v>45651</v>
       </c>
-      <c r="B153" s="0" t="n">
+      <c r="B153" s="2" t="n">
         <v>410</v>
       </c>
-      <c r="C153" s="0" t="n">
+      <c r="C153" s="2" t="n">
         <v>170</v>
       </c>
-      <c r="E153" s="0" t="n">
+      <c r="E153" s="2" t="n">
         <v>190</v>
       </c>
-      <c r="F153" s="0" t="n">
+      <c r="F153" s="2" t="n">
         <v>455</v>
       </c>
-      <c r="G153" s="0" t="n">
+      <c r="G153" s="2" t="n">
         <v>465</v>
       </c>
-      <c r="H153" s="0" t="n">
+      <c r="H153" s="2" t="n">
         <v>250</v>
       </c>
     </row>
@@ -3530,19 +3534,19 @@
       <c r="A154" s="1" t="n">
         <v>45651</v>
       </c>
-      <c r="C154" s="0" t="n">
+      <c r="C154" s="2" t="n">
         <v>145</v>
       </c>
-      <c r="E154" s="0" t="n">
+      <c r="E154" s="2" t="n">
         <v>325</v>
       </c>
-      <c r="F154" s="0" t="n">
+      <c r="F154" s="2" t="n">
         <v>255</v>
       </c>
-      <c r="G154" s="0" t="n">
+      <c r="G154" s="2" t="n">
         <v>345</v>
       </c>
-      <c r="H154" s="0" t="n">
+      <c r="H154" s="2" t="n">
         <v>320</v>
       </c>
     </row>
@@ -3550,22 +3554,22 @@
       <c r="A155" s="1" t="n">
         <v>45652</v>
       </c>
-      <c r="B155" s="0" t="n">
+      <c r="B155" s="2" t="n">
         <v>285</v>
       </c>
-      <c r="C155" s="0" t="n">
+      <c r="C155" s="2" t="n">
         <v>180</v>
       </c>
-      <c r="E155" s="0" t="n">
+      <c r="E155" s="2" t="n">
         <v>360</v>
       </c>
-      <c r="F155" s="0" t="n">
+      <c r="F155" s="2" t="n">
         <v>375</v>
       </c>
-      <c r="G155" s="0" t="n">
+      <c r="G155" s="2" t="n">
         <v>280</v>
       </c>
-      <c r="H155" s="0" t="n">
+      <c r="H155" s="2" t="n">
         <v>545</v>
       </c>
     </row>
@@ -3573,19 +3577,19 @@
       <c r="A156" s="1" t="n">
         <v>45652</v>
       </c>
-      <c r="C156" s="0" t="n">
+      <c r="C156" s="2" t="n">
         <v>35</v>
       </c>
-      <c r="E156" s="0" t="n">
+      <c r="E156" s="2" t="n">
         <v>345</v>
       </c>
-      <c r="F156" s="0" t="n">
+      <c r="F156" s="2" t="n">
         <v>325</v>
       </c>
-      <c r="G156" s="0" t="n">
+      <c r="G156" s="2" t="n">
         <v>240</v>
       </c>
-      <c r="H156" s="0" t="n">
+      <c r="H156" s="2" t="n">
         <v>460</v>
       </c>
     </row>
@@ -3593,25 +3597,25 @@
       <c r="A157" s="1" t="n">
         <v>45654</v>
       </c>
-      <c r="B157" s="0" t="n">
+      <c r="B157" s="2" t="n">
         <v>395</v>
       </c>
-      <c r="C157" s="0" t="n">
+      <c r="C157" s="2" t="n">
         <v>360</v>
       </c>
-      <c r="D157" s="0" t="n">
+      <c r="D157" s="2" t="n">
         <v>415</v>
       </c>
-      <c r="E157" s="0" t="n">
+      <c r="E157" s="2" t="n">
         <v>165</v>
       </c>
-      <c r="F157" s="0" t="n">
+      <c r="F157" s="2" t="n">
         <v>395</v>
       </c>
-      <c r="G157" s="0" t="n">
+      <c r="G157" s="2" t="n">
         <v>245</v>
       </c>
-      <c r="H157" s="0" t="n">
+      <c r="H157" s="2" t="n">
         <v>230</v>
       </c>
     </row>
@@ -3619,22 +3623,22 @@
       <c r="A158" s="1" t="n">
         <v>45654</v>
       </c>
-      <c r="C158" s="0" t="n">
+      <c r="C158" s="2" t="n">
         <v>165</v>
       </c>
-      <c r="D158" s="0" t="n">
+      <c r="D158" s="2" t="n">
         <v>380</v>
       </c>
-      <c r="E158" s="0" t="n">
+      <c r="E158" s="2" t="n">
         <v>345</v>
       </c>
-      <c r="F158" s="0" t="n">
+      <c r="F158" s="2" t="n">
         <v>290</v>
       </c>
-      <c r="G158" s="0" t="n">
+      <c r="G158" s="2" t="n">
         <v>150</v>
       </c>
-      <c r="H158" s="0" t="n">
+      <c r="H158" s="2" t="n">
         <v>260</v>
       </c>
     </row>
@@ -3642,19 +3646,19 @@
       <c r="A159" s="1" t="n">
         <v>45655</v>
       </c>
-      <c r="B159" s="0" t="n">
+      <c r="B159" s="2" t="n">
         <v>175</v>
       </c>
-      <c r="C159" s="0" t="n">
+      <c r="C159" s="2" t="n">
         <v>330</v>
       </c>
-      <c r="D159" s="0" t="n">
+      <c r="D159" s="2" t="n">
         <v>255</v>
       </c>
-      <c r="G159" s="0" t="n">
+      <c r="G159" s="2" t="n">
         <v>295</v>
       </c>
-      <c r="H159" s="0" t="n">
+      <c r="H159" s="2" t="n">
         <v>265</v>
       </c>
     </row>
@@ -3662,22 +3666,22 @@
       <c r="A160" s="1" t="n">
         <v>45657</v>
       </c>
-      <c r="C160" s="0" t="n">
+      <c r="C160" s="2" t="n">
         <v>185</v>
       </c>
-      <c r="D160" s="0" t="n">
+      <c r="D160" s="2" t="n">
         <v>235</v>
       </c>
-      <c r="E160" s="0" t="n">
+      <c r="E160" s="2" t="n">
         <v>325</v>
       </c>
-      <c r="F160" s="0" t="n">
+      <c r="F160" s="2" t="n">
         <v>258</v>
       </c>
-      <c r="G160" s="0" t="n">
+      <c r="G160" s="2" t="n">
         <v>325</v>
       </c>
-      <c r="H160" s="0" t="n">
+      <c r="H160" s="2" t="n">
         <v>465</v>
       </c>
     </row>
@@ -3685,22 +3689,22 @@
       <c r="A161" s="1" t="n">
         <v>45657</v>
       </c>
-      <c r="C161" s="0" t="n">
+      <c r="C161" s="2" t="n">
         <v>55</v>
       </c>
-      <c r="D161" s="0" t="n">
+      <c r="D161" s="2" t="n">
         <v>275</v>
       </c>
-      <c r="E161" s="0" t="n">
+      <c r="E161" s="2" t="n">
         <v>405</v>
       </c>
-      <c r="F161" s="0" t="n">
+      <c r="F161" s="2" t="n">
         <v>215</v>
       </c>
-      <c r="G161" s="0" t="n">
+      <c r="G161" s="2" t="n">
         <v>455</v>
       </c>
-      <c r="H161" s="0" t="n">
+      <c r="H161" s="2" t="n">
         <v>190</v>
       </c>
     </row>
@@ -3708,25 +3712,25 @@
       <c r="A162" s="1" t="n">
         <v>45658</v>
       </c>
-      <c r="B162" s="0" t="n">
+      <c r="B162" s="2" t="n">
         <v>140</v>
       </c>
-      <c r="C162" s="0" t="n">
+      <c r="C162" s="2" t="n">
         <v>240</v>
       </c>
-      <c r="D162" s="0" t="n">
+      <c r="D162" s="2" t="n">
         <v>285</v>
       </c>
-      <c r="E162" s="0" t="n">
+      <c r="E162" s="2" t="n">
         <v>285</v>
       </c>
-      <c r="F162" s="0" t="n">
+      <c r="F162" s="2" t="n">
         <v>260</v>
       </c>
-      <c r="G162" s="0" t="n">
+      <c r="G162" s="2" t="n">
         <v>545</v>
       </c>
-      <c r="H162" s="0" t="n">
+      <c r="H162" s="2" t="n">
         <v>570</v>
       </c>
     </row>
@@ -3734,25 +3738,25 @@
       <c r="A163" s="1" t="n">
         <v>45661</v>
       </c>
-      <c r="B163" s="0" t="n">
+      <c r="B163" s="2" t="n">
         <v>325</v>
       </c>
-      <c r="C163" s="0" t="n">
+      <c r="C163" s="2" t="n">
         <v>260</v>
       </c>
-      <c r="D163" s="0" t="n">
+      <c r="D163" s="2" t="n">
         <v>290</v>
       </c>
-      <c r="E163" s="0" t="n">
+      <c r="E163" s="2" t="n">
         <v>510</v>
       </c>
-      <c r="F163" s="0" t="n">
+      <c r="F163" s="2" t="n">
         <v>475</v>
       </c>
-      <c r="G163" s="0" t="n">
+      <c r="G163" s="2" t="n">
         <v>435</v>
       </c>
-      <c r="H163" s="0" t="n">
+      <c r="H163" s="2" t="n">
         <v>645</v>
       </c>
     </row>
@@ -3760,13 +3764,13 @@
       <c r="A164" s="1" t="n">
         <v>45668</v>
       </c>
-      <c r="B164" s="0" t="n">
+      <c r="B164" s="2" t="n">
         <v>115</v>
       </c>
-      <c r="E164" s="0" t="n">
+      <c r="E164" s="2" t="n">
         <v>170</v>
       </c>
-      <c r="F164" s="0" t="n">
+      <c r="F164" s="2" t="n">
         <v>545</v>
       </c>
     </row>
@@ -3774,16 +3778,16 @@
       <c r="A165" s="1" t="n">
         <v>45675</v>
       </c>
-      <c r="B165" s="0" t="n">
+      <c r="B165" s="2" t="n">
         <v>280</v>
       </c>
-      <c r="C165" s="0" t="n">
+      <c r="C165" s="2" t="n">
         <v>365</v>
       </c>
-      <c r="E165" s="0" t="n">
+      <c r="E165" s="2" t="n">
         <v>325</v>
       </c>
-      <c r="F165" s="0" t="n">
+      <c r="F165" s="2" t="n">
         <v>45</v>
       </c>
     </row>
@@ -3791,13 +3795,13 @@
       <c r="A166" s="1" t="n">
         <v>45675</v>
       </c>
-      <c r="C166" s="0" t="n">
+      <c r="C166" s="2" t="n">
         <v>235</v>
       </c>
-      <c r="E166" s="0" t="n">
+      <c r="E166" s="2" t="n">
         <v>140</v>
       </c>
-      <c r="F166" s="0" t="n">
+      <c r="F166" s="2" t="n">
         <v>150</v>
       </c>
     </row>
@@ -3805,16 +3809,16 @@
       <c r="A167" s="1" t="n">
         <v>45682</v>
       </c>
-      <c r="B167" s="0" t="n">
+      <c r="B167" s="2" t="n">
         <v>165</v>
       </c>
-      <c r="C167" s="0" t="n">
+      <c r="C167" s="2" t="n">
         <v>265</v>
       </c>
-      <c r="E167" s="0" t="n">
+      <c r="E167" s="2" t="n">
         <v>220</v>
       </c>
-      <c r="F167" s="0" t="n">
+      <c r="F167" s="2" t="n">
         <v>265</v>
       </c>
     </row>
@@ -3822,13 +3826,13 @@
       <c r="A168" s="1" t="n">
         <v>45682</v>
       </c>
-      <c r="C168" s="0" t="n">
+      <c r="C168" s="2" t="n">
         <v>445</v>
       </c>
-      <c r="E168" s="0" t="n">
+      <c r="E168" s="2" t="n">
         <v>240</v>
       </c>
-      <c r="F168" s="0" t="n">
+      <c r="F168" s="2" t="n">
         <v>300</v>
       </c>
     </row>
@@ -3836,19 +3840,19 @@
       <c r="A169" s="1" t="n">
         <v>45689</v>
       </c>
-      <c r="B169" s="0" t="n">
+      <c r="B169" s="2" t="n">
         <v>145</v>
       </c>
-      <c r="C169" s="0" t="n">
+      <c r="C169" s="2" t="n">
         <v>285</v>
       </c>
-      <c r="D169" s="0" t="n">
+      <c r="D169" s="2" t="n">
         <v>150</v>
       </c>
-      <c r="E169" s="0" t="n">
+      <c r="E169" s="2" t="n">
         <v>300</v>
       </c>
-      <c r="F169" s="0" t="n">
+      <c r="F169" s="2" t="n">
         <v>305</v>
       </c>
     </row>
@@ -3856,13 +3860,13 @@
       <c r="A170" s="1" t="n">
         <v>45696</v>
       </c>
-      <c r="C170" s="0" t="n">
+      <c r="C170" s="2" t="n">
         <v>135</v>
       </c>
-      <c r="E170" s="0" t="n">
+      <c r="E170" s="2" t="n">
         <v>110</v>
       </c>
-      <c r="F170" s="0" t="n">
+      <c r="F170" s="2" t="n">
         <v>175</v>
       </c>
     </row>
@@ -3870,13 +3874,13 @@
       <c r="A171" s="1" t="n">
         <v>45696</v>
       </c>
-      <c r="C171" s="0" t="n">
+      <c r="C171" s="2" t="n">
         <v>65</v>
       </c>
-      <c r="E171" s="0" t="n">
+      <c r="E171" s="2" t="n">
         <v>205</v>
       </c>
-      <c r="F171" s="0" t="n">
+      <c r="F171" s="2" t="n">
         <v>205</v>
       </c>
     </row>
@@ -3884,13 +3888,13 @@
       <c r="A172" s="1" t="n">
         <v>45696</v>
       </c>
-      <c r="C172" s="0" t="n">
+      <c r="C172" s="2" t="n">
         <v>190</v>
       </c>
-      <c r="E172" s="0" t="n">
+      <c r="E172" s="2" t="n">
         <v>305</v>
       </c>
-      <c r="F172" s="0" t="n">
+      <c r="F172" s="2" t="n">
         <v>115</v>
       </c>
     </row>
@@ -3898,13 +3902,13 @@
       <c r="A173" s="1" t="n">
         <v>45705</v>
       </c>
-      <c r="C173" s="0" t="n">
+      <c r="C173" s="2" t="n">
         <v>220</v>
       </c>
-      <c r="E173" s="0" t="n">
+      <c r="E173" s="2" t="n">
         <v>125</v>
       </c>
-      <c r="F173" s="0" t="n">
+      <c r="F173" s="2" t="n">
         <v>105</v>
       </c>
     </row>
@@ -3912,16 +3916,16 @@
       <c r="A174" s="1" t="n">
         <v>45737</v>
       </c>
-      <c r="E174" s="0" t="n">
+      <c r="E174" s="2" t="n">
         <v>145</v>
       </c>
-      <c r="F174" s="0" t="n">
+      <c r="F174" s="2" t="n">
         <v>245</v>
       </c>
-      <c r="G174" s="0" t="n">
+      <c r="G174" s="2" t="n">
         <v>385</v>
       </c>
-      <c r="H174" s="0" t="n">
+      <c r="H174" s="2" t="n">
         <v>65</v>
       </c>
     </row>
@@ -3929,16 +3933,16 @@
       <c r="A175" s="1" t="n">
         <v>45740</v>
       </c>
-      <c r="E175" s="0" t="n">
+      <c r="E175" s="2" t="n">
         <v>135</v>
       </c>
-      <c r="F175" s="0" t="n">
+      <c r="F175" s="2" t="n">
         <v>280</v>
       </c>
-      <c r="G175" s="0" t="n">
+      <c r="G175" s="2" t="n">
         <v>110</v>
       </c>
-      <c r="H175" s="0" t="n">
+      <c r="H175" s="2" t="n">
         <v>220</v>
       </c>
     </row>
@@ -3946,16 +3950,16 @@
       <c r="A176" s="1" t="n">
         <v>45746</v>
       </c>
-      <c r="E176" s="0" t="n">
+      <c r="E176" s="2" t="n">
         <v>300</v>
       </c>
-      <c r="F176" s="0" t="n">
+      <c r="F176" s="2" t="n">
         <v>260</v>
       </c>
-      <c r="G176" s="0" t="n">
+      <c r="G176" s="2" t="n">
         <v>195</v>
       </c>
-      <c r="H176" s="0" t="n">
+      <c r="H176" s="2" t="n">
         <v>260</v>
       </c>
     </row>
@@ -3963,19 +3967,19 @@
       <c r="A177" s="1" t="n">
         <v>45752</v>
       </c>
-      <c r="B177" s="0" t="n">
+      <c r="B177" s="2" t="n">
         <v>335</v>
       </c>
-      <c r="E177" s="0" t="n">
+      <c r="E177" s="2" t="n">
         <v>405</v>
       </c>
-      <c r="F177" s="0" t="n">
+      <c r="F177" s="2" t="n">
         <v>265</v>
       </c>
-      <c r="G177" s="0" t="n">
+      <c r="G177" s="2" t="n">
         <v>175</v>
       </c>
-      <c r="H177" s="0" t="n">
+      <c r="H177" s="2" t="n">
         <v>605</v>
       </c>
     </row>
@@ -3983,16 +3987,16 @@
       <c r="A178" s="1" t="n">
         <v>45752</v>
       </c>
-      <c r="E178" s="0" t="n">
+      <c r="E178" s="2" t="n">
         <v>255</v>
       </c>
-      <c r="F178" s="0" t="n">
+      <c r="F178" s="2" t="n">
         <v>185</v>
       </c>
-      <c r="G178" s="0" t="n">
+      <c r="G178" s="2" t="n">
         <v>250</v>
       </c>
-      <c r="H178" s="0" t="n">
+      <c r="H178" s="2" t="n">
         <v>450</v>
       </c>
     </row>
@@ -4000,16 +4004,16 @@
       <c r="A179" s="1" t="n">
         <v>45759</v>
       </c>
-      <c r="E179" s="0" t="n">
+      <c r="E179" s="2" t="n">
         <v>135</v>
       </c>
-      <c r="F179" s="0" t="n">
+      <c r="F179" s="2" t="n">
         <v>315</v>
       </c>
-      <c r="G179" s="0" t="n">
+      <c r="G179" s="2" t="n">
         <v>170</v>
       </c>
-      <c r="H179" s="0" t="n">
+      <c r="H179" s="2" t="n">
         <v>285</v>
       </c>
     </row>
@@ -4017,19 +4021,19 @@
       <c r="A180" s="1" t="n">
         <v>45773</v>
       </c>
-      <c r="C180" s="0" t="n">
+      <c r="C180" s="2" t="n">
         <v>320</v>
       </c>
-      <c r="E180" s="0" t="n">
+      <c r="E180" s="2" t="n">
         <v>280</v>
       </c>
-      <c r="F180" s="0" t="n">
+      <c r="F180" s="2" t="n">
         <v>120</v>
       </c>
-      <c r="G180" s="0" t="n">
+      <c r="G180" s="2" t="n">
         <v>235</v>
       </c>
-      <c r="H180" s="0" t="n">
+      <c r="H180" s="2" t="n">
         <v>395</v>
       </c>
     </row>
@@ -4037,16 +4041,16 @@
       <c r="A181" s="1" t="n">
         <v>45780</v>
       </c>
-      <c r="E181" s="0" t="n">
+      <c r="E181" s="2" t="n">
         <v>200</v>
       </c>
-      <c r="F181" s="0" t="n">
+      <c r="F181" s="2" t="n">
         <v>395</v>
       </c>
-      <c r="G181" s="0" t="n">
+      <c r="G181" s="2" t="n">
         <v>200</v>
       </c>
-      <c r="H181" s="0" t="n">
+      <c r="H181" s="2" t="n">
         <v>390</v>
       </c>
     </row>
@@ -4054,16 +4058,16 @@
       <c r="A182" s="1" t="n">
         <v>45780</v>
       </c>
-      <c r="E182" s="0" t="n">
+      <c r="E182" s="2" t="n">
         <v>220</v>
       </c>
-      <c r="F182" s="0" t="n">
+      <c r="F182" s="2" t="n">
         <v>115</v>
       </c>
-      <c r="G182" s="0" t="n">
+      <c r="G182" s="2" t="n">
         <v>435</v>
       </c>
-      <c r="H182" s="0" t="n">
+      <c r="H182" s="2" t="n">
         <v>280</v>
       </c>
     </row>
@@ -4071,16 +4075,16 @@
       <c r="A183" s="1" t="n">
         <v>45801</v>
       </c>
-      <c r="E183" s="0" t="n">
+      <c r="E183" s="2" t="n">
         <v>355</v>
       </c>
-      <c r="F183" s="0" t="n">
+      <c r="F183" s="2" t="n">
         <v>115</v>
       </c>
-      <c r="G183" s="0" t="n">
+      <c r="G183" s="2" t="n">
         <v>220</v>
       </c>
-      <c r="H183" s="0" t="n">
+      <c r="H183" s="2" t="n">
         <v>150</v>
       </c>
     </row>
@@ -4088,16 +4092,16 @@
       <c r="A184" s="1" t="n">
         <v>45801</v>
       </c>
-      <c r="E184" s="0" t="n">
+      <c r="E184" s="2" t="n">
         <v>250</v>
       </c>
-      <c r="F184" s="0" t="n">
+      <c r="F184" s="2" t="n">
         <v>215</v>
       </c>
-      <c r="G184" s="0" t="n">
+      <c r="G184" s="2" t="n">
         <v>130</v>
       </c>
-      <c r="H184" s="0" t="n">
+      <c r="H184" s="2" t="n">
         <v>235</v>
       </c>
     </row>
@@ -4105,16 +4109,16 @@
       <c r="A185" s="1" t="n">
         <v>45801</v>
       </c>
-      <c r="E185" s="0" t="n">
+      <c r="E185" s="2" t="n">
         <v>95</v>
       </c>
-      <c r="F185" s="0" t="n">
+      <c r="F185" s="2" t="n">
         <v>200</v>
       </c>
-      <c r="G185" s="0" t="n">
+      <c r="G185" s="2" t="n">
         <v>150</v>
       </c>
-      <c r="H185" s="0" t="n">
+      <c r="H185" s="2" t="n">
         <v>140</v>
       </c>
     </row>
@@ -4122,22 +4126,22 @@
       <c r="A186" s="1" t="n">
         <v>45808</v>
       </c>
-      <c r="C186" s="0" t="n">
+      <c r="C186" s="2" t="n">
         <v>410</v>
       </c>
-      <c r="D186" s="0" t="n">
+      <c r="D186" s="2" t="n">
         <v>190</v>
       </c>
-      <c r="E186" s="0" t="n">
+      <c r="E186" s="2" t="n">
         <v>290</v>
       </c>
-      <c r="F186" s="0" t="n">
+      <c r="F186" s="2" t="n">
         <v>210</v>
       </c>
-      <c r="G186" s="0" t="n">
+      <c r="G186" s="2" t="n">
         <v>215</v>
       </c>
-      <c r="H186" s="0" t="n">
+      <c r="H186" s="2" t="n">
         <v>345</v>
       </c>
     </row>
@@ -4145,16 +4149,16 @@
       <c r="A187" s="1" t="n">
         <v>45815</v>
       </c>
-      <c r="B187" s="0" t="n">
+      <c r="B187" s="2" t="n">
         <v>170</v>
       </c>
-      <c r="C187" s="0" t="n">
+      <c r="C187" s="2" t="n">
         <v>160</v>
       </c>
-      <c r="G187" s="0" t="n">
+      <c r="G187" s="2" t="n">
         <v>50</v>
       </c>
-      <c r="H187" s="0" t="n">
+      <c r="H187" s="2" t="n">
         <v>310</v>
       </c>
     </row>
@@ -4162,19 +4166,19 @@
       <c r="A188" s="1" t="n">
         <v>45836</v>
       </c>
-      <c r="B188" s="0" t="n">
+      <c r="B188" s="2" t="n">
         <v>210</v>
       </c>
-      <c r="C188" s="0" t="n">
+      <c r="C188" s="2" t="n">
         <v>145</v>
       </c>
-      <c r="D188" s="0" t="n">
+      <c r="D188" s="2" t="n">
         <v>320</v>
       </c>
-      <c r="G188" s="0" t="n">
+      <c r="G188" s="2" t="n">
         <v>340</v>
       </c>
-      <c r="H188" s="0" t="n">
+      <c r="H188" s="2" t="n">
         <v>290</v>
       </c>
     </row>
@@ -4182,16 +4186,16 @@
       <c r="A189" s="1" t="n">
         <v>45843</v>
       </c>
-      <c r="E189" s="0" t="n">
+      <c r="E189" s="2" t="n">
         <v>245</v>
       </c>
-      <c r="F189" s="0" t="n">
+      <c r="F189" s="2" t="n">
         <v>145</v>
       </c>
-      <c r="G189" s="0" t="n">
+      <c r="G189" s="2" t="n">
         <v>310</v>
       </c>
-      <c r="H189" s="0" t="n">
+      <c r="H189" s="2" t="n">
         <v>280</v>
       </c>
     </row>
@@ -4199,16 +4203,16 @@
       <c r="A190" s="1" t="n">
         <v>45843</v>
       </c>
-      <c r="E190" s="0" t="n">
+      <c r="E190" s="2" t="n">
         <v>300</v>
       </c>
-      <c r="F190" s="0" t="n">
+      <c r="F190" s="2" t="n">
         <v>100</v>
       </c>
-      <c r="G190" s="0" t="n">
+      <c r="G190" s="2" t="n">
         <v>310</v>
       </c>
-      <c r="H190" s="0" t="n">
+      <c r="H190" s="2" t="n">
         <v>210</v>
       </c>
     </row>
@@ -4216,16 +4220,16 @@
       <c r="A191" s="1" t="n">
         <v>45850</v>
       </c>
-      <c r="E191" s="0" t="n">
+      <c r="E191" s="2" t="n">
         <v>365</v>
       </c>
-      <c r="F191" s="0" t="n">
+      <c r="F191" s="2" t="n">
         <v>125</v>
       </c>
-      <c r="G191" s="0" t="n">
+      <c r="G191" s="2" t="n">
         <v>245</v>
       </c>
-      <c r="H191" s="0" t="n">
+      <c r="H191" s="2" t="n">
         <v>80</v>
       </c>
     </row>
@@ -4233,16 +4237,16 @@
       <c r="A192" s="1" t="n">
         <v>45850</v>
       </c>
-      <c r="E192" s="0" t="n">
+      <c r="E192" s="2" t="n">
         <v>355</v>
       </c>
-      <c r="F192" s="0" t="n">
+      <c r="F192" s="2" t="n">
         <v>320</v>
       </c>
-      <c r="G192" s="0" t="n">
+      <c r="G192" s="2" t="n">
         <v>210</v>
       </c>
-      <c r="H192" s="0" t="n">
+      <c r="H192" s="2" t="n">
         <v>170</v>
       </c>
     </row>
@@ -4250,16 +4254,16 @@
       <c r="A193" s="1" t="n">
         <v>45857</v>
       </c>
-      <c r="E193" s="0" t="n">
+      <c r="E193" s="2" t="n">
         <v>235</v>
       </c>
-      <c r="F193" s="0" t="n">
+      <c r="F193" s="2" t="n">
         <v>355</v>
       </c>
-      <c r="G193" s="0" t="n">
+      <c r="G193" s="2" t="n">
         <v>265</v>
       </c>
-      <c r="H193" s="0" t="n">
+      <c r="H193" s="2" t="n">
         <v>305</v>
       </c>
     </row>
@@ -4267,16 +4271,16 @@
       <c r="A194" s="1" t="n">
         <v>45886</v>
       </c>
-      <c r="E194" s="0" t="n">
+      <c r="E194" s="2" t="n">
         <v>265</v>
       </c>
-      <c r="F194" s="0" t="n">
+      <c r="F194" s="2" t="n">
         <v>330</v>
       </c>
-      <c r="G194" s="0" t="n">
+      <c r="G194" s="2" t="n">
         <v>250</v>
       </c>
-      <c r="H194" s="0" t="n">
+      <c r="H194" s="2" t="n">
         <v>250</v>
       </c>
     </row>
@@ -4284,19 +4288,19 @@
       <c r="A195" s="1" t="n">
         <v>45892</v>
       </c>
-      <c r="B195" s="0" t="n">
+      <c r="B195" s="2" t="n">
         <v>480</v>
       </c>
-      <c r="E195" s="0" t="n">
+      <c r="E195" s="2" t="n">
         <v>195</v>
       </c>
-      <c r="F195" s="0" t="n">
+      <c r="F195" s="2" t="n">
         <v>25</v>
       </c>
-      <c r="G195" s="0" t="n">
+      <c r="G195" s="2" t="n">
         <v>460</v>
       </c>
-      <c r="H195" s="0" t="n">
+      <c r="H195" s="2" t="n">
         <v>400</v>
       </c>
     </row>
@@ -4304,16 +4308,16 @@
       <c r="A196" s="1" t="n">
         <v>45892</v>
       </c>
-      <c r="E196" s="0" t="n">
+      <c r="E196" s="2" t="n">
         <v>250</v>
       </c>
-      <c r="F196" s="0" t="n">
+      <c r="F196" s="2" t="n">
         <v>75</v>
       </c>
-      <c r="G196" s="0" t="n">
+      <c r="G196" s="2" t="n">
         <v>380</v>
       </c>
-      <c r="H196" s="0" t="n">
+      <c r="H196" s="2" t="n">
         <v>260</v>
       </c>
     </row>
@@ -4321,391 +4325,391 @@
       <c r="A197" s="1" t="n">
         <v>45899</v>
       </c>
-      <c r="B197" s="0" t="n">
+      <c r="B197" s="2" t="n">
         <v>275</v>
       </c>
-      <c r="C197" s="0" t="n">
+      <c r="C197" s="2" t="n">
         <v>280</v>
       </c>
-      <c r="G197" s="0" t="n">
+      <c r="G197" s="2" t="n">
         <v>135</v>
       </c>
-      <c r="H197" s="0" t="n">
+      <c r="H197" s="2" t="n">
         <v>220</v>
       </c>
     </row>
     <row r="198" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A198" s="8" t="n">
+      <c r="A198" s="9" t="n">
         <v>45906</v>
       </c>
-      <c r="B198" s="0" t="n">
+      <c r="B198" s="2" t="n">
         <v>280</v>
       </c>
-      <c r="C198" s="0" t="n">
+      <c r="C198" s="2" t="n">
         <v>140</v>
       </c>
-      <c r="E198" s="0" t="n">
+      <c r="E198" s="2" t="n">
         <v>635</v>
       </c>
-      <c r="F198" s="0" t="n">
+      <c r="F198" s="2" t="n">
         <v>305</v>
       </c>
-      <c r="G198" s="0" t="n">
+      <c r="G198" s="2" t="n">
         <v>420</v>
       </c>
-      <c r="H198" s="0" t="n">
+      <c r="H198" s="2" t="n">
         <v>320</v>
       </c>
     </row>
     <row r="199" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A199" s="8" t="n">
+      <c r="A199" s="9" t="n">
         <v>45906</v>
       </c>
-      <c r="C199" s="0" t="n">
+      <c r="C199" s="2" t="n">
         <v>260</v>
       </c>
-      <c r="E199" s="0" t="n">
+      <c r="E199" s="2" t="n">
         <v>180</v>
       </c>
-      <c r="F199" s="0" t="n">
+      <c r="F199" s="2" t="n">
         <v>530</v>
       </c>
-      <c r="G199" s="0" t="n">
+      <c r="G199" s="2" t="n">
         <v>370</v>
       </c>
-      <c r="H199" s="0" t="n">
+      <c r="H199" s="2" t="n">
         <v>70</v>
       </c>
     </row>
     <row r="200" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A200" s="8" t="n">
+      <c r="A200" s="9" t="n">
         <v>45913</v>
       </c>
-      <c r="B200" s="0" t="n">
+      <c r="B200" s="2" t="n">
         <v>320</v>
       </c>
-      <c r="G200" s="0" t="n">
+      <c r="G200" s="2" t="n">
         <v>100</v>
       </c>
-      <c r="H200" s="0" t="n">
+      <c r="H200" s="2" t="n">
         <v>490</v>
       </c>
     </row>
     <row r="201" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A201" s="8" t="n">
+      <c r="A201" s="9" t="n">
         <v>45913</v>
       </c>
-      <c r="C201" s="0" t="n">
+      <c r="C201" s="2" t="n">
         <v>255</v>
       </c>
-      <c r="E201" s="0" t="n">
+      <c r="E201" s="2" t="n">
         <v>300</v>
       </c>
-      <c r="F201" s="0" t="n">
+      <c r="F201" s="2" t="n">
         <v>305</v>
       </c>
-      <c r="G201" s="0" t="n">
+      <c r="G201" s="2" t="n">
         <v>395</v>
       </c>
-      <c r="H201" s="0" t="n">
+      <c r="H201" s="2" t="n">
         <v>435</v>
       </c>
     </row>
     <row r="202" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A202" s="8" t="n">
+      <c r="A202" s="9" t="n">
         <v>45920</v>
       </c>
-      <c r="E202" s="0" t="n">
+      <c r="E202" s="2" t="n">
         <v>270</v>
       </c>
-      <c r="F202" s="0" t="n">
+      <c r="F202" s="2" t="n">
         <v>235</v>
       </c>
-      <c r="G202" s="0" t="n">
+      <c r="G202" s="2" t="n">
         <v>350</v>
       </c>
-      <c r="H202" s="0" t="n">
+      <c r="H202" s="2" t="n">
         <v>175</v>
       </c>
     </row>
     <row r="203" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A203" s="8" t="n">
+      <c r="A203" s="9" t="n">
         <v>45928</v>
       </c>
-      <c r="E203" s="0" t="n">
+      <c r="E203" s="2" t="n">
         <v>250</v>
       </c>
-      <c r="F203" s="0" t="n">
+      <c r="F203" s="2" t="n">
         <v>145</v>
       </c>
-      <c r="G203" s="0" t="n">
+      <c r="G203" s="2" t="n">
         <v>250</v>
       </c>
-      <c r="H203" s="0" t="n">
+      <c r="H203" s="2" t="n">
         <v>215</v>
       </c>
     </row>
     <row r="204" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A204" s="8" t="n">
+      <c r="A204" s="9" t="n">
         <v>45930</v>
       </c>
-      <c r="E204" s="0" t="n">
+      <c r="E204" s="2" t="n">
         <v>285</v>
       </c>
-      <c r="F204" s="0" t="n">
+      <c r="F204" s="2" t="n">
         <v>185</v>
       </c>
-      <c r="G204" s="0" t="n">
+      <c r="G204" s="2" t="n">
         <v>110</v>
       </c>
-      <c r="H204" s="0" t="n">
+      <c r="H204" s="2" t="n">
         <v>305</v>
       </c>
     </row>
     <row r="205" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A205" s="8" t="n">
+      <c r="A205" s="9" t="n">
         <v>45932</v>
       </c>
-      <c r="E205" s="0" t="n">
+      <c r="E205" s="2" t="n">
         <v>450</v>
       </c>
-      <c r="F205" s="0" t="n">
+      <c r="F205" s="2" t="n">
         <v>335</v>
       </c>
-      <c r="G205" s="0" t="n">
+      <c r="G205" s="2" t="n">
         <v>120</v>
       </c>
-      <c r="H205" s="0" t="n">
+      <c r="H205" s="2" t="n">
         <v>290</v>
       </c>
     </row>
     <row r="206" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A206" s="8" t="n">
+      <c r="A206" s="9" t="n">
         <v>45933</v>
       </c>
-      <c r="E206" s="0" t="n">
+      <c r="E206" s="2" t="n">
         <v>145</v>
       </c>
-      <c r="F206" s="0" t="n">
+      <c r="F206" s="2" t="n">
         <v>435</v>
       </c>
-      <c r="G206" s="0" t="n">
+      <c r="G206" s="2" t="n">
         <v>225</v>
       </c>
-      <c r="H206" s="0" t="n">
+      <c r="H206" s="2" t="n">
         <v>230</v>
       </c>
     </row>
     <row r="207" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A207" s="8" t="n">
+      <c r="A207" s="9" t="n">
         <v>45934</v>
       </c>
-      <c r="E207" s="0" t="n">
+      <c r="E207" s="2" t="n">
         <v>205</v>
       </c>
-      <c r="F207" s="0" t="n">
+      <c r="F207" s="2" t="n">
         <v>130</v>
       </c>
-      <c r="G207" s="0" t="n">
+      <c r="G207" s="2" t="n">
         <v>240</v>
       </c>
-      <c r="H207" s="0" t="n">
+      <c r="H207" s="2" t="n">
         <v>110</v>
       </c>
     </row>
     <row r="208" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A208" s="8" t="n">
+      <c r="A208" s="9" t="n">
         <v>45935</v>
       </c>
-      <c r="E208" s="0" t="n">
+      <c r="E208" s="2" t="n">
         <v>300</v>
       </c>
-      <c r="F208" s="0" t="n">
+      <c r="F208" s="2" t="n">
         <v>230</v>
       </c>
-      <c r="G208" s="0" t="n">
+      <c r="G208" s="2" t="n">
         <v>205</v>
       </c>
-      <c r="H208" s="0" t="n">
+      <c r="H208" s="2" t="n">
         <v>420</v>
       </c>
     </row>
     <row r="209" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A209" s="8" t="n">
+      <c r="A209" s="9" t="n">
         <v>45935</v>
       </c>
-      <c r="E209" s="0" t="n">
+      <c r="E209" s="2" t="n">
         <v>245</v>
       </c>
-      <c r="F209" s="0" t="n">
+      <c r="F209" s="2" t="n">
         <v>145</v>
       </c>
-      <c r="G209" s="0" t="n">
+      <c r="G209" s="2" t="n">
         <v>240</v>
       </c>
-      <c r="H209" s="0" t="n">
+      <c r="H209" s="2" t="n">
         <v>140</v>
       </c>
     </row>
     <row r="210" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A210" s="8" t="n">
+      <c r="A210" s="9" t="n">
         <v>45935</v>
       </c>
-      <c r="E210" s="0" t="n">
+      <c r="E210" s="2" t="n">
         <v>125</v>
       </c>
-      <c r="F210" s="0" t="n">
+      <c r="F210" s="2" t="n">
         <v>320</v>
       </c>
-      <c r="G210" s="0" t="n">
+      <c r="G210" s="2" t="n">
         <v>340</v>
       </c>
-      <c r="H210" s="0" t="n">
+      <c r="H210" s="2" t="n">
         <v>360</v>
       </c>
     </row>
     <row r="211" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A211" s="8" t="n">
+      <c r="A211" s="9" t="n">
         <v>45936</v>
       </c>
-      <c r="E211" s="0" t="n">
+      <c r="E211" s="2" t="n">
         <v>95</v>
       </c>
-      <c r="F211" s="0" t="n">
+      <c r="F211" s="2" t="n">
         <v>220</v>
       </c>
-      <c r="G211" s="0" t="n">
+      <c r="G211" s="2" t="n">
         <v>240</v>
       </c>
-      <c r="H211" s="0" t="n">
+      <c r="H211" s="2" t="n">
         <v>165</v>
       </c>
     </row>
     <row r="212" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A212" s="8" t="n">
+      <c r="A212" s="9" t="n">
         <v>45940</v>
       </c>
-      <c r="C212" s="0" t="n">
+      <c r="C212" s="2" t="n">
         <v>275</v>
       </c>
-      <c r="D212" s="0" t="n">
+      <c r="D212" s="2" t="n">
         <v>125</v>
       </c>
-      <c r="E212" s="0" t="n">
+      <c r="E212" s="2" t="n">
         <v>340</v>
       </c>
-      <c r="F212" s="0" t="n">
+      <c r="F212" s="2" t="n">
         <v>85</v>
       </c>
-      <c r="G212" s="0" t="n">
+      <c r="G212" s="2" t="n">
         <v>540</v>
       </c>
-      <c r="H212" s="0" t="n">
+      <c r="H212" s="2" t="n">
         <v>395</v>
       </c>
     </row>
     <row r="213" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A213" s="8" t="n">
+      <c r="A213" s="9" t="n">
         <v>45942</v>
       </c>
-      <c r="C213" s="0" t="n">
+      <c r="C213" s="2" t="n">
         <v>410</v>
       </c>
-      <c r="D213" s="0" t="n">
+      <c r="D213" s="2" t="n">
         <v>105</v>
       </c>
-      <c r="G213" s="0" t="n">
+      <c r="G213" s="2" t="n">
         <v>230</v>
       </c>
-      <c r="H213" s="0" t="n">
+      <c r="H213" s="2" t="n">
         <v>285</v>
       </c>
     </row>
     <row r="214" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A214" s="8" t="n">
+      <c r="A214" s="9" t="n">
         <v>45942</v>
       </c>
-      <c r="C214" s="0" t="n">
+      <c r="C214" s="2" t="n">
         <v>90</v>
       </c>
-      <c r="D214" s="0" t="n">
+      <c r="D214" s="2" t="n">
         <v>265</v>
       </c>
-      <c r="G214" s="0" t="n">
+      <c r="G214" s="2" t="n">
         <v>265</v>
       </c>
-      <c r="H214" s="0" t="n">
+      <c r="H214" s="2" t="n">
         <v>275</v>
       </c>
     </row>
     <row r="215" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A215" s="8" t="n">
+      <c r="A215" s="9" t="n">
         <v>45948</v>
       </c>
-      <c r="E215" s="0" t="n">
+      <c r="E215" s="2" t="n">
         <v>355</v>
       </c>
-      <c r="F215" s="0" t="n">
+      <c r="F215" s="2" t="n">
         <v>55</v>
       </c>
-      <c r="G215" s="0" t="n">
+      <c r="G215" s="2" t="n">
         <v>290</v>
       </c>
-      <c r="H215" s="0" t="n">
+      <c r="H215" s="2" t="n">
         <v>335</v>
       </c>
     </row>
     <row r="216" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A216" s="8" t="n">
+      <c r="A216" s="9" t="n">
         <v>45948</v>
       </c>
-      <c r="E216" s="0" t="n">
+      <c r="E216" s="2" t="n">
         <v>85</v>
       </c>
-      <c r="F216" s="0" t="n">
+      <c r="F216" s="2" t="n">
         <v>245</v>
       </c>
-      <c r="G216" s="0" t="n">
+      <c r="G216" s="2" t="n">
         <v>430</v>
       </c>
-      <c r="H216" s="0" t="n">
+      <c r="H216" s="2" t="n">
         <v>230</v>
       </c>
     </row>
     <row r="217" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A217" s="8" t="n">
+      <c r="A217" s="9" t="n">
         <v>45955</v>
       </c>
-      <c r="C217" s="0" t="n">
+      <c r="C217" s="2" t="n">
         <v>135</v>
       </c>
-      <c r="E217" s="0" t="n">
+      <c r="E217" s="2" t="n">
         <v>225</v>
       </c>
-      <c r="F217" s="0" t="n">
+      <c r="F217" s="2" t="n">
         <v>145</v>
       </c>
-      <c r="H217" s="0" t="n">
+      <c r="H217" s="2" t="n">
         <v>130</v>
       </c>
     </row>
     <row r="218" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A218" s="8" t="n">
+      <c r="A218" s="9" t="n">
         <v>45962</v>
       </c>
-      <c r="C218" s="0" t="n">
+      <c r="C218" s="2" t="n">
         <v>155</v>
       </c>
-      <c r="E218" s="0" t="n">
+      <c r="E218" s="2" t="n">
         <v>345</v>
       </c>
-      <c r="F218" s="0" t="n">
+      <c r="F218" s="2" t="n">
         <v>195</v>
       </c>
-      <c r="G218" s="0" t="n">
+      <c r="G218" s="2" t="n">
         <v>285</v>
       </c>
-      <c r="H218" s="0" t="n">
+      <c r="H218" s="2" t="n">
         <v>310</v>
       </c>
     </row>
@@ -4713,163 +4717,163 @@
       <c r="A219" s="1" t="n">
         <v>45969</v>
       </c>
-      <c r="C219" s="0" t="n">
+      <c r="C219" s="2" t="n">
         <v>420</v>
       </c>
-      <c r="D219" s="0" t="n">
+      <c r="D219" s="2" t="n">
         <v>200</v>
       </c>
-      <c r="E219" s="0" t="n">
+      <c r="E219" s="2" t="n">
         <v>485</v>
       </c>
-      <c r="F219" s="0" t="n">
+      <c r="F219" s="2" t="n">
         <v>175</v>
       </c>
-      <c r="G219" s="0" t="n">
+      <c r="G219" s="2" t="n">
         <v>305</v>
       </c>
-      <c r="H219" s="0" t="n">
+      <c r="H219" s="2" t="n">
         <v>475</v>
       </c>
     </row>
     <row r="220" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A220" s="8" t="n">
+      <c r="A220" s="9" t="n">
         <v>45983</v>
       </c>
-      <c r="B220" s="0" t="n">
+      <c r="B220" s="2" t="n">
         <v>50</v>
       </c>
-      <c r="C220" s="0" t="n">
+      <c r="C220" s="2" t="n">
         <v>140</v>
       </c>
-      <c r="E220" s="0" t="n">
+      <c r="E220" s="2" t="n">
         <v>245</v>
       </c>
-      <c r="F220" s="0" t="n">
+      <c r="F220" s="2" t="n">
         <v>340</v>
       </c>
     </row>
     <row r="221" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A221" s="8" t="n">
+      <c r="A221" s="9" t="n">
         <v>45983</v>
       </c>
-      <c r="B221" s="0" t="n">
+      <c r="B221" s="2" t="n">
         <v>435</v>
       </c>
-      <c r="C221" s="0" t="n">
+      <c r="C221" s="2" t="n">
         <v>180</v>
       </c>
-      <c r="E221" s="0" t="n">
+      <c r="E221" s="2" t="n">
         <v>160</v>
       </c>
-      <c r="F221" s="0" t="n">
+      <c r="F221" s="2" t="n">
         <v>80</v>
       </c>
     </row>
     <row r="222" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A222" s="8" t="n">
+      <c r="A222" s="9" t="n">
         <v>45990</v>
       </c>
-      <c r="C222" s="0" t="n">
+      <c r="C222" s="2" t="n">
         <v>355</v>
       </c>
-      <c r="E222" s="0" t="n">
+      <c r="E222" s="2" t="n">
         <v>135</v>
       </c>
-      <c r="F222" s="0" t="n">
+      <c r="F222" s="2" t="n">
         <v>135</v>
       </c>
     </row>
     <row r="223" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A223" s="8" t="n">
+      <c r="A223" s="9" t="n">
         <v>45990</v>
       </c>
-      <c r="C223" s="0" t="n">
+      <c r="C223" s="2" t="n">
         <v>120</v>
       </c>
-      <c r="E223" s="0" t="n">
+      <c r="E223" s="2" t="n">
         <v>185</v>
       </c>
-      <c r="F223" s="0" t="n">
+      <c r="F223" s="2" t="n">
         <v>380</v>
       </c>
     </row>
     <row r="224" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A224" s="8" t="n">
+      <c r="A224" s="9" t="n">
         <v>45990</v>
       </c>
-      <c r="C224" s="0" t="n">
+      <c r="C224" s="2" t="n">
         <v>260</v>
       </c>
-      <c r="E224" s="0" t="n">
+      <c r="E224" s="2" t="n">
         <v>95</v>
       </c>
-      <c r="F224" s="0" t="n">
+      <c r="F224" s="2" t="n">
         <v>230</v>
       </c>
     </row>
     <row r="225" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A225" s="8" t="n">
+      <c r="A225" s="9" t="n">
         <v>45990</v>
       </c>
-      <c r="C225" s="0" t="n">
+      <c r="C225" s="2" t="n">
         <v>125</v>
       </c>
-      <c r="E225" s="0" t="n">
+      <c r="E225" s="2" t="n">
         <v>240</v>
       </c>
-      <c r="F225" s="0" t="n">
+      <c r="F225" s="2" t="n">
         <v>130</v>
       </c>
     </row>
     <row r="226" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A226" s="8" t="n">
+      <c r="A226" s="9" t="n">
         <v>45997</v>
       </c>
-      <c r="B226" s="0" t="n">
+      <c r="B226" s="2" t="n">
         <v>175</v>
       </c>
-      <c r="C226" s="0" t="n">
+      <c r="C226" s="2" t="n">
         <v>275</v>
       </c>
-      <c r="E226" s="0" t="n">
+      <c r="E226" s="2" t="n">
         <v>105</v>
       </c>
-      <c r="F226" s="0" t="n">
+      <c r="F226" s="2" t="n">
         <v>240</v>
       </c>
     </row>
     <row r="227" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A227" s="8" t="n">
+      <c r="A227" s="9" t="n">
         <v>45997</v>
       </c>
-      <c r="B227" s="0" t="n">
+      <c r="B227" s="2" t="n">
         <v>60</v>
       </c>
-      <c r="C227" s="0" t="n">
+      <c r="C227" s="2" t="n">
         <v>235</v>
       </c>
-      <c r="E227" s="0" t="n">
+      <c r="E227" s="2" t="n">
         <v>340</v>
       </c>
-      <c r="F227" s="0" t="n">
+      <c r="F227" s="2" t="n">
         <v>260</v>
       </c>
     </row>
     <row r="228" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A228" s="8" t="n">
+      <c r="A228" s="9" t="n">
         <v>45997</v>
       </c>
-      <c r="B228" s="0" t="n">
+      <c r="B228" s="2" t="n">
         <v>370</v>
       </c>
-      <c r="C228" s="0" t="n">
+      <c r="C228" s="2" t="n">
         <v>415</v>
       </c>
-      <c r="E228" s="0" t="n">
+      <c r="E228" s="2" t="n">
         <v>230</v>
       </c>
-      <c r="F228" s="0" t="n">
+      <c r="F228" s="2" t="n">
         <v>370</v>
       </c>
     </row>
@@ -4877,16 +4881,16 @@
       <c r="A229" s="1" t="n">
         <v>46005</v>
       </c>
-      <c r="E229" s="0" t="n">
+      <c r="E229" s="2" t="n">
         <v>215</v>
       </c>
-      <c r="F229" s="0" t="n">
+      <c r="F229" s="2" t="n">
         <v>110</v>
       </c>
-      <c r="G229" s="0" t="n">
+      <c r="G229" s="2" t="n">
         <v>370</v>
       </c>
-      <c r="H229" s="0" t="n">
+      <c r="H229" s="2" t="n">
         <v>275</v>
       </c>
     </row>
@@ -4894,16 +4898,16 @@
       <c r="A230" s="1" t="n">
         <v>46005</v>
       </c>
-      <c r="E230" s="0" t="n">
+      <c r="E230" s="2" t="n">
         <v>325</v>
       </c>
-      <c r="F230" s="0" t="n">
+      <c r="F230" s="2" t="n">
         <v>285</v>
       </c>
-      <c r="G230" s="0" t="n">
+      <c r="G230" s="2" t="n">
         <v>270</v>
       </c>
-      <c r="H230" s="0" t="n">
+      <c r="H230" s="2" t="n">
         <v>215</v>
       </c>
     </row>
@@ -4911,19 +4915,19 @@
       <c r="A231" s="1" t="n">
         <v>46012</v>
       </c>
-      <c r="C231" s="0" t="n">
+      <c r="C231" s="2" t="n">
         <v>245</v>
       </c>
-      <c r="E231" s="0" t="n">
+      <c r="E231" s="2" t="n">
         <v>185</v>
       </c>
-      <c r="F231" s="0" t="n">
+      <c r="F231" s="2" t="n">
         <v>255</v>
       </c>
-      <c r="G231" s="0" t="n">
+      <c r="G231" s="2" t="n">
         <v>275</v>
       </c>
-      <c r="H231" s="0" t="n">
+      <c r="H231" s="2" t="n">
         <v>365</v>
       </c>
     </row>
@@ -4931,16 +4935,16 @@
       <c r="A232" s="1" t="n">
         <v>46012</v>
       </c>
-      <c r="E232" s="0" t="n">
+      <c r="E232" s="2" t="n">
         <v>345</v>
       </c>
-      <c r="F232" s="0" t="n">
+      <c r="F232" s="2" t="n">
         <v>90</v>
       </c>
-      <c r="G232" s="0" t="n">
+      <c r="G232" s="2" t="n">
         <v>180</v>
       </c>
-      <c r="H232" s="0" t="n">
+      <c r="H232" s="2" t="n">
         <v>145</v>
       </c>
     </row>
@@ -4948,16 +4952,16 @@
       <c r="A233" s="1" t="n">
         <v>46012</v>
       </c>
-      <c r="E233" s="0" t="n">
+      <c r="E233" s="2" t="n">
         <v>210</v>
       </c>
-      <c r="F233" s="0" t="n">
+      <c r="F233" s="2" t="n">
         <v>170</v>
       </c>
-      <c r="G233" s="0" t="n">
+      <c r="G233" s="2" t="n">
         <v>190</v>
       </c>
-      <c r="H233" s="0" t="n">
+      <c r="H233" s="2" t="n">
         <v>225</v>
       </c>
     </row>
@@ -4965,22 +4969,22 @@
       <c r="A234" s="1" t="n">
         <v>46015</v>
       </c>
-      <c r="B234" s="0" t="n">
+      <c r="B234" s="2" t="n">
         <v>135</v>
       </c>
-      <c r="C234" s="0" t="n">
+      <c r="C234" s="2" t="n">
         <v>285</v>
       </c>
-      <c r="E234" s="0" t="n">
+      <c r="E234" s="2" t="n">
         <v>185</v>
       </c>
-      <c r="F234" s="0" t="n">
+      <c r="F234" s="2" t="n">
         <v>405</v>
       </c>
-      <c r="G234" s="0" t="n">
+      <c r="G234" s="2" t="n">
         <v>450</v>
       </c>
-      <c r="H234" s="0" t="n">
+      <c r="H234" s="2" t="n">
         <v>345</v>
       </c>
     </row>
@@ -4988,22 +4992,22 @@
       <c r="A235" s="1" t="n">
         <v>46016</v>
       </c>
-      <c r="B235" s="0" t="n">
+      <c r="B235" s="2" t="n">
         <v>465</v>
       </c>
-      <c r="C235" s="0" t="n">
+      <c r="C235" s="2" t="n">
         <v>270</v>
       </c>
-      <c r="E235" s="0" t="n">
+      <c r="E235" s="2" t="n">
         <v>200</v>
       </c>
-      <c r="F235" s="0" t="n">
+      <c r="F235" s="2" t="n">
         <v>445</v>
       </c>
-      <c r="G235" s="0" t="n">
+      <c r="G235" s="2" t="n">
         <v>380</v>
       </c>
-      <c r="H235" s="0" t="n">
+      <c r="H235" s="2" t="n">
         <v>565</v>
       </c>
     </row>
@@ -5011,22 +5015,22 @@
       <c r="A236" s="1" t="n">
         <v>46020</v>
       </c>
-      <c r="B236" s="0" t="n">
+      <c r="B236" s="2" t="n">
         <v>405</v>
       </c>
-      <c r="C236" s="0" t="n">
+      <c r="C236" s="2" t="n">
         <v>370</v>
       </c>
-      <c r="D236" s="0" t="n">
+      <c r="D236" s="2" t="n">
         <v>385</v>
       </c>
-      <c r="E236" s="0" t="n">
+      <c r="E236" s="2" t="n">
         <v>185</v>
       </c>
-      <c r="F236" s="0" t="n">
+      <c r="F236" s="2" t="n">
         <v>430</v>
       </c>
-      <c r="H236" s="0" t="n">
+      <c r="H236" s="2" t="n">
         <v>270</v>
       </c>
     </row>
@@ -5034,13 +5038,13 @@
       <c r="A237" s="1" t="n">
         <v>46032</v>
       </c>
-      <c r="B237" s="0" t="n">
+      <c r="B237" s="2" t="n">
         <v>340</v>
       </c>
-      <c r="E237" s="0" t="n">
+      <c r="E237" s="2" t="n">
         <v>65</v>
       </c>
-      <c r="F237" s="0" t="n">
+      <c r="F237" s="2" t="n">
         <v>255</v>
       </c>
     </row>
@@ -5048,13 +5052,13 @@
       <c r="A238" s="1" t="n">
         <v>46032</v>
       </c>
-      <c r="B238" s="0" t="n">
+      <c r="B238" s="2" t="n">
         <v>245</v>
       </c>
-      <c r="E238" s="0" t="n">
+      <c r="E238" s="2" t="n">
         <v>210</v>
       </c>
-      <c r="F238" s="0" t="n">
+      <c r="F238" s="2" t="n">
         <v>190</v>
       </c>
     </row>
@@ -5062,16 +5066,16 @@
       <c r="A239" s="1" t="n">
         <v>46039</v>
       </c>
-      <c r="B239" s="0" t="n">
+      <c r="B239" s="2" t="n">
         <v>135</v>
       </c>
-      <c r="C239" s="0" t="n">
+      <c r="C239" s="2" t="n">
         <v>145</v>
       </c>
-      <c r="E239" s="0" t="n">
+      <c r="E239" s="2" t="n">
         <v>120</v>
       </c>
-      <c r="F239" s="0" t="n">
+      <c r="F239" s="2" t="n">
         <v>70</v>
       </c>
     </row>
@@ -5079,16 +5083,16 @@
       <c r="A240" s="1" t="n">
         <v>46039</v>
       </c>
-      <c r="B240" s="0" t="n">
+      <c r="B240" s="2" t="n">
         <v>180</v>
       </c>
-      <c r="C240" s="0" t="n">
+      <c r="C240" s="2" t="n">
         <v>140</v>
       </c>
-      <c r="E240" s="0" t="n">
+      <c r="E240" s="2" t="n">
         <v>145</v>
       </c>
-      <c r="F240" s="0" t="n">
+      <c r="F240" s="2" t="n">
         <v>425</v>
       </c>
     </row>
@@ -5096,16 +5100,16 @@
       <c r="A241" s="1" t="n">
         <v>46039</v>
       </c>
-      <c r="B241" s="0" t="n">
+      <c r="B241" s="2" t="n">
         <v>285</v>
       </c>
-      <c r="C241" s="0" t="n">
+      <c r="C241" s="2" t="n">
         <v>245</v>
       </c>
-      <c r="E241" s="0" t="n">
+      <c r="E241" s="2" t="n">
         <v>105</v>
       </c>
-      <c r="F241" s="0" t="n">
+      <c r="F241" s="2" t="n">
         <v>130</v>
       </c>
     </row>
@@ -5113,19 +5117,19 @@
       <c r="A242" s="1" t="n">
         <v>46067</v>
       </c>
-      <c r="B242" s="0" t="n">
+      <c r="B242" s="2" t="n">
         <v>325</v>
       </c>
-      <c r="C242" s="0" t="n">
+      <c r="C242" s="2" t="n">
         <v>225</v>
       </c>
-      <c r="D242" s="0" t="n">
+      <c r="D242" s="2" t="n">
         <v>250</v>
       </c>
-      <c r="E242" s="0" t="n">
+      <c r="E242" s="2" t="n">
         <v>420</v>
       </c>
-      <c r="F242" s="0" t="n">
+      <c r="F242" s="2" t="n">
         <v>340</v>
       </c>
     </row>
@@ -5133,16 +5137,16 @@
       <c r="A243" s="1" t="n">
         <v>46067</v>
       </c>
-      <c r="C243" s="0" t="n">
+      <c r="C243" s="2" t="n">
         <v>205</v>
       </c>
-      <c r="D243" s="0" t="n">
+      <c r="D243" s="2" t="n">
         <v>240</v>
       </c>
-      <c r="E243" s="0" t="n">
+      <c r="E243" s="2" t="n">
         <v>385</v>
       </c>
-      <c r="F243" s="0" t="n">
+      <c r="F243" s="2" t="n">
         <v>170</v>
       </c>
     </row>
@@ -5150,16 +5154,16 @@
       <c r="A244" s="1" t="n">
         <v>46067</v>
       </c>
-      <c r="B244" s="0" t="n">
+      <c r="B244" s="2" t="n">
         <v>305</v>
       </c>
-      <c r="C244" s="0" t="n">
+      <c r="C244" s="2" t="n">
         <v>45</v>
       </c>
-      <c r="E244" s="0" t="n">
+      <c r="E244" s="2" t="n">
         <v>230</v>
       </c>
-      <c r="F244" s="0" t="n">
+      <c r="F244" s="2" t="n">
         <v>290</v>
       </c>
     </row>
@@ -5167,16 +5171,16 @@
       <c r="A245" s="1" t="n">
         <v>46067</v>
       </c>
-      <c r="B245" s="0" t="n">
+      <c r="B245" s="2" t="n">
         <v>285</v>
       </c>
-      <c r="C245" s="0" t="n">
+      <c r="C245" s="2" t="n">
         <v>60</v>
       </c>
-      <c r="E245" s="0" t="n">
+      <c r="E245" s="2" t="n">
         <v>225</v>
       </c>
-      <c r="F245" s="0" t="n">
+      <c r="F245" s="2" t="n">
         <v>270</v>
       </c>
     </row>
@@ -5184,16 +5188,16 @@
       <c r="A246" s="1" t="n">
         <v>46074</v>
       </c>
-      <c r="B246" s="0" t="n">
+      <c r="B246" s="2" t="n">
         <v>95</v>
       </c>
-      <c r="C246" s="0" t="n">
+      <c r="C246" s="2" t="n">
         <v>340</v>
       </c>
-      <c r="E246" s="0" t="n">
+      <c r="E246" s="2" t="n">
         <v>215</v>
       </c>
-      <c r="F246" s="0" t="n">
+      <c r="F246" s="2" t="n">
         <v>260</v>
       </c>
     </row>
@@ -5201,16 +5205,16 @@
       <c r="A247" s="1" t="n">
         <v>46074</v>
       </c>
-      <c r="B247" s="0" t="n">
+      <c r="B247" s="2" t="n">
         <v>250</v>
       </c>
-      <c r="C247" s="0" t="n">
+      <c r="C247" s="2" t="n">
         <v>285</v>
       </c>
-      <c r="E247" s="0" t="n">
+      <c r="E247" s="2" t="n">
         <v>260</v>
       </c>
-      <c r="F247" s="0" t="n">
+      <c r="F247" s="2" t="n">
         <v>280</v>
       </c>
     </row>
@@ -5218,13 +5222,13 @@
       <c r="A248" s="1" t="n">
         <v>46081</v>
       </c>
-      <c r="B248" s="0" t="n">
+      <c r="B248" s="2" t="n">
         <v>180</v>
       </c>
-      <c r="E248" s="0" t="n">
+      <c r="E248" s="2" t="n">
         <v>355</v>
       </c>
-      <c r="F248" s="0" t="n">
+      <c r="F248" s="2" t="n">
         <v>120</v>
       </c>
     </row>
@@ -5232,13 +5236,13 @@
       <c r="A249" s="1" t="n">
         <v>46081</v>
       </c>
-      <c r="B249" s="0" t="n">
+      <c r="B249" s="2" t="n">
         <v>360</v>
       </c>
-      <c r="E249" s="0" t="n">
+      <c r="E249" s="2" t="n">
         <v>140</v>
       </c>
-      <c r="F249" s="0" t="n">
+      <c r="F249" s="2" t="n">
         <v>260</v>
       </c>
     </row>
@@ -5246,16 +5250,16 @@
       <c r="A250" s="1" t="n">
         <v>46109</v>
       </c>
-      <c r="B250" s="0" t="n">
+      <c r="B250" s="2" t="n">
         <v>610</v>
       </c>
-      <c r="C250" s="0" t="n">
+      <c r="C250" s="2" t="n">
         <v>345</v>
       </c>
-      <c r="E250" s="0" t="n">
+      <c r="E250" s="2" t="n">
         <v>75</v>
       </c>
-      <c r="F250" s="0" t="n">
+      <c r="F250" s="2" t="n">
         <v>170</v>
       </c>
     </row>
@@ -5263,16 +5267,16 @@
       <c r="A251" s="1" t="n">
         <v>46115</v>
       </c>
-      <c r="B251" s="0" t="n">
+      <c r="B251" s="2" t="n">
         <v>165</v>
       </c>
-      <c r="C251" s="0" t="n">
+      <c r="C251" s="2" t="n">
         <v>225</v>
       </c>
-      <c r="G251" s="0" t="n">
+      <c r="G251" s="2" t="n">
         <v>190</v>
       </c>
-      <c r="H251" s="0" t="n">
+      <c r="H251" s="2" t="n">
         <v>235</v>
       </c>
     </row>
@@ -5280,22 +5284,22 @@
       <c r="A252" s="1" t="n">
         <v>46123</v>
       </c>
-      <c r="B252" s="0" t="n">
+      <c r="B252" s="2" t="n">
         <v>275</v>
       </c>
-      <c r="C252" s="0" t="n">
+      <c r="C252" s="2" t="n">
         <v>290</v>
       </c>
-      <c r="E252" s="0" t="n">
+      <c r="E252" s="2" t="n">
         <v>295</v>
       </c>
-      <c r="F252" s="0" t="n">
+      <c r="F252" s="2" t="n">
         <v>300</v>
       </c>
-      <c r="G252" s="0" t="n">
+      <c r="G252" s="2" t="n">
         <v>335</v>
       </c>
-      <c r="H252" s="0" t="n">
+      <c r="H252" s="2" t="n">
         <v>280</v>
       </c>
     </row>
@@ -5303,16 +5307,16 @@
       <c r="A253" s="1" t="n">
         <v>46130</v>
       </c>
-      <c r="E253" s="0" t="n">
+      <c r="E253" s="2" t="n">
         <v>455</v>
       </c>
-      <c r="F253" s="0" t="n">
+      <c r="F253" s="2" t="n">
         <v>335</v>
       </c>
-      <c r="G253" s="0" t="n">
+      <c r="G253" s="2" t="n">
         <v>155</v>
       </c>
-      <c r="H253" s="0" t="n">
+      <c r="H253" s="2" t="n">
         <v>230</v>
       </c>
     </row>
@@ -5320,16 +5324,16 @@
       <c r="A254" s="1" t="n">
         <v>46137</v>
       </c>
-      <c r="E254" s="0" t="n">
+      <c r="E254" s="2" t="n">
         <v>340</v>
       </c>
-      <c r="F254" s="0" t="n">
+      <c r="F254" s="2" t="n">
         <v>440</v>
       </c>
-      <c r="G254" s="0" t="n">
+      <c r="G254" s="2" t="n">
         <v>260</v>
       </c>
-      <c r="H254" s="0" t="n">
+      <c r="H254" s="2" t="n">
         <v>420</v>
       </c>
     </row>
@@ -5337,19 +5341,19 @@
       <c r="A255" s="1" t="n">
         <v>46144</v>
       </c>
-      <c r="C255" s="0" t="n">
+      <c r="C255" s="2" t="n">
         <v>165</v>
       </c>
-      <c r="E255" s="0" t="n">
+      <c r="E255" s="2" t="n">
         <v>215</v>
       </c>
-      <c r="F255" s="0" t="n">
+      <c r="F255" s="2" t="n">
         <v>490</v>
       </c>
-      <c r="G255" s="0" t="n">
+      <c r="G255" s="2" t="n">
         <v>150</v>
       </c>
-      <c r="H255" s="0" t="n">
+      <c r="H255" s="2" t="n">
         <v>365</v>
       </c>
     </row>
@@ -5357,22 +5361,22 @@
       <c r="A256" s="1" t="n">
         <v>46151</v>
       </c>
-      <c r="C256" s="0" t="n">
+      <c r="C256" s="2" t="n">
         <v>475</v>
       </c>
-      <c r="D256" s="0" t="n">
+      <c r="D256" s="2" t="n">
         <v>300</v>
       </c>
-      <c r="E256" s="0" t="n">
+      <c r="E256" s="2" t="n">
         <v>240</v>
       </c>
-      <c r="F256" s="0" t="n">
+      <c r="F256" s="2" t="n">
         <v>355</v>
       </c>
-      <c r="G256" s="0" t="n">
+      <c r="G256" s="2" t="n">
         <v>440</v>
       </c>
-      <c r="H256" s="0" t="n">
+      <c r="H256" s="2" t="n">
         <v>390</v>
       </c>
     </row>
@@ -5380,22 +5384,22 @@
       <c r="A257" s="1" t="n">
         <v>46151</v>
       </c>
-      <c r="C257" s="0" t="n">
+      <c r="C257" s="2" t="n">
         <v>95</v>
       </c>
-      <c r="D257" s="0" t="n">
+      <c r="D257" s="2" t="n">
         <v>370</v>
       </c>
-      <c r="E257" s="0" t="n">
+      <c r="E257" s="2" t="n">
         <v>415</v>
       </c>
-      <c r="F257" s="0" t="n">
+      <c r="F257" s="2" t="n">
         <v>610</v>
       </c>
-      <c r="G257" s="0" t="n">
+      <c r="G257" s="2" t="n">
         <v>335</v>
       </c>
-      <c r="H257" s="0" t="n">
+      <c r="H257" s="2" t="n">
         <v>335</v>
       </c>
     </row>
@@ -5403,16 +5407,16 @@
       <c r="A258" s="1" t="n">
         <v>46165</v>
       </c>
-      <c r="E258" s="0" t="n">
+      <c r="E258" s="2" t="n">
         <v>310</v>
       </c>
-      <c r="F258" s="0" t="n">
+      <c r="F258" s="2" t="n">
         <v>180</v>
       </c>
-      <c r="G258" s="0" t="n">
+      <c r="G258" s="2" t="n">
         <v>175</v>
       </c>
-      <c r="H258" s="0" t="n">
+      <c r="H258" s="2" t="n">
         <v>220</v>
       </c>
     </row>
@@ -5420,16 +5424,16 @@
       <c r="A259" s="1" t="n">
         <v>46165</v>
       </c>
-      <c r="E259" s="0" t="n">
+      <c r="E259" s="2" t="n">
         <v>100</v>
       </c>
-      <c r="F259" s="0" t="n">
+      <c r="F259" s="2" t="n">
         <v>480</v>
       </c>
-      <c r="G259" s="0" t="n">
+      <c r="G259" s="2" t="n">
         <v>120</v>
       </c>
-      <c r="H259" s="0" t="n">
+      <c r="H259" s="2" t="n">
         <v>180</v>
       </c>
     </row>
@@ -5437,22 +5441,22 @@
       <c r="A260" s="1" t="n">
         <v>46172</v>
       </c>
-      <c r="B260" s="0" t="n">
+      <c r="B260" s="2" t="n">
         <v>245</v>
       </c>
-      <c r="C260" s="0" t="n">
+      <c r="C260" s="2" t="n">
         <v>465</v>
       </c>
-      <c r="E260" s="0" t="n">
+      <c r="E260" s="2" t="n">
         <v>370</v>
       </c>
-      <c r="F260" s="0" t="n">
+      <c r="F260" s="2" t="n">
         <v>80</v>
       </c>
-      <c r="G260" s="0" t="n">
+      <c r="G260" s="2" t="n">
         <v>310</v>
       </c>
-      <c r="H260" s="0" t="n">
+      <c r="H260" s="2" t="n">
         <v>275</v>
       </c>
     </row>
@@ -5460,19 +5464,19 @@
       <c r="A261" s="1" t="n">
         <v>46172</v>
       </c>
-      <c r="C261" s="0" t="n">
+      <c r="C261" s="2" t="n">
         <v>40</v>
       </c>
-      <c r="E261" s="0" t="n">
+      <c r="E261" s="2" t="n">
         <v>200</v>
       </c>
-      <c r="F261" s="0" t="n">
+      <c r="F261" s="2" t="n">
         <v>390</v>
       </c>
-      <c r="G261" s="0" t="n">
+      <c r="G261" s="2" t="n">
         <v>235</v>
       </c>
-      <c r="H261" s="0" t="n">
+      <c r="H261" s="2" t="n">
         <v>350</v>
       </c>
     </row>
@@ -5480,19 +5484,19 @@
       <c r="A262" s="1" t="n">
         <v>46179</v>
       </c>
-      <c r="C262" s="0" t="n">
+      <c r="C262" s="2" t="n">
         <v>180</v>
       </c>
-      <c r="E262" s="0" t="n">
+      <c r="E262" s="2" t="n">
         <v>475</v>
       </c>
-      <c r="F262" s="0" t="n">
+      <c r="F262" s="2" t="n">
         <v>410</v>
       </c>
-      <c r="G262" s="0" t="n">
+      <c r="G262" s="2" t="n">
         <v>300</v>
       </c>
-      <c r="H262" s="0" t="n">
+      <c r="H262" s="2" t="n">
         <v>195</v>
       </c>
     </row>
@@ -5500,16 +5504,16 @@
       <c r="A263" s="1" t="n">
         <v>46186</v>
       </c>
-      <c r="E263" s="0" t="n">
+      <c r="E263" s="2" t="n">
         <v>398</v>
       </c>
-      <c r="F263" s="0" t="n">
+      <c r="F263" s="2" t="n">
         <v>490</v>
       </c>
-      <c r="G263" s="0" t="n">
+      <c r="G263" s="2" t="n">
         <v>210</v>
       </c>
-      <c r="H263" s="0" t="n">
+      <c r="H263" s="2" t="n">
         <v>305</v>
       </c>
     </row>
@@ -5517,16 +5521,16 @@
       <c r="A264" s="1" t="n">
         <v>46186</v>
       </c>
-      <c r="E264" s="0" t="n">
+      <c r="E264" s="2" t="n">
         <v>235</v>
       </c>
-      <c r="F264" s="0" t="n">
+      <c r="F264" s="2" t="n">
         <v>250</v>
       </c>
-      <c r="G264" s="0" t="n">
+      <c r="G264" s="2" t="n">
         <v>315</v>
       </c>
-      <c r="H264" s="0" t="n">
+      <c r="H264" s="2" t="n">
         <v>325</v>
       </c>
     </row>
@@ -5534,16 +5538,16 @@
       <c r="A265" s="1" t="n">
         <v>46186</v>
       </c>
-      <c r="E265" s="0" t="n">
+      <c r="E265" s="2" t="n">
         <v>245</v>
       </c>
-      <c r="F265" s="0" t="n">
+      <c r="F265" s="2" t="n">
         <v>180</v>
       </c>
-      <c r="G265" s="0" t="n">
+      <c r="G265" s="2" t="n">
         <v>190</v>
       </c>
-      <c r="H265" s="0" t="n">
+      <c r="H265" s="2" t="n">
         <v>295</v>
       </c>
     </row>
@@ -5551,16 +5555,16 @@
       <c r="A266" s="1" t="n">
         <v>46193</v>
       </c>
-      <c r="E266" s="0" t="n">
+      <c r="E266" s="2" t="n">
         <v>145</v>
       </c>
-      <c r="F266" s="0" t="n">
+      <c r="F266" s="2" t="n">
         <v>125</v>
       </c>
-      <c r="G266" s="0" t="n">
+      <c r="G266" s="2" t="n">
         <v>280</v>
       </c>
-      <c r="H266" s="0" t="n">
+      <c r="H266" s="2" t="n">
         <v>240</v>
       </c>
     </row>
@@ -5568,16 +5572,16 @@
       <c r="A267" s="1" t="n">
         <v>46194</v>
       </c>
-      <c r="E267" s="0" t="n">
+      <c r="E267" s="2" t="n">
         <v>345</v>
       </c>
-      <c r="F267" s="0" t="n">
+      <c r="F267" s="2" t="n">
         <v>185</v>
       </c>
-      <c r="G267" s="0" t="n">
+      <c r="G267" s="2" t="n">
         <v>115</v>
       </c>
-      <c r="H267" s="0" t="n">
+      <c r="H267" s="2" t="n">
         <v>300</v>
       </c>
     </row>
@@ -5585,16 +5589,16 @@
       <c r="A268" s="1" t="n">
         <v>46207</v>
       </c>
-      <c r="E268" s="0" t="n">
+      <c r="E268" s="2" t="n">
         <v>275</v>
       </c>
-      <c r="F268" s="0" t="n">
+      <c r="F268" s="2" t="n">
         <v>150</v>
       </c>
-      <c r="G268" s="0" t="n">
+      <c r="G268" s="2" t="n">
         <v>300</v>
       </c>
-      <c r="H268" s="0" t="n">
+      <c r="H268" s="2" t="n">
         <v>175</v>
       </c>
     </row>
@@ -5602,16 +5606,16 @@
       <c r="A269" s="1" t="n">
         <v>46207</v>
       </c>
-      <c r="E269" s="0" t="n">
+      <c r="E269" s="2" t="n">
         <v>180</v>
       </c>
-      <c r="F269" s="0" t="n">
+      <c r="F269" s="2" t="n">
         <v>360</v>
       </c>
-      <c r="G269" s="0" t="n">
+      <c r="G269" s="2" t="n">
         <v>190</v>
       </c>
-      <c r="H269" s="0" t="n">
+      <c r="H269" s="2" t="n">
         <v>435</v>
       </c>
     </row>
@@ -5619,16 +5623,16 @@
       <c r="A270" s="1" t="n">
         <v>46214</v>
       </c>
-      <c r="E270" s="0" t="n">
+      <c r="E270" s="2" t="n">
         <v>285</v>
       </c>
-      <c r="F270" s="0" t="n">
+      <c r="F270" s="2" t="n">
         <v>105</v>
       </c>
-      <c r="G270" s="0" t="n">
+      <c r="G270" s="2" t="n">
         <v>410</v>
       </c>
-      <c r="H270" s="0" t="n">
+      <c r="H270" s="2" t="n">
         <v>380</v>
       </c>
     </row>
@@ -5636,16 +5640,16 @@
       <c r="A271" s="1" t="n">
         <v>46214</v>
       </c>
-      <c r="E271" s="0" t="n">
+      <c r="E271" s="2" t="n">
         <v>85</v>
       </c>
-      <c r="F271" s="0" t="n">
+      <c r="F271" s="2" t="n">
         <v>240</v>
       </c>
-      <c r="G271" s="0" t="n">
+      <c r="G271" s="2" t="n">
         <v>245</v>
       </c>
-      <c r="H271" s="0" t="n">
+      <c r="H271" s="2" t="n">
         <v>335</v>
       </c>
     </row>
@@ -5653,16 +5657,16 @@
       <c r="A272" s="1" t="n">
         <v>46220</v>
       </c>
-      <c r="C272" s="0" t="n">
+      <c r="C272" s="2" t="n">
         <v>40</v>
       </c>
-      <c r="D272" s="0" t="n">
+      <c r="D272" s="2" t="n">
         <v>370</v>
       </c>
-      <c r="G272" s="0" t="n">
+      <c r="G272" s="2" t="n">
         <v>320</v>
       </c>
-      <c r="H272" s="0" t="n">
+      <c r="H272" s="2" t="n">
         <v>175</v>
       </c>
     </row>
@@ -5670,19 +5674,19 @@
       <c r="A273" s="1" t="n">
         <v>46230</v>
       </c>
-      <c r="C273" s="0" t="n">
+      <c r="C273" s="2" t="n">
         <v>415</v>
       </c>
-      <c r="E273" s="0" t="n">
+      <c r="E273" s="2" t="n">
         <v>240</v>
       </c>
-      <c r="F273" s="0" t="n">
+      <c r="F273" s="2" t="n">
         <v>290</v>
       </c>
-      <c r="G273" s="0" t="n">
+      <c r="G273" s="2" t="n">
         <v>315</v>
       </c>
-      <c r="H273" s="0" t="n">
+      <c r="H273" s="2" t="n">
         <v>125</v>
       </c>
     </row>
@@ -5690,19 +5694,19 @@
       <c r="A274" s="1" t="n">
         <v>46230</v>
       </c>
-      <c r="C274" s="0" t="n">
+      <c r="C274" s="2" t="n">
         <v>200</v>
       </c>
-      <c r="E274" s="0" t="n">
+      <c r="E274" s="2" t="n">
         <v>160</v>
       </c>
-      <c r="F274" s="0" t="n">
+      <c r="F274" s="2" t="n">
         <v>500</v>
       </c>
-      <c r="G274" s="0" t="n">
+      <c r="G274" s="2" t="n">
         <v>360</v>
       </c>
-      <c r="H274" s="0" t="n">
+      <c r="H274" s="2" t="n">
         <v>185</v>
       </c>
     </row>
@@ -5710,16 +5714,16 @@
       <c r="A275" s="1" t="n">
         <v>46235</v>
       </c>
-      <c r="E275" s="0" t="n">
+      <c r="E275" s="2" t="n">
         <v>45</v>
       </c>
-      <c r="F275" s="0" t="n">
+      <c r="F275" s="2" t="n">
         <v>320</v>
       </c>
-      <c r="G275" s="0" t="n">
+      <c r="G275" s="2" t="n">
         <v>380</v>
       </c>
-      <c r="H275" s="0" t="n">
+      <c r="H275" s="2" t="n">
         <v>380</v>
       </c>
     </row>
@@ -5727,16 +5731,16 @@
       <c r="A276" s="1" t="n">
         <v>46235</v>
       </c>
-      <c r="E276" s="0" t="n">
+      <c r="E276" s="2" t="n">
         <v>225</v>
       </c>
-      <c r="F276" s="0" t="n">
+      <c r="F276" s="2" t="n">
         <v>135</v>
       </c>
-      <c r="G276" s="0" t="n">
+      <c r="G276" s="2" t="n">
         <v>285</v>
       </c>
-      <c r="H276" s="0" t="n">
+      <c r="H276" s="2" t="n">
         <v>40</v>
       </c>
     </row>
@@ -5744,16 +5748,16 @@
       <c r="A277" s="1" t="n">
         <v>46236</v>
       </c>
-      <c r="E277" s="0" t="n">
+      <c r="E277" s="2" t="n">
         <v>270</v>
       </c>
-      <c r="F277" s="0" t="n">
+      <c r="F277" s="2" t="n">
         <v>330</v>
       </c>
-      <c r="G277" s="0" t="n">
+      <c r="G277" s="2" t="n">
         <v>330</v>
       </c>
-      <c r="H277" s="0" t="n">
+      <c r="H277" s="2" t="n">
         <v>540</v>
       </c>
     </row>
@@ -5761,19 +5765,19 @@
       <c r="A278" s="1" t="n">
         <v>46256</v>
       </c>
-      <c r="C278" s="0" t="n">
+      <c r="C278" s="2" t="n">
         <v>200</v>
       </c>
-      <c r="E278" s="0" t="n">
+      <c r="E278" s="2" t="n">
         <v>305</v>
       </c>
-      <c r="F278" s="0" t="n">
+      <c r="F278" s="2" t="n">
         <v>420</v>
       </c>
-      <c r="G278" s="0" t="n">
+      <c r="G278" s="2" t="n">
         <v>130</v>
       </c>
-      <c r="H278" s="0" t="n">
+      <c r="H278" s="2" t="n">
         <v>175</v>
       </c>
     </row>
@@ -5781,19 +5785,19 @@
       <c r="A279" s="1" t="n">
         <v>46256</v>
       </c>
-      <c r="C279" s="0" t="n">
+      <c r="C279" s="2" t="n">
         <v>220</v>
       </c>
-      <c r="E279" s="0" t="n">
+      <c r="E279" s="2" t="n">
         <v>390</v>
       </c>
-      <c r="F279" s="0" t="n">
+      <c r="F279" s="2" t="n">
         <v>425</v>
       </c>
-      <c r="G279" s="0" t="n">
+      <c r="G279" s="2" t="n">
         <v>215</v>
       </c>
-      <c r="H279" s="0" t="n">
+      <c r="H279" s="2" t="n">
         <v>355</v>
       </c>
     </row>
@@ -5801,16 +5805,16 @@
       <c r="A280" s="1" t="n">
         <v>46267</v>
       </c>
-      <c r="E280" s="0" t="n">
+      <c r="E280" s="2" t="n">
         <v>240</v>
       </c>
-      <c r="F280" s="0" t="n">
+      <c r="F280" s="2" t="n">
         <v>310</v>
       </c>
-      <c r="G280" s="0" t="n">
+      <c r="G280" s="2" t="n">
         <v>260</v>
       </c>
-      <c r="H280" s="0" t="n">
+      <c r="H280" s="2" t="n">
         <v>315</v>
       </c>
     </row>
@@ -5818,16 +5822,16 @@
       <c r="A281" s="1" t="n">
         <v>46271</v>
       </c>
-      <c r="E281" s="0" t="n">
+      <c r="E281" s="2" t="n">
         <v>25</v>
       </c>
-      <c r="F281" s="0" t="n">
+      <c r="F281" s="2" t="n">
         <v>395</v>
       </c>
-      <c r="G281" s="0" t="n">
+      <c r="G281" s="2" t="n">
         <v>290</v>
       </c>
-      <c r="H281" s="0" t="n">
+      <c r="H281" s="2" t="n">
         <v>385</v>
       </c>
     </row>
@@ -5835,16 +5839,16 @@
       <c r="A282" s="1" t="n">
         <v>46272</v>
       </c>
-      <c r="E282" s="0" t="n">
+      <c r="E282" s="2" t="n">
         <v>320</v>
       </c>
-      <c r="F282" s="0" t="n">
+      <c r="F282" s="2" t="n">
         <v>420</v>
       </c>
-      <c r="G282" s="0" t="n">
+      <c r="G282" s="2" t="n">
         <v>245</v>
       </c>
-      <c r="H282" s="0" t="n">
+      <c r="H282" s="2" t="n">
         <v>70</v>
       </c>
     </row>
@@ -5852,16 +5856,16 @@
       <c r="A283" s="1" t="n">
         <v>46273</v>
       </c>
-      <c r="E283" s="0" t="n">
+      <c r="E283" s="2" t="n">
         <v>275</v>
       </c>
-      <c r="F283" s="0" t="n">
+      <c r="F283" s="2" t="n">
         <v>365</v>
       </c>
-      <c r="G283" s="0" t="n">
+      <c r="G283" s="2" t="n">
         <v>135</v>
       </c>
-      <c r="H283" s="0" t="n">
+      <c r="H283" s="2" t="n">
         <v>435</v>
       </c>
     </row>
@@ -5869,16 +5873,16 @@
       <c r="A284" s="1" t="n">
         <v>46274</v>
       </c>
-      <c r="E284" s="0" t="n">
+      <c r="E284" s="2" t="n">
         <v>80</v>
       </c>
-      <c r="F284" s="0" t="n">
+      <c r="F284" s="2" t="n">
         <v>340</v>
       </c>
-      <c r="G284" s="0" t="n">
+      <c r="G284" s="2" t="n">
         <v>230</v>
       </c>
-      <c r="H284" s="0" t="n">
+      <c r="H284" s="2" t="n">
         <v>305</v>
       </c>
     </row>
@@ -5886,16 +5890,16 @@
       <c r="A285" s="1" t="n">
         <v>46275</v>
       </c>
-      <c r="E285" s="0" t="n">
+      <c r="E285" s="2" t="n">
         <v>320</v>
       </c>
-      <c r="F285" s="0" t="n">
+      <c r="F285" s="2" t="n">
         <v>450</v>
       </c>
-      <c r="G285" s="0" t="n">
+      <c r="G285" s="2" t="n">
         <v>75</v>
       </c>
-      <c r="H285" s="0" t="n">
+      <c r="H285" s="2" t="n">
         <v>150</v>
       </c>
     </row>
@@ -5903,16 +5907,16 @@
       <c r="A286" s="1" t="n">
         <v>46276</v>
       </c>
-      <c r="E286" s="0" t="n">
+      <c r="E286" s="2" t="n">
         <v>225</v>
       </c>
-      <c r="F286" s="0" t="n">
+      <c r="F286" s="2" t="n">
         <v>425</v>
       </c>
-      <c r="G286" s="0" t="n">
+      <c r="G286" s="2" t="n">
         <v>100</v>
       </c>
-      <c r="H286" s="0" t="n">
+      <c r="H286" s="2" t="n">
         <v>250</v>
       </c>
     </row>
@@ -5920,16 +5924,16 @@
       <c r="A287" s="1" t="n">
         <v>46277</v>
       </c>
-      <c r="E287" s="0" t="n">
+      <c r="E287" s="2" t="n">
         <v>345</v>
       </c>
-      <c r="F287" s="0" t="n">
+      <c r="F287" s="2" t="n">
         <v>310</v>
       </c>
-      <c r="G287" s="0" t="n">
+      <c r="G287" s="2" t="n">
         <v>215</v>
       </c>
-      <c r="H287" s="0" t="n">
+      <c r="H287" s="2" t="n">
         <v>245</v>
       </c>
     </row>
@@ -5937,16 +5941,16 @@
       <c r="A288" s="1" t="n">
         <v>46291</v>
       </c>
-      <c r="E288" s="0" t="n">
+      <c r="E288" s="2" t="n">
         <v>210</v>
       </c>
-      <c r="F288" s="0" t="n">
+      <c r="F288" s="2" t="n">
         <v>160</v>
       </c>
-      <c r="G288" s="0" t="n">
+      <c r="G288" s="2" t="n">
         <v>250</v>
       </c>
-      <c r="H288" s="0" t="n">
+      <c r="H288" s="2" t="n">
         <v>225</v>
       </c>
     </row>
@@ -5954,16 +5958,16 @@
       <c r="A289" s="1" t="n">
         <v>46298</v>
       </c>
-      <c r="E289" s="0" t="n">
+      <c r="E289" s="2" t="n">
         <v>180</v>
       </c>
-      <c r="F289" s="0" t="n">
+      <c r="F289" s="2" t="n">
         <v>115</v>
       </c>
-      <c r="G289" s="0" t="n">
+      <c r="G289" s="2" t="n">
         <v>105</v>
       </c>
-      <c r="H289" s="0" t="n">
+      <c r="H289" s="2" t="n">
         <v>360</v>
       </c>
     </row>
@@ -5971,16 +5975,16 @@
       <c r="A290" s="1" t="n">
         <v>46305</v>
       </c>
-      <c r="C290" s="0" t="n">
+      <c r="C290" s="2" t="n">
         <v>175</v>
       </c>
-      <c r="D290" s="0" t="n">
+      <c r="D290" s="2" t="n">
         <v>265</v>
       </c>
-      <c r="G290" s="0" t="n">
+      <c r="G290" s="2" t="n">
         <v>60</v>
       </c>
-      <c r="H290" s="0" t="n">
+      <c r="H290" s="2" t="n">
         <v>380</v>
       </c>
     </row>
@@ -5988,20 +5992,34 @@
       <c r="A291" s="1" t="n">
         <v>46312</v>
       </c>
-      <c r="C291" s="0" t="n">
+      <c r="C291" s="2" t="n">
         <v>205</v>
       </c>
-      <c r="E291" s="0" t="n">
+      <c r="E291" s="2" t="n">
         <v>395</v>
       </c>
-      <c r="F291" s="0" t="n">
+      <c r="F291" s="2" t="n">
         <v>230</v>
       </c>
-      <c r="G291" s="0" t="n">
+      <c r="G291" s="2" t="n">
         <v>320</v>
       </c>
-      <c r="H291" s="0" t="n">
+      <c r="H291" s="2" t="n">
         <v>395</v>
+      </c>
+    </row>
+    <row r="292" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A292" s="1" t="n">
+        <v>46319</v>
+      </c>
+      <c r="B292" s="0" t="n">
+        <v>180</v>
+      </c>
+      <c r="G292" s="0" t="n">
+        <v>100</v>
+      </c>
+      <c r="H292" s="0" t="n">
+        <v>180</v>
       </c>
     </row>
   </sheetData>
